--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E2317C7-C18E-624B-A375-3D7426836A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC1FFB-AEAE-224B-8061-0A25F1ECF466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-28200" windowWidth="34420" windowHeight="28200" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="-28180" windowWidth="34380" windowHeight="28200" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2705" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="863">
   <si>
     <t>Property label</t>
   </si>
@@ -2701,6 +2701,24 @@
   </si>
   <si>
     <t>skos:ConceptScheme (IRI)</t>
+  </si>
+  <si>
+    <t>http://edamontology.org/</t>
+  </si>
+  <si>
+    <t>http://schema.org/</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/prov#</t>
+  </si>
+  <si>
+    <t>http://www.w3.org/ns/oa#</t>
+  </si>
+  <si>
+    <t>^http://snomed\\.info/id/[0-9]{6,18}$</t>
+  </si>
+  <si>
+    <t>^(http://snomed\\.info/id/[0-9]{6,18}|http://id\\.who\\.int/icd/entity/[0-9]+|http://www\\.orpha\\.net/ORDO/Orphanet_[0-9]+)$</t>
   </si>
 </sst>
 </file>
@@ -3715,10 +3733,13 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3731,9 +3752,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -7805,7 +7823,7 @@
         <v>75</v>
       </c>
       <c r="P9" s="203" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="S9" s="121" t="b">
         <v>1</v>
@@ -9274,7 +9292,7 @@
         <v>75</v>
       </c>
       <c r="O4" s="27" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="R4" s="27" t="b">
         <v>1</v>
@@ -9354,7 +9372,7 @@
       <c r="I6" s="220" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="219" t="s">
+      <c r="J6" s="213" t="s">
         <v>83</v>
       </c>
       <c r="K6" s="228" t="s">
@@ -9372,13 +9390,13 @@
       <c r="U6" s="91"/>
     </row>
     <row r="7" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="216"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
+      <c r="A7" s="217"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
       <c r="D7" s="179" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="216"/>
+      <c r="E7" s="217"/>
       <c r="F7" s="214"/>
       <c r="G7" s="214"/>
       <c r="H7" s="214"/>
@@ -9388,13 +9406,13 @@
       <c r="L7" s="214"/>
     </row>
     <row r="8" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="216"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="216"/>
+      <c r="A8" s="217"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
       <c r="D8" s="179" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="216"/>
+      <c r="E8" s="217"/>
       <c r="F8" s="214"/>
       <c r="G8" s="214"/>
       <c r="H8" s="214"/>
@@ -9404,13 +9422,13 @@
       <c r="L8" s="214"/>
     </row>
     <row r="9" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="216"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
+      <c r="A9" s="217"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
       <c r="D9" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="216"/>
+      <c r="E9" s="217"/>
       <c r="F9" s="214"/>
       <c r="G9" s="214"/>
       <c r="H9" s="214"/>
@@ -9420,13 +9438,13 @@
       <c r="L9" s="214"/>
     </row>
     <row r="10" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="216"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="216"/>
+      <c r="A10" s="217"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
       <c r="D10" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="216"/>
+      <c r="E10" s="217"/>
       <c r="F10" s="214"/>
       <c r="G10" s="214"/>
       <c r="H10" s="214"/>
@@ -9802,17 +9820,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <mergeCells count="11">
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="C6:C10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="L6:L10"/>
     <mergeCell ref="K6:K10"/>
     <mergeCell ref="F6:F10"/>
     <mergeCell ref="J6:J10"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="C6:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="226" priority="11" operator="equal">
@@ -10928,6 +10946,9 @@
       <c r="O22" t="s">
         <v>33</v>
       </c>
+      <c r="Q22" s="200" t="s">
+        <v>492</v>
+      </c>
       <c r="S22" s="87"/>
       <c r="T22" s="87"/>
       <c r="U22" s="87"/>
@@ -11554,6 +11575,7 @@
     <hyperlink ref="D16" r:id="rId4" xr:uid="{00000000-0004-0000-0B00-000003000000}"/>
     <hyperlink ref="D17" r:id="rId5" xr:uid="{00000000-0004-0000-0B00-000004000000}"/>
     <hyperlink ref="D22" r:id="rId6" xr:uid="{00000000-0004-0000-0B00-000005000000}"/>
+    <hyperlink ref="Q22" r:id="rId7" tooltip="http://publications.europa.eu/resource/authority/data-theme/heal" xr:uid="{3B9F00E5-3EDE-1A4B-8670-8337B0670862}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12876,6 +12898,9 @@
       </c>
       <c r="Q2" s="2" t="s">
         <v>155</v>
+      </c>
+      <c r="T2" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="U2" s="31"/>
       <c r="V2" s="31"/>
@@ -14396,7 +14421,7 @@
         <v>75</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="U3" s="36"/>
       <c r="V3" s="36"/>
@@ -16195,6 +16220,9 @@
       <c r="Q3" s="27" t="s">
         <v>155</v>
       </c>
+      <c r="T3" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="U3" s="36"/>
       <c r="V3" s="36"/>
       <c r="W3" s="36"/>
@@ -17115,7 +17143,7 @@
         <v>73</v>
       </c>
       <c r="H2" s="168" t="s">
-        <v>67</v>
+        <v>730</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>29</v>
@@ -17170,6 +17198,9 @@
       <c r="Q3" s="27" t="s">
         <v>155</v>
       </c>
+      <c r="T3" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="U3" s="36"/>
       <c r="V3" s="36"/>
       <c r="W3" s="36"/>
@@ -17209,7 +17240,10 @@
         <v>75</v>
       </c>
       <c r="Q4" s="27" t="s">
-        <v>155</v>
+        <v>76</v>
+      </c>
+      <c r="T4" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="U4" s="13"/>
       <c r="V4" s="13"/>
@@ -18176,20 +18210,32 @@
       <c r="A22" t="s">
         <v>198</v>
       </c>
+      <c r="B22" s="200" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>199</v>
       </c>
+      <c r="B23" s="200" t="s">
+        <v>860</v>
+      </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>200</v>
       </c>
+      <c r="B24" s="200" t="s">
+        <v>859</v>
+      </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>201</v>
+      </c>
+      <c r="B25" s="200" t="s">
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -18212,6 +18258,10 @@
     <hyperlink ref="B19" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
     <hyperlink ref="B20" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
     <hyperlink ref="B21" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
+    <hyperlink ref="B22" r:id="rId19" tooltip="http://edamontology.org/" xr:uid="{58418185-E732-F945-80DB-5E6738BC5BA8}"/>
+    <hyperlink ref="B25" r:id="rId20" tooltip="http://schema.org/" xr:uid="{DEAFF9D5-EB1E-F040-8316-167366B3631C}"/>
+    <hyperlink ref="B24" r:id="rId21" tooltip="http://www.w3.org/ns/prov#" display="http://www.w3.org/ns/prov" xr:uid="{9A1C84E5-E39B-B743-BD5F-D063A07D12B0}"/>
+    <hyperlink ref="B23" r:id="rId22" tooltip="http://www.w3.org/ns/oa#" display="http://www.w3.org/ns/oa" xr:uid="{962971F1-479E-7446-ADCB-7507A33072DE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19002,41 +19052,41 @@
       <c r="V7" s="91"/>
     </row>
     <row r="8" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="217" t="s">
+      <c r="A8" s="218" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="215" t="s">
+      <c r="B8" s="216" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="217" t="s">
+      <c r="C8" s="218" t="s">
         <v>79</v>
       </c>
       <c r="D8" s="176" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="218" t="s">
+      <c r="E8" s="219" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="213" t="s">
+      <c r="F8" s="215" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="213" t="s">
+      <c r="G8" s="215" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="213" t="s">
+      <c r="H8" s="215" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="219" t="s">
+      <c r="I8" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="219" t="s">
+      <c r="J8" s="213" t="s">
         <v>83</v>
       </c>
       <c r="K8" s="103"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
+      <c r="L8" s="213"/>
+      <c r="M8" s="213"/>
       <c r="O8" s="27" t="s">
-        <v>32</v>
+        <v>417</v>
       </c>
       <c r="P8" s="27" t="s">
         <v>33</v>
@@ -19047,13 +19097,13 @@
       <c r="V8" s="87"/>
     </row>
     <row r="9" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="216"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
+      <c r="A9" s="217"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
       <c r="D9" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="216"/>
+      <c r="E9" s="217"/>
       <c r="F9" s="214"/>
       <c r="G9" s="214"/>
       <c r="H9" s="214"/>
@@ -19065,13 +19115,13 @@
       <c r="S9" s="69"/>
     </row>
     <row r="10" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="216"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="216"/>
+      <c r="A10" s="217"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
       <c r="D10" s="177" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="216"/>
+      <c r="E10" s="217"/>
       <c r="F10" s="214"/>
       <c r="G10" s="214"/>
       <c r="H10" s="214"/>
@@ -19083,13 +19133,13 @@
       <c r="S10" s="69"/>
     </row>
     <row r="11" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="216"/>
-      <c r="B11" s="216"/>
-      <c r="C11" s="216"/>
+      <c r="A11" s="217"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
       <c r="D11" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="216"/>
+      <c r="E11" s="217"/>
       <c r="F11" s="214"/>
       <c r="G11" s="214"/>
       <c r="H11" s="214"/>
@@ -19101,13 +19151,13 @@
       <c r="S11" s="69"/>
     </row>
     <row r="12" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="216"/>
-      <c r="B12" s="216"/>
-      <c r="C12" s="216"/>
+      <c r="A12" s="217"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
       <c r="D12" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="216"/>
+      <c r="E12" s="217"/>
       <c r="F12" s="214"/>
       <c r="G12" s="214"/>
       <c r="H12" s="214"/>
@@ -19247,7 +19297,7 @@
       <c r="L15" s="95"/>
       <c r="M15" s="95"/>
       <c r="O15" s="27" t="s">
-        <v>32</v>
+        <v>417</v>
       </c>
       <c r="P15" s="27" t="s">
         <v>33</v>
@@ -19629,7 +19679,7 @@
       <c r="L23" s="95"/>
       <c r="M23" s="95"/>
       <c r="O23" s="27" t="s">
-        <v>32</v>
+        <v>417</v>
       </c>
       <c r="P23" s="27" t="s">
         <v>33</v>
@@ -19691,17 +19741,17 @@
   </sheetData>
   <autoFilter ref="A1:J24" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="11">
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="G8:G12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="J8:J12"/>
     <mergeCell ref="F8:F12"/>
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="G8:G12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="309" priority="20" operator="equal">
@@ -20101,6 +20151,9 @@
       <c r="Q5" s="27" t="s">
         <v>33</v>
       </c>
+      <c r="R5" s="27" t="s">
+        <v>861</v>
+      </c>
       <c r="U5" s="91"/>
       <c r="V5" s="91"/>
       <c r="W5" s="91"/>
@@ -20443,7 +20496,7 @@
         <v>75</v>
       </c>
       <c r="Q12" s="27" t="s">
-        <v>155</v>
+        <v>76</v>
       </c>
       <c r="T12" s="27" t="b">
         <v>1</v>
@@ -20657,7 +20710,7 @@
       <c r="E17" s="222" t="s">
         <v>329</v>
       </c>
-      <c r="F17" s="213" t="s">
+      <c r="F17" s="215" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="226" t="s">
@@ -20687,9 +20740,9 @@
       <c r="W17" s="91"/>
     </row>
     <row r="18" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="216"/>
-      <c r="B18" s="216"/>
-      <c r="C18" s="216"/>
+      <c r="A18" s="217"/>
+      <c r="B18" s="217"/>
+      <c r="C18" s="217"/>
       <c r="D18" s="179" t="s">
         <v>84</v>
       </c>
@@ -20705,9 +20758,9 @@
       <c r="N18" s="214"/>
     </row>
     <row r="19" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="216"/>
-      <c r="B19" s="216"/>
-      <c r="C19" s="216"/>
+      <c r="A19" s="217"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="217"/>
       <c r="D19" s="179" t="s">
         <v>85</v>
       </c>
@@ -20723,9 +20776,9 @@
       <c r="N19" s="214"/>
     </row>
     <row r="20" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="216"/>
-      <c r="B20" s="216"/>
-      <c r="C20" s="216"/>
+      <c r="A20" s="217"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="217"/>
       <c r="D20" s="105" t="s">
         <v>86</v>
       </c>
@@ -20741,9 +20794,9 @@
       <c r="N20" s="214"/>
     </row>
     <row r="21" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="216"/>
-      <c r="B21" s="216"/>
-      <c r="C21" s="216"/>
+      <c r="A21" s="217"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="217"/>
       <c r="D21" s="105" t="s">
         <v>87</v>
       </c>
@@ -20845,6 +20898,9 @@
       </c>
       <c r="Q23" s="27" t="s">
         <v>33</v>
+      </c>
+      <c r="R23" s="27" t="s">
+        <v>862</v>
       </c>
       <c r="U23" s="91"/>
       <c r="V23" s="91"/>
@@ -23096,7 +23152,7 @@
         <v>75</v>
       </c>
       <c r="Y4" s="102" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="AC4" s="45"/>
       <c r="AD4" s="45"/>
@@ -23150,7 +23206,7 @@
         <v>75</v>
       </c>
       <c r="Y5" s="102" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="AB5" s="102" t="b">
         <v>1</v>
@@ -24421,7 +24477,7 @@
         <v>75</v>
       </c>
       <c r="T4" s="102" t="s">
-        <v>76</v>
+        <v>155</v>
       </c>
       <c r="X4" s="45"/>
       <c r="Y4" s="45"/>

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/health-ri-metadata/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anakonrad/Library/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61CC1FFB-AEAE-224B-8061-0A25F1ECF466}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0BE25E-6F18-694D-9DF3-EA1FE8CFF571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-28180" windowWidth="34380" windowHeight="28200" firstSheet="8" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="-28200" windowWidth="34380" windowHeight="28200" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="863">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="865">
   <si>
     <t>Property label</t>
   </si>
@@ -2719,6 +2719,12 @@
   </si>
   <si>
     <t>^(http://snomed\\.info/id/[0-9]{6,18}|http://id\\.who\\.int/icd/entity/[0-9]+|http://www\\.orpha\\.net/ORDO/Orphanet_[0-9]+)$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Table group title.</t>
+  </si>
+  <si>
+    <t>Used to provide a human-readable title for the table group. Can appear in multiple languages.</t>
   </si>
 </sst>
 </file>
@@ -3733,13 +3739,10 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3752,6 +3755,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -9372,7 +9378,7 @@
       <c r="I6" s="220" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="213" t="s">
+      <c r="J6" s="219" t="s">
         <v>83</v>
       </c>
       <c r="K6" s="228" t="s">
@@ -9390,13 +9396,13 @@
       <c r="U6" s="91"/>
     </row>
     <row r="7" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="217"/>
-      <c r="B7" s="217"/>
-      <c r="C7" s="217"/>
+      <c r="A7" s="216"/>
+      <c r="B7" s="216"/>
+      <c r="C7" s="216"/>
       <c r="D7" s="179" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="217"/>
+      <c r="E7" s="216"/>
       <c r="F7" s="214"/>
       <c r="G7" s="214"/>
       <c r="H7" s="214"/>
@@ -9406,13 +9412,13 @@
       <c r="L7" s="214"/>
     </row>
     <row r="8" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="217"/>
-      <c r="B8" s="217"/>
-      <c r="C8" s="217"/>
+      <c r="A8" s="216"/>
+      <c r="B8" s="216"/>
+      <c r="C8" s="216"/>
       <c r="D8" s="179" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="217"/>
+      <c r="E8" s="216"/>
       <c r="F8" s="214"/>
       <c r="G8" s="214"/>
       <c r="H8" s="214"/>
@@ -9422,13 +9428,13 @@
       <c r="L8" s="214"/>
     </row>
     <row r="9" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="217"/>
-      <c r="B9" s="217"/>
-      <c r="C9" s="217"/>
+      <c r="A9" s="216"/>
+      <c r="B9" s="216"/>
+      <c r="C9" s="216"/>
       <c r="D9" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="217"/>
+      <c r="E9" s="216"/>
       <c r="F9" s="214"/>
       <c r="G9" s="214"/>
       <c r="H9" s="214"/>
@@ -9438,13 +9444,13 @@
       <c r="L9" s="214"/>
     </row>
     <row r="10" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="217"/>
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
+      <c r="A10" s="216"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="216"/>
       <c r="D10" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="217"/>
+      <c r="E10" s="216"/>
       <c r="F10" s="214"/>
       <c r="G10" s="214"/>
       <c r="H10" s="214"/>
@@ -9820,17 +9826,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <mergeCells count="11">
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="C6:C10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="L6:L10"/>
     <mergeCell ref="K6:K10"/>
     <mergeCell ref="F6:F10"/>
     <mergeCell ref="J6:J10"/>
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="C6:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="226" priority="11" operator="equal">
@@ -15308,15 +15314,40 @@
       <c r="V2" s="31"/>
       <c r="W2" s="31"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A3" s="13"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="4"/>
+    <row r="3" spans="1:23" ht="56" x14ac:dyDescent="0.2">
+      <c r="A3" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>864</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="T3" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="U3" s="13"/>
       <c r="V3" s="13"/>
       <c r="W3" s="13"/>
@@ -19052,39 +19083,39 @@
       <c r="V7" s="91"/>
     </row>
     <row r="8" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="218" t="s">
+      <c r="A8" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="216" t="s">
+      <c r="B8" s="215" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="218" t="s">
+      <c r="C8" s="217" t="s">
         <v>79</v>
       </c>
       <c r="D8" s="176" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="219" t="s">
+      <c r="E8" s="218" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="215" t="s">
+      <c r="F8" s="213" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="215" t="s">
+      <c r="G8" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="215" t="s">
+      <c r="H8" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="213" t="s">
+      <c r="I8" s="219" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="213" t="s">
+      <c r="J8" s="219" t="s">
         <v>83</v>
       </c>
       <c r="K8" s="103"/>
-      <c r="L8" s="213"/>
-      <c r="M8" s="213"/>
+      <c r="L8" s="219"/>
+      <c r="M8" s="219"/>
       <c r="O8" s="27" t="s">
         <v>417</v>
       </c>
@@ -19097,13 +19128,13 @@
       <c r="V8" s="87"/>
     </row>
     <row r="9" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="217"/>
-      <c r="B9" s="217"/>
-      <c r="C9" s="217"/>
+      <c r="A9" s="216"/>
+      <c r="B9" s="216"/>
+      <c r="C9" s="216"/>
       <c r="D9" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="217"/>
+      <c r="E9" s="216"/>
       <c r="F9" s="214"/>
       <c r="G9" s="214"/>
       <c r="H9" s="214"/>
@@ -19115,13 +19146,13 @@
       <c r="S9" s="69"/>
     </row>
     <row r="10" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="217"/>
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
+      <c r="A10" s="216"/>
+      <c r="B10" s="216"/>
+      <c r="C10" s="216"/>
       <c r="D10" s="177" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="217"/>
+      <c r="E10" s="216"/>
       <c r="F10" s="214"/>
       <c r="G10" s="214"/>
       <c r="H10" s="214"/>
@@ -19133,13 +19164,13 @@
       <c r="S10" s="69"/>
     </row>
     <row r="11" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="217"/>
-      <c r="B11" s="217"/>
-      <c r="C11" s="217"/>
+      <c r="A11" s="216"/>
+      <c r="B11" s="216"/>
+      <c r="C11" s="216"/>
       <c r="D11" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="217"/>
+      <c r="E11" s="216"/>
       <c r="F11" s="214"/>
       <c r="G11" s="214"/>
       <c r="H11" s="214"/>
@@ -19151,13 +19182,13 @@
       <c r="S11" s="69"/>
     </row>
     <row r="12" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="217"/>
-      <c r="B12" s="217"/>
-      <c r="C12" s="217"/>
+      <c r="A12" s="216"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="216"/>
       <c r="D12" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="217"/>
+      <c r="E12" s="216"/>
       <c r="F12" s="214"/>
       <c r="G12" s="214"/>
       <c r="H12" s="214"/>
@@ -19741,17 +19772,17 @@
   </sheetData>
   <autoFilter ref="A1:J24" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="11">
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="G8:G12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="J8:J12"/>
     <mergeCell ref="F8:F12"/>
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="G8:G12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="309" priority="20" operator="equal">
@@ -20710,7 +20741,7 @@
       <c r="E17" s="222" t="s">
         <v>329</v>
       </c>
-      <c r="F17" s="215" t="s">
+      <c r="F17" s="213" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="226" t="s">
@@ -20740,9 +20771,9 @@
       <c r="W17" s="91"/>
     </row>
     <row r="18" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="217"/>
-      <c r="B18" s="217"/>
-      <c r="C18" s="217"/>
+      <c r="A18" s="216"/>
+      <c r="B18" s="216"/>
+      <c r="C18" s="216"/>
       <c r="D18" s="179" t="s">
         <v>84</v>
       </c>
@@ -20758,9 +20789,9 @@
       <c r="N18" s="214"/>
     </row>
     <row r="19" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="217"/>
-      <c r="B19" s="217"/>
-      <c r="C19" s="217"/>
+      <c r="A19" s="216"/>
+      <c r="B19" s="216"/>
+      <c r="C19" s="216"/>
       <c r="D19" s="179" t="s">
         <v>85</v>
       </c>
@@ -20776,9 +20807,9 @@
       <c r="N19" s="214"/>
     </row>
     <row r="20" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="217"/>
-      <c r="B20" s="217"/>
-      <c r="C20" s="217"/>
+      <c r="A20" s="216"/>
+      <c r="B20" s="216"/>
+      <c r="C20" s="216"/>
       <c r="D20" s="105" t="s">
         <v>86</v>
       </c>
@@ -20794,9 +20825,9 @@
       <c r="N20" s="214"/>
     </row>
     <row r="21" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="217"/>
-      <c r="B21" s="217"/>
-      <c r="C21" s="217"/>
+      <c r="A21" s="216"/>
+      <c r="B21" s="216"/>
+      <c r="C21" s="216"/>
       <c r="D21" s="105" t="s">
         <v>87</v>
       </c>

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anakonrad/Library/health-ri-metadata/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B0BE25E-6F18-694D-9DF3-EA1FE8CFF571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF62ED4D-409F-E34E-ADE3-AC8BCFFF45B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="-28200" windowWidth="34380" windowHeight="28200" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-28200" windowWidth="34380" windowHeight="28200" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="865">
   <si>
     <t>Property label</t>
   </si>
@@ -15345,6 +15345,12 @@
       <c r="J3" s="2" t="s">
         <v>83</v>
       </c>
+      <c r="P3" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q3" s="27" t="s">
+        <v>155</v>
+      </c>
       <c r="T3" s="2" t="b">
         <v>1</v>
       </c>

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF62ED4D-409F-E34E-ADE3-AC8BCFFF45B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB47564-A50D-124C-B685-639E205C2899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-28200" windowWidth="34380" windowHeight="28200" firstSheet="8" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="-28200" windowWidth="34380" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2724" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="867">
   <si>
     <t>Property label</t>
   </si>
@@ -694,151 +694,94 @@
     <t>Resource</t>
   </si>
   <si>
-    <t>hri:Resource</t>
-  </si>
-  <si>
     <t>dcat:Resource</t>
   </si>
   <si>
     <t>Dataset</t>
   </si>
   <si>
-    <t>hri:Dataset</t>
-  </si>
-  <si>
     <t>Catalogue</t>
   </si>
   <si>
-    <t>hri:Catalog</t>
-  </si>
-  <si>
     <t>Agent</t>
   </si>
   <si>
-    <t>hri:Agent</t>
-  </si>
-  <si>
     <t>Kind</t>
   </si>
   <si>
-    <t>hri:Kind</t>
-  </si>
-  <si>
     <t>Distribution</t>
   </si>
   <si>
-    <t>hri:Distribution</t>
-  </si>
-  <si>
     <t>dcat:Distribution</t>
   </si>
   <si>
     <t>DatasetSeries</t>
   </si>
   <si>
-    <t>hri:DatasetSeries</t>
-  </si>
-  <si>
     <t>dcat:DatasetSeries</t>
   </si>
   <si>
     <t>DataService</t>
   </si>
   <si>
-    <t>hri:DataService</t>
-  </si>
-  <si>
     <t>adms_Identifier</t>
   </si>
   <si>
-    <t>hri:Identifier</t>
-  </si>
-  <si>
     <t>adms:Identifier</t>
   </si>
   <si>
     <t>PeriodOfTime</t>
   </si>
   <si>
-    <t>hri:PeriodOfTime</t>
-  </si>
-  <si>
     <t>Attribution</t>
   </si>
   <si>
-    <t>hri:Attribution</t>
-  </si>
-  <si>
     <t>prov:Attribution</t>
   </si>
   <si>
     <t>Relationship</t>
   </si>
   <si>
-    <t>hri:Relationship</t>
-  </si>
-  <si>
     <t>dcat:Relationship</t>
   </si>
   <si>
     <t>QualityCertificate</t>
   </si>
   <si>
-    <t>hri:QualityCertificate</t>
-  </si>
-  <si>
     <t>dqv:QualityCertificate</t>
   </si>
   <si>
     <t>Checksum</t>
   </si>
   <si>
-    <t>hri:Checksum</t>
-  </si>
-  <si>
     <t>spdx:Checksum</t>
   </si>
   <si>
     <t>TableGroup</t>
   </si>
   <si>
-    <t>hri:TableGroup</t>
-  </si>
-  <si>
     <t>csvw:TableGroup</t>
   </si>
   <si>
     <t>Table</t>
   </si>
   <si>
-    <t>hri:Table</t>
-  </si>
-  <si>
     <t>csvw:Table</t>
   </si>
   <si>
     <t>Column</t>
   </si>
   <si>
-    <t>hri:Column</t>
-  </si>
-  <si>
     <t>csvw:Column</t>
   </si>
   <si>
     <t>Activity</t>
   </si>
   <si>
-    <t>hri:Activity</t>
-  </si>
-  <si>
     <t>prov:Activity</t>
   </si>
   <si>
     <t>ProvenanceStatement</t>
-  </si>
-  <si>
-    <t>hri:ProvenanceStatement</t>
   </si>
   <si>
     <t>dct:ProvenanceStatement</t>
@@ -2725,6 +2668,123 @@
   </si>
   <si>
     <t>Used to provide a human-readable title for the table group. Can appear in multiple languages.</t>
+  </si>
+  <si>
+    <t>hrishapes:Resource</t>
+  </si>
+  <si>
+    <t>hrishapes:Dataset</t>
+  </si>
+  <si>
+    <t>hrishapes:Catalog</t>
+  </si>
+  <si>
+    <t>hrishapes:Agent</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hrishapes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Kind</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hrishapes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Distribution</t>
+    </r>
+  </si>
+  <si>
+    <t>hrishapes:DatasetSeries</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hrishapes:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DataService</t>
+    </r>
+  </si>
+  <si>
+    <t>hrishapes:Identifier</t>
+  </si>
+  <si>
+    <t>hrishapes:PeriodOfTime</t>
+  </si>
+  <si>
+    <t>hrishapes:Attribution</t>
+  </si>
+  <si>
+    <t>hrishapes:Relationship</t>
+  </si>
+  <si>
+    <t>hrishapes:QualityCertificate</t>
+  </si>
+  <si>
+    <t>hrishapes:Checksum</t>
+  </si>
+  <si>
+    <t>hrishapes:TableGroup</t>
+  </si>
+  <si>
+    <t>hrishapes:Table</t>
+  </si>
+  <si>
+    <t>hrishapes:Column</t>
+  </si>
+  <si>
+    <t>hrishapes:Activity</t>
+  </si>
+  <si>
+    <t>hrishapes:ProvenanceStatement</t>
+  </si>
+  <si>
+    <t>hrishapes</t>
+  </si>
+  <si>
+    <t>http://data.health-ri.nl/core/p2/</t>
   </si>
 </sst>
 </file>
@@ -3122,7 +3182,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="43" fillId="13" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="230">
+  <cellXfs count="231">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3739,10 +3799,13 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3755,9 +3818,6 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3789,6 +3849,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Accent1" xfId="2" builtinId="29"/>
@@ -7418,10 +7479,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="77" t="s">
-        <v>584</v>
+        <v>565</v>
       </c>
       <c r="M1" s="185" t="s">
-        <v>585</v>
+        <v>566</v>
       </c>
       <c r="N1" s="66" t="s">
         <v>13</v>
@@ -7453,19 +7514,19 @@
     </row>
     <row r="2" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="91" t="s">
-        <v>586</v>
+        <v>567</v>
       </c>
       <c r="B2" s="48" t="s">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>588</v>
+        <v>569</v>
       </c>
       <c r="D2" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>589</v>
+        <v>570</v>
       </c>
       <c r="F2" s="90" t="s">
         <v>26</v>
@@ -7483,13 +7544,13 @@
         <v>48</v>
       </c>
       <c r="K2" s="68" t="s">
-        <v>590</v>
+        <v>571</v>
       </c>
       <c r="L2" s="156" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="M2" s="156" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="O2" s="203" t="s">
         <v>32</v>
@@ -7504,25 +7565,25 @@
     </row>
     <row r="3" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="87" t="s">
-        <v>592</v>
+        <v>573</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>593</v>
+        <v>574</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>594</v>
+        <v>575</v>
       </c>
       <c r="D3" s="152" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="104" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="F3" s="93" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="90" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H3" s="99">
         <v>1</v>
@@ -7534,7 +7595,7 @@
         <v>48</v>
       </c>
       <c r="K3" s="68" t="s">
-        <v>596</v>
+        <v>577</v>
       </c>
       <c r="L3" s="76"/>
       <c r="M3" s="76"/>
@@ -7563,7 +7624,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="F4" s="90" t="s">
         <v>26</v>
@@ -7598,25 +7659,25 @@
     </row>
     <row r="5" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="97" t="s">
-        <v>598</v>
+        <v>579</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>600</v>
+        <v>581</v>
       </c>
       <c r="D5" s="78" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>602</v>
+        <v>583</v>
       </c>
       <c r="F5" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H5" s="99" t="s">
         <v>98</v>
@@ -7643,25 +7704,25 @@
     </row>
     <row r="6" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="91" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="B6" s="48" t="s">
-        <v>604</v>
+        <v>585</v>
       </c>
       <c r="C6" s="100" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="D6" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="92" t="s">
-        <v>606</v>
+        <v>587</v>
       </c>
       <c r="F6" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="93" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="H6" s="93" t="s">
         <v>98</v>
@@ -7673,7 +7734,7 @@
         <v>40</v>
       </c>
       <c r="K6" s="68" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="L6" s="95"/>
       <c r="M6" s="95"/>
@@ -7690,25 +7751,25 @@
     </row>
     <row r="7" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="87" t="s">
-        <v>608</v>
+        <v>589</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>610</v>
+        <v>591</v>
       </c>
       <c r="D7" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>611</v>
+        <v>592</v>
       </c>
       <c r="F7" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="94" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="H7" s="90" t="s">
         <v>98</v>
@@ -7720,16 +7781,16 @@
         <v>40</v>
       </c>
       <c r="K7" s="68" t="s">
-        <v>612</v>
+        <v>593</v>
       </c>
       <c r="L7" s="76" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="M7" s="76" t="s">
-        <v>613</v>
+        <v>594</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="O7" s="203" t="s">
         <v>52</v>
@@ -7744,25 +7805,25 @@
     </row>
     <row r="8" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="91" t="s">
-        <v>615</v>
+        <v>596</v>
       </c>
       <c r="B8" s="48" t="s">
-        <v>616</v>
+        <v>597</v>
       </c>
       <c r="C8" s="100" t="s">
-        <v>617</v>
+        <v>598</v>
       </c>
       <c r="D8" s="149" t="s">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="E8" s="92" t="s">
-        <v>619</v>
+        <v>600</v>
       </c>
       <c r="F8" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="93" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="H8" s="93" t="s">
         <v>98</v>
@@ -7774,7 +7835,7 @@
         <v>40</v>
       </c>
       <c r="K8" s="68" t="s">
-        <v>621</v>
+        <v>602</v>
       </c>
       <c r="L8" s="95"/>
       <c r="M8" s="95"/>
@@ -7803,7 +7864,7 @@
         <v>25</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="F9" s="90" t="s">
         <v>26</v>
@@ -7821,7 +7882,7 @@
         <v>40</v>
       </c>
       <c r="K9" s="68" t="s">
-        <v>623</v>
+        <v>604</v>
       </c>
       <c r="L9" s="76"/>
       <c r="M9" s="76"/>
@@ -7840,19 +7901,19 @@
     </row>
     <row r="10" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="91" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>94</v>
       </c>
       <c r="C10" s="91" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D10" s="151" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="92" t="s">
-        <v>624</v>
+        <v>605</v>
       </c>
       <c r="F10" s="93" t="s">
         <v>26</v>
@@ -7870,7 +7931,7 @@
         <v>40</v>
       </c>
       <c r="K10" s="68" t="s">
-        <v>625</v>
+        <v>606</v>
       </c>
       <c r="L10" s="95"/>
       <c r="M10" s="95"/>
@@ -7887,25 +7948,25 @@
     </row>
     <row r="11" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="87" t="s">
-        <v>626</v>
+        <v>607</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>627</v>
+        <v>608</v>
       </c>
       <c r="C11" s="107" t="s">
-        <v>628</v>
+        <v>609</v>
       </c>
       <c r="D11" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="29" t="s">
-        <v>629</v>
+        <v>610</v>
       </c>
       <c r="F11" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="90" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H11" s="90" t="s">
         <v>98</v>
@@ -7917,7 +7978,7 @@
         <v>48</v>
       </c>
       <c r="K11" s="68" t="s">
-        <v>630</v>
+        <v>611</v>
       </c>
       <c r="L11" s="76"/>
       <c r="M11" s="76"/>
@@ -7934,25 +7995,25 @@
     </row>
     <row r="12" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="91" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="B12" s="48" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="C12" s="91" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="D12" s="119" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="E12" s="92" t="s">
-        <v>635</v>
+        <v>616</v>
       </c>
       <c r="F12" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="93" t="s">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="H12" s="93" t="s">
         <v>98</v>
@@ -7964,7 +8025,7 @@
         <v>40</v>
       </c>
       <c r="K12" s="69" t="s">
-        <v>637</v>
+        <v>618</v>
       </c>
       <c r="L12" s="95"/>
       <c r="M12" s="95"/>
@@ -7993,7 +8054,7 @@
         <v>102</v>
       </c>
       <c r="E13" s="104" t="s">
-        <v>638</v>
+        <v>619</v>
       </c>
       <c r="F13" s="90" t="s">
         <v>26</v>
@@ -8011,7 +8072,7 @@
         <v>40</v>
       </c>
       <c r="K13" s="68" t="s">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="L13" s="76"/>
       <c r="M13" s="76"/>
@@ -8040,7 +8101,7 @@
         <v>109</v>
       </c>
       <c r="E14" s="54" t="s">
-        <v>640</v>
+        <v>621</v>
       </c>
       <c r="F14" s="93" t="s">
         <v>46</v>
@@ -8058,7 +8119,7 @@
         <v>48</v>
       </c>
       <c r="K14" s="68" t="s">
-        <v>641</v>
+        <v>622</v>
       </c>
       <c r="L14" s="95"/>
       <c r="M14" s="95"/>
@@ -8075,25 +8136,25 @@
     </row>
     <row r="15" spans="1:22" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="87" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D15" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>643</v>
+        <v>624</v>
       </c>
       <c r="F15" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="90" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H15" s="90" t="s">
         <v>28</v>
@@ -8105,7 +8166,7 @@
         <v>40</v>
       </c>
       <c r="K15" s="68" t="s">
-        <v>644</v>
+        <v>625</v>
       </c>
       <c r="L15" s="76"/>
       <c r="M15" s="76"/>
@@ -8122,25 +8183,25 @@
     </row>
     <row r="16" spans="1:22" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="91" t="s">
-        <v>645</v>
+        <v>626</v>
       </c>
       <c r="B16" s="48" t="s">
-        <v>646</v>
+        <v>627</v>
       </c>
       <c r="C16" s="91" t="s">
-        <v>647</v>
+        <v>628</v>
       </c>
       <c r="D16" s="149" t="s">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="E16" s="54" t="s">
-        <v>648</v>
+        <v>629</v>
       </c>
       <c r="F16" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="93" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="H16" s="93" t="s">
         <v>98</v>
@@ -8152,7 +8213,7 @@
         <v>40</v>
       </c>
       <c r="K16" s="68" t="s">
-        <v>649</v>
+        <v>630</v>
       </c>
       <c r="L16" s="95"/>
       <c r="M16" s="95"/>
@@ -8197,7 +8258,7 @@
         <v>40</v>
       </c>
       <c r="K17" s="68" t="s">
-        <v>650</v>
+        <v>631</v>
       </c>
       <c r="L17" s="76"/>
       <c r="M17" s="76"/>
@@ -8218,25 +8279,25 @@
     </row>
     <row r="18" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="91" t="s">
-        <v>651</v>
+        <v>632</v>
       </c>
       <c r="B18" s="48" t="s">
-        <v>652</v>
+        <v>633</v>
       </c>
       <c r="C18" s="91" t="s">
-        <v>653</v>
+        <v>634</v>
       </c>
       <c r="D18" s="149" t="s">
-        <v>618</v>
+        <v>599</v>
       </c>
       <c r="E18" s="48" t="s">
-        <v>654</v>
+        <v>635</v>
       </c>
       <c r="F18" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="93" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="H18" s="93" t="s">
         <v>98</v>
@@ -8248,7 +8309,7 @@
         <v>40</v>
       </c>
       <c r="K18" s="68" t="s">
-        <v>655</v>
+        <v>636</v>
       </c>
       <c r="L18" s="95"/>
       <c r="M18" s="95"/>
@@ -8277,7 +8338,7 @@
         <v>25</v>
       </c>
       <c r="E19" s="98" t="s">
-        <v>656</v>
+        <v>637</v>
       </c>
       <c r="F19" s="90" t="s">
         <v>26</v>
@@ -8295,7 +8356,7 @@
         <v>40</v>
       </c>
       <c r="K19" s="68" t="s">
-        <v>657</v>
+        <v>638</v>
       </c>
       <c r="L19" s="76"/>
       <c r="M19" s="76"/>
@@ -8316,17 +8377,17 @@
     </row>
     <row r="20" spans="1:22" ht="231" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="91" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="B20" s="92" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="C20" s="91" t="s">
-        <v>658</v>
+        <v>639</v>
       </c>
       <c r="D20" s="92"/>
       <c r="E20" s="48" t="s">
-        <v>659</v>
+        <v>640</v>
       </c>
       <c r="F20" s="93" t="s">
         <v>26</v>
@@ -8345,10 +8406,10 @@
       </c>
       <c r="K20" s="73"/>
       <c r="L20" s="95" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="M20" s="95" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>146</v>
@@ -8378,7 +8439,7 @@
         <v>25</v>
       </c>
       <c r="E21" s="53" t="s">
-        <v>660</v>
+        <v>641</v>
       </c>
       <c r="F21" s="154" t="s">
         <v>26</v>
@@ -8396,7 +8457,7 @@
         <v>40</v>
       </c>
       <c r="K21" s="69" t="s">
-        <v>661</v>
+        <v>642</v>
       </c>
       <c r="L21" s="76"/>
       <c r="M21" s="76"/>
@@ -8413,25 +8474,25 @@
     </row>
     <row r="22" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="91" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="B22" s="48" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="C22" s="91" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="D22" s="119" t="s">
-        <v>662</v>
+        <v>643</v>
       </c>
       <c r="E22" s="55" t="s">
-        <v>663</v>
+        <v>644</v>
       </c>
       <c r="F22" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H22" s="93" t="s">
         <v>98</v>
@@ -8443,7 +8504,7 @@
         <v>40</v>
       </c>
       <c r="K22" s="68" t="s">
-        <v>664</v>
+        <v>645</v>
       </c>
       <c r="L22" s="95"/>
       <c r="M22" s="95"/>
@@ -8460,25 +8521,25 @@
     </row>
     <row r="23" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="87" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="D23" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="98" t="s">
-        <v>665</v>
+        <v>646</v>
       </c>
       <c r="F23" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="90" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="H23" s="90" t="s">
         <v>98</v>
@@ -8517,7 +8578,7 @@
         <v>25</v>
       </c>
       <c r="E24" s="92" t="s">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="F24" s="93" t="s">
         <v>26</v>
@@ -8535,7 +8596,7 @@
         <v>40</v>
       </c>
       <c r="K24" s="68" t="s">
-        <v>667</v>
+        <v>648</v>
       </c>
       <c r="L24" s="95"/>
       <c r="M24" s="95"/>
@@ -9134,7 +9195,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="77" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="M1" s="66" t="s">
         <v>13</v>
@@ -9178,7 +9239,7 @@
         <v>25</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>669</v>
+        <v>650</v>
       </c>
       <c r="F2" s="90" t="s">
         <v>26</v>
@@ -9196,7 +9257,7 @@
         <v>40</v>
       </c>
       <c r="K2" s="68" t="s">
-        <v>670</v>
+        <v>651</v>
       </c>
       <c r="L2" s="95"/>
       <c r="N2" s="27" t="s">
@@ -9241,7 +9302,7 @@
         <v>40</v>
       </c>
       <c r="K3" s="68" t="s">
-        <v>671</v>
+        <v>652</v>
       </c>
       <c r="L3" s="76" t="s">
         <v>50</v>
@@ -9273,7 +9334,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="92" t="s">
-        <v>672</v>
+        <v>653</v>
       </c>
       <c r="F4" s="93" t="s">
         <v>46</v>
@@ -9291,7 +9352,7 @@
         <v>40</v>
       </c>
       <c r="K4" s="69" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="L4" s="95"/>
       <c r="N4" s="27" t="s">
@@ -9309,25 +9370,25 @@
     </row>
     <row r="5" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="87" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D5" s="88" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="E5" s="101" t="s">
-        <v>674</v>
+        <v>655</v>
       </c>
       <c r="F5" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H5" s="90" t="s">
         <v>98</v>
@@ -9364,7 +9425,7 @@
         <v>80</v>
       </c>
       <c r="E6" s="222" t="s">
-        <v>329</v>
+        <v>310</v>
       </c>
       <c r="F6" s="226" t="s">
         <v>26</v>
@@ -9378,11 +9439,11 @@
       <c r="I6" s="220" t="s">
         <v>29</v>
       </c>
-      <c r="J6" s="219" t="s">
+      <c r="J6" s="213" t="s">
         <v>83</v>
       </c>
       <c r="K6" s="228" t="s">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="L6" s="220"/>
       <c r="N6" s="27" t="s">
@@ -9396,13 +9457,13 @@
       <c r="U6" s="91"/>
     </row>
     <row r="7" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="216"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
+      <c r="A7" s="217"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
       <c r="D7" s="179" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="216"/>
+      <c r="E7" s="217"/>
       <c r="F7" s="214"/>
       <c r="G7" s="214"/>
       <c r="H7" s="214"/>
@@ -9412,13 +9473,13 @@
       <c r="L7" s="214"/>
     </row>
     <row r="8" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="216"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="216"/>
+      <c r="A8" s="217"/>
+      <c r="B8" s="217"/>
+      <c r="C8" s="217"/>
       <c r="D8" s="179" t="s">
         <v>85</v>
       </c>
-      <c r="E8" s="216"/>
+      <c r="E8" s="217"/>
       <c r="F8" s="214"/>
       <c r="G8" s="214"/>
       <c r="H8" s="214"/>
@@ -9428,13 +9489,13 @@
       <c r="L8" s="214"/>
     </row>
     <row r="9" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="216"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
+      <c r="A9" s="217"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
       <c r="D9" s="105" t="s">
         <v>86</v>
       </c>
-      <c r="E9" s="216"/>
+      <c r="E9" s="217"/>
       <c r="F9" s="214"/>
       <c r="G9" s="214"/>
       <c r="H9" s="214"/>
@@ -9444,13 +9505,13 @@
       <c r="L9" s="214"/>
     </row>
     <row r="10" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="216"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="216"/>
+      <c r="A10" s="217"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
       <c r="D10" s="105" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="216"/>
+      <c r="E10" s="217"/>
       <c r="F10" s="214"/>
       <c r="G10" s="214"/>
       <c r="H10" s="214"/>
@@ -9473,7 +9534,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="98" t="s">
-        <v>676</v>
+        <v>657</v>
       </c>
       <c r="F11" s="90" t="s">
         <v>26</v>
@@ -9491,7 +9552,7 @@
         <v>40</v>
       </c>
       <c r="K11" s="69" t="s">
-        <v>673</v>
+        <v>654</v>
       </c>
       <c r="L11" s="76"/>
       <c r="N11" s="27" t="s">
@@ -9521,7 +9582,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="92" t="s">
-        <v>677</v>
+        <v>658</v>
       </c>
       <c r="F12" s="90" t="s">
         <v>26</v>
@@ -9539,7 +9600,7 @@
         <v>40</v>
       </c>
       <c r="K12" s="68" t="s">
-        <v>678</v>
+        <v>659</v>
       </c>
       <c r="L12" s="95" t="s">
         <v>60</v>
@@ -9571,7 +9632,7 @@
         <v>25</v>
       </c>
       <c r="E13" s="98" t="s">
-        <v>679</v>
+        <v>660</v>
       </c>
       <c r="F13" s="93" t="s">
         <v>26</v>
@@ -9589,7 +9650,7 @@
         <v>40</v>
       </c>
       <c r="K13" s="68" t="s">
-        <v>680</v>
+        <v>661</v>
       </c>
       <c r="L13" s="76"/>
       <c r="N13" s="27" t="s">
@@ -9619,7 +9680,7 @@
         <v>25</v>
       </c>
       <c r="E14" s="92" t="s">
-        <v>681</v>
+        <v>662</v>
       </c>
       <c r="F14" s="90" t="s">
         <v>26</v>
@@ -9637,10 +9698,10 @@
         <v>40</v>
       </c>
       <c r="K14" s="68" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="L14" s="95" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="M14" s="27" t="s">
         <v>146</v>
@@ -9669,7 +9730,7 @@
         <v>25</v>
       </c>
       <c r="E15" s="87" t="s">
-        <v>683</v>
+        <v>664</v>
       </c>
       <c r="F15" s="93" t="s">
         <v>46</v>
@@ -9826,17 +9887,17 @@
   </sheetData>
   <autoFilter ref="A1:L15" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
   <mergeCells count="11">
+    <mergeCell ref="A6:A10"/>
+    <mergeCell ref="H6:H10"/>
+    <mergeCell ref="B6:B10"/>
+    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="C6:C10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="L6:L10"/>
     <mergeCell ref="K6:K10"/>
     <mergeCell ref="F6:F10"/>
     <mergeCell ref="J6:J10"/>
-    <mergeCell ref="A6:A10"/>
-    <mergeCell ref="H6:H10"/>
-    <mergeCell ref="B6:B10"/>
-    <mergeCell ref="E6:E10"/>
-    <mergeCell ref="C6:C10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" dxfId="226" priority="11" operator="equal">
@@ -9995,7 +10056,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="77" t="s">
-        <v>684</v>
+        <v>665</v>
       </c>
       <c r="M1" s="66" t="s">
         <v>13</v>
@@ -10027,19 +10088,19 @@
     </row>
     <row r="2" spans="1:21" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="D2" s="88" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E2" s="56" t="s">
-        <v>685</v>
+        <v>666</v>
       </c>
       <c r="F2" s="90" t="s">
         <v>46</v>
@@ -10057,7 +10118,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="76" t="s">
-        <v>686</v>
+        <v>667</v>
       </c>
       <c r="L2" s="150"/>
       <c r="N2" t="s">
@@ -10113,25 +10174,25 @@
     </row>
     <row r="4" spans="1:21" ht="92.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="87" t="s">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D4" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="158" t="s">
-        <v>688</v>
+        <v>669</v>
       </c>
       <c r="F4" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="90" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H4" s="90" t="s">
         <v>28</v>
@@ -10305,7 +10366,7 @@
         <v>25</v>
       </c>
       <c r="E8" s="56" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="F8" s="90" t="s">
         <v>46</v>
@@ -10323,7 +10384,7 @@
         <v>48</v>
       </c>
       <c r="K8" s="76" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="L8" s="76"/>
       <c r="N8" s="76" t="s">
@@ -10341,25 +10402,25 @@
     </row>
     <row r="9" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="91" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>692</v>
+        <v>673</v>
       </c>
       <c r="C9" s="91" t="s">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="D9" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="175" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="F9" s="93" t="s">
         <v>46</v>
       </c>
       <c r="G9" s="93" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H9" s="93">
         <v>1</v>
@@ -10371,7 +10432,7 @@
         <v>48</v>
       </c>
       <c r="K9" s="75" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="L9" s="95"/>
       <c r="N9" t="s">
@@ -10386,25 +10447,25 @@
     </row>
     <row r="10" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="87" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="C10" s="87" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="D10" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="F10" s="90" t="s">
         <v>46</v>
       </c>
       <c r="G10" s="90" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H10" s="99">
         <v>1</v>
@@ -10416,7 +10477,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="75" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="L10" s="76"/>
       <c r="N10" t="s">
@@ -10431,23 +10492,23 @@
     </row>
     <row r="11" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="91" t="s">
-        <v>631</v>
+        <v>612</v>
       </c>
       <c r="B11" s="48" t="s">
-        <v>632</v>
+        <v>613</v>
       </c>
       <c r="C11" s="100" t="s">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="D11" s="119" t="s">
-        <v>634</v>
+        <v>615</v>
       </c>
       <c r="E11" s="92"/>
       <c r="F11" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="93" t="s">
-        <v>636</v>
+        <v>617</v>
       </c>
       <c r="H11" s="93" t="s">
         <v>28</v>
@@ -10472,13 +10533,13 @@
     </row>
     <row r="12" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="87" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="D12" s="98" t="s">
         <v>25</v>
@@ -10488,7 +10549,7 @@
         <v>26</v>
       </c>
       <c r="G12" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H12" s="90" t="s">
         <v>28</v>
@@ -10513,19 +10574,19 @@
     </row>
     <row r="13" spans="1:21" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="155" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C13" s="100" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="D13" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="92" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="F13" s="93" t="s">
         <v>46</v>
@@ -10556,13 +10617,13 @@
     </row>
     <row r="14" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="87" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="D14" s="98" t="s">
         <v>25</v>
@@ -10597,19 +10658,19 @@
     </row>
     <row r="15" spans="1:21" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="91" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>705</v>
+        <v>686</v>
       </c>
       <c r="C15" s="91" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="D15" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="92" t="s">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="F15" s="93" t="s">
         <v>26</v>
@@ -10652,7 +10713,7 @@
         <v>102</v>
       </c>
       <c r="E16" s="29" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="F16" s="90" t="s">
         <v>26</v>
@@ -10695,7 +10756,7 @@
         <v>109</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>708</v>
+        <v>689</v>
       </c>
       <c r="F17" s="93" t="s">
         <v>46</v>
@@ -10713,7 +10774,7 @@
         <v>48</v>
       </c>
       <c r="K17" s="76" t="s">
-        <v>709</v>
+        <v>690</v>
       </c>
       <c r="L17" s="95"/>
       <c r="N17" t="s">
@@ -10740,7 +10801,7 @@
         <v>25</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>710</v>
+        <v>691</v>
       </c>
       <c r="F18" s="90" t="s">
         <v>26</v>
@@ -10774,13 +10835,13 @@
     </row>
     <row r="19" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="91" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="B19" s="48" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="C19" s="100" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="D19" s="92" t="s">
         <v>25</v>
@@ -10790,7 +10851,7 @@
         <v>26</v>
       </c>
       <c r="G19" s="94" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="H19" s="93" t="s">
         <v>28</v>
@@ -10803,10 +10864,10 @@
       </c>
       <c r="K19" s="75"/>
       <c r="L19" s="95" t="s">
-        <v>711</v>
+        <v>692</v>
       </c>
       <c r="M19" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="N19" t="s">
         <v>52</v>
@@ -10832,7 +10893,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>712</v>
+        <v>693</v>
       </c>
       <c r="F20" s="90" t="s">
         <v>46</v>
@@ -10868,19 +10929,19 @@
     </row>
     <row r="21" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="91" t="s">
-        <v>713</v>
+        <v>694</v>
       </c>
       <c r="B21" s="48" t="s">
-        <v>714</v>
+        <v>695</v>
       </c>
       <c r="C21" s="91" t="s">
-        <v>715</v>
+        <v>696</v>
       </c>
       <c r="D21" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E21" s="92" t="s">
-        <v>716</v>
+        <v>697</v>
       </c>
       <c r="F21" s="93" t="s">
         <v>26</v>
@@ -10898,10 +10959,10 @@
         <v>40</v>
       </c>
       <c r="K21" s="76" t="s">
-        <v>717</v>
+        <v>698</v>
       </c>
       <c r="L21" s="156" t="s">
-        <v>718</v>
+        <v>699</v>
       </c>
       <c r="N21" t="s">
         <v>32</v>
@@ -10915,25 +10976,25 @@
     </row>
     <row r="22" spans="1:21" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="87" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>148</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="D22" s="88" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="F22" s="90" t="s">
         <v>46</v>
       </c>
       <c r="G22" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H22" s="90" t="s">
         <v>67</v>
@@ -10953,7 +11014,7 @@
         <v>33</v>
       </c>
       <c r="Q22" s="200" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="S22" s="87"/>
       <c r="T22" s="87"/>
@@ -10973,7 +11034,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="92" t="s">
-        <v>720</v>
+        <v>701</v>
       </c>
       <c r="F23" s="93" t="s">
         <v>46</v>
@@ -10991,7 +11052,7 @@
         <v>40</v>
       </c>
       <c r="K23" s="75" t="s">
-        <v>721</v>
+        <v>702</v>
       </c>
       <c r="L23" s="159"/>
       <c r="N23" s="76" t="s">
@@ -11639,16 +11700,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>722</v>
+        <v>703</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>723</v>
+        <v>704</v>
       </c>
       <c r="N1" s="189" t="s">
-        <v>724</v>
+        <v>705</v>
       </c>
       <c r="O1" s="195" t="s">
-        <v>725</v>
+        <v>706</v>
       </c>
       <c r="P1" s="66" t="s">
         <v>13</v>
@@ -11680,19 +11741,19 @@
     </row>
     <row r="2" spans="1:24" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="160" t="s">
-        <v>726</v>
+        <v>707</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>727</v>
+        <v>708</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>728</v>
+        <v>709</v>
       </c>
       <c r="D2" s="160" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>729</v>
+        <v>710</v>
       </c>
       <c r="F2" s="162" t="s">
         <v>46</v>
@@ -11701,7 +11762,7 @@
         <v>73</v>
       </c>
       <c r="H2" s="162" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="I2" s="125" t="s">
         <v>29</v>
@@ -11725,13 +11786,13 @@
     </row>
     <row r="3" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46" t="s">
-        <v>731</v>
+        <v>712</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>732</v>
+        <v>713</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>733</v>
+        <v>714</v>
       </c>
       <c r="D3" s="46" t="s">
         <v>25</v>
@@ -11896,25 +11957,25 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>734</v>
+        <v>715</v>
       </c>
       <c r="M1" s="182" t="s">
-        <v>735</v>
+        <v>716</v>
       </c>
       <c r="N1" s="188" t="s">
-        <v>736</v>
+        <v>717</v>
       </c>
       <c r="O1" s="192" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="P1" s="189" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="Q1" s="193" t="s">
-        <v>739</v>
+        <v>720</v>
       </c>
       <c r="R1" s="195" t="s">
-        <v>740</v>
+        <v>721</v>
       </c>
       <c r="S1" s="66" t="s">
         <v>13</v>
@@ -11946,13 +12007,13 @@
     </row>
     <row r="2" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="41" t="s">
-        <v>741</v>
+        <v>722</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>742</v>
+        <v>723</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>743</v>
+        <v>724</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>25</v>
@@ -11992,13 +12053,13 @@
     </row>
     <row r="3" spans="1:27" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>744</v>
+        <v>725</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>745</v>
+        <v>726</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>746</v>
+        <v>727</v>
       </c>
       <c r="D3" s="35" t="s">
         <v>25</v>
@@ -12834,13 +12895,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>747</v>
+        <v>728</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>748</v>
+        <v>729</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>749</v>
+        <v>730</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>13</v>
@@ -12872,19 +12933,19 @@
     </row>
     <row r="2" spans="1:23" ht="176" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>750</v>
+        <v>731</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>751</v>
+        <v>732</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>752</v>
+        <v>733</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>753</v>
+        <v>734</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>26</v>
@@ -13352,16 +13413,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>755</v>
+        <v>736</v>
       </c>
       <c r="N1" s="189" t="s">
-        <v>756</v>
+        <v>737</v>
       </c>
       <c r="O1" s="195" t="s">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="P1" s="67" t="s">
         <v>13</v>
@@ -13393,19 +13454,19 @@
     </row>
     <row r="2" spans="1:24" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
-        <v>758</v>
+        <v>739</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>759</v>
+        <v>740</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>760</v>
+        <v>741</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>761</v>
+        <v>742</v>
       </c>
       <c r="F2" s="43" t="s">
         <v>26</v>
@@ -13447,25 +13508,25 @@
     </row>
     <row r="3" spans="1:24" ht="144" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="D3" s="37" t="s">
-        <v>765</v>
+        <v>746</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>766</v>
+        <v>747</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H3" s="38" t="s">
         <v>98</v>
@@ -13481,7 +13542,7 @@
       <c r="M3" s="86"/>
       <c r="N3" s="86"/>
       <c r="Q3" s="58" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="R3" s="58" t="s">
         <v>33</v>
@@ -13595,16 +13656,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="180" t="s">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="M1" s="191" t="s">
-        <v>768</v>
+        <v>749</v>
       </c>
       <c r="N1" s="190" t="s">
-        <v>769</v>
+        <v>750</v>
       </c>
       <c r="O1" s="195" t="s">
-        <v>770</v>
+        <v>751</v>
       </c>
       <c r="P1" s="67" t="s">
         <v>13</v>
@@ -13636,25 +13697,25 @@
     </row>
     <row r="2" spans="1:24" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>763</v>
+        <v>744</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>764</v>
+        <v>745</v>
       </c>
       <c r="D2" s="42" t="s">
-        <v>772</v>
+        <v>753</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>773</v>
+        <v>754</v>
       </c>
       <c r="F2" s="43" t="s">
         <v>46</v>
       </c>
       <c r="G2" s="81" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H2" s="43" t="s">
         <v>67</v>
@@ -13678,25 +13739,25 @@
     </row>
     <row r="3" spans="1:24" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>774</v>
+        <v>755</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>775</v>
+        <v>756</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H3" s="38" t="s">
         <v>67</v>
@@ -13826,16 +13887,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>778</v>
+        <v>759</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>779</v>
+        <v>760</v>
       </c>
       <c r="N1" s="189" t="s">
-        <v>780</v>
+        <v>761</v>
       </c>
       <c r="O1" s="195" t="s">
-        <v>781</v>
+        <v>762</v>
       </c>
       <c r="P1" s="67" t="s">
         <v>13</v>
@@ -13867,25 +13928,25 @@
     </row>
     <row r="2" spans="1:24" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
-        <v>782</v>
+        <v>763</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>783</v>
+        <v>764</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>784</v>
+        <v>765</v>
       </c>
       <c r="D2" s="41" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="F2" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H2" s="43" t="s">
         <v>98</v>
@@ -13909,25 +13970,25 @@
     </row>
     <row r="3" spans="1:24" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>786</v>
+        <v>767</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>787</v>
+        <v>768</v>
       </c>
       <c r="C3" s="51" t="s">
-        <v>788</v>
+        <v>769</v>
       </c>
       <c r="D3" s="82" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>789</v>
+        <v>770</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H3" s="38" t="s">
         <v>98</v>
@@ -14057,16 +14118,16 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>790</v>
+        <v>771</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>791</v>
+        <v>772</v>
       </c>
       <c r="N1" s="189" t="s">
-        <v>792</v>
+        <v>773</v>
       </c>
       <c r="O1" s="195" t="s">
-        <v>793</v>
+        <v>774</v>
       </c>
       <c r="P1" s="67" t="s">
         <v>13</v>
@@ -14098,25 +14159,25 @@
     </row>
     <row r="2" spans="1:24" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="58" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="D2" s="205" t="s">
-        <v>794</v>
+        <v>775</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="F2" s="43" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="33" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H2" s="43" t="s">
         <v>28</v>
@@ -14136,25 +14197,25 @@
     </row>
     <row r="3" spans="1:24" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="35" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>797</v>
+        <v>778</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>798</v>
+        <v>779</v>
       </c>
       <c r="D3" s="37" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>799</v>
+        <v>780</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>26</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H3" s="38" t="s">
         <v>28</v>
@@ -14314,13 +14375,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>800</v>
+        <v>781</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>13</v>
@@ -14352,25 +14413,25 @@
     </row>
     <row r="2" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>46</v>
       </c>
       <c r="G2" s="168" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="H2" s="34">
         <v>1</v>
@@ -14393,13 +14454,13 @@
     </row>
     <row r="3" spans="1:23" ht="71.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="36" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="D3" s="37" t="s">
         <v>25</v>
@@ -14409,7 +14470,7 @@
         <v>46</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>812</v>
+        <v>793</v>
       </c>
       <c r="H3" s="39">
         <v>1</v>
@@ -15234,13 +15295,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>13</v>
@@ -15272,25 +15333,25 @@
     </row>
     <row r="2" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>818</v>
+        <v>799</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>819</v>
+        <v>800</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>46</v>
       </c>
       <c r="G2" s="199" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="H2" s="34" t="s">
         <v>67</v>
@@ -15302,7 +15363,7 @@
         <v>83</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>820</v>
+        <v>801</v>
       </c>
       <c r="P2" s="27" t="s">
         <v>52</v>
@@ -15319,7 +15380,7 @@
         <v>151</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="C3" s="41" t="s">
         <v>153</v>
@@ -15328,7 +15389,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>46</v>
@@ -16143,13 +16204,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>13</v>
@@ -16181,25 +16242,25 @@
     </row>
     <row r="2" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>822</v>
+        <v>803</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>823</v>
+        <v>804</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>824</v>
+        <v>805</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>825</v>
+        <v>806</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>826</v>
+        <v>807</v>
       </c>
       <c r="H2" s="168" t="s">
         <v>98</v>
@@ -16225,7 +16286,7 @@
         <v>151</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>827</v>
+        <v>808</v>
       </c>
       <c r="C3" s="35" t="s">
         <v>153</v>
@@ -16234,7 +16295,7 @@
         <v>25</v>
       </c>
       <c r="E3" s="127" t="s">
-        <v>828</v>
+        <v>809</v>
       </c>
       <c r="F3" s="33" t="s">
         <v>46</v>
@@ -16266,19 +16327,19 @@
     </row>
     <row r="4" spans="1:23" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>829</v>
+        <v>810</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="D4" s="52" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>830</v>
+        <v>811</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>26</v>
@@ -16307,25 +16368,25 @@
     </row>
     <row r="5" spans="1:23" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="209" t="s">
-        <v>831</v>
+        <v>812</v>
       </c>
       <c r="B5" s="210" t="s">
-        <v>832</v>
+        <v>813</v>
       </c>
       <c r="C5" s="209" t="s">
-        <v>833</v>
+        <v>814</v>
       </c>
       <c r="D5" s="211" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="210" t="s">
-        <v>834</v>
+        <v>815</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>46</v>
       </c>
       <c r="G5" s="198" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="H5" s="212" t="s">
         <v>67</v>
@@ -16337,7 +16398,7 @@
         <v>83</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>835</v>
+        <v>816</v>
       </c>
       <c r="P5" s="27" t="s">
         <v>52</v>
@@ -17121,13 +17182,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="181" t="s">
-        <v>836</v>
+        <v>817</v>
       </c>
       <c r="M1" s="188" t="s">
-        <v>837</v>
+        <v>818</v>
       </c>
       <c r="N1" s="195" t="s">
-        <v>821</v>
+        <v>802</v>
       </c>
       <c r="O1" s="67" t="s">
         <v>13</v>
@@ -17159,19 +17220,19 @@
     </row>
     <row r="2" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="31" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>838</v>
+        <v>819</v>
       </c>
       <c r="C2" s="41" t="s">
-        <v>839</v>
+        <v>820</v>
       </c>
       <c r="D2" s="52" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="161" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="F2" s="33" t="s">
         <v>46</v>
@@ -17180,7 +17241,7 @@
         <v>73</v>
       </c>
       <c r="H2" s="168" t="s">
-        <v>730</v>
+        <v>711</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>29</v>
@@ -17203,16 +17264,16 @@
         <v>151</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>841</v>
+        <v>822</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="D3" s="207" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="127" t="s">
-        <v>843</v>
+        <v>824</v>
       </c>
       <c r="F3" s="33" t="s">
         <v>46</v>
@@ -17247,7 +17308,7 @@
         <v>69</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="C4" s="13" t="s">
         <v>71</v>
@@ -17256,7 +17317,7 @@
         <v>25</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>845</v>
+        <v>826</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>46</v>
@@ -17288,19 +17349,19 @@
     </row>
     <row r="5" spans="1:23" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="209" t="s">
-        <v>846</v>
+        <v>827</v>
       </c>
       <c r="B5" s="210" t="s">
-        <v>847</v>
+        <v>828</v>
       </c>
       <c r="C5" s="209" t="s">
-        <v>848</v>
+        <v>829</v>
       </c>
       <c r="D5" s="211" t="s">
-        <v>849</v>
+        <v>830</v>
       </c>
       <c r="E5" s="210" t="s">
-        <v>850</v>
+        <v>831</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>46</v>
@@ -17329,25 +17390,25 @@
     </row>
     <row r="6" spans="1:23" ht="154" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="13" t="s">
-        <v>851</v>
+        <v>832</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>852</v>
+        <v>833</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="D6" s="52" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>26</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>855</v>
+        <v>836</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>98</v>
@@ -18072,7 +18133,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
@@ -18248,7 +18309,7 @@
         <v>198</v>
       </c>
       <c r="B22" s="200" t="s">
-        <v>857</v>
+        <v>838</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -18256,7 +18317,7 @@
         <v>199</v>
       </c>
       <c r="B23" s="200" t="s">
-        <v>860</v>
+        <v>841</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
@@ -18264,15 +18325,23 @@
         <v>200</v>
       </c>
       <c r="B24" s="200" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>201</v>
       </c>
       <c r="B25" s="200" t="s">
-        <v>858</v>
+        <v>839</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>865</v>
+      </c>
+      <c r="B26" s="200" t="s">
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -18299,6 +18368,7 @@
     <hyperlink ref="B25" r:id="rId20" tooltip="http://schema.org/" xr:uid="{DEAFF9D5-EB1E-F040-8316-167366B3631C}"/>
     <hyperlink ref="B24" r:id="rId21" tooltip="http://www.w3.org/ns/prov#" display="http://www.w3.org/ns/prov" xr:uid="{9A1C84E5-E39B-B743-BD5F-D063A07D12B0}"/>
     <hyperlink ref="B23" r:id="rId22" tooltip="http://www.w3.org/ns/oa#" display="http://www.w3.org/ns/oa" xr:uid="{962971F1-479E-7446-ADCB-7507A33072DE}"/>
+    <hyperlink ref="B26" r:id="rId23" tooltip="http://data.health-ri.nl/core/p2/%3e" display="http://data.health-ri.nl/core/p2/%3e" xr:uid="{DC0AED85-1897-1E4F-BF07-039D5380ABBA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -18309,7 +18379,7 @@
   <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
   </cols>
@@ -18351,18 +18421,18 @@
         <v>211</v>
       </c>
       <c r="C2" t="s">
+        <v>846</v>
+      </c>
+      <c r="D2" t="s">
         <v>212</v>
-      </c>
-      <c r="D2" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C3" t="s">
-        <v>215</v>
+        <v>847</v>
       </c>
       <c r="D3" t="s">
         <v>66</v>
@@ -18373,10 +18443,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C4" t="s">
-        <v>217</v>
+        <v>848</v>
       </c>
       <c r="D4" t="s">
         <v>38</v>
@@ -18387,10 +18457,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C5" t="s">
-        <v>219</v>
+        <v>849</v>
       </c>
       <c r="D5" t="s">
         <v>58</v>
@@ -18398,10 +18468,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>220</v>
-      </c>
-      <c r="C6" t="s">
-        <v>221</v>
+        <v>216</v>
+      </c>
+      <c r="C6" s="230" t="s">
+        <v>850</v>
       </c>
       <c r="D6" t="s">
         <v>47</v>
@@ -18409,13 +18479,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C7" t="s">
-        <v>223</v>
+        <v>217</v>
+      </c>
+      <c r="C7" s="230" t="s">
+        <v>851</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
@@ -18423,13 +18493,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C8" t="s">
-        <v>226</v>
+        <v>852</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
@@ -18437,10 +18507,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>228</v>
-      </c>
-      <c r="C9" t="s">
-        <v>229</v>
+        <v>221</v>
+      </c>
+      <c r="C9" s="230" t="s">
+        <v>853</v>
       </c>
       <c r="D9" t="s">
         <v>139</v>
@@ -18448,21 +18518,21 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="C10" t="s">
-        <v>231</v>
+        <v>854</v>
       </c>
       <c r="D10" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
-        <v>234</v>
+        <v>855</v>
       </c>
       <c r="D11" t="s">
         <v>144</v>
@@ -18470,101 +18540,101 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>236</v>
+        <v>856</v>
       </c>
       <c r="D12" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="C13" t="s">
-        <v>239</v>
+        <v>857</v>
       </c>
       <c r="D13" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="C14" t="s">
-        <v>242</v>
+        <v>858</v>
       </c>
       <c r="D14" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>859</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>232</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>247</v>
+        <v>233</v>
       </c>
       <c r="C16" t="s">
-        <v>248</v>
+        <v>860</v>
       </c>
       <c r="D16" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>861</v>
       </c>
       <c r="D17" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C18" t="s">
-        <v>254</v>
+        <v>862</v>
       </c>
       <c r="D18" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>863</v>
       </c>
       <c r="D19" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="C20" t="s">
-        <v>260</v>
+        <v>864</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -18616,7 +18686,7 @@
         <v>10</v>
       </c>
       <c r="L1" s="77" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="M1" s="66" t="s">
         <v>13</v>
@@ -19089,41 +19159,41 @@
       <c r="V7" s="91"/>
     </row>
     <row r="8" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="217" t="s">
+      <c r="A8" s="218" t="s">
         <v>77</v>
       </c>
-      <c r="B8" s="215" t="s">
+      <c r="B8" s="216" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="217" t="s">
+      <c r="C8" s="218" t="s">
         <v>79</v>
       </c>
       <c r="D8" s="176" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="218" t="s">
+      <c r="E8" s="219" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="213" t="s">
+      <c r="F8" s="215" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="213" t="s">
+      <c r="G8" s="215" t="s">
         <v>82</v>
       </c>
-      <c r="H8" s="213" t="s">
+      <c r="H8" s="215" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="219" t="s">
+      <c r="I8" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="219" t="s">
+      <c r="J8" s="213" t="s">
         <v>83</v>
       </c>
       <c r="K8" s="103"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
+      <c r="L8" s="213"/>
+      <c r="M8" s="213"/>
       <c r="O8" s="27" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="P8" s="27" t="s">
         <v>33</v>
@@ -19134,13 +19204,13 @@
       <c r="V8" s="87"/>
     </row>
     <row r="9" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="216"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
+      <c r="A9" s="217"/>
+      <c r="B9" s="217"/>
+      <c r="C9" s="217"/>
       <c r="D9" s="177" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="216"/>
+      <c r="E9" s="217"/>
       <c r="F9" s="214"/>
       <c r="G9" s="214"/>
       <c r="H9" s="214"/>
@@ -19152,13 +19222,13 @@
       <c r="S9" s="69"/>
     </row>
     <row r="10" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="216"/>
-      <c r="B10" s="216"/>
-      <c r="C10" s="216"/>
+      <c r="A10" s="217"/>
+      <c r="B10" s="217"/>
+      <c r="C10" s="217"/>
       <c r="D10" s="177" t="s">
         <v>85</v>
       </c>
-      <c r="E10" s="216"/>
+      <c r="E10" s="217"/>
       <c r="F10" s="214"/>
       <c r="G10" s="214"/>
       <c r="H10" s="214"/>
@@ -19170,13 +19240,13 @@
       <c r="S10" s="69"/>
     </row>
     <row r="11" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="216"/>
-      <c r="B11" s="216"/>
-      <c r="C11" s="216"/>
+      <c r="A11" s="217"/>
+      <c r="B11" s="217"/>
+      <c r="C11" s="217"/>
       <c r="D11" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="E11" s="216"/>
+      <c r="E11" s="217"/>
       <c r="F11" s="214"/>
       <c r="G11" s="214"/>
       <c r="H11" s="214"/>
@@ -19188,13 +19258,13 @@
       <c r="S11" s="69"/>
     </row>
     <row r="12" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="216"/>
-      <c r="B12" s="216"/>
-      <c r="C12" s="216"/>
+      <c r="A12" s="217"/>
+      <c r="B12" s="217"/>
+      <c r="C12" s="217"/>
       <c r="D12" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="216"/>
+      <c r="E12" s="217"/>
       <c r="F12" s="214"/>
       <c r="G12" s="214"/>
       <c r="H12" s="214"/>
@@ -19334,7 +19404,7 @@
       <c r="L15" s="95"/>
       <c r="M15" s="95"/>
       <c r="O15" s="27" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="P15" s="27" t="s">
         <v>33</v>
@@ -19701,7 +19771,7 @@
         <v>26</v>
       </c>
       <c r="G23" s="93" t="s">
-        <v>856</v>
+        <v>837</v>
       </c>
       <c r="H23" s="93" t="s">
         <v>28</v>
@@ -19716,7 +19786,7 @@
       <c r="L23" s="95"/>
       <c r="M23" s="95"/>
       <c r="O23" s="27" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="P23" s="27" t="s">
         <v>33</v>
@@ -19778,17 +19848,17 @@
   </sheetData>
   <autoFilter ref="A1:J24" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
   <mergeCells count="11">
-    <mergeCell ref="M8:M12"/>
-    <mergeCell ref="I8:I12"/>
-    <mergeCell ref="G8:G12"/>
-    <mergeCell ref="L8:L12"/>
-    <mergeCell ref="J8:J12"/>
     <mergeCell ref="F8:F12"/>
     <mergeCell ref="H8:H12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="I8:I12"/>
+    <mergeCell ref="G8:G12"/>
+    <mergeCell ref="L8:L12"/>
+    <mergeCell ref="J8:J12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
     <cfRule type="cellIs" dxfId="309" priority="20" operator="equal">
@@ -19978,13 +20048,13 @@
         <v>10</v>
       </c>
       <c r="L1" s="77" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="M1" s="185" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="N1" s="186" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="O1" s="66" t="s">
         <v>13</v>
@@ -20016,19 +20086,19 @@
     </row>
     <row r="2" spans="1:23" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="97" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="C2" s="87" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="D2" s="88" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="E2" s="89" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="F2" s="90" t="s">
         <v>46</v>
@@ -20046,7 +20116,7 @@
         <v>30</v>
       </c>
       <c r="K2" s="75" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="L2" s="76"/>
       <c r="P2" s="27" t="s">
@@ -20061,19 +20131,19 @@
     </row>
     <row r="3" spans="1:23" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="91" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="B3" s="48" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="C3" s="91" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="D3" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="F3" s="90" t="s">
         <v>26</v>
@@ -20106,25 +20176,25 @@
     </row>
     <row r="4" spans="1:23" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="97" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="B4" s="97" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="C4" s="97" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="D4" s="97" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="206" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="F4" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="94" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H4" s="90" t="s">
         <v>28</v>
@@ -20136,10 +20206,10 @@
         <v>83</v>
       </c>
       <c r="K4" s="75" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="L4" s="76" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="P4" s="27" t="s">
         <v>32</v>
@@ -20153,25 +20223,25 @@
     </row>
     <row r="5" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="91" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="B5" s="48" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="C5" s="91" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="D5" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="F5" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G5" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H5" s="93" t="s">
         <v>28</v>
@@ -20189,7 +20259,7 @@
         <v>33</v>
       </c>
       <c r="R5" s="27" t="s">
-        <v>861</v>
+        <v>842</v>
       </c>
       <c r="U5" s="91"/>
       <c r="V5" s="91"/>
@@ -20209,7 +20279,7 @@
         <v>25</v>
       </c>
       <c r="E6" s="98" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="F6" s="90" t="s">
         <v>46</v>
@@ -20237,7 +20307,7 @@
         <v>33</v>
       </c>
       <c r="S6" s="83" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="U6" s="97"/>
       <c r="V6" s="97"/>
@@ -20245,25 +20315,25 @@
     </row>
     <row r="7" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="91" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="C7" s="100" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="D7" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E7" s="92" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="F7" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H7" s="93" t="s">
         <v>28</v>
@@ -20275,7 +20345,7 @@
         <v>83</v>
       </c>
       <c r="K7" s="96" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="L7" s="95"/>
       <c r="M7" s="95"/>
@@ -20292,25 +20362,25 @@
     </row>
     <row r="8" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="87" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="D8" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="98" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="F8" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="90" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H8" s="90" t="s">
         <v>28</v>
@@ -20322,7 +20392,7 @@
         <v>83</v>
       </c>
       <c r="K8" s="75" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="L8" s="76"/>
       <c r="P8" s="27" t="s">
@@ -20337,25 +20407,25 @@
     </row>
     <row r="9" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="91" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="B9" s="48" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="C9" s="91" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="D9" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E9" s="48" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="F9" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="93" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="H9" s="93" t="s">
         <v>28</v>
@@ -20367,7 +20437,7 @@
         <v>83</v>
       </c>
       <c r="K9" s="96" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="L9" s="95"/>
       <c r="M9" s="95"/>
@@ -20414,7 +20484,7 @@
         <v>48</v>
       </c>
       <c r="K10" s="75" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="L10" s="76" t="s">
         <v>50</v>
@@ -20452,7 +20522,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="F11" s="93" t="s">
         <v>46</v>
@@ -20470,7 +20540,7 @@
         <v>48</v>
       </c>
       <c r="K11" s="96" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="L11" s="95" t="s">
         <v>60</v>
@@ -20508,7 +20578,7 @@
         <v>25</v>
       </c>
       <c r="E12" s="29" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="F12" s="90" t="s">
         <v>46</v>
@@ -20544,25 +20614,25 @@
     </row>
     <row r="13" spans="1:23" ht="44" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="91" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="B13" s="48" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="C13" s="91" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="D13" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="106" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="F13" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="94" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H13" s="93" t="s">
         <v>28</v>
@@ -20575,13 +20645,13 @@
       </c>
       <c r="K13" s="96"/>
       <c r="L13" s="95" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="M13" s="95" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="N13" s="95" t="s">
-        <v>313</v>
+        <v>294</v>
       </c>
       <c r="O13" s="202"/>
       <c r="P13" s="202" t="s">
@@ -20598,19 +20668,19 @@
     </row>
     <row r="14" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="87" t="s">
-        <v>314</v>
+        <v>295</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>316</v>
+        <v>297</v>
       </c>
       <c r="D14" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="98" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="F14" s="90" t="s">
         <v>26</v>
@@ -20628,7 +20698,7 @@
         <v>83</v>
       </c>
       <c r="K14" s="75" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="L14" s="76"/>
       <c r="P14" s="27" t="s">
@@ -20643,25 +20713,25 @@
     </row>
     <row r="15" spans="1:23" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="91" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B15" s="48" t="s">
-        <v>320</v>
+        <v>301</v>
       </c>
       <c r="C15" s="91" t="s">
-        <v>321</v>
+        <v>302</v>
       </c>
       <c r="D15" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="48" t="s">
-        <v>322</v>
+        <v>303</v>
       </c>
       <c r="F15" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H15" s="93" t="s">
         <v>28</v>
@@ -20686,25 +20756,25 @@
     </row>
     <row r="16" spans="1:23" ht="69.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="87" t="s">
-        <v>323</v>
+        <v>304</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>324</v>
+        <v>305</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>325</v>
+        <v>306</v>
       </c>
       <c r="D16" s="88" t="s">
-        <v>326</v>
+        <v>307</v>
       </c>
       <c r="E16" s="104" t="s">
-        <v>327</v>
+        <v>308</v>
       </c>
       <c r="F16" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H16" s="90" t="s">
         <v>98</v>
@@ -20716,7 +20786,7 @@
         <v>83</v>
       </c>
       <c r="K16" s="204" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
       <c r="L16" s="107"/>
       <c r="M16" s="76"/>
@@ -20745,9 +20815,9 @@
         <v>80</v>
       </c>
       <c r="E17" s="222" t="s">
-        <v>329</v>
-      </c>
-      <c r="F17" s="213" t="s">
+        <v>310</v>
+      </c>
+      <c r="F17" s="215" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="226" t="s">
@@ -20777,9 +20847,9 @@
       <c r="W17" s="91"/>
     </row>
     <row r="18" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="216"/>
-      <c r="B18" s="216"/>
-      <c r="C18" s="216"/>
+      <c r="A18" s="217"/>
+      <c r="B18" s="217"/>
+      <c r="C18" s="217"/>
       <c r="D18" s="179" t="s">
         <v>84</v>
       </c>
@@ -20795,9 +20865,9 @@
       <c r="N18" s="214"/>
     </row>
     <row r="19" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="216"/>
-      <c r="B19" s="216"/>
-      <c r="C19" s="216"/>
+      <c r="A19" s="217"/>
+      <c r="B19" s="217"/>
+      <c r="C19" s="217"/>
       <c r="D19" s="179" t="s">
         <v>85</v>
       </c>
@@ -20813,9 +20883,9 @@
       <c r="N19" s="214"/>
     </row>
     <row r="20" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="216"/>
-      <c r="B20" s="216"/>
-      <c r="C20" s="216"/>
+      <c r="A20" s="217"/>
+      <c r="B20" s="217"/>
+      <c r="C20" s="217"/>
       <c r="D20" s="105" t="s">
         <v>86</v>
       </c>
@@ -20831,9 +20901,9 @@
       <c r="N20" s="214"/>
     </row>
     <row r="21" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="216"/>
-      <c r="B21" s="216"/>
-      <c r="C21" s="216"/>
+      <c r="A21" s="217"/>
+      <c r="B21" s="217"/>
+      <c r="C21" s="217"/>
       <c r="D21" s="105" t="s">
         <v>87</v>
       </c>
@@ -20850,19 +20920,19 @@
     </row>
     <row r="22" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="87" t="s">
-        <v>330</v>
+        <v>311</v>
       </c>
       <c r="B22" s="29" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="D22" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="104" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="F22" s="93" t="s">
         <v>26</v>
@@ -20880,10 +20950,10 @@
         <v>40</v>
       </c>
       <c r="K22" s="204" t="s">
-        <v>334</v>
+        <v>315</v>
       </c>
       <c r="L22" s="107" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="M22" s="76"/>
       <c r="N22" s="76"/>
@@ -20899,25 +20969,25 @@
     </row>
     <row r="23" spans="1:23" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="91" t="s">
-        <v>336</v>
+        <v>317</v>
       </c>
       <c r="B23" s="48" t="s">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="C23" s="91" t="s">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="D23" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E23" s="54" t="s">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="F23" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H23" s="93" t="s">
         <v>28</v>
@@ -20937,7 +21007,7 @@
         <v>33</v>
       </c>
       <c r="R23" s="27" t="s">
-        <v>862</v>
+        <v>843</v>
       </c>
       <c r="U23" s="91"/>
       <c r="V23" s="91"/>
@@ -20945,25 +21015,25 @@
     </row>
     <row r="24" spans="1:23" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="87" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="B24" s="29" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>342</v>
+        <v>323</v>
       </c>
       <c r="D24" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="53" t="s">
-        <v>343</v>
+        <v>324</v>
       </c>
       <c r="F24" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H24" s="90" t="s">
         <v>28</v>
@@ -20975,7 +21045,7 @@
         <v>83</v>
       </c>
       <c r="K24" s="75" t="s">
-        <v>344</v>
+        <v>325</v>
       </c>
       <c r="L24" s="76"/>
       <c r="P24" s="27" t="s">
@@ -20990,19 +21060,19 @@
     </row>
     <row r="25" spans="1:23" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="91" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C25" s="91" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="D25" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="171" t="s">
-        <v>348</v>
+        <v>329</v>
       </c>
       <c r="F25" s="93" t="s">
         <v>46</v>
@@ -21020,7 +21090,7 @@
         <v>48</v>
       </c>
       <c r="K25" s="96" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="L25" s="95"/>
       <c r="M25" s="95"/>
@@ -21037,25 +21107,25 @@
     </row>
     <row r="26" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="87" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="B26" s="29" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="C26" s="87" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="D26" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E26" s="98" t="s">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="F26" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="94" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="H26" s="90" t="s">
         <v>28</v>
@@ -21068,7 +21138,7 @@
       </c>
       <c r="K26" s="75"/>
       <c r="L26" s="107" t="s">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="P26" s="27" t="s">
         <v>32</v>
@@ -21082,25 +21152,25 @@
     </row>
     <row r="27" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="91" t="s">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B27" s="48" t="s">
-        <v>356</v>
+        <v>337</v>
       </c>
       <c r="C27" s="91" t="s">
-        <v>357</v>
+        <v>338</v>
       </c>
       <c r="D27" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>358</v>
+        <v>339</v>
       </c>
       <c r="F27" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="93" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H27" s="93" t="s">
         <v>28</v>
@@ -21112,7 +21182,7 @@
         <v>40</v>
       </c>
       <c r="K27" s="170" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="L27" s="95"/>
       <c r="M27" s="95"/>
@@ -21129,19 +21199,19 @@
     </row>
     <row r="28" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="87" t="s">
-        <v>361</v>
+        <v>342</v>
       </c>
       <c r="B28" s="29" t="s">
-        <v>362</v>
+        <v>343</v>
       </c>
       <c r="C28" s="107" t="s">
-        <v>363</v>
+        <v>344</v>
       </c>
       <c r="D28" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="47" t="s">
-        <v>364</v>
+        <v>345</v>
       </c>
       <c r="F28" s="90" t="s">
         <v>46</v>
@@ -21159,7 +21229,7 @@
         <v>40</v>
       </c>
       <c r="K28" s="75" t="s">
-        <v>365</v>
+        <v>346</v>
       </c>
       <c r="L28" s="76"/>
       <c r="P28" s="27" t="s">
@@ -21174,19 +21244,19 @@
     </row>
     <row r="29" spans="1:23" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="91" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="C29" s="100" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="D29" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="127" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="F29" s="90" t="s">
         <v>26</v>
@@ -21231,7 +21301,7 @@
         <v>102</v>
       </c>
       <c r="E30" s="98" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="F30" s="93" t="s">
         <v>26</v>
@@ -21266,25 +21336,25 @@
     </row>
     <row r="31" spans="1:23" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="91" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="B31" s="48" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="C31" s="100" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="D31" s="108" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="E31" s="92" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="F31" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="93" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="H31" s="93" t="s">
         <v>28</v>
@@ -21296,7 +21366,7 @@
         <v>83</v>
       </c>
       <c r="K31" s="96" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="L31" s="95"/>
       <c r="M31" s="202"/>
@@ -21313,25 +21383,25 @@
     </row>
     <row r="32" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="87" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="B32" s="29" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="D32" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="98" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="F32" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="90" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="H32" s="90" t="s">
         <v>98</v>
@@ -21343,7 +21413,7 @@
         <v>83</v>
       </c>
       <c r="K32" s="75" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="L32" s="76"/>
       <c r="M32" s="76"/>
@@ -21360,25 +21430,25 @@
     </row>
     <row r="33" spans="1:51" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="91" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="B33" s="48" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="C33" s="100" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="D33" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="92" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="F33" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="93" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="H33" s="93" t="s">
         <v>98</v>
@@ -21390,7 +21460,7 @@
         <v>83</v>
       </c>
       <c r="K33" s="96" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="L33" s="95"/>
       <c r="M33" s="202"/>
@@ -21407,25 +21477,25 @@
     </row>
     <row r="34" spans="1:51" ht="209.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="87" t="s">
-        <v>389</v>
+        <v>370</v>
       </c>
       <c r="B34" s="29" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="C34" s="107" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="D34" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E34" s="98" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="F34" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H34" s="90" t="s">
         <v>28</v>
@@ -21492,7 +21562,7 @@
         <v>25</v>
       </c>
       <c r="E35" s="48" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="F35" s="93" t="s">
         <v>26</v>
@@ -21530,25 +21600,25 @@
     </row>
     <row r="36" spans="1:51" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="87" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="D36" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E36" s="98" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="F36" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="90" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="H36" s="90" t="s">
         <v>98</v>
@@ -21560,7 +21630,7 @@
         <v>83</v>
       </c>
       <c r="K36" s="75" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="L36" s="76"/>
       <c r="P36" s="69" t="s">
@@ -21575,25 +21645,25 @@
     </row>
     <row r="37" spans="1:51" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="91" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="B37" s="48" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="C37" s="91" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="D37" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="48" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="F37" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="93" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="H37" s="93" t="s">
         <v>98</v>
@@ -21605,7 +21675,7 @@
         <v>83</v>
       </c>
       <c r="K37" s="96" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="L37" s="95"/>
       <c r="M37" s="95"/>
@@ -21622,25 +21692,25 @@
     </row>
     <row r="38" spans="1:51" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="87" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="B38" s="29" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="D38" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="98" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="F38" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="90" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="H38" s="90" t="s">
         <v>28</v>
@@ -21652,11 +21722,11 @@
         <v>40</v>
       </c>
       <c r="K38" s="75" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="L38" s="76"/>
       <c r="O38" s="27" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="P38" s="69" t="s">
         <v>52</v>
@@ -21670,25 +21740,25 @@
     </row>
     <row r="39" spans="1:51" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="91" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="B39" s="48" t="s">
-        <v>411</v>
+        <v>392</v>
       </c>
       <c r="C39" s="91" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="D39" s="108" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="E39" s="54" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="F39" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="93" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="H39" s="93" t="s">
         <v>28</v>
@@ -21700,13 +21770,13 @@
         <v>83</v>
       </c>
       <c r="K39" s="96" t="s">
-        <v>416</v>
+        <v>397</v>
       </c>
       <c r="L39" s="95"/>
       <c r="M39" s="95"/>
       <c r="N39" s="95"/>
       <c r="P39" s="69" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="Q39" s="69" t="s">
         <v>33</v>
@@ -21717,19 +21787,19 @@
     </row>
     <row r="40" spans="1:51" ht="59" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="87" t="s">
-        <v>418</v>
+        <v>399</v>
       </c>
       <c r="B40" s="29" t="s">
-        <v>419</v>
+        <v>400</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>420</v>
+        <v>401</v>
       </c>
       <c r="D40" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="98" t="s">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="F40" s="90" t="s">
         <v>26</v>
@@ -21747,7 +21817,7 @@
         <v>83</v>
       </c>
       <c r="K40" s="75" t="s">
-        <v>422</v>
+        <v>403</v>
       </c>
       <c r="L40" s="76"/>
       <c r="P40" s="69" t="s">
@@ -21762,25 +21832,25 @@
     </row>
     <row r="41" spans="1:51" ht="92" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="91" t="s">
-        <v>423</v>
+        <v>404</v>
       </c>
       <c r="B41" s="48" t="s">
-        <v>424</v>
+        <v>405</v>
       </c>
       <c r="C41" s="91" t="s">
-        <v>425</v>
+        <v>406</v>
       </c>
       <c r="D41" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E41" s="92" t="s">
-        <v>426</v>
+        <v>407</v>
       </c>
       <c r="F41" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="94" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="H41" s="93" t="s">
         <v>28</v>
@@ -21793,13 +21863,13 @@
       </c>
       <c r="K41" s="96"/>
       <c r="L41" s="95" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="M41" s="95" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="N41" s="95" t="s">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="P41" s="69" t="s">
         <v>32</v>
@@ -21825,7 +21895,7 @@
         <v>25</v>
       </c>
       <c r="E42" s="104" t="s">
-        <v>428</v>
+        <v>409</v>
       </c>
       <c r="F42" s="93" t="s">
         <v>46</v>
@@ -21869,25 +21939,25 @@
     </row>
     <row r="43" spans="1:51" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="91" t="s">
-        <v>429</v>
+        <v>410</v>
       </c>
       <c r="B43" s="48" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="C43" s="91" t="s">
-        <v>431</v>
+        <v>412</v>
       </c>
       <c r="D43" s="108" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="E43" s="54" t="s">
-        <v>433</v>
+        <v>414</v>
       </c>
       <c r="F43" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="93" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="H43" s="93" t="s">
         <v>28</v>
@@ -21899,13 +21969,13 @@
         <v>83</v>
       </c>
       <c r="K43" s="96" t="s">
-        <v>435</v>
+        <v>416</v>
       </c>
       <c r="L43" s="95"/>
       <c r="M43" s="202"/>
       <c r="N43" s="202"/>
       <c r="P43" s="27" t="s">
-        <v>417</v>
+        <v>398</v>
       </c>
       <c r="Q43" s="27" t="s">
         <v>33</v>
@@ -21916,25 +21986,25 @@
     </row>
     <row r="44" spans="1:51" ht="228" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="87" t="s">
-        <v>436</v>
+        <v>417</v>
       </c>
       <c r="B44" s="29" t="s">
-        <v>437</v>
+        <v>418</v>
       </c>
       <c r="C44" s="107" t="s">
-        <v>438</v>
+        <v>419</v>
       </c>
       <c r="D44" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="98" t="s">
-        <v>439</v>
+        <v>420</v>
       </c>
       <c r="F44" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="94" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="H44" s="90" t="s">
         <v>28</v>
@@ -21947,16 +22017,16 @@
       </c>
       <c r="K44" s="75"/>
       <c r="L44" s="76" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="M44" s="76" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="N44" s="76" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="O44" s="27" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="P44" s="27" t="s">
         <v>52</v>
@@ -21970,25 +22040,25 @@
     </row>
     <row r="45" spans="1:51" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="91" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="B45" s="48" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="C45" s="91" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="D45" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E45" s="92" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="F45" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="94" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H45" s="93" t="s">
         <v>28</v>
@@ -22000,19 +22070,19 @@
         <v>40</v>
       </c>
       <c r="K45" s="96" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="L45" s="95" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="M45" s="95" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="N45" s="95" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="O45" s="27" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="P45" s="27" t="s">
         <v>52</v>
@@ -22026,25 +22096,25 @@
     </row>
     <row r="46" spans="1:51" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="87" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="D46" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E46" s="98" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="F46" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="94" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="H46" s="90" t="s">
         <v>28</v>
@@ -22057,16 +22127,16 @@
       </c>
       <c r="K46" s="75"/>
       <c r="L46" s="76" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="M46" s="76" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="N46" s="76" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="O46" s="27" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="P46" s="27" t="s">
         <v>52</v>
@@ -22092,7 +22162,7 @@
         <v>25</v>
       </c>
       <c r="E47" s="92" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="F47" s="90" t="s">
         <v>26</v>
@@ -22130,19 +22200,19 @@
     </row>
     <row r="48" spans="1:51" ht="160" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="87" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="B48" s="29" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="D48" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="29" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="F48" s="93" t="s">
         <v>26</v>
@@ -22160,16 +22230,16 @@
         <v>83</v>
       </c>
       <c r="K48" s="75" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="L48" s="76" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="M48" s="76" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="N48" s="76" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="O48" s="27" t="s">
         <v>146</v>
@@ -22186,25 +22256,25 @@
     </row>
     <row r="49" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="91" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="B49" s="48" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="C49" s="91" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="D49" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E49" s="92" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="F49" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="94" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="H49" s="93" t="s">
         <v>28</v>
@@ -22216,10 +22286,10 @@
         <v>83</v>
       </c>
       <c r="K49" s="96" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="L49" s="100" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="M49" s="95"/>
       <c r="N49" s="95"/>
@@ -22235,19 +22305,19 @@
     </row>
     <row r="50" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="87" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="B50" s="29" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="C50" s="87" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="D50" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E50" s="104" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="F50" s="93" t="s">
         <v>26</v>
@@ -22265,10 +22335,10 @@
         <v>40</v>
       </c>
       <c r="K50" s="75" t="s">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="L50" s="107" t="s">
-        <v>473</v>
+        <v>454</v>
       </c>
       <c r="M50" s="76"/>
       <c r="N50" s="76"/>
@@ -22284,25 +22354,25 @@
     </row>
     <row r="51" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="91" t="s">
-        <v>474</v>
+        <v>455</v>
       </c>
       <c r="B51" s="48" t="s">
-        <v>475</v>
+        <v>456</v>
       </c>
       <c r="C51" s="91" t="s">
-        <v>476</v>
+        <v>457</v>
       </c>
       <c r="D51" s="108" t="s">
-        <v>477</v>
+        <v>458</v>
       </c>
       <c r="E51" s="92" t="s">
-        <v>478</v>
+        <v>459</v>
       </c>
       <c r="F51" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H51" s="93" t="s">
         <v>98</v>
@@ -22314,7 +22384,7 @@
         <v>48</v>
       </c>
       <c r="K51" s="96" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="L51" s="95"/>
       <c r="M51" s="95"/>
@@ -22343,7 +22413,7 @@
         <v>25</v>
       </c>
       <c r="E52" s="29" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="F52" s="93" t="s">
         <v>26</v>
@@ -22364,13 +22434,13 @@
         <v>145</v>
       </c>
       <c r="L52" s="76" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="M52" s="76" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="N52" s="76" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="O52" s="27" t="s">
         <v>146</v>
@@ -22387,25 +22457,25 @@
     </row>
     <row r="53" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="91" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="B53" s="48" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="C53" s="100" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="D53" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="92" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="F53" s="90" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="93" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="H53" s="93" t="s">
         <v>98</v>
@@ -22417,7 +22487,7 @@
         <v>48</v>
       </c>
       <c r="K53" s="96" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="L53" s="95"/>
       <c r="M53" s="95"/>
@@ -22434,25 +22504,25 @@
     </row>
     <row r="54" spans="1:23" ht="74.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="87" t="s">
-        <v>487</v>
+        <v>468</v>
       </c>
       <c r="B54" s="29" t="s">
         <v>148</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>488</v>
+        <v>469</v>
       </c>
       <c r="D54" s="88" t="s">
-        <v>489</v>
+        <v>470</v>
       </c>
       <c r="E54" s="29" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="F54" s="93" t="s">
         <v>46</v>
       </c>
       <c r="G54" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H54" s="90" t="s">
         <v>67</v>
@@ -22464,7 +22534,7 @@
         <v>83</v>
       </c>
       <c r="K54" s="75" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="L54" s="76"/>
       <c r="M54" s="76"/>
@@ -22476,7 +22546,7 @@
         <v>33</v>
       </c>
       <c r="S54" s="196" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="U54" s="87"/>
       <c r="V54" s="87"/>
@@ -22496,7 +22566,7 @@
         <v>25</v>
       </c>
       <c r="E55" s="92" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="F55" s="90" t="s">
         <v>46</v>
@@ -22534,25 +22604,25 @@
     </row>
     <row r="56" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="87" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="B56" s="29" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="D56" s="158" t="s">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="E56" s="53" t="s">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="F56" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="90" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H56" s="90" t="s">
         <v>28</v>
@@ -22564,7 +22634,7 @@
         <v>83</v>
       </c>
       <c r="K56" s="75" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="L56" s="76"/>
       <c r="M56" s="76"/>
@@ -22584,25 +22654,25 @@
     </row>
     <row r="57" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="91" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="B57" s="48" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="C57" s="91" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="D57" s="149" t="s">
         <v>25</v>
       </c>
       <c r="E57" s="57" t="s">
-        <v>503</v>
+        <v>484</v>
       </c>
       <c r="F57" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="94" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="H57" s="93" t="s">
         <v>28</v>
@@ -22615,16 +22685,16 @@
       </c>
       <c r="K57" s="96"/>
       <c r="L57" s="95" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="M57" s="95" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="N57" s="95" t="s">
-        <v>504</v>
+        <v>485</v>
       </c>
       <c r="O57" s="27" t="s">
-        <v>505</v>
+        <v>486</v>
       </c>
       <c r="P57" s="27" t="s">
         <v>52</v>
@@ -22638,19 +22708,19 @@
     </row>
     <row r="58" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="87" t="s">
-        <v>506</v>
+        <v>487</v>
       </c>
       <c r="B58" s="29" t="s">
-        <v>507</v>
+        <v>488</v>
       </c>
       <c r="C58" s="87" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="D58" s="98" t="s">
         <v>25</v>
       </c>
       <c r="E58" s="98" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="F58" s="90" t="s">
         <v>26</v>
@@ -22668,7 +22738,7 @@
         <v>48</v>
       </c>
       <c r="K58" s="75" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="L58" s="76"/>
       <c r="M58" s="76"/>
@@ -22686,19 +22756,19 @@
     </row>
     <row r="59" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="91" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="B59" s="48" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="C59" s="91" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="D59" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E59" s="48" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="F59" s="93" t="s">
         <v>26</v>
@@ -22716,7 +22786,7 @@
         <v>40</v>
       </c>
       <c r="K59" s="96" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="L59" s="95"/>
       <c r="M59" s="95"/>
@@ -22736,13 +22806,13 @@
     </row>
     <row r="60" spans="1:23" ht="84.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="87" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="B60" s="29" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="D60" s="98" t="s">
         <v>25</v>
@@ -22751,7 +22821,7 @@
         <v>26</v>
       </c>
       <c r="G60" s="94" t="s">
-        <v>258</v>
+        <v>240</v>
       </c>
       <c r="H60" s="90" t="s">
         <v>28</v>
@@ -22992,37 +23062,37 @@
         <v>10</v>
       </c>
       <c r="L1" s="185" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="M1" s="185" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="N1" s="77" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="O1" s="77" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="P1" s="185" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="Q1" s="185" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="R1" s="186" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="S1" s="186" t="s">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="T1" s="186" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="U1" s="186" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="V1" s="195" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="W1" s="66" t="s">
         <v>13</v>
@@ -23054,7 +23124,7 @@
     </row>
     <row r="2" spans="1:31" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="B2" s="122" t="s">
         <v>78</v>
@@ -23063,10 +23133,10 @@
         <v>79</v>
       </c>
       <c r="D2" s="117" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="E2" s="197" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>26</v>
@@ -23095,25 +23165,25 @@
     </row>
     <row r="3" spans="1:31" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="D3" s="127" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="148" t="s">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="F3" s="128" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="128" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H3" s="128">
         <v>1</v>
@@ -23125,7 +23195,7 @@
         <v>83</v>
       </c>
       <c r="K3" s="102" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="L3" s="95"/>
       <c r="M3" s="95"/>
@@ -23144,7 +23214,7 @@
         <v>33</v>
       </c>
       <c r="Z3" s="58" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="AC3" s="46"/>
       <c r="AD3" s="46"/>
@@ -23152,19 +23222,19 @@
     </row>
     <row r="4" spans="1:31" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="B4" s="122" t="s">
-        <v>346</v>
+        <v>327</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>347</v>
+        <v>328</v>
       </c>
       <c r="D4" s="47" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="E4" s="123" t="s">
-        <v>540</v>
+        <v>521</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>46</v>
@@ -23179,10 +23249,10 @@
         <v>39</v>
       </c>
       <c r="J4" s="125" t="s">
-        <v>541</v>
+        <v>522</v>
       </c>
       <c r="K4" s="102" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="L4" s="76"/>
       <c r="X4" s="102" t="s">
@@ -23197,19 +23267,19 @@
     </row>
     <row r="5" spans="1:31" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="130" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="C5" s="130" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="D5" s="92" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="F5" s="131" t="s">
         <v>46</v>
@@ -23227,7 +23297,7 @@
         <v>40</v>
       </c>
       <c r="K5" s="102" t="s">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="L5" s="95"/>
       <c r="M5" s="95"/>
@@ -23254,19 +23324,19 @@
     </row>
     <row r="6" spans="1:31" ht="96" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="133" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="B6" s="116" t="s">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="C6" s="133" t="s">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="D6" s="134" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="116" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="F6" s="99" t="s">
         <v>26</v>
@@ -23300,25 +23370,25 @@
     </row>
     <row r="7" spans="1:31" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="91" t="s">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="B7" s="48" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="C7" s="91" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="D7" s="136" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="E7" s="55" t="s">
-        <v>556</v>
+        <v>537</v>
       </c>
       <c r="F7" s="93" t="s">
         <v>26</v>
       </c>
       <c r="G7" s="93" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H7" s="93" t="s">
         <v>98</v>
@@ -23352,25 +23422,25 @@
     </row>
     <row r="8" spans="1:31" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="45" t="s">
-        <v>494</v>
+        <v>475</v>
       </c>
       <c r="B8" s="122" t="s">
-        <v>495</v>
+        <v>476</v>
       </c>
       <c r="C8" s="137" t="s">
-        <v>496</v>
+        <v>477</v>
       </c>
       <c r="D8" s="88" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="E8" s="101" t="s">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="F8" s="124" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="124" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="H8" s="124" t="s">
         <v>98</v>
@@ -23382,7 +23452,7 @@
         <v>40</v>
       </c>
       <c r="K8" s="102" t="s">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="L8" s="76"/>
       <c r="X8" s="102" t="s">
@@ -23397,7 +23467,7 @@
     </row>
     <row r="9" spans="1:31" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="130" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="B9" s="49" t="s">
         <v>94</v>
@@ -23409,13 +23479,13 @@
         <v>25</v>
       </c>
       <c r="E9" s="138" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="F9" s="131" t="s">
         <v>46</v>
       </c>
       <c r="G9" s="131" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H9" s="131">
         <v>1</v>
@@ -23427,7 +23497,7 @@
         <v>83</v>
       </c>
       <c r="K9" s="102" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="L9" s="95"/>
       <c r="M9" s="95"/>
@@ -24333,22 +24403,22 @@
         <v>10</v>
       </c>
       <c r="L1" s="187" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="M1" s="77" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="N1" s="185" t="s">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="O1" s="186" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="P1" s="194" t="s">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="Q1" s="195" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="R1" s="66" t="s">
         <v>13</v>
@@ -24380,25 +24450,25 @@
     </row>
     <row r="2" spans="1:26" ht="64.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="45" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="C2" s="137" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="D2" s="45" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="62" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="F2" s="124" t="s">
         <v>26</v>
       </c>
       <c r="G2" s="124" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H2" s="124" t="s">
         <v>28</v>
@@ -24410,7 +24480,7 @@
         <v>40</v>
       </c>
       <c r="K2" s="121" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="L2" s="102"/>
       <c r="S2" s="102" t="s">
@@ -24425,25 +24495,25 @@
     </row>
     <row r="3" spans="1:26" ht="128" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="D3" s="147" t="s">
         <v>25</v>
       </c>
       <c r="E3" s="148" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="F3" s="128" t="s">
         <v>46</v>
       </c>
       <c r="G3" s="128" t="s">
-        <v>359</v>
+        <v>340</v>
       </c>
       <c r="H3" s="128">
         <v>1</v>
@@ -24455,7 +24525,7 @@
         <v>40</v>
       </c>
       <c r="K3" s="121" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="L3" s="49"/>
       <c r="M3" s="44"/>
@@ -24469,7 +24539,7 @@
         <v>33</v>
       </c>
       <c r="U3" s="58" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="X3" s="46"/>
       <c r="Y3" s="46"/>
@@ -24477,25 +24547,25 @@
     </row>
     <row r="4" spans="1:26" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="45" t="s">
-        <v>578</v>
+        <v>559</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="D4" s="45" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="62" t="s">
-        <v>581</v>
+        <v>562</v>
       </c>
       <c r="F4" s="124" t="s">
         <v>26</v>
       </c>
       <c r="G4" s="124" t="s">
-        <v>582</v>
+        <v>563</v>
       </c>
       <c r="H4" s="124" t="s">
         <v>98</v>
@@ -24507,7 +24577,7 @@
         <v>40</v>
       </c>
       <c r="K4" s="121" t="s">
-        <v>583</v>
+        <v>564</v>
       </c>
       <c r="L4" s="102"/>
       <c r="S4" s="102" t="s">

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/temp/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexanderharms/Documents/Repositories/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69CDC95C-5D4F-794F-9990-F0E4C0D999D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAA4EFD-C56C-4E4B-A331-3A5335396BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="20540" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="780" windowWidth="36000" windowHeight="20540" firstSheet="2" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2744" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2746" uniqueCount="879">
   <si>
     <t>Property label</t>
   </si>
@@ -2764,6 +2764,9 @@
   </si>
   <si>
     <t>Sample Distribution</t>
+  </si>
+  <si>
+    <t>Data Service</t>
   </si>
 </sst>
 </file>
@@ -3808,32 +3811,17 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3844,6 +3832,9 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3851,6 +3842,18 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3865,7 +3868,47 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="322">
+  <dxfs count="326">
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -7431,7 +7474,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:W58"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="9" customWidth="1"/>
@@ -7448,12 +7491,12 @@
     <col min="12" max="12" width="28.1640625" style="2" customWidth="1"/>
     <col min="13" max="13" width="28.83203125" style="2" customWidth="1"/>
     <col min="14" max="14" width="9.1640625" style="2" customWidth="1"/>
-    <col min="15" max="19" width="9.1640625" style="2"/>
-    <col min="20" max="22" width="19.1640625" customWidth="1"/>
-    <col min="23" max="16384" width="9.1640625" style="2"/>
+    <col min="15" max="20" width="9.1640625" style="2"/>
+    <col min="21" max="23" width="19.1640625" customWidth="1"/>
+    <col min="24" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="165" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" s="165" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
@@ -7511,17 +7554,20 @@
       <c r="S1" s="66" t="s">
         <v>19</v>
       </c>
-      <c r="T1" s="63" t="s">
+      <c r="T1" s="66" t="s">
+        <v>874</v>
+      </c>
+      <c r="U1" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="U1" s="63" t="s">
+      <c r="V1" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="V1" s="63" t="s">
+      <c r="W1" s="63" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="91" t="s">
         <v>624</v>
       </c>
@@ -7571,11 +7617,14 @@
         <v>195</v>
       </c>
       <c r="S2" s="121"/>
-      <c r="T2" s="91"/>
+      <c r="T2" s="2" t="s">
+        <v>878</v>
+      </c>
       <c r="U2" s="91"/>
       <c r="V2" s="91"/>
-    </row>
-    <row r="3" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W2" s="91"/>
+    </row>
+    <row r="3" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="87" t="s">
         <v>630</v>
       </c>
@@ -7618,11 +7667,11 @@
         <v>57</v>
       </c>
       <c r="S3" s="121"/>
-      <c r="T3" s="87"/>
       <c r="U3" s="87"/>
       <c r="V3" s="87"/>
-    </row>
-    <row r="4" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W3" s="87"/>
+    </row>
+    <row r="4" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="91" t="s">
         <v>179</v>
       </c>
@@ -7665,11 +7714,11 @@
         <v>57</v>
       </c>
       <c r="S4" s="121"/>
-      <c r="T4" s="91"/>
       <c r="U4" s="91"/>
       <c r="V4" s="91"/>
-    </row>
-    <row r="5" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W4" s="91"/>
+    </row>
+    <row r="5" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="97" t="s">
         <v>636</v>
       </c>
@@ -7710,11 +7759,11 @@
         <v>57</v>
       </c>
       <c r="S5" s="121"/>
-      <c r="T5" s="97"/>
       <c r="U5" s="97"/>
       <c r="V5" s="97"/>
-    </row>
-    <row r="6" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W5" s="97"/>
+    </row>
+    <row r="6" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="91" t="s">
         <v>641</v>
       </c>
@@ -7757,11 +7806,11 @@
         <v>34</v>
       </c>
       <c r="S6" s="121"/>
-      <c r="T6" s="91"/>
       <c r="U6" s="91"/>
       <c r="V6" s="91"/>
-    </row>
-    <row r="7" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W6" s="91"/>
+    </row>
+    <row r="7" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="87" t="s">
         <v>646</v>
       </c>
@@ -7811,11 +7860,11 @@
         <v>195</v>
       </c>
       <c r="S7" s="121"/>
-      <c r="T7" s="87"/>
       <c r="U7" s="87"/>
       <c r="V7" s="87"/>
-    </row>
-    <row r="8" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W7" s="87"/>
+    </row>
+    <row r="8" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="91" t="s">
         <v>653</v>
       </c>
@@ -7858,11 +7907,11 @@
         <v>57</v>
       </c>
       <c r="S8" s="121"/>
-      <c r="T8" s="91"/>
       <c r="U8" s="91"/>
       <c r="V8" s="91"/>
-    </row>
-    <row r="9" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W8" s="91"/>
+    </row>
+    <row r="9" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="87" t="s">
         <v>40</v>
       </c>
@@ -7907,11 +7956,11 @@
       <c r="S9" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="T9" s="87"/>
       <c r="U9" s="87"/>
       <c r="V9" s="87"/>
-    </row>
-    <row r="10" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W9" s="87"/>
+    </row>
+    <row r="10" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="91" t="s">
         <v>350</v>
       </c>
@@ -7954,11 +8003,11 @@
         <v>57</v>
       </c>
       <c r="S10" s="121"/>
-      <c r="T10" s="91"/>
       <c r="U10" s="91"/>
       <c r="V10" s="91"/>
-    </row>
-    <row r="11" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W10" s="91"/>
+    </row>
+    <row r="11" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="87" t="s">
         <v>664</v>
       </c>
@@ -8001,11 +8050,11 @@
         <v>57</v>
       </c>
       <c r="S11" s="121"/>
-      <c r="T11" s="87"/>
       <c r="U11" s="87"/>
       <c r="V11" s="87"/>
-    </row>
-    <row r="12" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W11" s="87"/>
+    </row>
+    <row r="12" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="91" t="s">
         <v>669</v>
       </c>
@@ -8048,11 +8097,11 @@
         <v>57</v>
       </c>
       <c r="S12" s="121"/>
-      <c r="T12" s="91"/>
       <c r="U12" s="91"/>
       <c r="V12" s="91"/>
-    </row>
-    <row r="13" spans="1:22" ht="99" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W12" s="91"/>
+    </row>
+    <row r="13" spans="1:23" ht="99" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="87" t="s">
         <v>241</v>
       </c>
@@ -8095,11 +8144,11 @@
         <v>57</v>
       </c>
       <c r="S13" s="121"/>
-      <c r="T13" s="87"/>
       <c r="U13" s="87"/>
       <c r="V13" s="87"/>
-    </row>
-    <row r="14" spans="1:22" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W13" s="87"/>
+    </row>
+    <row r="14" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="91" t="s">
         <v>248</v>
       </c>
@@ -8142,11 +8191,11 @@
         <v>57</v>
       </c>
       <c r="S14" s="121"/>
-      <c r="T14" s="91"/>
       <c r="U14" s="91"/>
       <c r="V14" s="91"/>
-    </row>
-    <row r="15" spans="1:22" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W14" s="91"/>
+    </row>
+    <row r="15" spans="1:23" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="87" t="s">
         <v>680</v>
       </c>
@@ -8189,11 +8238,11 @@
         <v>57</v>
       </c>
       <c r="S15" s="121"/>
-      <c r="T15" s="87"/>
       <c r="U15" s="87"/>
       <c r="V15" s="87"/>
-    </row>
-    <row r="16" spans="1:22" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W15" s="87"/>
+    </row>
+    <row r="16" spans="1:23" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="91" t="s">
         <v>683</v>
       </c>
@@ -8236,11 +8285,11 @@
         <v>57</v>
       </c>
       <c r="S16" s="121"/>
-      <c r="T16" s="91"/>
       <c r="U16" s="91"/>
       <c r="V16" s="91"/>
-    </row>
-    <row r="17" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W16" s="91"/>
+    </row>
+    <row r="17" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="87" t="s">
         <v>255</v>
       </c>
@@ -8285,11 +8334,11 @@
         <v>261</v>
       </c>
       <c r="S17" s="69"/>
-      <c r="T17" s="87"/>
       <c r="U17" s="87"/>
       <c r="V17" s="87"/>
-    </row>
-    <row r="18" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W17" s="87"/>
+    </row>
+    <row r="18" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="91" t="s">
         <v>689</v>
       </c>
@@ -8332,11 +8381,11 @@
         <v>57</v>
       </c>
       <c r="S18" s="121"/>
-      <c r="T18" s="91"/>
       <c r="U18" s="91"/>
       <c r="V18" s="91"/>
-    </row>
-    <row r="19" spans="1:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W18" s="91"/>
+    </row>
+    <row r="19" spans="1:23" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="87" t="s">
         <v>268</v>
       </c>
@@ -8383,11 +8432,11 @@
         <v>261</v>
       </c>
       <c r="S19" s="69"/>
-      <c r="T19" s="87"/>
       <c r="U19" s="87"/>
       <c r="V19" s="87"/>
-    </row>
-    <row r="20" spans="1:22" ht="231" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W19" s="87"/>
+    </row>
+    <row r="20" spans="1:23" ht="231" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="91" t="s">
         <v>494</v>
       </c>
@@ -8433,11 +8482,11 @@
         <v>195</v>
       </c>
       <c r="S20" s="121"/>
-      <c r="T20" s="91"/>
       <c r="U20" s="91"/>
       <c r="V20" s="91"/>
-    </row>
-    <row r="21" spans="1:22" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W20" s="91"/>
+    </row>
+    <row r="21" spans="1:23" ht="112" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="87" t="s">
         <v>272</v>
       </c>
@@ -8480,11 +8529,11 @@
         <v>57</v>
       </c>
       <c r="S21" s="121"/>
-      <c r="T21" s="87"/>
       <c r="U21" s="87"/>
       <c r="V21" s="87"/>
-    </row>
-    <row r="22" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W21" s="87"/>
+    </row>
+    <row r="22" spans="1:23" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="91" t="s">
         <v>512</v>
       </c>
@@ -8527,11 +8576,11 @@
         <v>57</v>
       </c>
       <c r="S22" s="121"/>
-      <c r="T22" s="91"/>
       <c r="U22" s="91"/>
       <c r="V22" s="91"/>
-    </row>
-    <row r="23" spans="1:22" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W22" s="91"/>
+    </row>
+    <row r="23" spans="1:23" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="87" t="s">
         <v>519</v>
       </c>
@@ -8572,11 +8621,11 @@
         <v>34</v>
       </c>
       <c r="S23" s="121"/>
-      <c r="T23" s="87"/>
       <c r="U23" s="87"/>
       <c r="V23" s="87"/>
-    </row>
-    <row r="24" spans="1:22" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W23" s="87"/>
+    </row>
+    <row r="24" spans="1:23" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="91" t="s">
         <v>35</v>
       </c>
@@ -8621,11 +8670,11 @@
       <c r="S24" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="91"/>
       <c r="U24" s="91"/>
       <c r="V24" s="91"/>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="91"/>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" s="21"/>
       <c r="B25" s="8"/>
       <c r="C25" s="21"/>
@@ -8637,11 +8686,11 @@
       <c r="K25" s="70"/>
       <c r="L25" s="27"/>
       <c r="M25" s="27"/>
-      <c r="T25" s="21"/>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="21"/>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" s="21"/>
       <c r="B26" s="8"/>
       <c r="C26" s="26"/>
@@ -8653,11 +8702,11 @@
       <c r="K26" s="68"/>
       <c r="L26" s="27"/>
       <c r="M26" s="27"/>
-      <c r="T26" s="21"/>
       <c r="U26" s="21"/>
       <c r="V26" s="21"/>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="21"/>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" s="21"/>
       <c r="B27" s="8"/>
       <c r="C27" s="21"/>
@@ -8667,11 +8716,11 @@
       <c r="G27" s="20"/>
       <c r="H27" s="22"/>
       <c r="K27" s="70"/>
-      <c r="T27" s="21"/>
       <c r="U27" s="21"/>
       <c r="V27" s="21"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="21"/>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" s="21"/>
       <c r="B28" s="8"/>
       <c r="D28" s="23"/>
@@ -8680,11 +8729,11 @@
       <c r="G28" s="20"/>
       <c r="H28" s="22"/>
       <c r="K28" s="68"/>
-      <c r="T28" s="21"/>
       <c r="U28" s="21"/>
       <c r="V28" s="21"/>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="21"/>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" s="21"/>
       <c r="B29" s="8"/>
       <c r="C29" s="21"/>
@@ -8694,11 +8743,11 @@
       <c r="G29" s="20"/>
       <c r="H29" s="22"/>
       <c r="K29" s="68"/>
-      <c r="T29" s="21"/>
       <c r="U29" s="21"/>
       <c r="V29" s="21"/>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="21"/>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" s="21"/>
       <c r="B30" s="8"/>
       <c r="C30" s="21"/>
@@ -8707,11 +8756,11 @@
       <c r="G30" s="20"/>
       <c r="H30" s="22"/>
       <c r="K30" s="68"/>
-      <c r="T30" s="21"/>
       <c r="U30" s="21"/>
       <c r="V30" s="21"/>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="21"/>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" s="21"/>
       <c r="B31" s="8"/>
       <c r="C31" s="21"/>
@@ -8721,11 +8770,11 @@
       <c r="G31" s="20"/>
       <c r="H31" s="22"/>
       <c r="K31" s="68"/>
-      <c r="T31" s="21"/>
       <c r="U31" s="21"/>
       <c r="V31" s="21"/>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="21"/>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" s="21"/>
       <c r="B32" s="8"/>
       <c r="C32" s="26"/>
@@ -8735,11 +8784,11 @@
       <c r="G32" s="20"/>
       <c r="H32" s="22"/>
       <c r="K32" s="68"/>
-      <c r="T32" s="21"/>
       <c r="U32" s="21"/>
       <c r="V32" s="21"/>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="21"/>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" s="21"/>
       <c r="B33" s="8"/>
       <c r="C33" s="21"/>
@@ -8749,11 +8798,11 @@
       <c r="G33" s="20"/>
       <c r="H33" s="22"/>
       <c r="K33" s="68"/>
-      <c r="T33" s="21"/>
       <c r="U33" s="21"/>
       <c r="V33" s="21"/>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="21"/>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" s="21"/>
       <c r="B34" s="8"/>
       <c r="D34" s="23"/>
@@ -8762,11 +8811,11 @@
       <c r="G34" s="20"/>
       <c r="H34" s="22"/>
       <c r="K34" s="72"/>
-      <c r="T34" s="21"/>
       <c r="U34" s="21"/>
       <c r="V34" s="21"/>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="21"/>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" s="21"/>
       <c r="B35" s="8"/>
       <c r="C35" s="21"/>
@@ -8776,11 +8825,11 @@
       <c r="G35" s="20"/>
       <c r="H35" s="22"/>
       <c r="K35" s="68"/>
-      <c r="T35" s="21"/>
       <c r="U35" s="21"/>
       <c r="V35" s="21"/>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="21"/>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" s="21"/>
       <c r="B36" s="8"/>
       <c r="C36" s="21"/>
@@ -8789,11 +8838,11 @@
       <c r="G36" s="20"/>
       <c r="H36" s="22"/>
       <c r="K36" s="68"/>
-      <c r="T36" s="21"/>
       <c r="U36" s="21"/>
       <c r="V36" s="21"/>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W36" s="21"/>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" s="21"/>
       <c r="B37" s="8"/>
       <c r="C37" s="21"/>
@@ -8803,11 +8852,11 @@
       <c r="G37" s="20"/>
       <c r="H37" s="22"/>
       <c r="K37" s="68"/>
-      <c r="T37" s="21"/>
       <c r="U37" s="21"/>
       <c r="V37" s="21"/>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W37" s="21"/>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" s="21"/>
       <c r="B38" s="8"/>
       <c r="C38" s="26"/>
@@ -8817,11 +8866,11 @@
       <c r="G38" s="20"/>
       <c r="H38" s="22"/>
       <c r="K38" s="68"/>
-      <c r="T38" s="21"/>
       <c r="U38" s="21"/>
       <c r="V38" s="21"/>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="21"/>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" s="21"/>
       <c r="B39" s="8"/>
       <c r="C39" s="21"/>
@@ -8831,11 +8880,11 @@
       <c r="G39" s="20"/>
       <c r="H39" s="22"/>
       <c r="K39" s="68"/>
-      <c r="T39" s="21"/>
       <c r="U39" s="21"/>
       <c r="V39" s="21"/>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="21"/>
+    </row>
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" s="21"/>
       <c r="B40" s="8"/>
       <c r="C40" s="21"/>
@@ -8844,11 +8893,11 @@
       <c r="G40" s="20"/>
       <c r="H40" s="22"/>
       <c r="K40" s="68"/>
-      <c r="T40" s="21"/>
       <c r="U40" s="21"/>
       <c r="V40" s="21"/>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="21"/>
+    </row>
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="21"/>
       <c r="B41" s="8"/>
       <c r="C41" s="21"/>
@@ -8858,11 +8907,11 @@
       <c r="G41" s="20"/>
       <c r="H41" s="22"/>
       <c r="K41" s="68"/>
-      <c r="T41" s="21"/>
       <c r="U41" s="21"/>
       <c r="V41" s="21"/>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="21"/>
+    </row>
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="21"/>
       <c r="B42" s="8"/>
       <c r="C42" s="26"/>
@@ -8872,11 +8921,11 @@
       <c r="G42" s="20"/>
       <c r="H42" s="22"/>
       <c r="K42" s="68"/>
-      <c r="T42" s="21"/>
       <c r="U42" s="21"/>
       <c r="V42" s="21"/>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="21"/>
+    </row>
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" s="21"/>
       <c r="B43" s="8"/>
       <c r="C43" s="21"/>
@@ -8886,11 +8935,11 @@
       <c r="G43" s="20"/>
       <c r="H43" s="22"/>
       <c r="K43" s="68"/>
-      <c r="T43" s="21"/>
       <c r="U43" s="21"/>
       <c r="V43" s="21"/>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="21"/>
+    </row>
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" s="21"/>
       <c r="B44" s="8"/>
       <c r="D44" s="23"/>
@@ -8899,11 +8948,11 @@
       <c r="G44" s="20"/>
       <c r="H44" s="22"/>
       <c r="K44" s="68"/>
-      <c r="T44" s="21"/>
       <c r="U44" s="21"/>
       <c r="V44" s="21"/>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="21"/>
+    </row>
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" s="21"/>
       <c r="B45" s="8"/>
       <c r="C45" s="21"/>
@@ -8913,11 +8962,11 @@
       <c r="G45" s="20"/>
       <c r="H45" s="22"/>
       <c r="K45" s="68"/>
-      <c r="T45" s="21"/>
       <c r="U45" s="21"/>
       <c r="V45" s="21"/>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="21"/>
+    </row>
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" s="21"/>
       <c r="B46" s="8"/>
       <c r="C46" s="21"/>
@@ -8926,11 +8975,11 @@
       <c r="G46" s="20"/>
       <c r="H46" s="22"/>
       <c r="K46" s="68"/>
-      <c r="T46" s="21"/>
       <c r="U46" s="21"/>
       <c r="V46" s="21"/>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="21"/>
+    </row>
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" s="21"/>
       <c r="B47" s="8"/>
       <c r="C47" s="21"/>
@@ -8940,11 +8989,11 @@
       <c r="G47" s="20"/>
       <c r="H47" s="22"/>
       <c r="K47" s="68"/>
-      <c r="T47" s="21"/>
       <c r="U47" s="21"/>
       <c r="V47" s="21"/>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="21"/>
+    </row>
+    <row r="48" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A48" s="21"/>
       <c r="B48" s="8"/>
       <c r="C48" s="26"/>
@@ -8954,11 +9003,11 @@
       <c r="G48" s="20"/>
       <c r="H48" s="22"/>
       <c r="K48" s="68"/>
-      <c r="T48" s="21"/>
       <c r="U48" s="21"/>
       <c r="V48" s="21"/>
-    </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="21"/>
+    </row>
+    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" s="21"/>
       <c r="B49" s="8"/>
       <c r="C49" s="21"/>
@@ -8967,11 +9016,11 @@
       <c r="G49" s="20"/>
       <c r="H49" s="22"/>
       <c r="K49" s="68"/>
-      <c r="T49" s="21"/>
       <c r="U49" s="21"/>
       <c r="V49" s="21"/>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="21"/>
+    </row>
+    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" s="21"/>
       <c r="B50" s="8"/>
       <c r="C50" s="21"/>
@@ -8980,11 +9029,11 @@
       <c r="G50" s="20"/>
       <c r="H50" s="22"/>
       <c r="K50" s="68"/>
-      <c r="T50" s="21"/>
       <c r="U50" s="21"/>
       <c r="V50" s="21"/>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="21"/>
+    </row>
+    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" s="21"/>
       <c r="B51" s="8"/>
       <c r="C51" s="21"/>
@@ -8994,11 +9043,11 @@
       <c r="G51" s="20"/>
       <c r="H51" s="22"/>
       <c r="K51" s="68"/>
-      <c r="T51" s="21"/>
       <c r="U51" s="21"/>
       <c r="V51" s="21"/>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="21"/>
+    </row>
+    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52" s="21"/>
       <c r="B52" s="8"/>
       <c r="D52" s="23"/>
@@ -9007,11 +9056,11 @@
       <c r="G52" s="20"/>
       <c r="H52" s="22"/>
       <c r="K52" s="68"/>
-      <c r="T52" s="21"/>
       <c r="U52" s="21"/>
       <c r="V52" s="21"/>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="21"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53" s="21"/>
       <c r="B53" s="8"/>
       <c r="C53" s="21"/>
@@ -9021,11 +9070,11 @@
       <c r="G53" s="20"/>
       <c r="H53" s="22"/>
       <c r="K53" s="68"/>
-      <c r="T53" s="21"/>
       <c r="U53" s="21"/>
       <c r="V53" s="21"/>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="21"/>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54" s="21"/>
       <c r="B54" s="8"/>
       <c r="C54" s="21"/>
@@ -9035,73 +9084,87 @@
       <c r="G54" s="20"/>
       <c r="H54" s="22"/>
       <c r="K54" s="68"/>
-      <c r="T54" s="21"/>
       <c r="U54" s="21"/>
       <c r="V54" s="21"/>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="21"/>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K55" s="68"/>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K56" s="68"/>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K57" s="68"/>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K58" s="69"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J24" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <conditionalFormatting sqref="F2:F54">
-    <cfRule type="cellIs" dxfId="240" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H54">
-    <cfRule type="cellIs" dxfId="239" priority="17" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="243" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="242" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F54">
-    <cfRule type="cellIs" dxfId="237" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="241" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="240" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="238" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J54">
-    <cfRule type="containsText" dxfId="233" priority="13" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="237" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="232" priority="14" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="236" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="231" priority="15" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="235" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="230" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="234" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="233" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="227" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="231" priority="8" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Optional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9424,40 +9487,40 @@
       <c r="U5" s="87"/>
     </row>
     <row r="6" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="226" t="s">
+      <c r="A6" s="220" t="s">
         <v>221</v>
       </c>
-      <c r="B6" s="230" t="s">
+      <c r="B6" s="226" t="s">
         <v>222</v>
       </c>
-      <c r="C6" s="226" t="s">
+      <c r="C6" s="220" t="s">
         <v>223</v>
       </c>
       <c r="D6" s="178" t="s">
         <v>224</v>
       </c>
-      <c r="E6" s="227" t="s">
+      <c r="E6" s="222" t="s">
         <v>365</v>
       </c>
-      <c r="F6" s="231" t="s">
+      <c r="F6" s="227" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="231" t="s">
+      <c r="G6" s="227" t="s">
         <v>226</v>
       </c>
-      <c r="H6" s="231" t="s">
+      <c r="H6" s="227" t="s">
         <v>183</v>
       </c>
-      <c r="I6" s="225" t="s">
+      <c r="I6" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="J6" s="222" t="s">
+      <c r="J6" s="232" t="s">
         <v>32</v>
       </c>
       <c r="K6" s="233" t="s">
         <v>713</v>
       </c>
-      <c r="L6" s="225"/>
+      <c r="L6" s="218"/>
       <c r="N6" s="69" t="s">
         <v>321</v>
       </c>
@@ -9469,68 +9532,68 @@
       <c r="U6" s="91"/>
     </row>
     <row r="7" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="219"/>
-      <c r="B7" s="219"/>
-      <c r="C7" s="219"/>
+      <c r="A7" s="221"/>
+      <c r="B7" s="221"/>
+      <c r="C7" s="221"/>
       <c r="D7" s="179" t="s">
         <v>227</v>
       </c>
-      <c r="E7" s="219"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
+      <c r="E7" s="221"/>
+      <c r="F7" s="219"/>
+      <c r="G7" s="219"/>
+      <c r="H7" s="219"/>
+      <c r="I7" s="219"/>
+      <c r="J7" s="219"/>
       <c r="K7" s="234"/>
-      <c r="L7" s="223"/>
+      <c r="L7" s="219"/>
     </row>
     <row r="8" spans="1:21" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="219"/>
-      <c r="B8" s="219"/>
-      <c r="C8" s="219"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="221"/>
+      <c r="C8" s="221"/>
       <c r="D8" s="179" t="s">
         <v>228</v>
       </c>
-      <c r="E8" s="219"/>
-      <c r="F8" s="223"/>
-      <c r="G8" s="223"/>
-      <c r="H8" s="223"/>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
+      <c r="E8" s="221"/>
+      <c r="F8" s="219"/>
+      <c r="G8" s="219"/>
+      <c r="H8" s="219"/>
+      <c r="I8" s="219"/>
+      <c r="J8" s="219"/>
       <c r="K8" s="234"/>
-      <c r="L8" s="223"/>
+      <c r="L8" s="219"/>
     </row>
     <row r="9" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="219"/>
-      <c r="B9" s="219"/>
-      <c r="C9" s="219"/>
+      <c r="A9" s="221"/>
+      <c r="B9" s="221"/>
+      <c r="C9" s="221"/>
       <c r="D9" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="E9" s="219"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="223"/>
+      <c r="E9" s="221"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="219"/>
+      <c r="H9" s="219"/>
+      <c r="I9" s="219"/>
+      <c r="J9" s="219"/>
       <c r="K9" s="234"/>
-      <c r="L9" s="223"/>
+      <c r="L9" s="219"/>
     </row>
     <row r="10" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="219"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="221"/>
+      <c r="C10" s="221"/>
       <c r="D10" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="E10" s="219"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="223"/>
+      <c r="E10" s="221"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="219"/>
+      <c r="H10" s="219"/>
+      <c r="I10" s="219"/>
+      <c r="J10" s="219"/>
       <c r="K10" s="234"/>
-      <c r="L10" s="223"/>
+      <c r="L10" s="219"/>
     </row>
     <row r="11" spans="1:21" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="87" t="s">
@@ -9912,65 +9975,65 @@
     <mergeCell ref="G6:G10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="226" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="11" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H6 H11 G12:I12">
-    <cfRule type="cellIs" dxfId="225" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="229" priority="12" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="224" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="228" priority="13" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="223" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="227" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="226" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="221" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="224" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="containsText" dxfId="219" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="223" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="222" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="217" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="221" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J15">
-    <cfRule type="containsText" dxfId="216" priority="8" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="220" priority="8" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="9" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="219" priority="9" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="10" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="218" priority="10" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="213" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="212" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="216" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="215" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="214" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11578,54 +11641,54 @@
   </sheetData>
   <autoFilter ref="A1:J23" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="209" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="213" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="208" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="212" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="211" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="206" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="210" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="202" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="206" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="201" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="205" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="200" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="204" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="199" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="201" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11844,49 +11907,49 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="195" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="199" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="194" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="198" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="197" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="196" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="190" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="194" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="193" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="191" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:U1">
-    <cfRule type="cellIs" dxfId="186" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="190" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="188" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="187" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12746,85 +12809,85 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="182" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="185" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="178" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="174" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="173" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="169" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="173" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="167" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:X1">
-    <cfRule type="cellIs" dxfId="163" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="165" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13262,88 +13325,88 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D11:E13">
-    <cfRule type="cellIs" dxfId="159" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="155" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 A12:B13">
-    <cfRule type="cellIs" dxfId="150" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="153" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="152" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F23">
-    <cfRule type="cellIs" dxfId="146" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="145" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H12 H21:H23">
-    <cfRule type="cellIs" dxfId="141" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="145" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13568,35 +13631,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="135" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="134" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="137" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="136" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="130" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="134" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="132" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13799,35 +13862,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="121" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14030,35 +14093,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="117" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="116" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="112" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14253,49 +14316,49 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A3:E3">
-    <cfRule type="cellIs" dxfId="108" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="107" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="106" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="105" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="104" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="13" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="103" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="102" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="101" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="100" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="104" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="99" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="103" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="98" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="102" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="97" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="101" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="96" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="100" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15140,88 +15203,88 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="95" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="99" priority="21" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="94" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="98" priority="22" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="93" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="97" priority="23" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="92" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="96" priority="24" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="91" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="95" priority="25" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="94" priority="26" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="89" priority="27" operator="equal">
+    <cfRule type="cellIs" dxfId="93" priority="27" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="28" operator="equal">
+    <cfRule type="cellIs" dxfId="92" priority="28" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="87" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="91" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="86" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="90" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="85" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="89" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="84" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="88" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="83" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="87" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="82" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="86" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G3">
-    <cfRule type="cellIs" dxfId="81" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="85" priority="16" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="80" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="84" priority="17" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="79" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="83" priority="18" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="78" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="82" priority="19" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="77" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="29" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="80" priority="30" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="75" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="79" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="78" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="77" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="76" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16049,90 +16112,90 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D39:E41">
-    <cfRule type="cellIs" dxfId="71" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="74" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="73" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="72" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="67" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="66" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="70" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="65" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="64" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:F2">
-    <cfRule type="cellIs" dxfId="63" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F2 F4:F51 A40:B41">
-    <cfRule type="cellIs" dxfId="62" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="66" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="61" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="65" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="64" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="59" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4:F51">
-    <cfRule type="cellIs" dxfId="58" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="57" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="56" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="55" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="54" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H8 H10:H14 H16:H24 H26:H40 H49:H51">
-    <cfRule type="cellIs" dxfId="53" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="56" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="52" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17029,88 +17092,88 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="47" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="43" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="42" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="44" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="39" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="43" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F52 A41:B42">
-    <cfRule type="cellIs" dxfId="38" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="42" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="41" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="34" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="33" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="36" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="29" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18035,88 +18098,88 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F52 A41:B42">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="5" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18766,44 +18829,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1 H1:I1">
-    <cfRule type="cellIs" dxfId="321" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="325" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="320" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="324" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="323" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="322" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="317" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="321" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="320" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="319" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="314" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="318" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:Q1">
-    <cfRule type="cellIs" dxfId="313" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="317" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="316" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="311" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="315" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="314" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19213,39 +19276,39 @@
       <c r="V7" s="91"/>
     </row>
     <row r="8" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="218" t="s">
+      <c r="A8" s="229" t="s">
         <v>221</v>
       </c>
-      <c r="B8" s="220" t="s">
+      <c r="B8" s="230" t="s">
         <v>222</v>
       </c>
-      <c r="C8" s="218" t="s">
+      <c r="C8" s="229" t="s">
         <v>223</v>
       </c>
       <c r="D8" s="176" t="s">
         <v>224</v>
       </c>
-      <c r="E8" s="221" t="s">
+      <c r="E8" s="231" t="s">
         <v>225</v>
       </c>
-      <c r="F8" s="224" t="s">
+      <c r="F8" s="225" t="s">
         <v>53</v>
       </c>
-      <c r="G8" s="224" t="s">
+      <c r="G8" s="225" t="s">
         <v>226</v>
       </c>
-      <c r="H8" s="224" t="s">
+      <c r="H8" s="225" t="s">
         <v>183</v>
       </c>
-      <c r="I8" s="222" t="s">
+      <c r="I8" s="232" t="s">
         <v>31</v>
       </c>
-      <c r="J8" s="222" t="s">
+      <c r="J8" s="232" t="s">
         <v>32</v>
       </c>
       <c r="K8" s="103"/>
-      <c r="L8" s="222"/>
-      <c r="M8" s="222"/>
+      <c r="L8" s="232"/>
+      <c r="M8" s="232"/>
       <c r="O8" s="27" t="s">
         <v>321</v>
       </c>
@@ -19258,75 +19321,75 @@
       <c r="V8" s="87"/>
     </row>
     <row r="9" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="219"/>
-      <c r="B9" s="219"/>
-      <c r="C9" s="219"/>
+      <c r="A9" s="221"/>
+      <c r="B9" s="221"/>
+      <c r="C9" s="221"/>
       <c r="D9" s="177" t="s">
         <v>227</v>
       </c>
-      <c r="E9" s="219"/>
-      <c r="F9" s="223"/>
-      <c r="G9" s="223"/>
-      <c r="H9" s="223"/>
-      <c r="I9" s="223"/>
-      <c r="J9" s="223"/>
+      <c r="E9" s="221"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="219"/>
+      <c r="H9" s="219"/>
+      <c r="I9" s="219"/>
+      <c r="J9" s="219"/>
       <c r="K9" s="103"/>
-      <c r="L9" s="223"/>
-      <c r="M9" s="223"/>
+      <c r="L9" s="219"/>
+      <c r="M9" s="219"/>
       <c r="S9" s="69"/>
     </row>
     <row r="10" spans="1:22" ht="29" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="219"/>
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="221"/>
+      <c r="C10" s="221"/>
       <c r="D10" s="177" t="s">
         <v>228</v>
       </c>
-      <c r="E10" s="219"/>
-      <c r="F10" s="223"/>
-      <c r="G10" s="223"/>
-      <c r="H10" s="223"/>
-      <c r="I10" s="223"/>
-      <c r="J10" s="223"/>
+      <c r="E10" s="221"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="219"/>
+      <c r="H10" s="219"/>
+      <c r="I10" s="219"/>
+      <c r="J10" s="219"/>
       <c r="K10" s="103"/>
-      <c r="L10" s="223"/>
-      <c r="M10" s="223"/>
+      <c r="L10" s="219"/>
+      <c r="M10" s="219"/>
       <c r="S10" s="69"/>
     </row>
     <row r="11" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="219"/>
-      <c r="B11" s="219"/>
-      <c r="C11" s="219"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="221"/>
+      <c r="C11" s="221"/>
       <c r="D11" s="117" t="s">
         <v>229</v>
       </c>
-      <c r="E11" s="219"/>
-      <c r="F11" s="223"/>
-      <c r="G11" s="223"/>
-      <c r="H11" s="223"/>
-      <c r="I11" s="223"/>
-      <c r="J11" s="223"/>
+      <c r="E11" s="221"/>
+      <c r="F11" s="219"/>
+      <c r="G11" s="219"/>
+      <c r="H11" s="219"/>
+      <c r="I11" s="219"/>
+      <c r="J11" s="219"/>
       <c r="K11" s="118"/>
-      <c r="L11" s="223"/>
-      <c r="M11" s="223"/>
+      <c r="L11" s="219"/>
+      <c r="M11" s="219"/>
       <c r="S11" s="69"/>
     </row>
     <row r="12" spans="1:22" ht="14.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="219"/>
-      <c r="B12" s="219"/>
-      <c r="C12" s="219"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="221"/>
+      <c r="C12" s="221"/>
       <c r="D12" s="117" t="s">
         <v>230</v>
       </c>
-      <c r="E12" s="219"/>
-      <c r="F12" s="223"/>
-      <c r="G12" s="223"/>
-      <c r="H12" s="223"/>
-      <c r="I12" s="223"/>
-      <c r="J12" s="223"/>
+      <c r="E12" s="221"/>
+      <c r="F12" s="219"/>
+      <c r="G12" s="219"/>
+      <c r="H12" s="219"/>
+      <c r="I12" s="219"/>
+      <c r="J12" s="219"/>
       <c r="K12" s="103"/>
-      <c r="L12" s="223"/>
-      <c r="M12" s="223"/>
+      <c r="L12" s="219"/>
+      <c r="M12" s="219"/>
       <c r="S12" s="69"/>
     </row>
     <row r="13" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
@@ -19921,85 +19984,85 @@
     <mergeCell ref="H8:H12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="309" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="313" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:F24">
-    <cfRule type="cellIs" dxfId="308" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="312" priority="30" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="311" priority="33" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="306" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="310" priority="34" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="305" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="309" priority="35" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="308" priority="36" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H8 H13:H24">
-    <cfRule type="cellIs" dxfId="303" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="307" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="302" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="306" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F8">
-    <cfRule type="cellIs" dxfId="301" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="305" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="304" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="299" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="303" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="302" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J8 J13:J24">
-    <cfRule type="containsText" dxfId="297" priority="17" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="301" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="296" priority="18" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="300" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="295" priority="19" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="299" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="294" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="298" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="293" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="297" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="296" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="295" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="290" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="294" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="293" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="288" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="292" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="287" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="291" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20873,40 +20936,40 @@
       <c r="X16" s="87"/>
     </row>
     <row r="17" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="226" t="s">
+      <c r="A17" s="220" t="s">
         <v>221</v>
       </c>
-      <c r="B17" s="230" t="s">
+      <c r="B17" s="226" t="s">
         <v>222</v>
       </c>
-      <c r="C17" s="226" t="s">
+      <c r="C17" s="220" t="s">
         <v>223</v>
       </c>
       <c r="D17" s="178" t="s">
         <v>224</v>
       </c>
-      <c r="E17" s="227" t="s">
+      <c r="E17" s="222" t="s">
         <v>365</v>
       </c>
-      <c r="F17" s="224" t="s">
+      <c r="F17" s="225" t="s">
         <v>53</v>
       </c>
-      <c r="G17" s="231" t="s">
+      <c r="G17" s="227" t="s">
         <v>226</v>
       </c>
-      <c r="H17" s="231" t="s">
+      <c r="H17" s="227" t="s">
         <v>183</v>
       </c>
-      <c r="I17" s="225" t="s">
+      <c r="I17" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="J17" s="225" t="s">
+      <c r="J17" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="K17" s="232"/>
-      <c r="L17" s="225"/>
-      <c r="M17" s="229"/>
-      <c r="N17" s="229"/>
+      <c r="K17" s="228"/>
+      <c r="L17" s="218"/>
+      <c r="M17" s="224"/>
+      <c r="N17" s="224"/>
       <c r="P17" s="69" t="s">
         <v>321</v>
       </c>
@@ -20918,76 +20981,76 @@
       <c r="X17" s="91"/>
     </row>
     <row r="18" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="219"/>
-      <c r="B18" s="219"/>
-      <c r="C18" s="219"/>
+      <c r="A18" s="221"/>
+      <c r="B18" s="221"/>
+      <c r="C18" s="221"/>
       <c r="D18" s="179" t="s">
         <v>227</v>
       </c>
-      <c r="E18" s="228"/>
-      <c r="F18" s="223"/>
-      <c r="G18" s="223"/>
-      <c r="H18" s="223"/>
-      <c r="I18" s="223"/>
-      <c r="J18" s="223"/>
-      <c r="K18" s="223"/>
-      <c r="L18" s="223"/>
-      <c r="M18" s="223"/>
-      <c r="N18" s="223"/>
+      <c r="E18" s="223"/>
+      <c r="F18" s="219"/>
+      <c r="G18" s="219"/>
+      <c r="H18" s="219"/>
+      <c r="I18" s="219"/>
+      <c r="J18" s="219"/>
+      <c r="K18" s="219"/>
+      <c r="L18" s="219"/>
+      <c r="M18" s="219"/>
+      <c r="N18" s="219"/>
     </row>
     <row r="19" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="219"/>
-      <c r="B19" s="219"/>
-      <c r="C19" s="219"/>
+      <c r="A19" s="221"/>
+      <c r="B19" s="221"/>
+      <c r="C19" s="221"/>
       <c r="D19" s="179" t="s">
         <v>228</v>
       </c>
-      <c r="E19" s="228"/>
-      <c r="F19" s="223"/>
-      <c r="G19" s="223"/>
-      <c r="H19" s="223"/>
-      <c r="I19" s="223"/>
-      <c r="J19" s="223"/>
-      <c r="K19" s="223"/>
-      <c r="L19" s="223"/>
-      <c r="M19" s="223"/>
-      <c r="N19" s="223"/>
+      <c r="E19" s="223"/>
+      <c r="F19" s="219"/>
+      <c r="G19" s="219"/>
+      <c r="H19" s="219"/>
+      <c r="I19" s="219"/>
+      <c r="J19" s="219"/>
+      <c r="K19" s="219"/>
+      <c r="L19" s="219"/>
+      <c r="M19" s="219"/>
+      <c r="N19" s="219"/>
     </row>
     <row r="20" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="219"/>
-      <c r="B20" s="219"/>
-      <c r="C20" s="219"/>
+      <c r="A20" s="221"/>
+      <c r="B20" s="221"/>
+      <c r="C20" s="221"/>
       <c r="D20" s="105" t="s">
         <v>229</v>
       </c>
-      <c r="E20" s="228"/>
-      <c r="F20" s="223"/>
-      <c r="G20" s="223"/>
-      <c r="H20" s="223"/>
-      <c r="I20" s="223"/>
-      <c r="J20" s="223"/>
-      <c r="K20" s="223"/>
-      <c r="L20" s="223"/>
-      <c r="M20" s="223"/>
-      <c r="N20" s="223"/>
+      <c r="E20" s="223"/>
+      <c r="F20" s="219"/>
+      <c r="G20" s="219"/>
+      <c r="H20" s="219"/>
+      <c r="I20" s="219"/>
+      <c r="J20" s="219"/>
+      <c r="K20" s="219"/>
+      <c r="L20" s="219"/>
+      <c r="M20" s="219"/>
+      <c r="N20" s="219"/>
     </row>
     <row r="21" spans="1:24" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="219"/>
-      <c r="B21" s="219"/>
-      <c r="C21" s="219"/>
+      <c r="A21" s="221"/>
+      <c r="B21" s="221"/>
+      <c r="C21" s="221"/>
       <c r="D21" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="E21" s="228"/>
-      <c r="F21" s="223"/>
-      <c r="G21" s="223"/>
-      <c r="H21" s="223"/>
-      <c r="I21" s="223"/>
-      <c r="J21" s="223"/>
-      <c r="K21" s="223"/>
-      <c r="L21" s="223"/>
-      <c r="M21" s="223"/>
-      <c r="N21" s="223"/>
+      <c r="E21" s="223"/>
+      <c r="F21" s="219"/>
+      <c r="G21" s="219"/>
+      <c r="H21" s="219"/>
+      <c r="I21" s="219"/>
+      <c r="J21" s="219"/>
+      <c r="K21" s="219"/>
+      <c r="L21" s="219"/>
+      <c r="M21" s="219"/>
+      <c r="N21" s="219"/>
     </row>
     <row r="22" spans="1:24" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="87" t="s">
@@ -22977,68 +23040,68 @@
     <mergeCell ref="I17:I21"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="286" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="290" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H17 H22:H61">
-    <cfRule type="cellIs" dxfId="285" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="289" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="284" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="288" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="283" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="287" priority="23" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="282" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="286" priority="24" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="281" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="285" priority="25" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="284" priority="26" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J17 J22:J61">
-    <cfRule type="containsText" dxfId="279" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="283" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="278" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="282" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="277" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="281" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="276" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="280" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="275" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="279" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="278" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="277" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:U1">
-    <cfRule type="cellIs" dxfId="272" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="276" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="275" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="274" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="269" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="273" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24353,54 +24416,54 @@
   </sheetData>
   <autoFilter ref="A1:J9" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <conditionalFormatting sqref="F2:F55">
-    <cfRule type="cellIs" dxfId="268" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="272" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H55">
-    <cfRule type="cellIs" dxfId="267" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="271" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="270" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F55">
-    <cfRule type="cellIs" dxfId="265" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="269" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="268" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="263" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="267" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="266" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J55">
-    <cfRule type="containsText" dxfId="261" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="265" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="260" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="264" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="259" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="263" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:AB1">
-    <cfRule type="cellIs" dxfId="258" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="262" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="257" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="261" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="260" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="259" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25530,54 +25593,54 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="254" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="258" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="253" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="257" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="256" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="251" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="255" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="254" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="253" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="248" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="252" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="247" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="251" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="250" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="245" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="249" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1">
-    <cfRule type="cellIs" dxfId="244" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="248" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="247" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="242" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="246" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="245" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -133,7 +133,7 @@
     <t>NA</t>
   </si>
   <si>
-    <t>Technical variable name required to match a column header in the CSV file (synthetic, anonymized representation of the real data), can appear in multiple languages.</t>
+    <t>A technical variable name is required to match a column header in the CSV file (a synthetic, anonymised representation of the real data).</t>
   </si>
   <si>
     <t>Mandatory</t>
@@ -209,7 +209,8 @@
     <t>csvw:propertyUrl</t>
   </si>
   <si>
-    <t>The propertyUrl may point to standard, controlled vocabularies, or ontologies that define the semantic meaning of the column. For example: csvw:propertyUrl http://publications.europa.eu/resource/authority/country For advanced usage, refer to the official specification: https://www.w3.org/TR/tabular-metadata/#propertyurl</t>
+    <t>The propertyUrl may point to standard vocabularies, controlled vocabularies or ontologies that define the semantic meaning of the column. For example: csvw:propertyUrl http://publications.europa.eu/resource/authority/country
+For advanced usage, refer to the official specification: https://www.w3.org/TR/tabular-metadata/#propertyurl</t>
   </si>
   <si>
     <t>Recommended</t>
@@ -626,7 +627,7 @@
     <t>DCAT-AP v3</t>
   </si>
   <si>
-    <t>If applicable, add URI to connected dcat:Catalog</t>
+    <t>If applicable, enter the URI of the connected dcat:Catalog.</t>
   </si>
   <si>
     <t>hrishapes:CatalogShape</t>
@@ -698,7 +699,7 @@
     <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
   </si>
   <si>
-    <t>Add URI to all datasets contained in this catalogue</t>
+    <t>Enter the URI for all datasets contained in this catalogue.</t>
   </si>
   <si>
     <t>hrishapes:DatasetShape</t>
@@ -811,7 +812,7 @@
     <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
   </si>
   <si>
-    <t>The licence under which the catalogue (with resource description) is made available.
+    <t>The licence under which the catalogue (with its resource description) is made available.
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
   </si>
   <si>
@@ -899,7 +900,7 @@
     <t>Some datasets may have real-time Data Services (e.g., Beacon API counting individuals). IT teams should define the relationship between the catalogue and the Data Service via this property. While crucial for interoperability, this property is not relevant for end users to collect.</t>
   </si>
   <si>
-    <t>If applicable, add URI to dcat:DataService</t>
+    <t>If applicable, enter the URI for dcat:DataService.</t>
   </si>
   <si>
     <t>hrishapes:DataServiceShape</t>
@@ -965,7 +966,7 @@
     <t>http://publications.europa.eu/resource/authority/access-right</t>
   </si>
   <si>
-    <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. It is foreseen that one of the three options has to be used: public, restricted, non-public.
+    <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. One of the three options must be used: public, restricted, non-public.
     Open Data (Public): The dataset is available under general open data rules, such as those covered by the High Value Datasets Implementing Regulation.
     Protected Data (Restricted): The dataset contains protected data and is accessible only under specific conditions, as outlined in regulations like the Data Governance Act.
     Sensitive Data (Non-public): The dataset includes resources that may contain sensitive or personal information, falling under regulations such as the EHDS Regulation.
@@ -996,7 +997,7 @@
     <t>healthdcatap:analytics</t>
   </si>
   <si>
-    <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would not be Distributions but rather DatasetServices.</t>
+    <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would be Data Services rather than Distributions.</t>
   </si>
   <si>
     <t>custom:analytics</t>
@@ -1186,7 +1187,7 @@
     <t>custom:has_version</t>
   </si>
   <si>
-    <t>fill in URI to dcat:Dataset that is another version of current Dataset</t>
+    <t>Enter the URI for the dcat:Dataset that is another version of the current Dataset.</t>
   </si>
   <si>
     <t>health condition of interest</t>
@@ -1512,8 +1513,8 @@
   <si>
     <t>This property makes use of another small class (prov:Attribution). There, you can choose one of the roles as listed in the controlled vocabulary and link that to a specific Agent (expressed with foaf:Agent).
 Repeat this property if you wish to specify multiple roles for the same agent.
-Refer to the Attribution class for more information how to fill this.
-Use this property if you would like to indicate the funder of the (research project that resulted in creation of the) dataset.
+Refer to the Attribution class for more information on how to fill this in.
+Use this property if you would like to indicate the funder of the dataset (or of the research project that resulted in its creation).
 The value for role in the Attribution class then becomes: https://standards.iso.org/iso/19115/resources/Codelists/gml/CI_RoleCode.xml#funder</t>
   </si>
   <si>
@@ -1882,7 +1883,7 @@
   </si>
   <si>
     <t>Note: This property will be deprecated in the next major release.
-Choose a term from the controlled vocabulary, which includes the following types: Academia-ScientificOrganisation, Company, IndustryConsortium, LocalAuthority, NationalAuthority, NonGovernmentalOrganisation, NonProfitOrganisation, PrivateIndividual, RegionalAuthority, StandardisationBody and SupraNationalAuthority. These should use the following URL: http://purl.org/adms/publishertype/[type].</t>
+Choose a term from the controlled vocabulary, which includes the following types: Academia-ScientificOrganisation, Company, IndustryConsortium, LocalAuthority, NationalAuthority, NonGovernmentalOrganisation, NonProfitOrganisation, PrivateIndividual, RegionalAuthority, StandardisationBody and SupraNationalAuthority. These should use URLs of the following form: http://purl.org/adms/publishertype/[type].</t>
   </si>
   <si>
     <t>This property should be filled using ADMS vocabulary (http://purl.org/adms/publishertype/1.0).</t>
@@ -2131,7 +2132,7 @@
     <t>resource:format</t>
   </si>
   <si>
-    <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions might have a language, for example imaging data.
+    <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions necessarily have a language; for example, those containing imaging data may not.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
   </si>
   <si>

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anakonrad/Library/health-ri-metadata/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6BC147-5817-E84D-92E3-F4AFD43450AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AB7EBB9-189E-AB42-ABC2-E936CFBA35A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="-19160" windowWidth="30240" windowHeight="17260" firstSheet="10" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="720" yWindow="-19160" windowWidth="30240" windowHeight="17260" firstSheet="10" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -3855,7 +3855,37 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="322">
+  <dxfs count="318">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color theme="1"/>
@@ -3868,6 +3898,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -3898,6 +3958,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -3908,6 +3998,146 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -3918,6 +4148,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4058,6 +4298,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4068,6 +4328,36 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -4078,6 +4368,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4088,6 +4398,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4102,6 +4442,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -4138,6 +4488,36 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4148,6 +4528,96 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4158,6 +4628,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4252,7 +4732,17 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4268,6 +4758,46 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4292,7 +4822,37 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor theme="2"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4342,6 +4902,16 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -4378,6 +4948,26 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -4388,6 +4978,246 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
@@ -4398,6 +5228,16 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color theme="1"/>
       </font>
       <fill>
@@ -4492,7 +5332,67 @@
       </font>
       <fill>
         <patternFill patternType="solid">
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor theme="2"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4503,946 +5403,6 @@
       <fill>
         <patternFill patternType="solid">
           <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="7" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="4" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
@@ -9050,54 +9010,54 @@
   </sheetData>
   <autoFilter ref="A1:J24" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
   <conditionalFormatting sqref="F2:F54">
-    <cfRule type="cellIs" dxfId="240" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="236" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H54">
-    <cfRule type="cellIs" dxfId="239" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="235" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="238" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="234" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F54">
-    <cfRule type="cellIs" dxfId="237" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="233" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="236" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="232" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="235" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="231" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="234" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="230" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J54">
-    <cfRule type="containsText" dxfId="233" priority="17" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="229" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="232" priority="18" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="228" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="231" priority="19" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="227" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:T1">
-    <cfRule type="cellIs" dxfId="230" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="226" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="229" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="225" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="228" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="224" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="227" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="223" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9908,65 +9868,65 @@
     <mergeCell ref="G6:G10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="226" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="222" priority="11" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H6 H11 G12:I12">
-    <cfRule type="cellIs" dxfId="225" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="221" priority="12" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="224" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="220" priority="13" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F6 F11:F15">
-    <cfRule type="cellIs" dxfId="223" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="219" priority="14" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="222" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="218" priority="15" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="221" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="217" priority="16" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="220" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="216" priority="17" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J6">
-    <cfRule type="containsText" dxfId="219" priority="5" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="215" priority="5" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="218" priority="6" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="214" priority="6" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="217" priority="7" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="213" priority="7" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:J15">
-    <cfRule type="containsText" dxfId="216" priority="8" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="212" priority="8" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="215" priority="9" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="211" priority="9" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J11)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="214" priority="10" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="210" priority="10" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J11)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="213" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="209" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="212" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="208" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="211" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="207" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="210" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="206" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11574,54 +11534,54 @@
   </sheetData>
   <autoFilter ref="A1:J23" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="209" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="205" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="208" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="204" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="207" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="203" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="206" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="202" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="205" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="201" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="204" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="200" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="203" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="199" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="202" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="198" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="201" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="197" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="200" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="196" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:R1">
-    <cfRule type="cellIs" dxfId="199" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="195" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="198" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="194" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="197" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="193" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="196" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="192" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11840,49 +11800,49 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="195" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="191" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="194" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="190" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="193" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="189" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="192" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="188" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="191" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="187" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="190" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="186" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="189" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="185" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="188" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="184" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="187" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="183" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:U1">
-    <cfRule type="cellIs" dxfId="186" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="182" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="185" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="181" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="184" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="180" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="183" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="179" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12742,85 +12702,85 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A41:B42">
-    <cfRule type="cellIs" dxfId="182" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="178" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="181" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="177" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="180" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="176" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="179" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="175" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D40:E42">
-    <cfRule type="cellIs" dxfId="178" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="174" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="177" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="173" priority="20" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="176" priority="21" operator="equal">
+    <cfRule type="cellIs" dxfId="172" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="175" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="171" priority="22" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F52">
-    <cfRule type="cellIs" dxfId="174" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="170" priority="9" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="173" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="169" priority="10" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="172" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="168" priority="11" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="171" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="167" priority="12" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="170" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="166" priority="13" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="169" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="165" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="168" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="164" priority="24" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="167" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="163" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="166" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="162" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="165" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="161" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="164" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="160" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="S1:X1">
-    <cfRule type="cellIs" dxfId="163" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="159" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="162" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="158" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="161" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="157" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="160" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="156" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12959,7 +12919,7 @@
         <v>787</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G2" s="168" t="s">
         <v>29</v>
@@ -13258,89 +13218,89 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="D11:E13">
-    <cfRule type="cellIs" dxfId="159" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="155" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="158" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="154" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="153" priority="21" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="152" priority="20" operator="equal">
       <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="157" priority="21" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="156" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
-    <cfRule type="cellIs" dxfId="155" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="151" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="154" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="150" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="153" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="149" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="152" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="148" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="151" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="147" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 A12:B13">
-    <cfRule type="cellIs" dxfId="150" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="146" priority="15" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="149" priority="16" operator="equal">
+    <cfRule type="cellIs" dxfId="145" priority="16" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="148" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="144" priority="17" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="147" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="143" priority="18" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F23">
-    <cfRule type="cellIs" dxfId="146" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="142" priority="10" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="145" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="141" priority="11" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="144" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="140" priority="12" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="143" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="139" priority="13" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="142" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="138" priority="14" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H12 H21:H23">
-    <cfRule type="cellIs" dxfId="141" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="137" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="136" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="140" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="139" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="135" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="134" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="133" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="132" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="138" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="137" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="136" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -13564,35 +13524,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="135" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="131" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="134" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="130" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="133" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="129" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="132" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="128" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="131" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="127" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="130" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="126" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="129" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="125" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="128" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="124" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="127" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="123" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13795,35 +13755,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="126" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="122" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="125" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="121" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="124" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="120" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="119" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="122" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="118" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="121" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="117" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="116" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="119" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="115" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="118" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="114" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14026,35 +13986,35 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F3">
-    <cfRule type="cellIs" dxfId="117" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="113" priority="5" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H3">
-    <cfRule type="cellIs" dxfId="116" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="112" priority="6" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="115" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="111" priority="7" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="114" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="110" priority="8" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="113" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="109" priority="9" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F3">
-    <cfRule type="cellIs" dxfId="112" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="108" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="111" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="107" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="110" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="106" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="109" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="105" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15098,14 +15058,14 @@
     <cfRule type="cellIs" dxfId="91" priority="25" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="90" priority="26" operator="equal">
-      <formula>"Recommended"</formula>
+    <cfRule type="cellIs" dxfId="90" priority="28" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="89" priority="27" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="88" priority="28" operator="equal">
-      <formula>"Conditional"</formula>
+    <cfRule type="cellIs" dxfId="88" priority="26" operator="equal">
+      <formula>"Recommended"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
@@ -15145,25 +15105,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="77" priority="29" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="30" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="76" priority="29" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="76" priority="30" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F52">
-    <cfRule type="cellIs" dxfId="75" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="75" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="74" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="73" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="72" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="74" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="73" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="72" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -15993,14 +15953,14 @@
     <cfRule type="cellIs" dxfId="71" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="70" priority="20" operator="equal">
-      <formula>"Recommended"</formula>
+    <cfRule type="cellIs" dxfId="70" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="69" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="68" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
+    <cfRule type="cellIs" dxfId="68" priority="20" operator="equal">
+      <formula>"Recommended"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2">
@@ -16056,25 +16016,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H8 H10:H14 H16:H24 H26:H40 H49:H51">
-    <cfRule type="cellIs" dxfId="53" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="52" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="52" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="51" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="51" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="50" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="49" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="48" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="50" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="48" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -16973,14 +16933,14 @@
     <cfRule type="cellIs" dxfId="47" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="20" operator="equal">
-      <formula>"Recommended"</formula>
+    <cfRule type="cellIs" dxfId="46" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="45" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="44" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
+    <cfRule type="cellIs" dxfId="44" priority="20" operator="equal">
+      <formula>"Recommended"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
@@ -17034,25 +16994,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="29" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="26" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="26" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -17979,14 +17939,14 @@
     <cfRule type="cellIs" dxfId="23" priority="19" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="equal">
-      <formula>"Recommended"</formula>
+    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+      <formula>"Conditional"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="21" priority="21" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="22" operator="equal">
-      <formula>"Conditional"</formula>
+    <cfRule type="cellIs" dxfId="20" priority="20" operator="equal">
+      <formula>"Recommended"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E3">
@@ -18040,25 +18000,25 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H6:H9 H11:H15 H17:H25 H27:H41 H50:H52">
-    <cfRule type="cellIs" dxfId="5" priority="23" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="5" priority="24" operator="equal">
+      <formula>"needs review"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="greaterThan">
       <formula>"reviewd"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="24" operator="equal">
-      <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"Conditional"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"Mandatory"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"Recommended"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Optional"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>"Recommended"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
-      <formula>"Mandatory"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
-      <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
@@ -18707,44 +18667,44 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F1 H1:I1">
-    <cfRule type="cellIs" dxfId="321" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="317" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="320" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="316" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="319" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="315" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="318" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="314" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="317" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="313" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="316" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="312" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="315" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="311" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="314" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="310" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M1:Q1">
-    <cfRule type="cellIs" dxfId="313" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="309" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="312" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="308" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="311" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="307" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="310" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="306" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19862,85 +19822,85 @@
     <mergeCell ref="H8:H12"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F8">
-    <cfRule type="cellIs" dxfId="309" priority="20" operator="equal">
+    <cfRule type="cellIs" dxfId="305" priority="20" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F13:F24">
-    <cfRule type="cellIs" dxfId="308" priority="30" operator="equal">
+    <cfRule type="cellIs" dxfId="304" priority="30" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="307" priority="33" operator="equal">
+    <cfRule type="cellIs" dxfId="303" priority="33" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="306" priority="34" operator="equal">
+    <cfRule type="cellIs" dxfId="302" priority="34" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="305" priority="35" operator="equal">
+    <cfRule type="cellIs" dxfId="301" priority="35" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="304" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="300" priority="36" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H8 H13:H24">
-    <cfRule type="cellIs" dxfId="303" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="299" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="302" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="298" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F8">
-    <cfRule type="cellIs" dxfId="301" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="297" priority="9" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="300" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="296" priority="10" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="299" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="295" priority="11" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="298" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="294" priority="12" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J8 J13:J24">
-    <cfRule type="containsText" dxfId="297" priority="17" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="293" priority="17" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="296" priority="18" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="292" priority="18" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="295" priority="19" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="291" priority="19" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="294" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="290" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="293" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="289" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="292" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="288" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="291" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="287" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1:S1">
-    <cfRule type="cellIs" dxfId="290" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="286" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="289" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="285" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="288" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="284" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="287" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="283" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -22918,68 +22878,68 @@
     <mergeCell ref="I17:I21"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="286" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="282" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H17 H22:H61">
-    <cfRule type="cellIs" dxfId="285" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="281" priority="21" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="284" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="280" priority="22" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F17 F22:F61">
-    <cfRule type="cellIs" dxfId="283" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="279" priority="23" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="282" priority="24" operator="equal">
+    <cfRule type="cellIs" dxfId="278" priority="24" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="281" priority="25" operator="equal">
+    <cfRule type="cellIs" dxfId="277" priority="25" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="280" priority="26" operator="equal">
+    <cfRule type="cellIs" dxfId="276" priority="26" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J17 J22:J61">
-    <cfRule type="containsText" dxfId="279" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="275" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="278" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="274" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="277" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="273" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K1">
-    <cfRule type="cellIs" dxfId="276" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="272" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="275" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="271" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="274" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="270" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="273" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="269" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1:U1">
-    <cfRule type="cellIs" dxfId="272" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="268" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="271" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="267" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="270" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="266" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="269" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="265" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -24294,54 +24254,54 @@
   </sheetData>
   <autoFilter ref="A1:J9" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
   <conditionalFormatting sqref="F2:F55">
-    <cfRule type="cellIs" dxfId="268" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="264" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H55">
-    <cfRule type="cellIs" dxfId="267" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="263" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="266" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="262" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F55">
-    <cfRule type="cellIs" dxfId="265" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="261" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="264" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="260" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="263" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="259" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="262" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="258" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J55">
-    <cfRule type="containsText" dxfId="261" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="257" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="260" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="256" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="259" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="255" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W1:AB1">
-    <cfRule type="cellIs" dxfId="258" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="254" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="257" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="253" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="256" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="252" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="255" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="251" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -25471,54 +25431,54 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F2:F53">
-    <cfRule type="cellIs" dxfId="254" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="250" priority="12" operator="equal">
       <formula>"Not added"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H53">
-    <cfRule type="cellIs" dxfId="253" priority="13" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="249" priority="13" operator="greaterThan">
       <formula>"reviewd"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="252" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="248" priority="14" operator="equal">
       <formula>"needs review"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:I1 F1:F53">
-    <cfRule type="cellIs" dxfId="251" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="247" priority="5" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="250" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="246" priority="6" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="249" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="245" priority="7" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="248" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="244" priority="8" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J53">
-    <cfRule type="containsText" dxfId="247" priority="9" operator="containsText" text="Health and NL">
+    <cfRule type="containsText" dxfId="243" priority="9" operator="containsText" text="Health and NL">
       <formula>NOT(ISERROR(SEARCH("Health and NL",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="246" priority="10" operator="containsText" text="HealthDCAT-AP">
+    <cfRule type="containsText" dxfId="242" priority="10" operator="containsText" text="HealthDCAT-AP">
       <formula>NOT(ISERROR(SEARCH("HealthDCAT-AP",J2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="245" priority="11" operator="containsText" text="DCAT-AP NL">
+    <cfRule type="containsText" dxfId="241" priority="11" operator="containsText" text="DCAT-AP NL">
       <formula>NOT(ISERROR(SEARCH("DCAT-AP NL",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1">
-    <cfRule type="cellIs" dxfId="244" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="240" priority="1" operator="equal">
       <formula>"Optional"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="243" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="239" priority="2" operator="equal">
       <formula>"Recommended"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="242" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="238" priority="3" operator="equal">
       <formula>"Mandatory"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="241" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="237" priority="4" operator="equal">
       <formula>"Conditional"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="-28200" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="-28200" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -1084,13 +1084,10 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -1103,6 +1100,9 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -6075,8 +6075,8 @@
     <col width="28.83203125" customWidth="1" style="234" min="13" max="13"/>
     <col width="9.1640625" customWidth="1" style="234" min="14" max="20"/>
     <col width="19.1640625" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="24"/>
-    <col width="9.1640625" customWidth="1" style="234" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
+    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customFormat="1" customHeight="1" s="165">
@@ -6222,7 +6222,7 @@
           <t>This property links the distribution class to the corresponding data service(s).</t>
         </is>
       </c>
-      <c r="F2" s="220" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6242,7 +6242,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J2" s="218" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6288,7 +6288,7 @@
       <c r="W2" s="226" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="221" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>access URL</t>
         </is>
@@ -6298,7 +6298,7 @@
           <t>A URL of the resource that gives access to a distribution of the dataset. E.g., landing page, feed, SPARQL endpoint.</t>
         </is>
       </c>
-      <c r="C3" s="221" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dcat:accessURL</t>
         </is>
@@ -6308,7 +6308,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="224" t="inlineStr">
+      <c r="E3" s="223" t="inlineStr">
         <is>
           <t>Add a link that points to where the dataset can be found. If it’s hosted in a Data Repository, include the link to its entry. For datasets not in a repository (like registries), but still available for secondary use, provide a link to an access request form or a webpage with instructions for accessing the data.</t>
         </is>
@@ -6318,7 +6318,7 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G3" s="220" t="inlineStr">
+      <c r="G3" s="218" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -6326,12 +6326,12 @@
       <c r="H3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="218" t="inlineStr">
+      <c r="I3" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="218" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6341,8 +6341,8 @@
           <t>resource:access_url</t>
         </is>
       </c>
-      <c r="L3" s="218" t="n"/>
-      <c r="M3" s="218" t="n"/>
+      <c r="L3" s="224" t="n"/>
+      <c r="M3" s="224" t="n"/>
       <c r="O3" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6354,9 +6354,9 @@
         </is>
       </c>
       <c r="S3" s="121" t="n"/>
-      <c r="U3" s="221" t="n"/>
-      <c r="V3" s="221" t="n"/>
-      <c r="W3" s="221" t="n"/>
+      <c r="U3" s="220" t="n"/>
+      <c r="V3" s="220" t="n"/>
+      <c r="W3" s="220" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="226" t="inlineStr">
@@ -6384,7 +6384,7 @@
           <t>The legislation that mandates the creation or management of the Distribution.</t>
         </is>
       </c>
-      <c r="F4" s="220" t="inlineStr">
+      <c r="F4" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6404,7 +6404,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="218" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -6442,7 +6442,7 @@
           <t>An indication of how long it is planned to keep the Distribution of the Dataset available.</t>
         </is>
       </c>
-      <c r="C5" s="221" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>dcatap:availability</t>
         </is>
@@ -6457,12 +6457,12 @@
           <t>To indicate the planned availability of the Distribution, the EU planned-availability controlled vocabulary MUST be used.</t>
         </is>
       </c>
-      <c r="F5" s="220" t="inlineStr">
+      <c r="F5" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="220" t="inlineStr">
+      <c r="G5" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
@@ -6472,19 +6472,19 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="218" t="inlineStr">
+      <c r="I5" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="218" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="69" t="n"/>
-      <c r="L5" s="218" t="n"/>
-      <c r="M5" s="218" t="n"/>
+      <c r="L5" s="224" t="n"/>
+      <c r="M5" s="224" t="n"/>
       <c r="O5" s="203" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -6546,7 +6546,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="218" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6574,7 +6574,7 @@
       <c r="W6" s="226" t="n"/>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="221" t="inlineStr">
+      <c r="A7" s="220" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
@@ -6584,7 +6584,7 @@
           <t>The checksum property provides a mechanism that can be used to verify that the contents of a file or package have not changed.</t>
         </is>
       </c>
-      <c r="C7" s="221" t="inlineStr">
+      <c r="C7" s="220" t="inlineStr">
         <is>
           <t>spdx:checksum</t>
         </is>
@@ -6599,7 +6599,7 @@
           <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate the checksum algorithm and checksum value (see Checksum class for further details).</t>
         </is>
       </c>
-      <c r="F7" s="220" t="inlineStr">
+      <c r="F7" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6609,17 +6609,17 @@
           <t>spdx:Checksum</t>
         </is>
       </c>
-      <c r="H7" s="220" t="inlineStr">
+      <c r="H7" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="218" t="inlineStr">
+      <c r="I7" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="218" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6629,12 +6629,12 @@
           <t>resource:hash_algorithm/resource:hash_algorithm</t>
         </is>
       </c>
-      <c r="L7" s="218" t="inlineStr">
+      <c r="L7" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
       </c>
-      <c r="M7" s="218" t="inlineStr">
+      <c r="M7" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
@@ -6655,9 +6655,9 @@
         </is>
       </c>
       <c r="S7" s="121" t="n"/>
-      <c r="U7" s="221" t="n"/>
-      <c r="V7" s="221" t="n"/>
-      <c r="W7" s="221" t="n"/>
+      <c r="U7" s="220" t="n"/>
+      <c r="V7" s="220" t="n"/>
+      <c r="W7" s="220" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
       <c r="A8" s="226" t="inlineStr">
@@ -6705,7 +6705,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="218" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6733,7 +6733,7 @@
       <c r="W8" s="226" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="221" t="inlineStr">
+      <c r="A9" s="220" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6743,7 +6743,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C9" s="221" t="inlineStr">
+      <c r="C9" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -6758,27 +6758,27 @@
           <t>Provide specific details about the distribution here, complementing the description of the related Dataset. This field can be repeated for different language versions of the description.</t>
         </is>
       </c>
-      <c r="F9" s="220" t="inlineStr">
+      <c r="F9" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="220" t="inlineStr">
+      <c r="G9" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H9" s="220" t="inlineStr">
+      <c r="H9" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="218" t="inlineStr">
+      <c r="I9" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="218" t="inlineStr">
+      <c r="J9" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6788,8 +6788,8 @@
           <t>resource:description</t>
         </is>
       </c>
-      <c r="L9" s="218" t="n"/>
-      <c r="M9" s="218" t="n"/>
+      <c r="L9" s="224" t="n"/>
+      <c r="M9" s="224" t="n"/>
       <c r="O9" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6803,9 +6803,9 @@
       <c r="S9" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="U9" s="221" t="n"/>
-      <c r="V9" s="221" t="n"/>
-      <c r="W9" s="221" t="n"/>
+      <c r="U9" s="220" t="n"/>
+      <c r="V9" s="220" t="n"/>
+      <c r="W9" s="220" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="226" t="inlineStr">
@@ -6853,7 +6853,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J10" s="218" t="inlineStr">
+      <c r="J10" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6881,7 +6881,7 @@
       <c r="W10" s="226" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="221" t="inlineStr">
+      <c r="A11" s="220" t="inlineStr">
         <is>
           <t>download URL</t>
         </is>
@@ -6906,27 +6906,27 @@
           <t>If the dataset is openly accessible and available in a repository, you can directly include a link to the downloadable file here.</t>
         </is>
       </c>
-      <c r="F11" s="220" t="inlineStr">
+      <c r="F11" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="220" t="inlineStr">
+      <c r="G11" s="218" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="220" t="inlineStr">
+      <c r="H11" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="218" t="inlineStr">
+      <c r="I11" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="218" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6936,8 +6936,8 @@
           <t>resource:download_url</t>
         </is>
       </c>
-      <c r="L11" s="218" t="n"/>
-      <c r="M11" s="218" t="n"/>
+      <c r="L11" s="224" t="n"/>
+      <c r="M11" s="224" t="n"/>
       <c r="O11" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6949,9 +6949,9 @@
         </is>
       </c>
       <c r="S11" s="121" t="n"/>
-      <c r="U11" s="221" t="n"/>
-      <c r="V11" s="221" t="n"/>
-      <c r="W11" s="221" t="n"/>
+      <c r="U11" s="220" t="n"/>
+      <c r="V11" s="220" t="n"/>
+      <c r="W11" s="220" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
       <c r="A12" s="226" t="inlineStr">
@@ -6999,7 +6999,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="218" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7027,7 +7027,7 @@
       <c r="W12" s="226" t="n"/>
     </row>
     <row r="13" ht="99" customHeight="1">
-      <c r="A13" s="221" t="inlineStr">
+      <c r="A13" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -7037,7 +7037,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="221" t="inlineStr">
+      <c r="C13" s="220" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -7047,33 +7047,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E13" s="224" t="inlineStr">
+      <c r="E13" s="223" t="inlineStr">
         <is>
           <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions necessarily have a language; for example, those containing imaging data may not.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="220" t="inlineStr">
+      <c r="F13" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="220" t="inlineStr">
+      <c r="G13" s="218" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H13" s="220" t="inlineStr">
+      <c r="H13" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="218" t="inlineStr">
+      <c r="I13" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="218" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7083,8 +7083,8 @@
           <t>resource:language</t>
         </is>
       </c>
-      <c r="L13" s="218" t="n"/>
-      <c r="M13" s="218" t="n"/>
+      <c r="L13" s="224" t="n"/>
+      <c r="M13" s="224" t="n"/>
       <c r="O13" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7096,9 +7096,9 @@
         </is>
       </c>
       <c r="S13" s="121" t="n"/>
-      <c r="U13" s="221" t="n"/>
-      <c r="V13" s="221" t="n"/>
-      <c r="W13" s="221" t="n"/>
+      <c r="U13" s="220" t="n"/>
+      <c r="V13" s="220" t="n"/>
+      <c r="W13" s="220" t="n"/>
     </row>
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="226" t="inlineStr">
@@ -7144,7 +7144,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J14" s="218" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -7172,7 +7172,7 @@
       <c r="W14" s="226" t="n"/>
     </row>
     <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="221" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>linked schemas</t>
         </is>
@@ -7182,7 +7182,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C15" s="221" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -7197,27 +7197,27 @@
           <t xml:space="preserve">This property SHOULD be used to indicate the model, schema, ontology, view or profile that this representation of a dataset conforms to, in a machine-readable form. This is (generally) a complementary concern to the media-type or format. Use a reference to the official publication of the respective schema. </t>
         </is>
       </c>
-      <c r="F15" s="220" t="inlineStr">
+      <c r="F15" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="220" t="inlineStr">
+      <c r="G15" s="218" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="220" t="inlineStr">
+      <c r="H15" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="218" t="inlineStr">
+      <c r="I15" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="218" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7227,8 +7227,8 @@
           <t>resource:conforms_to</t>
         </is>
       </c>
-      <c r="L15" s="218" t="n"/>
-      <c r="M15" s="218" t="n"/>
+      <c r="L15" s="224" t="n"/>
+      <c r="M15" s="224" t="n"/>
       <c r="O15" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7240,9 +7240,9 @@
         </is>
       </c>
       <c r="S15" s="121" t="n"/>
-      <c r="U15" s="221" t="n"/>
-      <c r="V15" s="221" t="n"/>
-      <c r="W15" s="221" t="n"/>
+      <c r="U15" s="220" t="n"/>
+      <c r="V15" s="220" t="n"/>
+      <c r="W15" s="220" t="n"/>
     </row>
     <row r="16" ht="112" customHeight="1">
       <c r="A16" s="226" t="inlineStr">
@@ -7292,7 +7292,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J16" s="218" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7320,7 +7320,7 @@
       <c r="W16" s="226" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="221" t="inlineStr">
+      <c r="A17" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -7341,27 +7341,27 @@
         </is>
       </c>
       <c r="E17" s="98" t="n"/>
-      <c r="F17" s="220" t="inlineStr">
+      <c r="F17" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="220" t="inlineStr">
+      <c r="G17" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="220" t="inlineStr">
+      <c r="H17" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="218" t="inlineStr">
+      <c r="I17" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="218" t="inlineStr">
+      <c r="J17" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7371,8 +7371,8 @@
           <t>resource:modified</t>
         </is>
       </c>
-      <c r="L17" s="218" t="n"/>
-      <c r="M17" s="218" t="n"/>
+      <c r="L17" s="224" t="n"/>
+      <c r="M17" s="224" t="n"/>
       <c r="N17" s="219" t="n"/>
       <c r="O17" s="219" t="inlineStr">
         <is>
@@ -7390,9 +7390,9 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="U17" s="221" t="n"/>
-      <c r="V17" s="221" t="n"/>
-      <c r="W17" s="221" t="n"/>
+      <c r="U17" s="220" t="n"/>
+      <c r="V17" s="220" t="n"/>
+      <c r="W17" s="220" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
       <c r="A18" s="226" t="inlineStr">
@@ -7440,7 +7440,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="218" t="inlineStr">
+      <c r="J18" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7468,7 +7468,7 @@
       <c r="W18" s="226" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="221" t="inlineStr">
+      <c r="A19" s="220" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -7478,7 +7478,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="221" t="inlineStr">
+      <c r="C19" s="220" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -7493,27 +7493,27 @@
           <t>The date the dataset distribution was issued.</t>
         </is>
       </c>
-      <c r="F19" s="220" t="inlineStr">
+      <c r="F19" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="220" t="inlineStr">
+      <c r="G19" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="220" t="inlineStr">
+      <c r="H19" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="218" t="inlineStr">
+      <c r="I19" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="218" t="inlineStr">
+      <c r="J19" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7523,8 +7523,8 @@
           <t>resource:issued</t>
         </is>
       </c>
-      <c r="L19" s="218" t="n"/>
-      <c r="M19" s="218" t="n"/>
+      <c r="L19" s="224" t="n"/>
+      <c r="M19" s="224" t="n"/>
       <c r="N19" s="219" t="n"/>
       <c r="O19" s="219" t="inlineStr">
         <is>
@@ -7542,9 +7542,9 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="U19" s="221" t="n"/>
-      <c r="V19" s="221" t="n"/>
-      <c r="W19" s="221" t="n"/>
+      <c r="U19" s="220" t="n"/>
+      <c r="V19" s="220" t="n"/>
+      <c r="W19" s="220" t="n"/>
     </row>
     <row r="20" ht="231" customHeight="1">
       <c r="A20" s="226" t="inlineStr">
@@ -7593,7 +7593,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="218" t="inlineStr">
+      <c r="J20" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -7630,7 +7630,7 @@
       <c r="W20" s="226" t="n"/>
     </row>
     <row r="21" ht="112" customHeight="1">
-      <c r="A21" s="221" t="inlineStr">
+      <c r="A21" s="220" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -7640,7 +7640,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C21" s="221" t="inlineStr">
+      <c r="C21" s="220" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -7661,7 +7661,7 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="220" t="inlineStr">
+      <c r="G21" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
@@ -7671,12 +7671,12 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I21" s="218" t="inlineStr">
+      <c r="I21" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J21" s="218" t="inlineStr">
+      <c r="J21" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7686,8 +7686,8 @@
           <t>resource:rights</t>
         </is>
       </c>
-      <c r="L21" s="218" t="n"/>
-      <c r="M21" s="218" t="n"/>
+      <c r="L21" s="224" t="n"/>
+      <c r="M21" s="224" t="n"/>
       <c r="O21" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7699,9 +7699,9 @@
         </is>
       </c>
       <c r="S21" s="121" t="n"/>
-      <c r="U21" s="221" t="n"/>
-      <c r="V21" s="221" t="n"/>
-      <c r="W21" s="221" t="n"/>
+      <c r="U21" s="220" t="n"/>
+      <c r="V21" s="220" t="n"/>
+      <c r="W21" s="220" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
       <c r="A22" s="226" t="inlineStr">
@@ -7750,7 +7750,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="218" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7778,7 +7778,7 @@
       <c r="W22" s="226" t="n"/>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="221" t="inlineStr">
+      <c r="A23" s="220" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
@@ -7788,7 +7788,7 @@
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
       </c>
-      <c r="C23" s="221" t="inlineStr">
+      <c r="C23" s="220" t="inlineStr">
         <is>
           <t>dcat:temporalResolution</t>
         </is>
@@ -7803,34 +7803,34 @@
           <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (for more information, see: https://www.w3schools.com/xml/schema_dtypes_date.asp).</t>
         </is>
       </c>
-      <c r="F23" s="220" t="inlineStr">
+      <c r="F23" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="220" t="inlineStr">
+      <c r="G23" s="218" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H23" s="220" t="inlineStr">
+      <c r="H23" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I23" s="218" t="inlineStr">
+      <c r="I23" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="218" t="inlineStr">
+      <c r="J23" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="74" t="n"/>
-      <c r="L23" s="218" t="n"/>
-      <c r="M23" s="218" t="n"/>
+      <c r="L23" s="224" t="n"/>
+      <c r="M23" s="224" t="n"/>
       <c r="O23" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7842,9 +7842,9 @@
         </is>
       </c>
       <c r="S23" s="121" t="n"/>
-      <c r="U23" s="221" t="n"/>
-      <c r="V23" s="221" t="n"/>
-      <c r="W23" s="221" t="n"/>
+      <c r="U23" s="220" t="n"/>
+      <c r="V23" s="220" t="n"/>
+      <c r="W23" s="220" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
       <c r="A24" s="226" t="inlineStr">
@@ -7892,7 +7892,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J24" s="218" t="inlineStr">
+      <c r="J24" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8452,11 +8452,11 @@
   <dimension ref="A1:U55"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="22.5" customWidth="1" style="222" min="1" max="1"/>
-    <col width="43.5" bestFit="1" customWidth="1" style="222" min="2" max="2"/>
-    <col width="26.5" customWidth="1" style="222" min="3" max="3"/>
+    <col width="22.5" customWidth="1" style="221" min="1" max="1"/>
+    <col width="43.5" bestFit="1" customWidth="1" style="221" min="2" max="2"/>
+    <col width="26.5" customWidth="1" style="221" min="3" max="3"/>
     <col width="24" customWidth="1" style="228" min="4" max="4"/>
-    <col width="76.5" customWidth="1" style="222" min="5" max="5"/>
+    <col width="76.5" customWidth="1" style="221" min="5" max="5"/>
     <col width="16.5" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
     <col width="20.1640625" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
     <col width="11.83203125" customWidth="1" style="219" min="8" max="8"/>
@@ -8466,8 +8466,8 @@
     <col width="24.6640625" customWidth="1" style="219" min="12" max="12"/>
     <col width="9.1640625" customWidth="1" style="219" min="13" max="18"/>
     <col width="22.5" customWidth="1" min="19" max="21"/>
-    <col width="9.1640625" customWidth="1" style="219" min="22" max="22"/>
-    <col width="9.1640625" customWidth="1" style="219" min="23" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="22" max="23"/>
+    <col width="9.1640625" customWidth="1" style="219" min="24" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customFormat="1" customHeight="1" s="163">
@@ -8603,7 +8603,7 @@
           <t>The legislation that mandates the creation or management of the Dataset Series.</t>
         </is>
       </c>
-      <c r="F2" s="220" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -8623,7 +8623,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="218" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8649,7 +8649,7 @@
       <c r="U2" s="155" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="221" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -8659,7 +8659,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C3" s="221" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -8675,7 +8675,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F3" s="220" t="inlineStr">
+      <c r="F3" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -8685,17 +8685,17 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H3" s="220" t="inlineStr">
+      <c r="H3" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="218" t="inlineStr">
+      <c r="I3" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="218" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8705,7 +8705,7 @@
           <t>data_series::contact</t>
         </is>
       </c>
-      <c r="L3" s="218" t="inlineStr">
+      <c r="L3" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -8725,9 +8725,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S3" s="221" t="n"/>
-      <c r="T3" s="221" t="n"/>
-      <c r="U3" s="221" t="n"/>
+      <c r="S3" s="220" t="n"/>
+      <c r="T3" s="220" t="n"/>
+      <c r="U3" s="220" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
       <c r="A4" s="226" t="inlineStr">
@@ -8775,7 +8775,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J4" s="218" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8804,7 +8804,7 @@
       <c r="U4" s="226" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="221" t="inlineStr">
+      <c r="A5" s="220" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -8814,7 +8814,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C5" s="221" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -8829,33 +8829,33 @@
           <t>The frequency of a dataset series is not equal to the frequency of the dataset in the collection.</t>
         </is>
       </c>
-      <c r="F5" s="220" t="inlineStr">
+      <c r="F5" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="220" t="inlineStr">
+      <c r="G5" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="220" t="inlineStr">
+      <c r="H5" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="218" t="inlineStr">
+      <c r="I5" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="218" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="74" t="n"/>
-      <c r="L5" s="218" t="n"/>
+      <c r="L5" s="224" t="n"/>
       <c r="N5" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -8866,9 +8866,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S5" s="221" t="n"/>
-      <c r="T5" s="221" t="n"/>
-      <c r="U5" s="221" t="n"/>
+      <c r="S5" s="220" t="n"/>
+      <c r="T5" s="220" t="n"/>
+      <c r="U5" s="220" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" s="226" t="inlineStr">
@@ -8916,7 +8916,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="218" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -8970,7 +8970,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="221" t="inlineStr">
+      <c r="A11" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -8980,7 +8980,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C11" s="221" t="inlineStr">
+      <c r="C11" s="220" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -8995,27 +8995,27 @@
           <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F11" s="220" t="inlineStr">
+      <c r="F11" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="220" t="inlineStr">
+      <c r="G11" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H11" s="220" t="inlineStr">
+      <c r="H11" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="218" t="inlineStr">
+      <c r="I11" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J11" s="218" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9025,7 +9025,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L11" s="218" t="n"/>
+      <c r="L11" s="224" t="n"/>
       <c r="N11" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9041,9 +9041,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S11" s="221" t="n"/>
-      <c r="T11" s="221" t="n"/>
-      <c r="U11" s="221" t="n"/>
+      <c r="S11" s="220" t="n"/>
+      <c r="T11" s="220" t="n"/>
+      <c r="U11" s="220" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
       <c r="A12" s="226" t="inlineStr">
@@ -9071,7 +9071,7 @@
           <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets. For example, a digital archive could take over the publishing of older datasets in the series. </t>
         </is>
       </c>
-      <c r="F12" s="220" t="inlineStr">
+      <c r="F12" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -9091,7 +9091,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J12" s="218" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9126,7 +9126,7 @@
       <c r="U12" s="226" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="221" t="inlineStr">
+      <c r="A13" s="220" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -9136,7 +9136,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="221" t="inlineStr">
+      <c r="C13" s="220" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -9156,22 +9156,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="220" t="inlineStr">
+      <c r="G13" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H13" s="220" t="inlineStr">
+      <c r="H13" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I13" s="220" t="inlineStr">
+      <c r="I13" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J13" s="218" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9181,7 +9181,7 @@
           <t>data_series:issued</t>
         </is>
       </c>
-      <c r="L13" s="218" t="n"/>
+      <c r="L13" s="224" t="n"/>
       <c r="N13" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9197,9 +9197,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S13" s="221" t="n"/>
-      <c r="T13" s="221" t="n"/>
-      <c r="U13" s="221" t="n"/>
+      <c r="S13" s="220" t="n"/>
+      <c r="T13" s="220" t="n"/>
+      <c r="U13" s="220" t="n"/>
     </row>
     <row r="14" ht="49" customHeight="1">
       <c r="A14" s="226" t="inlineStr">
@@ -9227,7 +9227,7 @@
           <t>When temporal coverage is a dimension in the dataset series, the temporal coverage of each dataset in the collection should be part of the series' temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
         </is>
       </c>
-      <c r="F14" s="220" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -9247,7 +9247,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="218" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9282,17 +9282,17 @@
       <c r="U14" s="226" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="221" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B15" s="221" t="inlineStr">
+      <c r="B15" s="220" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C15" s="221" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -9302,7 +9302,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="221" t="inlineStr">
+      <c r="E15" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide a unique title for your Dataset Series, which can be repeated in multiple languages. </t>
         </is>
@@ -9312,22 +9312,22 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G15" s="220" t="inlineStr">
+      <c r="G15" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H15" s="220" t="inlineStr">
+      <c r="H15" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I15" s="220" t="inlineStr">
+      <c r="I15" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J15" s="218" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9337,7 +9337,7 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L15" s="218" t="n"/>
+      <c r="L15" s="224" t="n"/>
       <c r="N15" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9351,9 +9351,9 @@
       <c r="R15" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="S15" s="221" t="n"/>
-      <c r="T15" s="221" t="n"/>
-      <c r="U15" s="221" t="n"/>
+      <c r="S15" s="220" t="n"/>
+      <c r="T15" s="220" t="n"/>
+      <c r="U15" s="220" t="n"/>
     </row>
     <row r="16">
       <c r="K16" s="219" t="n"/>
@@ -9479,16 +9479,16 @@
   <autoFilter ref="A1:L15"/>
   <mergeCells count="11">
     <mergeCell ref="K6:K10"/>
-    <mergeCell ref="A6:A10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="F6:F10"/>
     <mergeCell ref="C6:C10"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="G6:G10"/>
+    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="J6:J10"/>
     <mergeCell ref="E6:E10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="L6:L10"/>
+    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
@@ -9732,7 +9732,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="221" t="inlineStr">
+      <c r="C2" s="220" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -9747,30 +9747,30 @@
           <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property must take one of the predefined values listed in the Access Rights Named Authority List provided by the Publications Office. This designation informs data users whether the dataset is considered open data or is classified as non-public. For example, for non-public data, use the value: http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC</t>
         </is>
       </c>
-      <c r="F2" s="220" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="220" t="inlineStr">
+      <c r="G2" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="220" t="n">
+      <c r="H2" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="218" t="inlineStr">
+      <c r="I2" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="218" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K2" s="218" t="inlineStr">
+      <c r="K2" s="224" t="inlineStr">
         <is>
           <t>access_service:access_rights</t>
         </is>
@@ -9832,7 +9832,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="218" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9854,7 +9854,7 @@
       <c r="U3" s="226" t="n"/>
     </row>
     <row r="4" ht="92.25" customHeight="1">
-      <c r="A4" s="221" t="inlineStr">
+      <c r="A4" s="220" t="inlineStr">
         <is>
           <t>application profile</t>
         </is>
@@ -9864,7 +9864,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C4" s="221" t="inlineStr">
+      <c r="C4" s="220" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -9879,33 +9879,33 @@
           <t>The standards referred to here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance, the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
         </is>
       </c>
-      <c r="F4" s="220" t="inlineStr">
+      <c r="F4" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="220" t="inlineStr">
+      <c r="G4" s="218" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="220" t="inlineStr">
+      <c r="H4" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="218" t="inlineStr">
+      <c r="I4" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="218" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K4" s="218" t="n"/>
-      <c r="L4" s="218" t="n"/>
+      <c r="K4" s="224" t="n"/>
+      <c r="L4" s="224" t="n"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9916,9 +9916,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S4" s="221" t="n"/>
-      <c r="T4" s="221" t="n"/>
-      <c r="U4" s="221" t="n"/>
+      <c r="S4" s="220" t="n"/>
+      <c r="T4" s="220" t="n"/>
+      <c r="U4" s="220" t="n"/>
     </row>
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="155" t="inlineStr">
@@ -9965,7 +9965,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="218" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -9996,7 +9996,7 @@
       <c r="U5" s="155" t="n"/>
     </row>
     <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="221" t="inlineStr">
+      <c r="A6" s="220" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
@@ -10006,7 +10006,7 @@
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C6" s="221" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -10023,7 +10023,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="220" t="inlineStr">
+      <c r="F6" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -10033,23 +10033,23 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H6" s="220" t="inlineStr">
+      <c r="H6" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="218" t="inlineStr">
+      <c r="I6" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="218" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K6" s="75" t="n"/>
-      <c r="L6" s="218" t="inlineStr">
+      <c r="L6" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -10069,9 +10069,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S6" s="221" t="n"/>
-      <c r="T6" s="221" t="n"/>
-      <c r="U6" s="221" t="n"/>
+      <c r="S6" s="220" t="n"/>
+      <c r="T6" s="220" t="n"/>
+      <c r="U6" s="220" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="226" t="inlineStr">
@@ -10115,12 +10115,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="218" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K7" s="218" t="n"/>
+      <c r="K7" s="224" t="n"/>
       <c r="L7" s="225" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="221" t="inlineStr">
+      <c r="C8" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -10162,43 +10162,43 @@
           <t>Briefly describe the data service provided. You can repeat this description in multiple languages. Example: A data service that provides API access to real-time electrocardiogram (ECG) monitoring data for clinical research applications.</t>
         </is>
       </c>
-      <c r="F8" s="220" t="inlineStr">
+      <c r="F8" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G8" s="220" t="inlineStr">
+      <c r="G8" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H8" s="220" t="inlineStr">
+      <c r="H8" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I8" s="218" t="inlineStr">
+      <c r="I8" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="218" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K8" s="218" t="inlineStr">
+      <c r="K8" s="224" t="inlineStr">
         <is>
           <t>access_service:description</t>
         </is>
       </c>
-      <c r="L8" s="218" t="n"/>
-      <c r="N8" s="218" t="inlineStr">
+      <c r="L8" s="224" t="n"/>
+      <c r="N8" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O8" s="218" t="inlineStr">
+      <c r="O8" s="224" t="inlineStr">
         <is>
           <t>dash:TextAreaEditor</t>
         </is>
@@ -10254,7 +10254,7 @@
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="218" t="inlineStr">
+      <c r="J9" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10280,7 +10280,7 @@
       <c r="U9" s="226" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="221" t="inlineStr">
+      <c r="A10" s="220" t="inlineStr">
         <is>
           <t>endpoint URL</t>
         </is>
@@ -10290,7 +10290,7 @@
           <t>The root location or primary endpoint of the service (a Web-resolvable IRI).</t>
         </is>
       </c>
-      <c r="C10" s="221" t="inlineStr">
+      <c r="C10" s="220" t="inlineStr">
         <is>
           <t>dcat:endpointURL</t>
         </is>
@@ -10305,12 +10305,12 @@
           <t>Provide the URL of the endpoint that users can interact with to access the data service. This should be a direct link to the service's endpoint, such as an API URL, SPARQL endpoint, or similar.</t>
         </is>
       </c>
-      <c r="F10" s="220" t="inlineStr">
+      <c r="F10" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G10" s="220" t="inlineStr">
+      <c r="G10" s="218" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -10318,12 +10318,12 @@
       <c r="H10" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="218" t="inlineStr">
+      <c r="I10" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="218" t="inlineStr">
+      <c r="J10" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10333,7 +10333,7 @@
           <t>access_service:endpoint_url</t>
         </is>
       </c>
-      <c r="L10" s="218" t="n"/>
+      <c r="L10" s="224" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10344,9 +10344,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S10" s="221" t="n"/>
-      <c r="T10" s="221" t="n"/>
-      <c r="U10" s="221" t="n"/>
+      <c r="S10" s="220" t="n"/>
+      <c r="T10" s="220" t="n"/>
+      <c r="U10" s="220" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="226" t="inlineStr">
@@ -10390,12 +10390,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J11" s="218" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K11" s="218" t="n"/>
+      <c r="K11" s="224" t="n"/>
       <c r="L11" s="225" t="n"/>
       <c r="N11" s="69" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
       <c r="U11" s="226" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="221" t="inlineStr">
+      <c r="A12" s="220" t="inlineStr">
         <is>
           <t>HVD Category</t>
         </is>
@@ -10422,7 +10422,7 @@
           <t>A data category defined in the High Value Dataset Implementing Regulation.</t>
         </is>
       </c>
-      <c r="C12" s="221" t="inlineStr">
+      <c r="C12" s="220" t="inlineStr">
         <is>
           <t>dcatap:hvdCategory</t>
         </is>
@@ -10433,33 +10433,33 @@
         </is>
       </c>
       <c r="E12" s="98" t="n"/>
-      <c r="F12" s="220" t="inlineStr">
+      <c r="F12" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="220" t="inlineStr">
+      <c r="G12" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="220" t="inlineStr">
+      <c r="H12" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I12" s="218" t="inlineStr">
+      <c r="I12" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="218" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K12" s="75" t="n"/>
-      <c r="L12" s="218" t="n"/>
+      <c r="L12" s="224" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10470,9 +10470,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S12" s="221" t="n"/>
-      <c r="T12" s="221" t="n"/>
-      <c r="U12" s="221" t="n"/>
+      <c r="S12" s="220" t="n"/>
+      <c r="T12" s="220" t="n"/>
+      <c r="U12" s="220" t="n"/>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="155" t="inlineStr">
@@ -10518,19 +10518,19 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="218" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K13" s="75" t="n"/>
       <c r="L13" s="225" t="n"/>
-      <c r="N13" s="218" t="inlineStr">
+      <c r="N13" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O13" s="218" t="inlineStr">
+      <c r="O13" s="224" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -10540,7 +10540,7 @@
       <c r="U13" s="155" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="221" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -10550,7 +10550,7 @@
           <t>A keyword or tag describing the resource.</t>
         </is>
       </c>
-      <c r="C14" s="221" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>dcat:keyword</t>
         </is>
@@ -10561,46 +10561,46 @@
         </is>
       </c>
       <c r="E14" s="29" t="n"/>
-      <c r="F14" s="220" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="220" t="inlineStr">
+      <c r="G14" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H14" s="220" t="inlineStr">
+      <c r="H14" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="218" t="inlineStr">
+      <c r="I14" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="218" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="75" t="n"/>
-      <c r="L14" s="218" t="n"/>
-      <c r="N14" s="218" t="inlineStr">
+      <c r="L14" s="224" t="n"/>
+      <c r="N14" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O14" s="218" t="inlineStr">
+      <c r="O14" s="224" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="S14" s="221" t="n"/>
-      <c r="T14" s="221" t="n"/>
-      <c r="U14" s="221" t="n"/>
+      <c r="S14" s="220" t="n"/>
+      <c r="T14" s="220" t="n"/>
+      <c r="U14" s="220" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="226" t="inlineStr">
@@ -10648,7 +10648,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="218" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -10670,7 +10670,7 @@
       <c r="U15" s="226" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="221" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -10680,7 +10680,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C16" s="221" t="inlineStr">
+      <c r="C16" s="220" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -10695,33 +10695,33 @@
           <t>Indicates the natural language used in the data service, indicated with a value from the EU controlled vocabulary.</t>
         </is>
       </c>
-      <c r="F16" s="220" t="inlineStr">
+      <c r="F16" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="220" t="inlineStr">
+      <c r="G16" s="218" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="220" t="inlineStr">
+      <c r="H16" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I16" s="218" t="inlineStr">
+      <c r="I16" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="218" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K16" s="75" t="n"/>
-      <c r="L16" s="218" t="n"/>
+      <c r="L16" s="224" t="n"/>
       <c r="N16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -10732,9 +10732,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S16" s="221" t="n"/>
-      <c r="T16" s="221" t="n"/>
-      <c r="U16" s="221" t="n"/>
+      <c r="S16" s="220" t="n"/>
+      <c r="T16" s="220" t="n"/>
+      <c r="U16" s="220" t="n"/>
     </row>
     <row r="17" ht="64" customHeight="1">
       <c r="A17" s="226" t="inlineStr">
@@ -10780,12 +10780,12 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="218" t="inlineStr">
+      <c r="J17" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K17" s="218" t="inlineStr">
+      <c r="K17" s="224" t="inlineStr">
         <is>
           <t>access_service:license</t>
         </is>
@@ -10806,7 +10806,7 @@
       <c r="U17" s="226" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="221" t="inlineStr">
+      <c r="A18" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -10816,7 +10816,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C18" s="221" t="inlineStr">
+      <c r="C18" s="220" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -10831,33 +10831,33 @@
           <t>This property indicates the date of the last changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F18" s="220" t="inlineStr">
+      <c r="F18" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="220" t="inlineStr">
+      <c r="G18" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H18" s="220" t="inlineStr">
+      <c r="H18" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="218" t="inlineStr">
+      <c r="I18" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="218" t="inlineStr">
+      <c r="J18" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K18" s="75" t="n"/>
-      <c r="L18" s="218" t="n"/>
+      <c r="L18" s="224" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -10873,9 +10873,9 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S18" s="221" t="n"/>
-      <c r="T18" s="221" t="n"/>
-      <c r="U18" s="221" t="n"/>
+      <c r="S18" s="220" t="n"/>
+      <c r="T18" s="220" t="n"/>
+      <c r="U18" s="220" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="226" t="inlineStr">
@@ -10919,7 +10919,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="218" t="inlineStr">
+      <c r="J19" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10950,7 +10950,7 @@
       <c r="U19" s="226" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="221" t="inlineStr">
+      <c r="A20" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -10960,7 +10960,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C20" s="221" t="inlineStr">
+      <c r="C20" s="220" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -10975,7 +10975,7 @@
           <t>The organisation or individual responsible for making the data service available. In the context of data services, the publisher is typically the organisation that manages or provides access to the service. For details, see the class Agent.</t>
         </is>
       </c>
-      <c r="F20" s="220" t="inlineStr">
+      <c r="F20" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -10985,21 +10985,21 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H20" s="220" t="n">
+      <c r="H20" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="218" t="inlineStr">
+      <c r="I20" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="218" t="inlineStr">
+      <c r="J20" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K20" s="218" t="n"/>
-      <c r="L20" s="218" t="inlineStr">
+      <c r="K20" s="224" t="n"/>
+      <c r="L20" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -11019,9 +11019,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S20" s="221" t="n"/>
-      <c r="T20" s="221" t="n"/>
-      <c r="U20" s="221" t="n"/>
+      <c r="S20" s="220" t="n"/>
+      <c r="T20" s="220" t="n"/>
+      <c r="U20" s="220" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
       <c r="A21" s="226" t="inlineStr">
@@ -11069,12 +11069,12 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="218" t="inlineStr">
+      <c r="J21" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="218" t="inlineStr">
+      <c r="K21" s="224" t="inlineStr">
         <is>
           <t>access_service:serves_dataset</t>
         </is>
@@ -11104,7 +11104,7 @@
       <c r="U21" s="226" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="221" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -11114,7 +11114,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C22" s="221" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -11129,33 +11129,33 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, most data services will use NAL:data-theme 'HEAL', but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F22" s="220" t="inlineStr">
+      <c r="F22" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G22" s="220" t="inlineStr">
+      <c r="G22" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="220" t="inlineStr">
+      <c r="H22" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I22" s="218" t="inlineStr">
+      <c r="I22" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="218" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K22" s="75" t="n"/>
-      <c r="L22" s="218" t="n"/>
+      <c r="L22" s="224" t="n"/>
       <c r="N22" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -11171,9 +11171,9 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="S22" s="221" t="n"/>
-      <c r="T22" s="221" t="n"/>
-      <c r="U22" s="221" t="n"/>
+      <c r="S22" s="220" t="n"/>
+      <c r="T22" s="220" t="n"/>
+      <c r="U22" s="220" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="226" t="inlineStr">
@@ -11221,7 +11221,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J23" s="218" t="inlineStr">
+      <c r="J23" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -11232,12 +11232,12 @@
         </is>
       </c>
       <c r="L23" s="159" t="n"/>
-      <c r="N23" s="218" t="inlineStr">
+      <c r="N23" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O23" s="218" t="inlineStr">
+      <c r="O23" s="224" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -12197,8 +12197,8 @@
     <col width="32.1640625" customWidth="1" style="234" min="18" max="18"/>
     <col width="9.1640625" customWidth="1" style="234" min="19" max="24"/>
     <col width="24.5" customWidth="1" min="25" max="27"/>
-    <col width="9.1640625" customWidth="1" style="234" min="28" max="28"/>
-    <col width="9.1640625" customWidth="1" style="234" min="29" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="29"/>
+    <col width="9.1640625" customWidth="1" style="234" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="112" customHeight="1">
@@ -13239,8 +13239,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="24"/>
-    <col width="9.1640625" customWidth="1" style="234" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
+    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -13827,8 +13827,8 @@
     <col width="28.83203125" customWidth="1" style="58" min="15" max="15"/>
     <col width="9.1640625" customWidth="1" style="58" min="16" max="21"/>
     <col width="20.1640625" customWidth="1" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="58" min="25" max="25"/>
-    <col width="9.1640625" customWidth="1" style="58" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="58" min="25" max="26"/>
+    <col width="9.1640625" customWidth="1" style="58" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="80" customHeight="1">
@@ -15119,8 +15119,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="24"/>
-    <col width="9.1640625" customWidth="1" style="234" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
+    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -16129,8 +16129,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="24"/>
-    <col width="9.1640625" customWidth="1" style="234" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
+    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -17135,8 +17135,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="24"/>
-    <col width="9.1640625" customWidth="1" style="234" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
+    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -18259,8 +18259,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="24"/>
-    <col width="9.1640625" customWidth="1" style="234" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
+    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -20393,11 +20393,11 @@
   <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="20" bestFit="1" customWidth="1" style="222" min="1" max="1"/>
-    <col width="40.5" customWidth="1" style="222" min="2" max="2"/>
-    <col width="25.5" bestFit="1" customWidth="1" style="222" min="3" max="3"/>
+    <col width="20" bestFit="1" customWidth="1" style="221" min="1" max="1"/>
+    <col width="40.5" customWidth="1" style="221" min="2" max="2"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="221" min="3" max="3"/>
     <col width="25.5" customWidth="1" style="228" min="4" max="4"/>
-    <col width="54.5" customWidth="1" style="222" min="5" max="5"/>
+    <col width="54.5" customWidth="1" style="221" min="5" max="5"/>
     <col width="22.1640625" customWidth="1" style="219" min="6" max="6"/>
     <col width="24" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
     <col width="10.5" bestFit="1" customWidth="1" style="219" min="8" max="8"/>
@@ -20408,8 +20408,8 @@
     <col width="27" customWidth="1" style="219" min="13" max="13"/>
     <col width="9.1640625" customWidth="1" style="219" min="14" max="19"/>
     <col width="20" customWidth="1" min="20" max="22"/>
-    <col width="9.1640625" customWidth="1" style="219" min="23" max="23"/>
-    <col width="9.1640625" customWidth="1" style="219" min="24" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="23" max="24"/>
+    <col width="9.1640625" customWidth="1" style="219" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="64" customFormat="1" customHeight="1" s="163">
@@ -20546,12 +20546,12 @@
         </is>
       </c>
       <c r="E2" s="98" t="n"/>
-      <c r="F2" s="220" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="220" t="inlineStr">
+      <c r="G2" s="218" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -20561,12 +20561,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I2" s="218" t="inlineStr">
+      <c r="I2" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="218" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -20576,8 +20576,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="218" t="n"/>
-      <c r="M2" s="218" t="n"/>
+      <c r="L2" s="224" t="n"/>
+      <c r="M2" s="224" t="n"/>
       <c r="O2" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20639,7 +20639,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J3" s="218" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20682,7 +20682,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C4" s="221" t="inlineStr">
+      <c r="C4" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -20698,7 +20698,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F4" s="220" t="inlineStr">
+      <c r="F4" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20708,30 +20708,30 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H4" s="220" t="n">
+      <c r="H4" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="218" t="inlineStr">
+      <c r="I4" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="218" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K4" s="218" t="inlineStr">
+      <c r="K4" s="224" t="inlineStr">
         <is>
           <t>custom:contact</t>
         </is>
       </c>
-      <c r="L4" s="218" t="inlineStr">
+      <c r="L4" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M4" s="218" t="inlineStr">
+      <c r="M4" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -20804,7 +20804,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="218" t="n"/>
+      <c r="J5" s="224" t="n"/>
       <c r="K5" s="232" t="inlineStr">
         <is>
           <t>custom:creator</t>
@@ -20841,7 +20841,7 @@
       <c r="V5" s="226" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="221" t="inlineStr">
+      <c r="A6" s="220" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
@@ -20851,7 +20851,7 @@
           <t>A dataset that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C6" s="221" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dcat:dataset</t>
         </is>
@@ -20866,7 +20866,7 @@
           <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="220" t="inlineStr">
+      <c r="F6" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20881,12 +20881,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="218" t="inlineStr">
+      <c r="I6" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J6" s="218" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20897,7 +20897,7 @@
           <t>Enter the URI for all datasets contained in this catalogue.</t>
         </is>
       </c>
-      <c r="M6" s="218" t="n"/>
+      <c r="M6" s="224" t="n"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -20914,9 +20914,9 @@
         </is>
       </c>
       <c r="S6" s="69" t="n"/>
-      <c r="T6" s="221" t="n"/>
-      <c r="U6" s="221" t="n"/>
-      <c r="V6" s="221" t="n"/>
+      <c r="T6" s="220" t="n"/>
+      <c r="U6" s="220" t="n"/>
+      <c r="V6" s="220" t="n"/>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="226" t="inlineStr">
@@ -20964,7 +20964,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J7" s="218" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20994,17 +20994,17 @@
       <c r="V7" s="226" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1">
-      <c r="A8" s="221" t="inlineStr">
+      <c r="A8" s="220" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B8" s="223" t="inlineStr">
+      <c r="B8" s="222" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="221" t="inlineStr">
+      <c r="C8" s="220" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -21014,39 +21014,39 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E8" s="224" t="inlineStr">
+      <c r="E8" s="223" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used.</t>
         </is>
       </c>
-      <c r="F8" s="220" t="inlineStr">
+      <c r="F8" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="220" t="inlineStr">
+      <c r="G8" s="218" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="220" t="inlineStr">
+      <c r="H8" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="218" t="inlineStr">
+      <c r="I8" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="218" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K8" s="103" t="n"/>
-      <c r="L8" s="218" t="n"/>
-      <c r="M8" s="218" t="n"/>
+      <c r="L8" s="224" t="n"/>
+      <c r="M8" s="224" t="n"/>
       <c r="O8" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21058,9 +21058,9 @@
         </is>
       </c>
       <c r="S8" s="69" t="n"/>
-      <c r="T8" s="221" t="n"/>
-      <c r="U8" s="221" t="n"/>
-      <c r="V8" s="221" t="n"/>
+      <c r="T8" s="220" t="n"/>
+      <c r="U8" s="220" t="n"/>
+      <c r="V8" s="220" t="n"/>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="D9" s="177" t="inlineStr">
@@ -21145,7 +21145,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="218" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21178,7 +21178,7 @@
       <c r="V13" s="226" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="221" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>home page</t>
         </is>
@@ -21188,7 +21188,7 @@
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C14" s="221" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>foaf:homepage</t>
         </is>
@@ -21203,34 +21203,34 @@
           <t>The home page of the catalogue, if available.</t>
         </is>
       </c>
-      <c r="F14" s="220" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="220" t="inlineStr">
+      <c r="G14" s="218" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="220" t="inlineStr">
+      <c r="H14" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I14" s="218" t="inlineStr">
+      <c r="I14" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="218" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="103" t="n"/>
-      <c r="L14" s="218" t="n"/>
-      <c r="M14" s="218" t="n"/>
+      <c r="L14" s="224" t="n"/>
+      <c r="M14" s="224" t="n"/>
       <c r="O14" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21242,9 +21242,9 @@
         </is>
       </c>
       <c r="S14" s="69" t="n"/>
-      <c r="T14" s="221" t="n"/>
-      <c r="U14" s="221" t="n"/>
-      <c r="V14" s="221" t="n"/>
+      <c r="T14" s="220" t="n"/>
+      <c r="U14" s="220" t="n"/>
+      <c r="V14" s="220" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
       <c r="A15" s="226" t="inlineStr">
@@ -21293,7 +21293,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="218" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21321,7 +21321,7 @@
       <c r="V15" s="226" t="n"/>
     </row>
     <row r="16" ht="85.25" customHeight="1">
-      <c r="A16" s="221" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
@@ -21347,27 +21347,27 @@
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
         </is>
       </c>
-      <c r="F16" s="220" t="inlineStr">
+      <c r="F16" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="220" t="inlineStr">
+      <c r="G16" s="218" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="220" t="inlineStr">
+      <c r="H16" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="218" t="inlineStr">
+      <c r="I16" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="218" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21377,8 +21377,8 @@
           <t>custom:licence</t>
         </is>
       </c>
-      <c r="L16" s="218" t="n"/>
-      <c r="M16" s="218" t="n"/>
+      <c r="L16" s="224" t="n"/>
+      <c r="M16" s="224" t="n"/>
       <c r="O16" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21390,9 +21390,9 @@
         </is>
       </c>
       <c r="S16" s="69" t="n"/>
-      <c r="T16" s="221" t="n"/>
-      <c r="U16" s="221" t="n"/>
-      <c r="V16" s="221" t="n"/>
+      <c r="T16" s="220" t="n"/>
+      <c r="U16" s="220" t="n"/>
+      <c r="V16" s="220" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
       <c r="A17" s="226" t="inlineStr">
@@ -21436,7 +21436,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="218" t="inlineStr">
+      <c r="J17" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21469,7 +21469,7 @@
       <c r="V17" s="226" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="221" t="inlineStr">
+      <c r="A18" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -21494,7 +21494,7 @@
           <t>The organisation or individual that is the holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
         </is>
       </c>
-      <c r="F18" s="220" t="inlineStr">
+      <c r="F18" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -21504,15 +21504,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H18" s="220" t="n">
+      <c r="H18" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="218" t="inlineStr">
+      <c r="I18" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J18" s="218" t="inlineStr">
+      <c r="J18" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21522,12 +21522,12 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L18" s="218" t="inlineStr">
+      <c r="L18" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M18" s="218" t="inlineStr">
+      <c r="M18" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -21548,9 +21548,9 @@
         </is>
       </c>
       <c r="S18" s="69" t="n"/>
-      <c r="T18" s="221" t="n"/>
-      <c r="U18" s="221" t="n"/>
-      <c r="V18" s="221" t="n"/>
+      <c r="T18" s="220" t="n"/>
+      <c r="U18" s="220" t="n"/>
+      <c r="V18" s="220" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
       <c r="A19" s="226" t="inlineStr">
@@ -21627,7 +21627,7 @@
       <c r="V19" s="226" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="221" t="inlineStr">
+      <c r="A20" s="220" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -21637,7 +21637,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C20" s="221" t="inlineStr">
+      <c r="C20" s="220" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -21652,34 +21652,34 @@
           <t>The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
         </is>
       </c>
-      <c r="F20" s="220" t="inlineStr">
+      <c r="F20" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G20" s="220" t="inlineStr">
+      <c r="G20" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H20" s="220" t="inlineStr">
+      <c r="H20" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="218" t="inlineStr">
+      <c r="I20" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="218" t="inlineStr">
+      <c r="J20" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K20" s="75" t="n"/>
-      <c r="L20" s="218" t="n"/>
-      <c r="M20" s="218" t="n"/>
+      <c r="L20" s="224" t="n"/>
+      <c r="M20" s="224" t="n"/>
       <c r="O20" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21691,9 +21691,9 @@
         </is>
       </c>
       <c r="S20" s="69" t="n"/>
-      <c r="T20" s="221" t="n"/>
-      <c r="U20" s="221" t="n"/>
-      <c r="V20" s="221" t="n"/>
+      <c r="T20" s="220" t="n"/>
+      <c r="U20" s="220" t="n"/>
+      <c r="V20" s="220" t="n"/>
     </row>
     <row r="21" ht="64" customHeight="1">
       <c r="A21" s="226" t="inlineStr">
@@ -21774,7 +21774,7 @@
       <c r="V21" s="226" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="221" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -21784,7 +21784,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C22" s="221" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="E22" s="29" t="n"/>
-      <c r="F22" s="220" t="inlineStr">
+      <c r="F22" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21805,17 +21805,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H22" s="220" t="inlineStr">
+      <c r="H22" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="218" t="inlineStr">
+      <c r="I22" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="218" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21825,8 +21825,8 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L22" s="218" t="n"/>
-      <c r="M22" s="218" t="n"/>
+      <c r="L22" s="224" t="n"/>
+      <c r="M22" s="224" t="n"/>
       <c r="N22" s="219" t="inlineStr">
         <is>
           <t>hrishapes:PeriodOfTimeShape</t>
@@ -21843,9 +21843,9 @@
         </is>
       </c>
       <c r="S22" s="69" t="n"/>
-      <c r="T22" s="221" t="n"/>
-      <c r="U22" s="221" t="n"/>
-      <c r="V22" s="221" t="n"/>
+      <c r="T22" s="220" t="n"/>
+      <c r="U22" s="220" t="n"/>
+      <c r="V22" s="220" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
       <c r="A23" s="226" t="inlineStr">
@@ -21917,7 +21917,7 @@
       <c r="V23" s="226" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="221" t="inlineStr">
+      <c r="A24" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -21927,7 +21927,7 @@
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="221" t="inlineStr">
+      <c r="C24" s="220" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -21942,27 +21942,27 @@
           <t>Provide a unique title for your catalogue, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
         </is>
       </c>
-      <c r="F24" s="220" t="inlineStr">
+      <c r="F24" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G24" s="220" t="inlineStr">
+      <c r="G24" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="220" t="inlineStr">
+      <c r="H24" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I24" s="218" t="inlineStr">
+      <c r="I24" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J24" s="218" t="inlineStr">
+      <c r="J24" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21972,8 +21972,8 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L24" s="218" t="n"/>
-      <c r="M24" s="218" t="n"/>
+      <c r="L24" s="224" t="n"/>
+      <c r="M24" s="224" t="n"/>
       <c r="O24" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21987,22 +21987,22 @@
       <c r="S24" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="221" t="n"/>
-      <c r="U24" s="221" t="n"/>
-      <c r="V24" s="221" t="n"/>
+      <c r="T24" s="220" t="n"/>
+      <c r="U24" s="220" t="n"/>
+      <c r="V24" s="220" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J24"/>
   <mergeCells count="11">
     <mergeCell ref="H8:H12"/>
+    <mergeCell ref="B8:B12"/>
     <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="I8:I12"/>
     <mergeCell ref="G8:G12"/>
+    <mergeCell ref="L8:L12"/>
     <mergeCell ref="F8:F12"/>
-    <mergeCell ref="L8:L12"/>
     <mergeCell ref="J8:J12"/>
     <mergeCell ref="M8:M12"/>
   </mergeCells>
@@ -22139,9 +22139,9 @@
   <dimension ref="A1:AZ61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15"/>
   <cols>
-    <col width="25.5" bestFit="1" customWidth="1" style="222" min="1" max="1"/>
-    <col width="40.5" customWidth="1" style="222" min="2" max="2"/>
-    <col width="28.83203125" customWidth="1" style="222" min="3" max="3"/>
+    <col width="25.5" bestFit="1" customWidth="1" style="221" min="1" max="1"/>
+    <col width="40.5" customWidth="1" style="221" min="2" max="2"/>
+    <col width="28.83203125" customWidth="1" style="221" min="3" max="3"/>
     <col width="22.5" customWidth="1" style="228" min="4" max="4"/>
     <col width="68.83203125" customWidth="1" style="228" min="5" max="5"/>
     <col width="18.5" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
@@ -22156,8 +22156,8 @@
     <col width="25.83203125" customWidth="1" style="219" min="15" max="15"/>
     <col width="9.1640625" customWidth="1" style="219" min="16" max="21"/>
     <col width="25.5" customWidth="1" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="219" min="25" max="25"/>
-    <col width="9.1640625" customWidth="1" style="219" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="25" max="26"/>
+    <col width="9.1640625" customWidth="1" style="219" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customFormat="1" customHeight="1" s="163">
@@ -22293,7 +22293,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="221" t="inlineStr">
+      <c r="C2" s="220" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -22312,25 +22312,25 @@
 Since most data contain personal information, these datasets will need to take the value 'non-public' for the access rights property.</t>
         </is>
       </c>
-      <c r="F2" s="220" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="220" t="inlineStr">
+      <c r="G2" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="220" t="n">
+      <c r="H2" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="218" t="inlineStr">
+      <c r="I2" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="218" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -22340,7 +22340,7 @@
           <t>custom:access_rights</t>
         </is>
       </c>
-      <c r="L2" s="218" t="n"/>
+      <c r="L2" s="224" t="n"/>
       <c r="P2" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22381,7 +22381,7 @@
           <t>This property contains an alternative name for the Dataset. This property can be repeated for parallel language versions of the alternative name.</t>
         </is>
       </c>
-      <c r="F3" s="220" t="inlineStr">
+      <c r="F3" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22401,7 +22401,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="218" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22460,17 +22460,17 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H4" s="220" t="inlineStr">
+      <c r="H4" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="218" t="inlineStr">
+      <c r="I4" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="218" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22480,7 +22480,7 @@
           <t>custom:analytics</t>
         </is>
       </c>
-      <c r="L4" s="218" t="inlineStr">
+      <c r="L4" s="224" t="inlineStr">
         <is>
           <t>If available, add the URI for the analytics distribution here.</t>
         </is>
@@ -22552,7 +22552,7 @@
         </is>
       </c>
       <c r="I5" s="225" t="n"/>
-      <c r="J5" s="218" t="n"/>
+      <c r="J5" s="224" t="n"/>
       <c r="K5" s="232" t="n"/>
       <c r="L5" s="100" t="n"/>
       <c r="M5" s="225" t="n"/>
@@ -22587,7 +22587,7 @@
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C6" s="221" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -22605,12 +22605,12 @@
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) describes the legal basis for initial collection and processing of (personal) data.</t>
         </is>
       </c>
-      <c r="F6" s="220" t="inlineStr">
+      <c r="F6" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G6" s="220" t="inlineStr">
+      <c r="G6" s="218" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -22620,12 +22620,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="218" t="inlineStr">
+      <c r="I6" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="218" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22635,7 +22635,7 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L6" s="218" t="n"/>
+      <c r="L6" s="224" t="n"/>
       <c r="P6" s="83" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22702,7 +22702,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="218" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22730,7 +22730,7 @@
       <c r="X7" s="226" t="n"/>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="221" t="inlineStr">
+      <c r="A8" s="220" t="inlineStr">
         <is>
           <t>coding system</t>
         </is>
@@ -22740,7 +22740,7 @@
           <t>Coding systems in use (e.g. ICD-10-CM, DGRs, SNOMED CT, ...)</t>
         </is>
       </c>
-      <c r="C8" s="221" t="inlineStr">
+      <c r="C8" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:hasCodingSystem</t>
         </is>
@@ -22756,27 +22756,27 @@
 This property provides information on which coding systems are in use in your dataset. For this, Wikidata URIs must be used.</t>
         </is>
       </c>
-      <c r="F8" s="220" t="inlineStr">
+      <c r="F8" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="220" t="inlineStr">
+      <c r="G8" s="218" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="220" t="inlineStr">
+      <c r="H8" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="218" t="inlineStr">
+      <c r="I8" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="218" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22786,7 +22786,7 @@
           <t>custom:coding_system</t>
         </is>
       </c>
-      <c r="L8" s="218" t="n"/>
+      <c r="L8" s="224" t="n"/>
       <c r="P8" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22797,9 +22797,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V8" s="221" t="n"/>
-      <c r="W8" s="221" t="n"/>
-      <c r="X8" s="221" t="n"/>
+      <c r="V8" s="220" t="n"/>
+      <c r="W8" s="220" t="n"/>
+      <c r="X8" s="220" t="n"/>
     </row>
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="226" t="inlineStr">
@@ -22848,7 +22848,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J9" s="218" t="inlineStr">
+      <c r="J9" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22876,7 +22876,7 @@
       <c r="X9" s="226" t="n"/>
     </row>
     <row r="10" ht="123.75" customHeight="1">
-      <c r="A10" s="221" t="inlineStr">
+      <c r="A10" s="220" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -22886,7 +22886,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C10" s="221" t="inlineStr">
+      <c r="C10" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -22902,7 +22902,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F10" s="220" t="inlineStr">
+      <c r="F10" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -22912,15 +22912,15 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H10" s="220" t="n">
+      <c r="H10" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="218" t="inlineStr">
+      <c r="I10" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="218" t="inlineStr">
+      <c r="J10" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -22930,17 +22930,17 @@
           <t>custom:contact_</t>
         </is>
       </c>
-      <c r="L10" s="218" t="inlineStr">
+      <c r="L10" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M10" s="218" t="inlineStr">
+      <c r="M10" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="N10" s="218" t="inlineStr">
+      <c r="N10" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -22960,9 +22960,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V10" s="221" t="n"/>
-      <c r="W10" s="221" t="n"/>
-      <c r="X10" s="221" t="n"/>
+      <c r="V10" s="220" t="n"/>
+      <c r="W10" s="220" t="n"/>
+      <c r="X10" s="220" t="n"/>
     </row>
     <row r="11" ht="176" customHeight="1">
       <c r="A11" s="226" t="inlineStr">
@@ -23012,7 +23012,7 @@
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="218" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -23057,7 +23057,7 @@
       <c r="X11" s="226" t="n"/>
     </row>
     <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="221" t="inlineStr">
+      <c r="A12" s="220" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -23067,7 +23067,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="221" t="inlineStr">
+      <c r="C12" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -23082,27 +23082,27 @@
           <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ‘Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.’</t>
         </is>
       </c>
-      <c r="F12" s="220" t="inlineStr">
+      <c r="F12" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G12" s="220" t="inlineStr">
+      <c r="G12" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H12" s="220" t="inlineStr">
+      <c r="H12" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I12" s="218" t="inlineStr">
+      <c r="I12" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J12" s="218" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23112,7 +23112,7 @@
           <t>notes</t>
         </is>
       </c>
-      <c r="L12" s="218" t="n"/>
+      <c r="L12" s="224" t="n"/>
       <c r="P12" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23126,9 +23126,9 @@
       <c r="T12" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V12" s="221" t="n"/>
-      <c r="W12" s="221" t="n"/>
-      <c r="X12" s="221" t="n"/>
+      <c r="V12" s="220" t="n"/>
+      <c r="W12" s="220" t="n"/>
+      <c r="X12" s="220" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="226" t="inlineStr">
@@ -23219,7 +23219,7 @@
       <c r="X13" s="226" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="221" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
@@ -23229,7 +23229,7 @@
           <t>A page or document about this thing.</t>
         </is>
       </c>
-      <c r="C14" s="221" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -23244,27 +23244,27 @@
           <t>The value of this property is the IRI pointing to the web page or document about the dataset.</t>
         </is>
       </c>
-      <c r="F14" s="220" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="220" t="inlineStr">
+      <c r="G14" s="218" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="220" t="inlineStr">
+      <c r="H14" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="218" t="inlineStr">
+      <c r="I14" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="218" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23274,7 +23274,7 @@
           <t>custom:documentation</t>
         </is>
       </c>
-      <c r="L14" s="218" t="n"/>
+      <c r="L14" s="224" t="n"/>
       <c r="P14" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23285,9 +23285,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V14" s="221" t="n"/>
-      <c r="W14" s="221" t="n"/>
-      <c r="X14" s="221" t="n"/>
+      <c r="V14" s="220" t="n"/>
+      <c r="W14" s="220" t="n"/>
+      <c r="X14" s="220" t="n"/>
     </row>
     <row r="15" ht="160" customHeight="1">
       <c r="A15" s="226" t="inlineStr">
@@ -23318,7 +23318,7 @@
 See the property "measurement technique" for more information about the technique(s) used to generate the data in the Dataset.</t>
         </is>
       </c>
-      <c r="F15" s="220" t="inlineStr">
+      <c r="F15" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23358,7 +23358,7 @@
       <c r="X15" s="226" t="n"/>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="221" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -23368,7 +23368,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C16" s="221" t="inlineStr">
+      <c r="C16" s="220" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -23378,7 +23378,7 @@
           <t>http://publications.europa.eu/resource/authority/frequency</t>
         </is>
       </c>
-      <c r="E16" s="224" t="inlineStr">
+      <c r="E16" s="223" t="inlineStr">
         <is>
           <t>The value of this property should be the IRI from the listed controlled vocabulary indicating the frequency at which the dataset is updated.
 For example: http://publications.europa.eu/resource/authority/frequency/WEEKLY</t>
@@ -23389,22 +23389,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="220" t="inlineStr">
+      <c r="G16" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="220" t="inlineStr">
+      <c r="H16" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="218" t="inlineStr">
+      <c r="I16" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="218" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23415,8 +23415,8 @@
         </is>
       </c>
       <c r="L16" s="107" t="n"/>
-      <c r="M16" s="218" t="n"/>
-      <c r="N16" s="218" t="n"/>
+      <c r="M16" s="224" t="n"/>
+      <c r="N16" s="224" t="n"/>
       <c r="P16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23427,9 +23427,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V16" s="221" t="n"/>
-      <c r="W16" s="221" t="n"/>
-      <c r="X16" s="221" t="n"/>
+      <c r="V16" s="220" t="n"/>
+      <c r="W16" s="220" t="n"/>
+      <c r="X16" s="220" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
       <c r="A17" s="226" t="inlineStr">
@@ -23457,7 +23457,7 @@
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F17" s="220" t="inlineStr">
+      <c r="F17" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23529,7 +23529,7 @@
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="221" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>has version</t>
         </is>
@@ -23539,7 +23539,7 @@
           <t>This resource has a more specific, versioned resource.</t>
         </is>
       </c>
-      <c r="C22" s="221" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>dcat:hasVersion</t>
         </is>
@@ -23549,7 +23549,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E22" s="224" t="inlineStr">
+      <c r="E22" s="223" t="inlineStr">
         <is>
           <t>Indicate the dataset that is another version of the current dataset.</t>
         </is>
@@ -23564,17 +23564,17 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H22" s="220" t="inlineStr">
+      <c r="H22" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="218" t="inlineStr">
+      <c r="I22" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="218" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23589,8 +23589,8 @@
           <t>Enter the URI for the dcat:Dataset that is another version of the current Dataset.</t>
         </is>
       </c>
-      <c r="M22" s="218" t="n"/>
-      <c r="N22" s="218" t="n"/>
+      <c r="M22" s="224" t="n"/>
+      <c r="N22" s="224" t="n"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -23606,9 +23606,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V22" s="221" t="n"/>
-      <c r="W22" s="221" t="n"/>
-      <c r="X22" s="221" t="n"/>
+      <c r="V22" s="220" t="n"/>
+      <c r="W22" s="220" t="n"/>
+      <c r="X22" s="220" t="n"/>
     </row>
     <row r="23" ht="124" customHeight="1">
       <c r="A23" s="226" t="inlineStr">
@@ -23639,7 +23639,7 @@
 Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
         </is>
       </c>
-      <c r="F23" s="220" t="inlineStr">
+      <c r="F23" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23676,7 +23676,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
+          <t>^(http://snomed[.]info/id/[0-9]+|^http://id[.]who[.]int/icd/entity/[0-9]+$|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
         </is>
       </c>
       <c r="V23" s="226" t="n"/>
@@ -23684,7 +23684,7 @@
       <c r="X23" s="226" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="221" t="inlineStr">
+      <c r="A24" s="220" t="inlineStr">
         <is>
           <t>health theme</t>
         </is>
@@ -23694,7 +23694,7 @@
           <t>A category of the Dataset or tag describing the Dataset.</t>
         </is>
       </c>
-      <c r="C24" s="221" t="inlineStr">
+      <c r="C24" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:healthTheme</t>
         </is>
@@ -23710,27 +23710,27 @@
 This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The Wikidata URI of the health theme must be used here.</t>
         </is>
       </c>
-      <c r="F24" s="220" t="inlineStr">
+      <c r="F24" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="220" t="inlineStr">
+      <c r="G24" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H24" s="220" t="inlineStr">
+      <c r="H24" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="218" t="inlineStr">
+      <c r="I24" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J24" s="218" t="inlineStr">
+      <c r="J24" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23740,7 +23740,7 @@
           <t>custom:health_theme</t>
         </is>
       </c>
-      <c r="L24" s="218" t="n"/>
+      <c r="L24" s="224" t="n"/>
       <c r="P24" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23751,9 +23751,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V24" s="221" t="n"/>
-      <c r="W24" s="221" t="n"/>
-      <c r="X24" s="221" t="n"/>
+      <c r="V24" s="220" t="n"/>
+      <c r="W24" s="220" t="n"/>
+      <c r="X24" s="220" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1">
       <c r="A25" s="226" t="inlineStr">
@@ -23828,7 +23828,7 @@
       <c r="X25" s="226" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="221" t="inlineStr">
+      <c r="A26" s="220" t="inlineStr">
         <is>
           <t>in series</t>
         </is>
@@ -23838,7 +23838,7 @@
           <t>A dataset series of which the dataset is part.</t>
         </is>
       </c>
-      <c r="C26" s="221" t="inlineStr">
+      <c r="C26" s="220" t="inlineStr">
         <is>
           <t>dcat:inSeries</t>
         </is>
@@ -23853,7 +23853,7 @@
           <t xml:space="preserve">This property points to the Dataset Series of which the Dataset is part. </t>
         </is>
       </c>
-      <c r="F26" s="220" t="inlineStr">
+      <c r="F26" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23863,17 +23863,17 @@
           <t>dcat:DatasetSeries</t>
         </is>
       </c>
-      <c r="H26" s="220" t="inlineStr">
+      <c r="H26" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I26" s="218" t="inlineStr">
+      <c r="I26" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J26" s="218" t="inlineStr">
+      <c r="J26" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23904,9 +23904,9 @@
           <t>Dataset Series</t>
         </is>
       </c>
-      <c r="V26" s="221" t="n"/>
-      <c r="W26" s="221" t="n"/>
-      <c r="X26" s="221" t="n"/>
+      <c r="V26" s="220" t="n"/>
+      <c r="W26" s="220" t="n"/>
+      <c r="X26" s="220" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
       <c r="A27" s="226" t="inlineStr">
@@ -23983,7 +23983,7 @@
       <c r="X27" s="226" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="221" t="inlineStr">
+      <c r="A28" s="220" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -24008,27 +24008,27 @@
           <t>Add keywords to increase dataset discoverability. You can include keywords in different languages, submitting each keyword as a separate entry. Example: Physiological measures, Heart Rate, Stress Measures.</t>
         </is>
       </c>
-      <c r="F28" s="220" t="inlineStr">
+      <c r="F28" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G28" s="220" t="inlineStr">
+      <c r="G28" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H28" s="220" t="inlineStr">
+      <c r="H28" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I28" s="218" t="inlineStr">
+      <c r="I28" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J28" s="218" t="inlineStr">
+      <c r="J28" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24038,7 +24038,7 @@
           <t>tags</t>
         </is>
       </c>
-      <c r="L28" s="218" t="n"/>
+      <c r="L28" s="224" t="n"/>
       <c r="P28" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24049,9 +24049,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V28" s="221" t="n"/>
-      <c r="W28" s="221" t="n"/>
-      <c r="X28" s="221" t="n"/>
+      <c r="V28" s="220" t="n"/>
+      <c r="W28" s="220" t="n"/>
+      <c r="X28" s="220" t="n"/>
     </row>
     <row r="29" ht="128" customHeight="1">
       <c r="A29" s="226" t="inlineStr">
@@ -24080,7 +24080,7 @@
 Example: For an EGA Dataset, dcat:landingPage points to the corresponding human-readable EGA Dataset page, like https://ega-archive.org/datasets/EGAD00001005083.</t>
         </is>
       </c>
-      <c r="F29" s="220" t="inlineStr">
+      <c r="F29" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24124,7 +24124,7 @@
       <c r="X29" s="226" t="n"/>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="221" t="inlineStr">
+      <c r="A30" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -24154,12 +24154,12 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G30" s="220" t="inlineStr">
+      <c r="G30" s="218" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H30" s="220" t="inlineStr">
+      <c r="H30" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
@@ -24179,9 +24179,9 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L30" s="218" t="n"/>
-      <c r="M30" s="218" t="n"/>
-      <c r="N30" s="218" t="n"/>
+      <c r="L30" s="224" t="n"/>
+      <c r="M30" s="224" t="n"/>
+      <c r="N30" s="224" t="n"/>
       <c r="P30" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24192,9 +24192,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V30" s="221" t="n"/>
-      <c r="W30" s="221" t="n"/>
-      <c r="X30" s="221" t="n"/>
+      <c r="V30" s="220" t="n"/>
+      <c r="W30" s="220" t="n"/>
+      <c r="X30" s="220" t="n"/>
     </row>
     <row r="31" ht="160" customHeight="1">
       <c r="A31" s="226" t="inlineStr">
@@ -24225,7 +24225,7 @@
 An example value for this property could be dpv:Consent.</t>
         </is>
       </c>
-      <c r="F31" s="220" t="inlineStr">
+      <c r="F31" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24273,7 +24273,7 @@
       <c r="X31" s="226" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="221" t="inlineStr">
+      <c r="A32" s="220" t="inlineStr">
         <is>
           <t>maximum typical age</t>
         </is>
@@ -24283,7 +24283,7 @@
           <t>Maximum typical age of the population within the dataset</t>
         </is>
       </c>
-      <c r="C32" s="221" t="inlineStr">
+      <c r="C32" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:maxTypicalAge</t>
         </is>
@@ -24303,22 +24303,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G32" s="220" t="inlineStr">
+      <c r="G32" s="218" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H32" s="220" t="inlineStr">
+      <c r="H32" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I32" s="218" t="inlineStr">
+      <c r="I32" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J32" s="218" t="inlineStr">
+      <c r="J32" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24328,9 +24328,9 @@
           <t>custom:max_typical_age</t>
         </is>
       </c>
-      <c r="L32" s="218" t="n"/>
-      <c r="M32" s="218" t="n"/>
-      <c r="N32" s="218" t="n"/>
+      <c r="L32" s="224" t="n"/>
+      <c r="M32" s="224" t="n"/>
+      <c r="N32" s="224" t="n"/>
       <c r="P32" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24341,9 +24341,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V32" s="221" t="n"/>
-      <c r="W32" s="221" t="n"/>
-      <c r="X32" s="221" t="n"/>
+      <c r="V32" s="220" t="n"/>
+      <c r="W32" s="220" t="n"/>
+      <c r="X32" s="220" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="226" t="inlineStr">
@@ -24371,7 +24371,7 @@
           <t>The approximate minimum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F33" s="220" t="inlineStr">
+      <c r="F33" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24419,7 +24419,7 @@
       <c r="X33" s="226" t="n"/>
     </row>
     <row r="34" ht="209.25" customHeight="1">
-      <c r="A34" s="221" t="inlineStr">
+      <c r="A34" s="220" t="inlineStr">
         <is>
           <t>measurement technique</t>
         </is>
@@ -24446,73 +24446,73 @@
 Note: This is a temporary location and it will change with the next release. </t>
         </is>
       </c>
-      <c r="F34" s="220" t="inlineStr">
+      <c r="F34" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G34" s="220" t="inlineStr">
+      <c r="G34" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H34" s="220" t="inlineStr">
+      <c r="H34" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I34" s="218" t="n"/>
-      <c r="J34" s="218" t="n"/>
+      <c r="I34" s="224" t="n"/>
+      <c r="J34" s="224" t="n"/>
       <c r="K34" s="75" t="n"/>
-      <c r="L34" s="218" t="n"/>
-      <c r="M34" s="218" t="n"/>
-      <c r="N34" s="218" t="n"/>
-      <c r="O34" s="218" t="n"/>
-      <c r="P34" s="218" t="inlineStr">
+      <c r="L34" s="224" t="n"/>
+      <c r="M34" s="224" t="n"/>
+      <c r="N34" s="224" t="n"/>
+      <c r="O34" s="224" t="n"/>
+      <c r="P34" s="224" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
         </is>
       </c>
-      <c r="Q34" s="218" t="inlineStr">
+      <c r="Q34" s="224" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="R34" s="218" t="n"/>
-      <c r="S34" s="218" t="n"/>
-      <c r="T34" s="218" t="n"/>
-      <c r="U34" s="218" t="n"/>
-      <c r="V34" s="221" t="n"/>
-      <c r="W34" s="221" t="n"/>
-      <c r="X34" s="221" t="n"/>
-      <c r="Y34" s="218" t="n"/>
-      <c r="Z34" s="218" t="n"/>
-      <c r="AA34" s="218" t="n"/>
-      <c r="AB34" s="218" t="n"/>
-      <c r="AC34" s="218" t="n"/>
-      <c r="AD34" s="218" t="n"/>
-      <c r="AE34" s="218" t="n"/>
-      <c r="AF34" s="218" t="n"/>
-      <c r="AG34" s="218" t="n"/>
-      <c r="AH34" s="218" t="n"/>
-      <c r="AI34" s="218" t="n"/>
-      <c r="AJ34" s="218" t="n"/>
-      <c r="AK34" s="218" t="n"/>
-      <c r="AL34" s="218" t="n"/>
-      <c r="AM34" s="218" t="n"/>
-      <c r="AN34" s="218" t="n"/>
-      <c r="AO34" s="218" t="n"/>
-      <c r="AP34" s="218" t="n"/>
-      <c r="AQ34" s="218" t="n"/>
-      <c r="AR34" s="218" t="n"/>
-      <c r="AS34" s="218" t="n"/>
-      <c r="AT34" s="218" t="n"/>
-      <c r="AU34" s="218" t="n"/>
-      <c r="AV34" s="218" t="n"/>
-      <c r="AW34" s="218" t="n"/>
-      <c r="AX34" s="218" t="n"/>
-      <c r="AY34" s="218" t="n"/>
-      <c r="AZ34" s="218" t="n"/>
+      <c r="R34" s="224" t="n"/>
+      <c r="S34" s="224" t="n"/>
+      <c r="T34" s="224" t="n"/>
+      <c r="U34" s="224" t="n"/>
+      <c r="V34" s="220" t="n"/>
+      <c r="W34" s="220" t="n"/>
+      <c r="X34" s="220" t="n"/>
+      <c r="Y34" s="224" t="n"/>
+      <c r="Z34" s="224" t="n"/>
+      <c r="AA34" s="224" t="n"/>
+      <c r="AB34" s="224" t="n"/>
+      <c r="AC34" s="224" t="n"/>
+      <c r="AD34" s="224" t="n"/>
+      <c r="AE34" s="224" t="n"/>
+      <c r="AF34" s="224" t="n"/>
+      <c r="AG34" s="224" t="n"/>
+      <c r="AH34" s="224" t="n"/>
+      <c r="AI34" s="224" t="n"/>
+      <c r="AJ34" s="224" t="n"/>
+      <c r="AK34" s="224" t="n"/>
+      <c r="AL34" s="224" t="n"/>
+      <c r="AM34" s="224" t="n"/>
+      <c r="AN34" s="224" t="n"/>
+      <c r="AO34" s="224" t="n"/>
+      <c r="AP34" s="224" t="n"/>
+      <c r="AQ34" s="224" t="n"/>
+      <c r="AR34" s="224" t="n"/>
+      <c r="AS34" s="224" t="n"/>
+      <c r="AT34" s="224" t="n"/>
+      <c r="AU34" s="224" t="n"/>
+      <c r="AV34" s="224" t="n"/>
+      <c r="AW34" s="224" t="n"/>
+      <c r="AX34" s="224" t="n"/>
+      <c r="AY34" s="224" t="n"/>
+      <c r="AZ34" s="224" t="n"/>
     </row>
     <row r="35" ht="48" customHeight="1">
       <c r="A35" s="226" t="inlineStr">
@@ -24593,7 +24593,7 @@
       <c r="X35" s="226" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="221" t="inlineStr">
+      <c r="A36" s="220" t="inlineStr">
         <is>
           <t>number of records</t>
         </is>
@@ -24603,7 +24603,7 @@
           <t>Size of the dataset in terms of the number of records</t>
         </is>
       </c>
-      <c r="C36" s="221" t="inlineStr">
+      <c r="C36" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfRecords</t>
         </is>
@@ -24618,27 +24618,27 @@
           <t>Number of records inside a Dataset.</t>
         </is>
       </c>
-      <c r="F36" s="220" t="inlineStr">
+      <c r="F36" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G36" s="220" t="inlineStr">
+      <c r="G36" s="218" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H36" s="220" t="inlineStr">
+      <c r="H36" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I36" s="218" t="inlineStr">
+      <c r="I36" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J36" s="218" t="inlineStr">
+      <c r="J36" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24648,7 +24648,7 @@
           <t>custom:number_of_records</t>
         </is>
       </c>
-      <c r="L36" s="218" t="n"/>
+      <c r="L36" s="224" t="n"/>
       <c r="P36" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24659,9 +24659,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V36" s="221" t="n"/>
-      <c r="W36" s="221" t="n"/>
-      <c r="X36" s="221" t="n"/>
+      <c r="V36" s="220" t="n"/>
+      <c r="W36" s="220" t="n"/>
+      <c r="X36" s="220" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="226" t="inlineStr">
@@ -24737,7 +24737,7 @@
       <c r="X37" s="226" t="n"/>
     </row>
     <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="221" t="inlineStr">
+      <c r="A38" s="220" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
@@ -24747,7 +24747,7 @@
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
       </c>
-      <c r="C38" s="221" t="inlineStr">
+      <c r="C38" s="220" t="inlineStr">
         <is>
           <t>adms:identifier</t>
         </is>
@@ -24762,27 +24762,27 @@
           <t>Examples of secondary identifiers include MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (e.g. DOI).</t>
         </is>
       </c>
-      <c r="F38" s="220" t="inlineStr">
+      <c r="F38" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G38" s="220" t="inlineStr">
+      <c r="G38" s="218" t="inlineStr">
         <is>
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H38" s="220" t="inlineStr">
+      <c r="H38" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I38" s="218" t="inlineStr">
+      <c r="I38" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J38" s="218" t="inlineStr">
+      <c r="J38" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24792,7 +24792,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="L38" s="218" t="n"/>
+      <c r="L38" s="224" t="n"/>
       <c r="O38" s="219" t="inlineStr">
         <is>
           <t>hrishapes:IdentifierShape</t>
@@ -24808,9 +24808,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V38" s="221" t="n"/>
-      <c r="W38" s="221" t="n"/>
-      <c r="X38" s="221" t="n"/>
+      <c r="V38" s="220" t="n"/>
+      <c r="W38" s="220" t="n"/>
+      <c r="X38" s="220" t="n"/>
     </row>
     <row r="39" ht="64" customHeight="1">
       <c r="A39" s="226" t="inlineStr">
@@ -24887,7 +24887,7 @@
       <c r="X39" s="226" t="n"/>
     </row>
     <row r="40" ht="59" customHeight="1">
-      <c r="A40" s="221" t="inlineStr">
+      <c r="A40" s="220" t="inlineStr">
         <is>
           <t>population coverage</t>
         </is>
@@ -24897,7 +24897,7 @@
           <t>A definition of the population within the dataset</t>
         </is>
       </c>
-      <c r="C40" s="221" t="inlineStr">
+      <c r="C40" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:populationCoverage</t>
         </is>
@@ -24912,27 +24912,27 @@
           <t>This field is a free-text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
         </is>
       </c>
-      <c r="F40" s="220" t="inlineStr">
+      <c r="F40" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G40" s="220" t="inlineStr">
+      <c r="G40" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H40" s="220" t="inlineStr">
+      <c r="H40" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I40" s="218" t="inlineStr">
+      <c r="I40" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J40" s="218" t="inlineStr">
+      <c r="J40" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24942,7 +24942,7 @@
           <t>custom:populatiion_coverage</t>
         </is>
       </c>
-      <c r="L40" s="218" t="n"/>
+      <c r="L40" s="224" t="n"/>
       <c r="P40" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24953,9 +24953,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V40" s="221" t="n"/>
-      <c r="W40" s="221" t="n"/>
-      <c r="X40" s="221" t="n"/>
+      <c r="V40" s="220" t="n"/>
+      <c r="W40" s="220" t="n"/>
+      <c r="X40" s="220" t="n"/>
     </row>
     <row r="41" ht="92" customHeight="1">
       <c r="A41" s="226" t="inlineStr">
@@ -24984,7 +24984,7 @@
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
         </is>
       </c>
-      <c r="F41" s="220" t="inlineStr">
+      <c r="F41" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25045,7 +25045,7 @@
       <c r="X41" s="226" t="n"/>
     </row>
     <row r="42" ht="112" customHeight="1">
-      <c r="A42" s="221" t="inlineStr">
+      <c r="A42" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -25055,7 +25055,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C42" s="221" t="inlineStr">
+      <c r="C42" s="220" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -25065,7 +25065,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E42" s="224" t="inlineStr">
+      <c r="E42" s="223" t="inlineStr">
         <is>
           <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalogue publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide information about the contributing organisations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
         </is>
@@ -25080,15 +25080,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H42" s="220" t="n">
+      <c r="H42" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="218" t="inlineStr">
+      <c r="I42" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J42" s="218" t="inlineStr">
+      <c r="J42" s="224" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -25098,17 +25098,17 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L42" s="218" t="inlineStr">
+      <c r="L42" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M42" s="218" t="inlineStr">
+      <c r="M42" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N42" s="218" t="inlineStr">
+      <c r="N42" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -25128,9 +25128,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V42" s="221" t="n"/>
-      <c r="W42" s="221" t="n"/>
-      <c r="X42" s="221" t="n"/>
+      <c r="V42" s="220" t="n"/>
+      <c r="W42" s="220" t="n"/>
+      <c r="X42" s="220" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1">
       <c r="A43" s="226" t="inlineStr">
@@ -25159,7 +25159,7 @@
 An example value could be dpv:ResearchAndDevelopment.</t>
         </is>
       </c>
-      <c r="F43" s="220" t="inlineStr">
+      <c r="F43" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25207,7 +25207,7 @@
       <c r="X43" s="226" t="n"/>
     </row>
     <row r="44" ht="228" customHeight="1">
-      <c r="A44" s="221" t="inlineStr">
+      <c r="A44" s="220" t="inlineStr">
         <is>
           <t>qualified attribution</t>
         </is>
@@ -25246,33 +25246,33 @@
           <t>prov:Attribution</t>
         </is>
       </c>
-      <c r="H44" s="220" t="inlineStr">
+      <c r="H44" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I44" s="218" t="inlineStr">
+      <c r="I44" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J44" s="218" t="inlineStr">
+      <c r="J44" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K44" s="75" t="n"/>
-      <c r="L44" s="218" t="inlineStr">
+      <c r="L44" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="M44" s="218" t="inlineStr">
+      <c r="M44" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="N44" s="218" t="inlineStr">
+      <c r="N44" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
@@ -25292,9 +25292,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V44" s="221" t="n"/>
-      <c r="W44" s="221" t="n"/>
-      <c r="X44" s="221" t="n"/>
+      <c r="V44" s="220" t="n"/>
+      <c r="W44" s="220" t="n"/>
+      <c r="X44" s="220" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
       <c r="A45" s="226" t="inlineStr">
@@ -25322,7 +25322,7 @@
           <t>This property makes use of another small class (dcat:Relationship), in which you can indicate the related resource (via its identifier) and the nature of the relation (based on a controlled vocabulary, which is described in the information of the class).</t>
         </is>
       </c>
-      <c r="F45" s="220" t="inlineStr">
+      <c r="F45" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25387,7 +25387,7 @@
       <c r="X45" s="226" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="221" t="inlineStr">
+      <c r="A46" s="220" t="inlineStr">
         <is>
           <t>quality annotation</t>
         </is>
@@ -25397,7 +25397,7 @@
           <t>Refers to a quality annotation.</t>
         </is>
       </c>
-      <c r="C46" s="221" t="inlineStr">
+      <c r="C46" s="220" t="inlineStr">
         <is>
           <t>dqv:hasQualityAnnotation</t>
         </is>
@@ -25422,33 +25422,33 @@
           <t>dqv:QualityCertificate</t>
         </is>
       </c>
-      <c r="H46" s="220" t="inlineStr">
+      <c r="H46" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I46" s="218" t="inlineStr">
+      <c r="I46" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J46" s="218" t="inlineStr">
+      <c r="J46" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K46" s="75" t="n"/>
-      <c r="L46" s="218" t="inlineStr">
+      <c r="L46" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="M46" s="218" t="inlineStr">
+      <c r="M46" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="N46" s="218" t="inlineStr">
+      <c r="N46" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
@@ -25468,9 +25468,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V46" s="221" t="n"/>
-      <c r="W46" s="221" t="n"/>
-      <c r="X46" s="221" t="n"/>
+      <c r="V46" s="220" t="n"/>
+      <c r="W46" s="220" t="n"/>
+      <c r="X46" s="220" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="226" t="inlineStr">
@@ -25498,7 +25498,7 @@
           <t>This property should point to the first known date of issuance, such as the publication date in a data repository. Example: 2023-12-10T13:16:10.246Z.</t>
         </is>
       </c>
-      <c r="F47" s="220" t="inlineStr">
+      <c r="F47" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25551,7 +25551,7 @@
       <c r="X47" s="226" t="n"/>
     </row>
     <row r="48" ht="160" customHeight="1">
-      <c r="A48" s="221" t="inlineStr">
+      <c r="A48" s="220" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -25561,7 +25561,7 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C48" s="221" t="inlineStr">
+      <c r="C48" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:retentionPeriod</t>
         </is>
@@ -25590,17 +25590,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H48" s="220" t="inlineStr">
+      <c r="H48" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I48" s="218" t="inlineStr">
+      <c r="I48" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J48" s="218" t="inlineStr">
+      <c r="J48" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -25610,17 +25610,17 @@
           <t>custom:retention_period</t>
         </is>
       </c>
-      <c r="L48" s="218" t="inlineStr">
+      <c r="L48" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M48" s="218" t="inlineStr">
+      <c r="M48" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N48" s="218" t="inlineStr">
+      <c r="N48" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -25640,9 +25640,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V48" s="221" t="n"/>
-      <c r="W48" s="221" t="n"/>
-      <c r="X48" s="221" t="n"/>
+      <c r="V48" s="220" t="n"/>
+      <c r="W48" s="220" t="n"/>
+      <c r="X48" s="220" t="n"/>
     </row>
     <row r="49" ht="80" customHeight="1">
       <c r="A49" s="226" t="inlineStr">
@@ -25670,7 +25670,7 @@
           <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can consist of anonymised or synthetic data, or a data dictionary provided in CSVW format. This is currently being further developed by the TEHDAS2 programme. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
         </is>
       </c>
-      <c r="F49" s="220" t="inlineStr">
+      <c r="F49" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25732,7 +25732,7 @@
       <c r="X49" s="226" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="221" t="inlineStr">
+      <c r="A50" s="220" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -25742,7 +25742,7 @@
           <t>A related resource from which the described resource is derived.</t>
         </is>
       </c>
-      <c r="C50" s="221" t="inlineStr">
+      <c r="C50" s="220" t="inlineStr">
         <is>
           <t>dct:source</t>
         </is>
@@ -25752,7 +25752,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E50" s="224" t="inlineStr">
+      <c r="E50" s="223" t="inlineStr">
         <is>
           <t>Indicate the dataset on which this described dataset is based.</t>
         </is>
@@ -25767,17 +25767,17 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H50" s="220" t="inlineStr">
+      <c r="H50" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I50" s="218" t="inlineStr">
+      <c r="I50" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J50" s="218" t="inlineStr">
+      <c r="J50" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -25792,8 +25792,8 @@
           <t>If applicable, add the URI for the source dataset here.</t>
         </is>
       </c>
-      <c r="M50" s="218" t="n"/>
-      <c r="N50" s="218" t="n"/>
+      <c r="M50" s="224" t="n"/>
+      <c r="N50" s="224" t="n"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -25809,9 +25809,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V50" s="221" t="n"/>
-      <c r="W50" s="221" t="n"/>
-      <c r="X50" s="221" t="n"/>
+      <c r="V50" s="220" t="n"/>
+      <c r="W50" s="220" t="n"/>
+      <c r="X50" s="220" t="n"/>
     </row>
     <row r="51" ht="64" customHeight="1">
       <c r="A51" s="226" t="inlineStr">
@@ -25840,7 +25840,7 @@
 For example: http://publications.europa.eu/resource/authority/dataset-status/COMPLETED</t>
         </is>
       </c>
-      <c r="F51" s="220" t="inlineStr">
+      <c r="F51" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25888,7 +25888,7 @@
       <c r="X51" s="226" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="221" t="inlineStr">
+      <c r="A52" s="220" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -25898,7 +25898,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C52" s="221" t="inlineStr">
+      <c r="C52" s="220" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -25923,17 +25923,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H52" s="220" t="inlineStr">
+      <c r="H52" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I52" s="218" t="inlineStr">
+      <c r="I52" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J52" s="218" t="inlineStr">
+      <c r="J52" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -25943,17 +25943,17 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L52" s="218" t="inlineStr">
+      <c r="L52" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M52" s="218" t="inlineStr">
+      <c r="M52" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N52" s="218" t="inlineStr">
+      <c r="N52" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -25973,9 +25973,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V52" s="221" t="n"/>
-      <c r="W52" s="221" t="n"/>
-      <c r="X52" s="221" t="n"/>
+      <c r="V52" s="220" t="n"/>
+      <c r="W52" s="220" t="n"/>
+      <c r="X52" s="220" t="n"/>
     </row>
     <row r="53" ht="64" customHeight="1">
       <c r="A53" s="226" t="inlineStr">
@@ -26003,7 +26003,7 @@
           <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of datasets, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
         </is>
       </c>
-      <c r="F53" s="220" t="inlineStr">
+      <c r="F53" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -26051,7 +26051,7 @@
       <c r="X53" s="226" t="n"/>
     </row>
     <row r="54" ht="74.25" customHeight="1">
-      <c r="A54" s="221" t="inlineStr">
+      <c r="A54" s="220" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -26061,7 +26061,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C54" s="221" t="inlineStr">
+      <c r="C54" s="220" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -26081,22 +26081,22 @@
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G54" s="220" t="inlineStr">
+      <c r="G54" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H54" s="220" t="inlineStr">
+      <c r="H54" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I54" s="218" t="inlineStr">
+      <c r="I54" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J54" s="218" t="inlineStr">
+      <c r="J54" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -26106,9 +26106,9 @@
           <t>custom:theme</t>
         </is>
       </c>
-      <c r="L54" s="218" t="n"/>
-      <c r="M54" s="218" t="n"/>
-      <c r="N54" s="218" t="n"/>
+      <c r="L54" s="224" t="n"/>
+      <c r="M54" s="224" t="n"/>
+      <c r="N54" s="224" t="n"/>
       <c r="P54" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -26124,9 +26124,9 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="V54" s="221" t="n"/>
-      <c r="W54" s="221" t="n"/>
-      <c r="X54" s="221" t="n"/>
+      <c r="V54" s="220" t="n"/>
+      <c r="W54" s="220" t="n"/>
+      <c r="X54" s="220" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
       <c r="A55" s="226" t="inlineStr">
@@ -26154,7 +26154,7 @@
           <t>Provide a unique title for your Dataset, which can be repeated in multiple languages. Example: Healthy Brain Study - Physiological Data</t>
         </is>
       </c>
-      <c r="F55" s="220" t="inlineStr">
+      <c r="F55" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -26205,7 +26205,7 @@
       <c r="X55" s="226" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="221" t="inlineStr">
+      <c r="A56" s="220" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -26215,7 +26215,7 @@
           <t>The nature or genre of the resource.</t>
         </is>
       </c>
-      <c r="C56" s="221" t="inlineStr">
+      <c r="C56" s="220" t="inlineStr">
         <is>
           <t>dct:type</t>
         </is>
@@ -26236,22 +26236,22 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G56" s="220" t="inlineStr">
+      <c r="G56" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H56" s="220" t="inlineStr">
+      <c r="H56" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I56" s="218" t="inlineStr">
+      <c r="I56" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J56" s="218" t="inlineStr">
+      <c r="J56" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -26261,9 +26261,9 @@
           <t>custom:dcat_type</t>
         </is>
       </c>
-      <c r="L56" s="218" t="n"/>
-      <c r="M56" s="218" t="n"/>
-      <c r="N56" s="218" t="n"/>
+      <c r="L56" s="224" t="n"/>
+      <c r="M56" s="224" t="n"/>
+      <c r="N56" s="224" t="n"/>
       <c r="O56" s="84" t="n"/>
       <c r="P56" s="69" t="inlineStr">
         <is>
@@ -26277,9 +26277,9 @@
       </c>
       <c r="R56" s="84" t="n"/>
       <c r="T56" s="84" t="n"/>
-      <c r="V56" s="221" t="n"/>
-      <c r="W56" s="221" t="n"/>
-      <c r="X56" s="221" t="n"/>
+      <c r="V56" s="220" t="n"/>
+      <c r="W56" s="220" t="n"/>
+      <c r="X56" s="220" t="n"/>
     </row>
     <row r="57" ht="80" customHeight="1">
       <c r="A57" s="226" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="U57" s="219" t="inlineStr">
         <is>
-          <t>Table Group</t>
+          <t>Variables</t>
         </is>
       </c>
       <c r="V57" s="226" t="n"/>
@@ -26374,7 +26374,7 @@
       <c r="X57" s="226" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="221" t="inlineStr">
+      <c r="A58" s="220" t="inlineStr">
         <is>
           <t>version</t>
         </is>
@@ -26384,7 +26384,7 @@
           <t>The version indicator (name or identifier) of a resource.</t>
         </is>
       </c>
-      <c r="C58" s="221" t="inlineStr">
+      <c r="C58" s="220" t="inlineStr">
         <is>
           <t>dcat:version</t>
         </is>
@@ -26399,27 +26399,27 @@
           <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
         </is>
       </c>
-      <c r="F58" s="220" t="inlineStr">
+      <c r="F58" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G58" s="220" t="inlineStr">
+      <c r="G58" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H58" s="220" t="inlineStr">
+      <c r="H58" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I58" s="218" t="inlineStr">
+      <c r="I58" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J58" s="218" t="inlineStr">
+      <c r="J58" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -26429,9 +26429,9 @@
           <t>custom:version</t>
         </is>
       </c>
-      <c r="L58" s="218" t="n"/>
-      <c r="M58" s="218" t="n"/>
-      <c r="N58" s="218" t="n"/>
+      <c r="L58" s="224" t="n"/>
+      <c r="M58" s="224" t="n"/>
+      <c r="N58" s="224" t="n"/>
       <c r="P58" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26443,9 +26443,9 @@
         </is>
       </c>
       <c r="S58" s="84" t="n"/>
-      <c r="V58" s="221" t="n"/>
-      <c r="W58" s="221" t="n"/>
-      <c r="X58" s="221" t="n"/>
+      <c r="V58" s="220" t="n"/>
+      <c r="W58" s="220" t="n"/>
+      <c r="X58" s="220" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
       <c r="A59" s="226" t="inlineStr">
@@ -26524,7 +26524,7 @@
       <c r="X59" s="226" t="n"/>
     </row>
     <row r="60" ht="84.75" customHeight="1">
-      <c r="A60" s="221" t="inlineStr">
+      <c r="A60" s="220" t="inlineStr">
         <is>
           <t>was generated by</t>
         </is>
@@ -26534,7 +26534,7 @@
           <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
         </is>
       </c>
-      <c r="C60" s="221" t="inlineStr">
+      <c r="C60" s="220" t="inlineStr">
         <is>
           <t>prov:wasGeneratedBy</t>
         </is>
@@ -26544,7 +26544,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="F60" s="220" t="inlineStr">
+      <c r="F60" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -26554,25 +26554,25 @@
           <t>prov:Activity</t>
         </is>
       </c>
-      <c r="H60" s="220" t="inlineStr">
+      <c r="H60" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I60" s="218" t="inlineStr">
+      <c r="I60" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J60" s="218" t="inlineStr">
+      <c r="J60" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K60" s="75" t="n"/>
-      <c r="L60" s="218" t="n"/>
-      <c r="M60" s="218" t="n"/>
-      <c r="N60" s="218" t="n"/>
+      <c r="L60" s="224" t="n"/>
+      <c r="M60" s="224" t="n"/>
+      <c r="N60" s="224" t="n"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>hrishapes:ActivityShape</t>
@@ -26588,9 +26588,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V60" s="221" t="n"/>
-      <c r="W60" s="221" t="n"/>
-      <c r="X60" s="221" t="n"/>
+      <c r="V60" s="220" t="n"/>
+      <c r="W60" s="220" t="n"/>
+      <c r="X60" s="220" t="n"/>
     </row>
     <row r="61" customFormat="1" s="84">
       <c r="A61" s="110" t="n"/>
@@ -26771,8 +26771,8 @@
     <col width="36.5" customWidth="1" style="102" min="22" max="22"/>
     <col width="8.83203125" customWidth="1" style="102" min="23" max="28"/>
     <col width="18" customWidth="1" min="29" max="31"/>
-    <col width="8.83203125" customWidth="1" style="102" min="32" max="32"/>
-    <col width="8.83203125" customWidth="1" style="102" min="33" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="102" min="32" max="33"/>
+    <col width="8.83203125" customWidth="1" style="102" min="34" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customFormat="1" customHeight="1" s="165">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="J2" s="125" t="n"/>
       <c r="K2" s="126" t="n"/>
-      <c r="L2" s="218" t="n"/>
+      <c r="L2" s="224" t="n"/>
       <c r="X2" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27142,7 +27142,7 @@
           <t>_id</t>
         </is>
       </c>
-      <c r="L4" s="218" t="n"/>
+      <c r="L4" s="224" t="n"/>
       <c r="X4" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27246,7 +27246,7 @@
           <t>publisher note</t>
         </is>
       </c>
-      <c r="B6" s="223" t="inlineStr">
+      <c r="B6" s="222" t="inlineStr">
         <is>
           <t>A description of the publisher's activities.</t>
         </is>
@@ -27261,7 +27261,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E6" s="223" t="inlineStr">
+      <c r="E6" s="222" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the next major release.
 This property can be repeated for parallel language versions of the publisher notes. Example: "Sciensano is a research institute and the national public health institute of Belgium. It is a so-called federal scientific institution that operates under the authority of the federal minister of Public Health and the federal minister of Agriculture of Belgium."@en</t>
@@ -27293,7 +27293,7 @@
         </is>
       </c>
       <c r="K6" s="126" t="n"/>
-      <c r="L6" s="218" t="n"/>
+      <c r="L6" s="224" t="n"/>
       <c r="X6" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27444,7 +27444,7 @@
           <t>_type</t>
         </is>
       </c>
-      <c r="L8" s="218" t="n"/>
+      <c r="L8" s="224" t="n"/>
       <c r="X8" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -28384,8 +28384,8 @@
     <col width="33.5" customWidth="1" style="58" min="17" max="17"/>
     <col width="8.83203125" customWidth="1" style="58" min="18" max="23"/>
     <col width="24.5" customWidth="1" min="24" max="26"/>
-    <col width="8.83203125" customWidth="1" style="58" min="27" max="27"/>
-    <col width="8.83203125" customWidth="1" style="58" min="28" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="58" min="27" max="28"/>
+    <col width="8.83203125" customWidth="1" style="58" min="29" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="80" customFormat="1" customHeight="1" s="165">

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="-28200" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="0" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="-28200" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="4" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -1083,32 +1083,17 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1119,6 +1104,9 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1126,6 +1114,18 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6075,8 +6075,8 @@
     <col width="28.83203125" customWidth="1" style="234" min="13" max="13"/>
     <col width="9.1640625" customWidth="1" style="234" min="14" max="20"/>
     <col width="19.1640625" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
-    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
+    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customFormat="1" customHeight="1" s="165">
@@ -6197,17 +6197,17 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="226" t="inlineStr">
+      <c r="A2" s="220" t="inlineStr">
         <is>
           <t>access service</t>
         </is>
       </c>
-      <c r="B2" s="230" t="inlineStr">
+      <c r="B2" s="226" t="inlineStr">
         <is>
           <t>A data service that gives access to the distribution of the dataset.</t>
         </is>
       </c>
-      <c r="C2" s="226" t="inlineStr">
+      <c r="C2" s="220" t="inlineStr">
         <is>
           <t>dcat:accessService</t>
         </is>
@@ -6222,7 +6222,7 @@
           <t>This property links the distribution class to the corresponding data service(s).</t>
         </is>
       </c>
-      <c r="F2" s="218" t="inlineStr">
+      <c r="F2" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6232,17 +6232,17 @@
           <t>dcat:DataService</t>
         </is>
       </c>
-      <c r="H2" s="231" t="inlineStr">
+      <c r="H2" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I2" s="225" t="inlineStr">
+      <c r="I2" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J2" s="224" t="inlineStr">
+      <c r="J2" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6283,12 +6283,12 @@
           <t>Data Service</t>
         </is>
       </c>
-      <c r="U2" s="226" t="n"/>
-      <c r="V2" s="226" t="n"/>
-      <c r="W2" s="226" t="n"/>
+      <c r="U2" s="220" t="n"/>
+      <c r="V2" s="220" t="n"/>
+      <c r="W2" s="220" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="220" t="inlineStr">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>access URL</t>
         </is>
@@ -6298,7 +6298,7 @@
           <t>A URL of the resource that gives access to a distribution of the dataset. E.g., landing page, feed, SPARQL endpoint.</t>
         </is>
       </c>
-      <c r="C3" s="220" t="inlineStr">
+      <c r="C3" s="230" t="inlineStr">
         <is>
           <t>dcat:accessURL</t>
         </is>
@@ -6308,17 +6308,17 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="223" t="inlineStr">
+      <c r="E3" s="231" t="inlineStr">
         <is>
           <t>Add a link that points to where the dataset can be found. If it’s hosted in a Data Repository, include the link to its entry. For datasets not in a repository (like registries), but still available for secondary use, provide a link to an access request form or a webpage with instructions for accessing the data.</t>
         </is>
       </c>
-      <c r="F3" s="231" t="inlineStr">
+      <c r="F3" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G3" s="218" t="inlineStr">
+      <c r="G3" s="225" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -6326,12 +6326,12 @@
       <c r="H3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="224" t="inlineStr">
+      <c r="I3" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="224" t="inlineStr">
+      <c r="J3" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6341,8 +6341,8 @@
           <t>resource:access_url</t>
         </is>
       </c>
-      <c r="L3" s="224" t="n"/>
-      <c r="M3" s="224" t="n"/>
+      <c r="L3" s="232" t="n"/>
+      <c r="M3" s="232" t="n"/>
       <c r="O3" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6354,22 +6354,22 @@
         </is>
       </c>
       <c r="S3" s="121" t="n"/>
-      <c r="U3" s="220" t="n"/>
-      <c r="V3" s="220" t="n"/>
-      <c r="W3" s="220" t="n"/>
+      <c r="U3" s="230" t="n"/>
+      <c r="V3" s="230" t="n"/>
+      <c r="W3" s="230" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="226" t="inlineStr">
+      <c r="A4" s="220" t="inlineStr">
         <is>
           <t>applicable legislation</t>
         </is>
       </c>
-      <c r="B4" s="230" t="inlineStr">
+      <c r="B4" s="226" t="inlineStr">
         <is>
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C4" s="226" t="inlineStr">
+      <c r="C4" s="220" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -6384,27 +6384,27 @@
           <t>The legislation that mandates the creation or management of the Distribution.</t>
         </is>
       </c>
-      <c r="F4" s="218" t="inlineStr">
+      <c r="F4" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="231" t="inlineStr">
+      <c r="G4" s="227" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="231" t="inlineStr">
+      <c r="H4" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="225" t="inlineStr">
+      <c r="I4" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="224" t="inlineStr">
+      <c r="J4" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -6414,8 +6414,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L4" s="225" t="n"/>
-      <c r="M4" s="225" t="n"/>
+      <c r="L4" s="218" t="n"/>
+      <c r="M4" s="218" t="n"/>
       <c r="O4" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6427,9 +6427,9 @@
         </is>
       </c>
       <c r="S4" s="121" t="n"/>
-      <c r="U4" s="226" t="n"/>
-      <c r="V4" s="226" t="n"/>
-      <c r="W4" s="226" t="n"/>
+      <c r="U4" s="220" t="n"/>
+      <c r="V4" s="220" t="n"/>
+      <c r="W4" s="220" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="97" t="inlineStr">
@@ -6442,7 +6442,7 @@
           <t>An indication of how long it is planned to keep the Distribution of the Dataset available.</t>
         </is>
       </c>
-      <c r="C5" s="220" t="inlineStr">
+      <c r="C5" s="230" t="inlineStr">
         <is>
           <t>dcatap:availability</t>
         </is>
@@ -6457,12 +6457,12 @@
           <t>To indicate the planned availability of the Distribution, the EU planned-availability controlled vocabulary MUST be used.</t>
         </is>
       </c>
-      <c r="F5" s="218" t="inlineStr">
+      <c r="F5" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="218" t="inlineStr">
+      <c r="G5" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
@@ -6472,19 +6472,19 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="224" t="inlineStr">
+      <c r="I5" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="224" t="inlineStr">
+      <c r="J5" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="69" t="n"/>
-      <c r="L5" s="224" t="n"/>
-      <c r="M5" s="224" t="n"/>
+      <c r="L5" s="232" t="n"/>
+      <c r="M5" s="232" t="n"/>
       <c r="O5" s="203" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -6501,12 +6501,12 @@
       <c r="W5" s="97" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="226" t="inlineStr">
+      <c r="A6" s="220" t="inlineStr">
         <is>
           <t>byte size</t>
         </is>
       </c>
-      <c r="B6" s="230" t="inlineStr">
+      <c r="B6" s="226" t="inlineStr">
         <is>
           <t>The size of a distribution in bytes.</t>
         </is>
@@ -6526,27 +6526,27 @@
           <t>Describes the size of the distribution (the actual file) in bytes, and is therefore expressed as a non-negative integer. If the actual size is not known, it can be estimated.</t>
         </is>
       </c>
-      <c r="F6" s="231" t="inlineStr">
+      <c r="F6" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G6" s="231" t="inlineStr">
+      <c r="G6" s="227" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H6" s="231" t="inlineStr">
+      <c r="H6" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I6" s="225" t="inlineStr">
+      <c r="I6" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="224" t="inlineStr">
+      <c r="J6" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6556,8 +6556,8 @@
           <t>resource:size</t>
         </is>
       </c>
-      <c r="L6" s="225" t="n"/>
-      <c r="M6" s="225" t="n"/>
+      <c r="L6" s="218" t="n"/>
+      <c r="M6" s="218" t="n"/>
       <c r="O6" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6569,12 +6569,12 @@
         </is>
       </c>
       <c r="S6" s="121" t="n"/>
-      <c r="U6" s="226" t="n"/>
-      <c r="V6" s="226" t="n"/>
-      <c r="W6" s="226" t="n"/>
+      <c r="U6" s="220" t="n"/>
+      <c r="V6" s="220" t="n"/>
+      <c r="W6" s="220" t="n"/>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="220" t="inlineStr">
+      <c r="A7" s="230" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
@@ -6584,7 +6584,7 @@
           <t>The checksum property provides a mechanism that can be used to verify that the contents of a file or package have not changed.</t>
         </is>
       </c>
-      <c r="C7" s="220" t="inlineStr">
+      <c r="C7" s="230" t="inlineStr">
         <is>
           <t>spdx:checksum</t>
         </is>
@@ -6599,7 +6599,7 @@
           <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate the checksum algorithm and checksum value (see Checksum class for further details).</t>
         </is>
       </c>
-      <c r="F7" s="218" t="inlineStr">
+      <c r="F7" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6609,17 +6609,17 @@
           <t>spdx:Checksum</t>
         </is>
       </c>
-      <c r="H7" s="218" t="inlineStr">
+      <c r="H7" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="224" t="inlineStr">
+      <c r="I7" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="224" t="inlineStr">
+      <c r="J7" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6629,12 +6629,12 @@
           <t>resource:hash_algorithm/resource:hash_algorithm</t>
         </is>
       </c>
-      <c r="L7" s="224" t="inlineStr">
+      <c r="L7" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
       </c>
-      <c r="M7" s="224" t="inlineStr">
+      <c r="M7" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
@@ -6655,17 +6655,17 @@
         </is>
       </c>
       <c r="S7" s="121" t="n"/>
-      <c r="U7" s="220" t="n"/>
-      <c r="V7" s="220" t="n"/>
-      <c r="W7" s="220" t="n"/>
+      <c r="U7" s="230" t="n"/>
+      <c r="V7" s="230" t="n"/>
+      <c r="W7" s="230" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="226" t="inlineStr">
+      <c r="A8" s="220" t="inlineStr">
         <is>
           <t>compression format</t>
         </is>
       </c>
-      <c r="B8" s="230" t="inlineStr">
+      <c r="B8" s="226" t="inlineStr">
         <is>
           <t>The compression format of the distribution in which the data is compressed, e.g., to reduce the size of the downloadable file.</t>
         </is>
@@ -6685,27 +6685,27 @@
           <t>It MUST be expressed using a media type as defined in the official register of media types managed by IANA.</t>
         </is>
       </c>
-      <c r="F8" s="231" t="inlineStr">
+      <c r="F8" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="231" t="inlineStr">
+      <c r="G8" s="227" t="inlineStr">
         <is>
           <t>dct:MediaType (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="231" t="inlineStr">
+      <c r="H8" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I8" s="225" t="inlineStr">
+      <c r="I8" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="224" t="inlineStr">
+      <c r="J8" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6715,8 +6715,8 @@
           <t>resource:compress_format</t>
         </is>
       </c>
-      <c r="L8" s="225" t="n"/>
-      <c r="M8" s="225" t="n"/>
+      <c r="L8" s="218" t="n"/>
+      <c r="M8" s="218" t="n"/>
       <c r="O8" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -6728,12 +6728,12 @@
         </is>
       </c>
       <c r="S8" s="121" t="n"/>
-      <c r="U8" s="226" t="n"/>
-      <c r="V8" s="226" t="n"/>
-      <c r="W8" s="226" t="n"/>
+      <c r="U8" s="220" t="n"/>
+      <c r="V8" s="220" t="n"/>
+      <c r="W8" s="220" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="220" t="inlineStr">
+      <c r="A9" s="230" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6743,7 +6743,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C9" s="220" t="inlineStr">
+      <c r="C9" s="230" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -6758,27 +6758,27 @@
           <t>Provide specific details about the distribution here, complementing the description of the related Dataset. This field can be repeated for different language versions of the description.</t>
         </is>
       </c>
-      <c r="F9" s="218" t="inlineStr">
+      <c r="F9" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="218" t="inlineStr">
+      <c r="G9" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H9" s="218" t="inlineStr">
+      <c r="H9" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="224" t="inlineStr">
+      <c r="I9" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="224" t="inlineStr">
+      <c r="J9" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6788,8 +6788,8 @@
           <t>resource:description</t>
         </is>
       </c>
-      <c r="L9" s="224" t="n"/>
-      <c r="M9" s="224" t="n"/>
+      <c r="L9" s="232" t="n"/>
+      <c r="M9" s="232" t="n"/>
       <c r="O9" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6803,22 +6803,22 @@
       <c r="S9" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="U9" s="220" t="n"/>
-      <c r="V9" s="220" t="n"/>
-      <c r="W9" s="220" t="n"/>
+      <c r="U9" s="230" t="n"/>
+      <c r="V9" s="230" t="n"/>
+      <c r="W9" s="230" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="226" t="inlineStr">
+      <c r="A10" s="220" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
       </c>
-      <c r="B10" s="230" t="inlineStr">
+      <c r="B10" s="226" t="inlineStr">
         <is>
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C10" s="226" t="inlineStr">
+      <c r="C10" s="220" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -6833,27 +6833,27 @@
           <t>This page can contain additional information about the distribution.</t>
         </is>
       </c>
-      <c r="F10" s="231" t="inlineStr">
+      <c r="F10" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G10" s="231" t="inlineStr">
+      <c r="G10" s="227" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H10" s="231" t="inlineStr">
+      <c r="H10" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I10" s="225" t="inlineStr">
+      <c r="I10" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J10" s="224" t="inlineStr">
+      <c r="J10" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6863,8 +6863,8 @@
           <t>resource:documentation</t>
         </is>
       </c>
-      <c r="L10" s="225" t="n"/>
-      <c r="M10" s="225" t="n"/>
+      <c r="L10" s="218" t="n"/>
+      <c r="M10" s="218" t="n"/>
       <c r="O10" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6876,12 +6876,12 @@
         </is>
       </c>
       <c r="S10" s="121" t="n"/>
-      <c r="U10" s="226" t="n"/>
-      <c r="V10" s="226" t="n"/>
-      <c r="W10" s="226" t="n"/>
+      <c r="U10" s="220" t="n"/>
+      <c r="V10" s="220" t="n"/>
+      <c r="W10" s="220" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="220" t="inlineStr">
+      <c r="A11" s="230" t="inlineStr">
         <is>
           <t>download URL</t>
         </is>
@@ -6906,27 +6906,27 @@
           <t>If the dataset is openly accessible and available in a repository, you can directly include a link to the downloadable file here.</t>
         </is>
       </c>
-      <c r="F11" s="218" t="inlineStr">
+      <c r="F11" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="218" t="inlineStr">
+      <c r="G11" s="225" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="218" t="inlineStr">
+      <c r="H11" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="224" t="inlineStr">
+      <c r="I11" s="232" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="224" t="inlineStr">
+      <c r="J11" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6936,8 +6936,8 @@
           <t>resource:download_url</t>
         </is>
       </c>
-      <c r="L11" s="224" t="n"/>
-      <c r="M11" s="224" t="n"/>
+      <c r="L11" s="232" t="n"/>
+      <c r="M11" s="232" t="n"/>
       <c r="O11" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6949,22 +6949,22 @@
         </is>
       </c>
       <c r="S11" s="121" t="n"/>
-      <c r="U11" s="220" t="n"/>
-      <c r="V11" s="220" t="n"/>
-      <c r="W11" s="220" t="n"/>
+      <c r="U11" s="230" t="n"/>
+      <c r="V11" s="230" t="n"/>
+      <c r="W11" s="230" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="226" t="inlineStr">
+      <c r="A12" s="220" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="B12" s="230" t="inlineStr">
+      <c r="B12" s="226" t="inlineStr">
         <is>
           <t>The file format, physical medium, or dimensions of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="226" t="inlineStr">
+      <c r="C12" s="220" t="inlineStr">
         <is>
           <t>dct:format</t>
         </is>
@@ -6979,27 +6979,27 @@
           <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL from the File Type vocabulary.</t>
         </is>
       </c>
-      <c r="F12" s="231" t="inlineStr">
+      <c r="F12" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="231" t="inlineStr">
+      <c r="G12" s="227" t="inlineStr">
         <is>
           <t>dct:MediaTypeOrExtent (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="231" t="inlineStr">
+      <c r="H12" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I12" s="225" t="inlineStr">
+      <c r="I12" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="224" t="inlineStr">
+      <c r="J12" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7009,8 +7009,8 @@
           <t>resource:format</t>
         </is>
       </c>
-      <c r="L12" s="225" t="n"/>
-      <c r="M12" s="225" t="n"/>
+      <c r="L12" s="218" t="n"/>
+      <c r="M12" s="218" t="n"/>
       <c r="O12" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7022,12 +7022,12 @@
         </is>
       </c>
       <c r="S12" s="121" t="n"/>
-      <c r="U12" s="226" t="n"/>
-      <c r="V12" s="226" t="n"/>
-      <c r="W12" s="226" t="n"/>
+      <c r="U12" s="220" t="n"/>
+      <c r="V12" s="220" t="n"/>
+      <c r="W12" s="220" t="n"/>
     </row>
     <row r="13" ht="99" customHeight="1">
-      <c r="A13" s="220" t="inlineStr">
+      <c r="A13" s="230" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -7037,7 +7037,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="220" t="inlineStr">
+      <c r="C13" s="230" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -7047,33 +7047,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E13" s="223" t="inlineStr">
+      <c r="E13" s="231" t="inlineStr">
         <is>
           <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions necessarily have a language; for example, those containing imaging data may not.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="218" t="inlineStr">
+      <c r="F13" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="218" t="inlineStr">
+      <c r="G13" s="225" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H13" s="218" t="inlineStr">
+      <c r="H13" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="224" t="inlineStr">
+      <c r="I13" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="224" t="inlineStr">
+      <c r="J13" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7083,8 +7083,8 @@
           <t>resource:language</t>
         </is>
       </c>
-      <c r="L13" s="224" t="n"/>
-      <c r="M13" s="224" t="n"/>
+      <c r="L13" s="232" t="n"/>
+      <c r="M13" s="232" t="n"/>
       <c r="O13" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7096,22 +7096,22 @@
         </is>
       </c>
       <c r="S13" s="121" t="n"/>
-      <c r="U13" s="220" t="n"/>
-      <c r="V13" s="220" t="n"/>
-      <c r="W13" s="220" t="n"/>
+      <c r="U13" s="230" t="n"/>
+      <c r="V13" s="230" t="n"/>
+      <c r="W13" s="230" t="n"/>
     </row>
     <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="226" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
       </c>
-      <c r="B14" s="230" t="inlineStr">
+      <c r="B14" s="226" t="inlineStr">
         <is>
           <t>A legal document giving official permission to do something with the resource.</t>
         </is>
       </c>
-      <c r="C14" s="226" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>dct:license</t>
         </is>
@@ -7121,30 +7121,30 @@
           <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
         </is>
       </c>
-      <c r="E14" s="227" t="inlineStr">
+      <c r="E14" s="222" t="inlineStr">
         <is>
           <t>For public data, use a Creative Commons (CC) licence (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue distributions, where data is not public, use the 'not open' licence from Geonovum and specify data reuse agreements in the dct:rights property.</t>
         </is>
       </c>
-      <c r="F14" s="231" t="inlineStr">
+      <c r="F14" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G14" s="231" t="inlineStr">
+      <c r="G14" s="227" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="231" t="n">
+      <c r="H14" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="225" t="inlineStr">
+      <c r="I14" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J14" s="224" t="inlineStr">
+      <c r="J14" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -7154,8 +7154,8 @@
           <t>resource:license</t>
         </is>
       </c>
-      <c r="L14" s="225" t="n"/>
-      <c r="M14" s="225" t="n"/>
+      <c r="L14" s="218" t="n"/>
+      <c r="M14" s="218" t="n"/>
       <c r="O14" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7167,12 +7167,12 @@
         </is>
       </c>
       <c r="S14" s="121" t="n"/>
-      <c r="U14" s="226" t="n"/>
-      <c r="V14" s="226" t="n"/>
-      <c r="W14" s="226" t="n"/>
+      <c r="U14" s="220" t="n"/>
+      <c r="V14" s="220" t="n"/>
+      <c r="W14" s="220" t="n"/>
     </row>
     <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="220" t="inlineStr">
+      <c r="A15" s="230" t="inlineStr">
         <is>
           <t>linked schemas</t>
         </is>
@@ -7182,7 +7182,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C15" s="220" t="inlineStr">
+      <c r="C15" s="230" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -7197,27 +7197,27 @@
           <t xml:space="preserve">This property SHOULD be used to indicate the model, schema, ontology, view or profile that this representation of a dataset conforms to, in a machine-readable form. This is (generally) a complementary concern to the media-type or format. Use a reference to the official publication of the respective schema. </t>
         </is>
       </c>
-      <c r="F15" s="218" t="inlineStr">
+      <c r="F15" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="218" t="inlineStr">
+      <c r="G15" s="225" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="218" t="inlineStr">
+      <c r="H15" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="224" t="inlineStr">
+      <c r="I15" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="224" t="inlineStr">
+      <c r="J15" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7227,8 +7227,8 @@
           <t>resource:conforms_to</t>
         </is>
       </c>
-      <c r="L15" s="224" t="n"/>
-      <c r="M15" s="224" t="n"/>
+      <c r="L15" s="232" t="n"/>
+      <c r="M15" s="232" t="n"/>
       <c r="O15" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7240,22 +7240,22 @@
         </is>
       </c>
       <c r="S15" s="121" t="n"/>
-      <c r="U15" s="220" t="n"/>
-      <c r="V15" s="220" t="n"/>
-      <c r="W15" s="220" t="n"/>
+      <c r="U15" s="230" t="n"/>
+      <c r="V15" s="230" t="n"/>
+      <c r="W15" s="230" t="n"/>
     </row>
     <row r="16" ht="112" customHeight="1">
-      <c r="A16" s="226" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>media type</t>
         </is>
       </c>
-      <c r="B16" s="230" t="inlineStr">
+      <c r="B16" s="226" t="inlineStr">
         <is>
           <t>The media type of the distribution as defined by IANA.</t>
         </is>
       </c>
-      <c r="C16" s="226" t="inlineStr">
+      <c r="C16" s="220" t="inlineStr">
         <is>
           <t>dcat:mediaType</t>
         </is>
@@ -7265,34 +7265,34 @@
           <t>IANA Media Types</t>
         </is>
       </c>
-      <c r="E16" s="227" t="inlineStr">
+      <c r="E16" s="222" t="inlineStr">
         <is>
           <t>Use the specified vocabularies, prioritising IANA media types whenever possible. If unavailable, consider other ontologies, such as ZonMw generic terms, to describe the format.
 Example: https://www.iana.org/assignments/media-types/text/csv (for csv)
 If IANA media types do not sufficiently describe the format, use "format" to describe it in more detail.</t>
         </is>
       </c>
-      <c r="F16" s="231" t="inlineStr">
+      <c r="F16" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="231" t="inlineStr">
+      <c r="G16" s="227" t="inlineStr">
         <is>
           <t>dct:MediaType (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="231" t="inlineStr">
+      <c r="H16" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="225" t="inlineStr">
+      <c r="I16" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J16" s="224" t="inlineStr">
+      <c r="J16" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7302,8 +7302,8 @@
           <t>resource:mimetype</t>
         </is>
       </c>
-      <c r="L16" s="225" t="n"/>
-      <c r="M16" s="225" t="n"/>
+      <c r="L16" s="218" t="n"/>
+      <c r="M16" s="218" t="n"/>
       <c r="O16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7315,12 +7315,12 @@
         </is>
       </c>
       <c r="S16" s="121" t="n"/>
-      <c r="U16" s="226" t="n"/>
-      <c r="V16" s="226" t="n"/>
-      <c r="W16" s="226" t="n"/>
+      <c r="U16" s="220" t="n"/>
+      <c r="V16" s="220" t="n"/>
+      <c r="W16" s="220" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="220" t="inlineStr">
+      <c r="A17" s="230" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -7341,27 +7341,27 @@
         </is>
       </c>
       <c r="E17" s="98" t="n"/>
-      <c r="F17" s="218" t="inlineStr">
+      <c r="F17" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="218" t="inlineStr">
+      <c r="G17" s="225" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="218" t="inlineStr">
+      <c r="H17" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="224" t="inlineStr">
+      <c r="I17" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="224" t="inlineStr">
+      <c r="J17" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7371,8 +7371,8 @@
           <t>resource:modified</t>
         </is>
       </c>
-      <c r="L17" s="224" t="n"/>
-      <c r="M17" s="224" t="n"/>
+      <c r="L17" s="232" t="n"/>
+      <c r="M17" s="232" t="n"/>
       <c r="N17" s="219" t="n"/>
       <c r="O17" s="219" t="inlineStr">
         <is>
@@ -7390,22 +7390,22 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="U17" s="220" t="n"/>
-      <c r="V17" s="220" t="n"/>
-      <c r="W17" s="220" t="n"/>
+      <c r="U17" s="230" t="n"/>
+      <c r="V17" s="230" t="n"/>
+      <c r="W17" s="230" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="226" t="inlineStr">
+      <c r="A18" s="220" t="inlineStr">
         <is>
           <t>packaging format</t>
         </is>
       </c>
-      <c r="B18" s="230" t="inlineStr">
+      <c r="B18" s="226" t="inlineStr">
         <is>
           <t>The package format of the distribution in which one or more data files are grouped together, e.g., to enable a set of related files to be downloaded together.</t>
         </is>
       </c>
-      <c r="C18" s="226" t="inlineStr">
+      <c r="C18" s="220" t="inlineStr">
         <is>
           <t>dcat:packageFormat</t>
         </is>
@@ -7415,32 +7415,32 @@
           <t>IANA Media Types</t>
         </is>
       </c>
-      <c r="E18" s="230" t="inlineStr">
+      <c r="E18" s="226" t="inlineStr">
         <is>
           <t xml:space="preserve">It SHOULD be expressed using a media type as defined in the official register of media types managed by IANA. </t>
         </is>
       </c>
-      <c r="F18" s="231" t="inlineStr">
+      <c r="F18" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="231" t="inlineStr">
+      <c r="G18" s="227" t="inlineStr">
         <is>
           <t>dct:MediaType (IRI)</t>
         </is>
       </c>
-      <c r="H18" s="231" t="inlineStr">
+      <c r="H18" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="225" t="inlineStr">
+      <c r="I18" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="224" t="inlineStr">
+      <c r="J18" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7450,8 +7450,8 @@
           <t>resource:package_format</t>
         </is>
       </c>
-      <c r="L18" s="225" t="n"/>
-      <c r="M18" s="225" t="n"/>
+      <c r="L18" s="218" t="n"/>
+      <c r="M18" s="218" t="n"/>
       <c r="O18" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7463,12 +7463,12 @@
         </is>
       </c>
       <c r="S18" s="121" t="n"/>
-      <c r="U18" s="226" t="n"/>
-      <c r="V18" s="226" t="n"/>
-      <c r="W18" s="226" t="n"/>
+      <c r="U18" s="220" t="n"/>
+      <c r="V18" s="220" t="n"/>
+      <c r="W18" s="220" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="220" t="inlineStr">
+      <c r="A19" s="230" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -7478,7 +7478,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="220" t="inlineStr">
+      <c r="C19" s="230" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -7493,27 +7493,27 @@
           <t>The date the dataset distribution was issued.</t>
         </is>
       </c>
-      <c r="F19" s="218" t="inlineStr">
+      <c r="F19" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="218" t="inlineStr">
+      <c r="G19" s="225" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="218" t="inlineStr">
+      <c r="H19" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="224" t="inlineStr">
+      <c r="I19" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="224" t="inlineStr">
+      <c r="J19" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7523,8 +7523,8 @@
           <t>resource:issued</t>
         </is>
       </c>
-      <c r="L19" s="224" t="n"/>
-      <c r="M19" s="224" t="n"/>
+      <c r="L19" s="232" t="n"/>
+      <c r="M19" s="232" t="n"/>
       <c r="N19" s="219" t="n"/>
       <c r="O19" s="219" t="inlineStr">
         <is>
@@ -7542,12 +7542,12 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="U19" s="220" t="n"/>
-      <c r="V19" s="220" t="n"/>
-      <c r="W19" s="220" t="n"/>
+      <c r="U19" s="230" t="n"/>
+      <c r="V19" s="230" t="n"/>
+      <c r="W19" s="230" t="n"/>
     </row>
     <row r="20" ht="231" customHeight="1">
-      <c r="A20" s="226" t="inlineStr">
+      <c r="A20" s="220" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -7557,13 +7557,13 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C20" s="226" t="inlineStr">
+      <c r="C20" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:retentionperiod</t>
         </is>
       </c>
       <c r="D20" s="92" t="n"/>
-      <c r="E20" s="230" t="inlineStr">
+      <c r="E20" s="226" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the upcoming major release. It is recommended to indicate the planned availability of the distribution with the newly added Distribution.availability property. 
 Use this property if the Distribution is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
@@ -7573,7 +7573,7 @@
 If a limit is known, provide both dcat:startDate and dcat:endDate.</t>
         </is>
       </c>
-      <c r="F20" s="231" t="inlineStr">
+      <c r="F20" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7583,28 +7583,28 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H20" s="231" t="inlineStr">
+      <c r="H20" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="225" t="inlineStr">
+      <c r="I20" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="224" t="inlineStr">
+      <c r="J20" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K20" s="73" t="n"/>
-      <c r="L20" s="225" t="inlineStr">
+      <c r="L20" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M20" s="225" t="inlineStr">
+      <c r="M20" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -7625,12 +7625,12 @@
         </is>
       </c>
       <c r="S20" s="121" t="n"/>
-      <c r="U20" s="226" t="n"/>
-      <c r="V20" s="226" t="n"/>
-      <c r="W20" s="226" t="n"/>
+      <c r="U20" s="220" t="n"/>
+      <c r="V20" s="220" t="n"/>
+      <c r="W20" s="220" t="n"/>
     </row>
     <row r="21" ht="112" customHeight="1">
-      <c r="A21" s="220" t="inlineStr">
+      <c r="A21" s="230" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -7640,7 +7640,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C21" s="220" t="inlineStr">
+      <c r="C21" s="230" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -7661,7 +7661,7 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="218" t="inlineStr">
+      <c r="G21" s="225" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
@@ -7671,12 +7671,12 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I21" s="224" t="inlineStr">
+      <c r="I21" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J21" s="224" t="inlineStr">
+      <c r="J21" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7686,8 +7686,8 @@
           <t>resource:rights</t>
         </is>
       </c>
-      <c r="L21" s="224" t="n"/>
-      <c r="M21" s="224" t="n"/>
+      <c r="L21" s="232" t="n"/>
+      <c r="M21" s="232" t="n"/>
       <c r="O21" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7699,22 +7699,22 @@
         </is>
       </c>
       <c r="S21" s="121" t="n"/>
-      <c r="U21" s="220" t="n"/>
-      <c r="V21" s="220" t="n"/>
-      <c r="W21" s="220" t="n"/>
+      <c r="U21" s="230" t="n"/>
+      <c r="V21" s="230" t="n"/>
+      <c r="W21" s="230" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="226" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B22" s="230" t="inlineStr">
+      <c r="B22" s="226" t="inlineStr">
         <is>
           <t>The status of the Asset in the context of a particular workflow process.</t>
         </is>
       </c>
-      <c r="C22" s="226" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>adms:status</t>
         </is>
@@ -7730,27 +7730,27 @@
           <t>It MUST take one of the following values from the provided controlled vocabulary: Completed, Deprecated, Under Development or Withdrawn.</t>
         </is>
       </c>
-      <c r="F22" s="231" t="inlineStr">
+      <c r="F22" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G22" s="231" t="inlineStr">
+      <c r="G22" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="231" t="inlineStr">
+      <c r="H22" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I22" s="225" t="inlineStr">
+      <c r="I22" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="224" t="inlineStr">
+      <c r="J22" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7760,8 +7760,8 @@
           <t>resource:status</t>
         </is>
       </c>
-      <c r="L22" s="225" t="n"/>
-      <c r="M22" s="225" t="n"/>
+      <c r="L22" s="218" t="n"/>
+      <c r="M22" s="218" t="n"/>
       <c r="O22" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7773,12 +7773,12 @@
         </is>
       </c>
       <c r="S22" s="121" t="n"/>
-      <c r="U22" s="226" t="n"/>
-      <c r="V22" s="226" t="n"/>
-      <c r="W22" s="226" t="n"/>
+      <c r="U22" s="220" t="n"/>
+      <c r="V22" s="220" t="n"/>
+      <c r="W22" s="220" t="n"/>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="220" t="inlineStr">
+      <c r="A23" s="230" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
@@ -7788,7 +7788,7 @@
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
       </c>
-      <c r="C23" s="220" t="inlineStr">
+      <c r="C23" s="230" t="inlineStr">
         <is>
           <t>dcat:temporalResolution</t>
         </is>
@@ -7803,34 +7803,34 @@
           <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (for more information, see: https://www.w3schools.com/xml/schema_dtypes_date.asp).</t>
         </is>
       </c>
-      <c r="F23" s="218" t="inlineStr">
+      <c r="F23" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="218" t="inlineStr">
+      <c r="G23" s="225" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H23" s="218" t="inlineStr">
+      <c r="H23" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I23" s="224" t="inlineStr">
+      <c r="I23" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="224" t="inlineStr">
+      <c r="J23" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="74" t="n"/>
-      <c r="L23" s="224" t="n"/>
-      <c r="M23" s="224" t="n"/>
+      <c r="L23" s="232" t="n"/>
+      <c r="M23" s="232" t="n"/>
       <c r="O23" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7842,22 +7842,22 @@
         </is>
       </c>
       <c r="S23" s="121" t="n"/>
-      <c r="U23" s="220" t="n"/>
-      <c r="V23" s="220" t="n"/>
-      <c r="W23" s="220" t="n"/>
+      <c r="U23" s="230" t="n"/>
+      <c r="V23" s="230" t="n"/>
+      <c r="W23" s="230" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="226" t="inlineStr">
+      <c r="A24" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B24" s="230" t="inlineStr">
+      <c r="B24" s="226" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="226" t="inlineStr">
+      <c r="C24" s="220" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -7872,27 +7872,27 @@
           <t>A title given to the distribution, e.g. Data Access Request for the Healthy Brain Study</t>
         </is>
       </c>
-      <c r="F24" s="231" t="inlineStr">
+      <c r="F24" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="231" t="inlineStr">
+      <c r="G24" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="231" t="inlineStr">
+      <c r="H24" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="225" t="inlineStr">
+      <c r="I24" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J24" s="224" t="inlineStr">
+      <c r="J24" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7902,8 +7902,8 @@
           <t>resource:name</t>
         </is>
       </c>
-      <c r="L24" s="225" t="n"/>
-      <c r="M24" s="225" t="n"/>
+      <c r="L24" s="218" t="n"/>
+      <c r="M24" s="218" t="n"/>
       <c r="O24" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7917,9 +7917,9 @@
       <c r="S24" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="U24" s="226" t="n"/>
-      <c r="V24" s="226" t="n"/>
-      <c r="W24" s="226" t="n"/>
+      <c r="U24" s="220" t="n"/>
+      <c r="V24" s="220" t="n"/>
+      <c r="W24" s="220" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n"/>
@@ -8455,7 +8455,7 @@
     <col width="22.5" customWidth="1" style="221" min="1" max="1"/>
     <col width="43.5" bestFit="1" customWidth="1" style="221" min="2" max="2"/>
     <col width="26.5" customWidth="1" style="221" min="3" max="3"/>
-    <col width="24" customWidth="1" style="228" min="4" max="4"/>
+    <col width="24" customWidth="1" style="223" min="4" max="4"/>
     <col width="76.5" customWidth="1" style="221" min="5" max="5"/>
     <col width="16.5" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
     <col width="20.1640625" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
@@ -8466,8 +8466,8 @@
     <col width="24.6640625" customWidth="1" style="219" min="12" max="12"/>
     <col width="9.1640625" customWidth="1" style="219" min="13" max="18"/>
     <col width="22.5" customWidth="1" min="19" max="21"/>
-    <col width="9.1640625" customWidth="1" style="219" min="22" max="23"/>
-    <col width="9.1640625" customWidth="1" style="219" min="24" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="22" max="24"/>
+    <col width="9.1640625" customWidth="1" style="219" min="25" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customFormat="1" customHeight="1" s="163">
@@ -8583,32 +8583,32 @@
           <t>applicable legislation</t>
         </is>
       </c>
-      <c r="B2" s="230" t="inlineStr">
+      <c r="B2" s="226" t="inlineStr">
         <is>
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C2" s="230" t="inlineStr">
+      <c r="C2" s="226" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
       </c>
-      <c r="D2" s="230" t="inlineStr">
+      <c r="D2" s="226" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E2" s="230" t="inlineStr">
+      <c r="E2" s="226" t="inlineStr">
         <is>
           <t>The legislation that mandates the creation or management of the Dataset Series.</t>
         </is>
       </c>
-      <c r="F2" s="218" t="inlineStr">
+      <c r="F2" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="231" t="inlineStr">
+      <c r="G2" s="227" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -8623,7 +8623,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="224" t="inlineStr">
+      <c r="J2" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8633,7 +8633,7 @@
           <t>data_series:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="225" t="n"/>
+      <c r="L2" s="218" t="n"/>
       <c r="N2" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -8649,7 +8649,7 @@
       <c r="U2" s="155" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="220" t="inlineStr">
+      <c r="A3" s="230" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -8659,7 +8659,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C3" s="220" t="inlineStr">
+      <c r="C3" s="230" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -8675,7 +8675,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F3" s="218" t="inlineStr">
+      <c r="F3" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -8685,17 +8685,17 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H3" s="218" t="inlineStr">
+      <c r="H3" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="224" t="inlineStr">
+      <c r="I3" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="224" t="inlineStr">
+      <c r="J3" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8705,7 +8705,7 @@
           <t>data_series::contact</t>
         </is>
       </c>
-      <c r="L3" s="224" t="inlineStr">
+      <c r="L3" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -8725,22 +8725,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S3" s="220" t="n"/>
-      <c r="T3" s="220" t="n"/>
-      <c r="U3" s="220" t="n"/>
+      <c r="S3" s="230" t="n"/>
+      <c r="T3" s="230" t="n"/>
+      <c r="U3" s="230" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="226" t="inlineStr">
+      <c r="A4" s="220" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B4" s="230" t="inlineStr">
+      <c r="B4" s="226" t="inlineStr">
         <is>
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C4" s="226" t="inlineStr">
+      <c r="C4" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -8755,27 +8755,27 @@
           <t xml:space="preserve">Briefly describe the dataset series in the catalogue. You can repeat this in multiple languages. </t>
         </is>
       </c>
-      <c r="F4" s="231" t="inlineStr">
+      <c r="F4" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G4" s="231" t="inlineStr">
+      <c r="G4" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H4" s="231" t="inlineStr">
+      <c r="H4" s="227" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I4" s="225" t="inlineStr">
+      <c r="I4" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J4" s="224" t="inlineStr">
+      <c r="J4" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8785,7 +8785,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L4" s="225" t="n"/>
+      <c r="L4" s="218" t="n"/>
       <c r="N4" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -8799,12 +8799,12 @@
       <c r="R4" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="S4" s="226" t="n"/>
-      <c r="T4" s="226" t="n"/>
-      <c r="U4" s="226" t="n"/>
+      <c r="S4" s="220" t="n"/>
+      <c r="T4" s="220" t="n"/>
+      <c r="U4" s="220" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="220" t="inlineStr">
+      <c r="A5" s="230" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -8814,7 +8814,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C5" s="220" t="inlineStr">
+      <c r="C5" s="230" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -8829,33 +8829,33 @@
           <t>The frequency of a dataset series is not equal to the frequency of the dataset in the collection.</t>
         </is>
       </c>
-      <c r="F5" s="218" t="inlineStr">
+      <c r="F5" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="218" t="inlineStr">
+      <c r="G5" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="218" t="inlineStr">
+      <c r="H5" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="224" t="inlineStr">
+      <c r="I5" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="224" t="inlineStr">
+      <c r="J5" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="74" t="n"/>
-      <c r="L5" s="224" t="n"/>
+      <c r="L5" s="232" t="n"/>
       <c r="N5" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -8866,22 +8866,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S5" s="220" t="n"/>
-      <c r="T5" s="220" t="n"/>
-      <c r="U5" s="220" t="n"/>
+      <c r="S5" s="230" t="n"/>
+      <c r="T5" s="230" t="n"/>
+      <c r="U5" s="230" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="226" t="inlineStr">
+      <c r="A6" s="220" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B6" s="230" t="inlineStr">
+      <c r="B6" s="226" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C6" s="226" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -8891,32 +8891,32 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E6" s="227" t="inlineStr">
+      <c r="E6" s="222" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F6" s="231" t="inlineStr">
+      <c r="F6" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G6" s="231" t="inlineStr">
+      <c r="G6" s="227" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H6" s="231" t="inlineStr">
+      <c r="H6" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="225" t="inlineStr">
+      <c r="I6" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="224" t="inlineStr">
+      <c r="J6" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -8926,7 +8926,7 @@
           <t>data_series::coverage</t>
         </is>
       </c>
-      <c r="L6" s="225" t="n"/>
+      <c r="L6" s="218" t="n"/>
       <c r="N6" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -8937,9 +8937,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S6" s="226" t="n"/>
-      <c r="T6" s="226" t="n"/>
-      <c r="U6" s="226" t="n"/>
+      <c r="S6" s="220" t="n"/>
+      <c r="T6" s="220" t="n"/>
+      <c r="U6" s="220" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="D7" s="179" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="220" t="inlineStr">
+      <c r="A11" s="230" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -8980,7 +8980,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C11" s="220" t="inlineStr">
+      <c r="C11" s="230" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -8995,27 +8995,27 @@
           <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F11" s="218" t="inlineStr">
+      <c r="F11" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="218" t="inlineStr">
+      <c r="G11" s="225" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H11" s="218" t="inlineStr">
+      <c r="H11" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="224" t="inlineStr">
+      <c r="I11" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J11" s="224" t="inlineStr">
+      <c r="J11" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9025,7 +9025,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L11" s="224" t="n"/>
+      <c r="L11" s="232" t="n"/>
       <c r="N11" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9041,12 +9041,12 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S11" s="220" t="n"/>
-      <c r="T11" s="220" t="n"/>
-      <c r="U11" s="220" t="n"/>
+      <c r="S11" s="230" t="n"/>
+      <c r="T11" s="230" t="n"/>
+      <c r="U11" s="230" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="226" t="inlineStr">
+      <c r="A12" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -9056,7 +9056,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C12" s="226" t="inlineStr">
+      <c r="C12" s="220" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -9071,7 +9071,7 @@
           <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets. For example, a digital archive could take over the publishing of older datasets in the series. </t>
         </is>
       </c>
-      <c r="F12" s="218" t="inlineStr">
+      <c r="F12" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -9081,17 +9081,17 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H12" s="231" t="inlineStr">
+      <c r="H12" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I12" s="231" t="inlineStr">
+      <c r="I12" s="227" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J12" s="224" t="inlineStr">
+      <c r="J12" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9101,7 +9101,7 @@
           <t>data_series::publisher</t>
         </is>
       </c>
-      <c r="L12" s="225" t="inlineStr">
+      <c r="L12" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -9121,12 +9121,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S12" s="226" t="n"/>
-      <c r="T12" s="226" t="n"/>
-      <c r="U12" s="226" t="n"/>
+      <c r="S12" s="220" t="n"/>
+      <c r="T12" s="220" t="n"/>
+      <c r="U12" s="220" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="220" t="inlineStr">
+      <c r="A13" s="230" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -9136,7 +9136,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="220" t="inlineStr">
+      <c r="C13" s="230" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -9151,27 +9151,27 @@
           <t>The moment when the dataset series was established as a managed resource. This is not equal to the release date of the oldest dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F13" s="231" t="inlineStr">
+      <c r="F13" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="218" t="inlineStr">
+      <c r="G13" s="225" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H13" s="218" t="inlineStr">
+      <c r="H13" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I13" s="218" t="inlineStr">
+      <c r="I13" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J13" s="224" t="inlineStr">
+      <c r="J13" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9181,7 +9181,7 @@
           <t>data_series:issued</t>
         </is>
       </c>
-      <c r="L13" s="224" t="n"/>
+      <c r="L13" s="232" t="n"/>
       <c r="N13" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9197,22 +9197,22 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S13" s="220" t="n"/>
-      <c r="T13" s="220" t="n"/>
-      <c r="U13" s="220" t="n"/>
+      <c r="S13" s="230" t="n"/>
+      <c r="T13" s="230" t="n"/>
+      <c r="U13" s="230" t="n"/>
     </row>
     <row r="14" ht="49" customHeight="1">
-      <c r="A14" s="226" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
       </c>
-      <c r="B14" s="226" t="inlineStr">
+      <c r="B14" s="220" t="inlineStr">
         <is>
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C14" s="226" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -9227,7 +9227,7 @@
           <t>When temporal coverage is a dimension in the dataset series, the temporal coverage of each dataset in the collection should be part of the series' temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
         </is>
       </c>
-      <c r="F14" s="218" t="inlineStr">
+      <c r="F14" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -9247,7 +9247,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="224" t="inlineStr">
+      <c r="J14" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9257,7 +9257,7 @@
           <t>data_series::temporal</t>
         </is>
       </c>
-      <c r="L14" s="225" t="inlineStr">
+      <c r="L14" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -9277,22 +9277,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S14" s="226" t="n"/>
-      <c r="T14" s="226" t="n"/>
-      <c r="U14" s="226" t="n"/>
+      <c r="S14" s="220" t="n"/>
+      <c r="T14" s="220" t="n"/>
+      <c r="U14" s="220" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="220" t="inlineStr">
+      <c r="A15" s="230" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B15" s="220" t="inlineStr">
+      <c r="B15" s="230" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C15" s="220" t="inlineStr">
+      <c r="C15" s="230" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -9302,32 +9302,32 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="220" t="inlineStr">
+      <c r="E15" s="230" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide a unique title for your Dataset Series, which can be repeated in multiple languages. </t>
         </is>
       </c>
-      <c r="F15" s="231" t="inlineStr">
+      <c r="F15" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G15" s="218" t="inlineStr">
+      <c r="G15" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H15" s="218" t="inlineStr">
+      <c r="H15" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I15" s="218" t="inlineStr">
+      <c r="I15" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J15" s="224" t="inlineStr">
+      <c r="J15" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9337,7 +9337,7 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L15" s="224" t="n"/>
+      <c r="L15" s="232" t="n"/>
       <c r="N15" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9351,9 +9351,9 @@
       <c r="R15" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="S15" s="220" t="n"/>
-      <c r="T15" s="220" t="n"/>
-      <c r="U15" s="220" t="n"/>
+      <c r="S15" s="230" t="n"/>
+      <c r="T15" s="230" t="n"/>
+      <c r="U15" s="230" t="n"/>
     </row>
     <row r="16">
       <c r="K16" s="219" t="n"/>
@@ -9478,16 +9478,16 @@
   </sheetData>
   <autoFilter ref="A1:L15"/>
   <mergeCells count="11">
-    <mergeCell ref="K6:K10"/>
+    <mergeCell ref="J6:J10"/>
+    <mergeCell ref="C6:C10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="B6:B10"/>
+    <mergeCell ref="E6:E10"/>
     <mergeCell ref="F6:F10"/>
-    <mergeCell ref="C6:C10"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="G6:G10"/>
     <mergeCell ref="L6:L10"/>
-    <mergeCell ref="J6:J10"/>
-    <mergeCell ref="E6:E10"/>
+    <mergeCell ref="K6:K10"/>
     <mergeCell ref="A6:A10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
@@ -9732,7 +9732,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="220" t="inlineStr">
+      <c r="C2" s="230" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -9747,30 +9747,30 @@
           <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property must take one of the predefined values listed in the Access Rights Named Authority List provided by the Publications Office. This designation informs data users whether the dataset is considered open data or is classified as non-public. For example, for non-public data, use the value: http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC</t>
         </is>
       </c>
-      <c r="F2" s="218" t="inlineStr">
+      <c r="F2" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="218" t="inlineStr">
+      <c r="G2" s="225" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="218" t="n">
+      <c r="H2" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="224" t="inlineStr">
+      <c r="I2" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="224" t="inlineStr">
+      <c r="J2" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K2" s="224" t="inlineStr">
+      <c r="K2" s="232" t="inlineStr">
         <is>
           <t>access_service:access_rights</t>
         </is>
@@ -9791,17 +9791,17 @@
       <c r="U2" s="97" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="226" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>applicable legislation</t>
         </is>
       </c>
-      <c r="B3" s="230" t="inlineStr">
+      <c r="B3" s="226" t="inlineStr">
         <is>
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C3" s="226" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -9811,34 +9811,34 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="230" t="n"/>
-      <c r="F3" s="231" t="inlineStr">
+      <c r="E3" s="226" t="n"/>
+      <c r="F3" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G3" s="231" t="inlineStr">
+      <c r="G3" s="227" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
       </c>
-      <c r="H3" s="231" t="inlineStr">
+      <c r="H3" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="225" t="inlineStr">
+      <c r="I3" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="224" t="inlineStr">
+      <c r="J3" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K3" s="75" t="n"/>
-      <c r="L3" s="225" t="n"/>
+      <c r="L3" s="218" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9849,12 +9849,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S3" s="226" t="n"/>
-      <c r="T3" s="226" t="n"/>
-      <c r="U3" s="226" t="n"/>
+      <c r="S3" s="220" t="n"/>
+      <c r="T3" s="220" t="n"/>
+      <c r="U3" s="220" t="n"/>
     </row>
     <row r="4" ht="92.25" customHeight="1">
-      <c r="A4" s="220" t="inlineStr">
+      <c r="A4" s="230" t="inlineStr">
         <is>
           <t>application profile</t>
         </is>
@@ -9864,7 +9864,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C4" s="220" t="inlineStr">
+      <c r="C4" s="230" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -9879,33 +9879,33 @@
           <t>The standards referred to here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance, the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
         </is>
       </c>
-      <c r="F4" s="218" t="inlineStr">
+      <c r="F4" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="218" t="inlineStr">
+      <c r="G4" s="225" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="218" t="inlineStr">
+      <c r="H4" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="224" t="inlineStr">
+      <c r="I4" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="224" t="inlineStr">
+      <c r="J4" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K4" s="224" t="n"/>
-      <c r="L4" s="224" t="n"/>
+      <c r="K4" s="232" t="n"/>
+      <c r="L4" s="232" t="n"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9916,9 +9916,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S4" s="220" t="n"/>
-      <c r="T4" s="220" t="n"/>
-      <c r="U4" s="220" t="n"/>
+      <c r="S4" s="230" t="n"/>
+      <c r="T4" s="230" t="n"/>
+      <c r="U4" s="230" t="n"/>
     </row>
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="155" t="inlineStr">
@@ -9926,12 +9926,12 @@
           <t>contact point</t>
         </is>
       </c>
-      <c r="B5" s="230" t="inlineStr">
+      <c r="B5" s="226" t="inlineStr">
         <is>
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C5" s="226" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -9947,7 +9947,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F5" s="231" t="inlineStr">
+      <c r="F5" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -9957,21 +9957,21 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H5" s="231" t="n">
+      <c r="H5" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="225" t="inlineStr">
+      <c r="I5" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="224" t="inlineStr">
+      <c r="J5" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K5" s="75" t="n"/>
-      <c r="L5" s="225" t="inlineStr">
+      <c r="L5" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -9996,7 +9996,7 @@
       <c r="U5" s="155" t="n"/>
     </row>
     <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="220" t="inlineStr">
+      <c r="A6" s="230" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
@@ -10006,7 +10006,7 @@
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C6" s="220" t="inlineStr">
+      <c r="C6" s="230" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -10023,7 +10023,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="218" t="inlineStr">
+      <c r="F6" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -10033,23 +10033,23 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H6" s="218" t="inlineStr">
+      <c r="H6" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="224" t="inlineStr">
+      <c r="I6" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="224" t="inlineStr">
+      <c r="J6" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K6" s="75" t="n"/>
-      <c r="L6" s="224" t="inlineStr">
+      <c r="L6" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -10069,22 +10069,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S6" s="220" t="n"/>
-      <c r="T6" s="220" t="n"/>
-      <c r="U6" s="220" t="n"/>
+      <c r="S6" s="230" t="n"/>
+      <c r="T6" s="230" t="n"/>
+      <c r="U6" s="230" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="226" t="inlineStr">
+      <c r="A7" s="220" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
       </c>
-      <c r="B7" s="230" t="inlineStr">
+      <c r="B7" s="226" t="inlineStr">
         <is>
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C7" s="226" t="inlineStr">
+      <c r="C7" s="220" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -10095,33 +10095,33 @@
         </is>
       </c>
       <c r="E7" s="92" t="n"/>
-      <c r="F7" s="231" t="inlineStr">
+      <c r="F7" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G7" s="231" t="inlineStr">
+      <c r="G7" s="227" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H7" s="231" t="inlineStr">
+      <c r="H7" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I7" s="225" t="inlineStr">
+      <c r="I7" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="224" t="inlineStr">
+      <c r="J7" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K7" s="224" t="n"/>
-      <c r="L7" s="225" t="n"/>
+      <c r="K7" s="232" t="n"/>
+      <c r="L7" s="218" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10132,9 +10132,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S7" s="226" t="n"/>
-      <c r="T7" s="226" t="n"/>
-      <c r="U7" s="226" t="n"/>
+      <c r="S7" s="220" t="n"/>
+      <c r="T7" s="220" t="n"/>
+      <c r="U7" s="220" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="97" t="inlineStr">
@@ -10147,7 +10147,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="220" t="inlineStr">
+      <c r="C8" s="230" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -10162,43 +10162,43 @@
           <t>Briefly describe the data service provided. You can repeat this description in multiple languages. Example: A data service that provides API access to real-time electrocardiogram (ECG) monitoring data for clinical research applications.</t>
         </is>
       </c>
-      <c r="F8" s="218" t="inlineStr">
+      <c r="F8" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G8" s="218" t="inlineStr">
+      <c r="G8" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H8" s="218" t="inlineStr">
+      <c r="H8" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I8" s="224" t="inlineStr">
+      <c r="I8" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="224" t="inlineStr">
+      <c r="J8" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K8" s="224" t="inlineStr">
+      <c r="K8" s="232" t="inlineStr">
         <is>
           <t>access_service:description</t>
         </is>
       </c>
-      <c r="L8" s="224" t="n"/>
-      <c r="N8" s="224" t="inlineStr">
+      <c r="L8" s="232" t="n"/>
+      <c r="N8" s="232" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O8" s="224" t="inlineStr">
+      <c r="O8" s="232" t="inlineStr">
         <is>
           <t>dash:TextAreaEditor</t>
         </is>
@@ -10211,17 +10211,17 @@
       <c r="U8" s="97" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="226" t="inlineStr">
+      <c r="A9" s="220" t="inlineStr">
         <is>
           <t>endpoint description</t>
         </is>
       </c>
-      <c r="B9" s="230" t="inlineStr">
+      <c r="B9" s="226" t="inlineStr">
         <is>
           <t>A description of the services available via the endpoints, including their operations, parameters, etc.</t>
         </is>
       </c>
-      <c r="C9" s="226" t="inlineStr">
+      <c r="C9" s="220" t="inlineStr">
         <is>
           <t>dcat:endpointDescription</t>
         </is>
@@ -10236,25 +10236,25 @@
           <t>Provides technical documentation that explains how to access and interact with the data service’s endpoint.</t>
         </is>
       </c>
-      <c r="F9" s="231" t="inlineStr">
+      <c r="F9" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G9" s="231" t="inlineStr">
+      <c r="G9" s="227" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H9" s="231" t="n">
+      <c r="H9" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="225" t="inlineStr">
+      <c r="I9" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="224" t="inlineStr">
+      <c r="J9" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10264,7 +10264,7 @@
           <t>access_service:endpoint_description</t>
         </is>
       </c>
-      <c r="L9" s="225" t="n"/>
+      <c r="L9" s="218" t="n"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10275,12 +10275,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S9" s="226" t="n"/>
-      <c r="T9" s="226" t="n"/>
-      <c r="U9" s="226" t="n"/>
+      <c r="S9" s="220" t="n"/>
+      <c r="T9" s="220" t="n"/>
+      <c r="U9" s="220" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="220" t="inlineStr">
+      <c r="A10" s="230" t="inlineStr">
         <is>
           <t>endpoint URL</t>
         </is>
@@ -10290,7 +10290,7 @@
           <t>The root location or primary endpoint of the service (a Web-resolvable IRI).</t>
         </is>
       </c>
-      <c r="C10" s="220" t="inlineStr">
+      <c r="C10" s="230" t="inlineStr">
         <is>
           <t>dcat:endpointURL</t>
         </is>
@@ -10305,12 +10305,12 @@
           <t>Provide the URL of the endpoint that users can interact with to access the data service. This should be a direct link to the service's endpoint, such as an API URL, SPARQL endpoint, or similar.</t>
         </is>
       </c>
-      <c r="F10" s="218" t="inlineStr">
+      <c r="F10" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G10" s="218" t="inlineStr">
+      <c r="G10" s="225" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -10318,12 +10318,12 @@
       <c r="H10" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="224" t="inlineStr">
+      <c r="I10" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="224" t="inlineStr">
+      <c r="J10" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10333,7 +10333,7 @@
           <t>access_service:endpoint_url</t>
         </is>
       </c>
-      <c r="L10" s="224" t="n"/>
+      <c r="L10" s="232" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10344,17 +10344,17 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S10" s="220" t="n"/>
-      <c r="T10" s="220" t="n"/>
-      <c r="U10" s="220" t="n"/>
+      <c r="S10" s="230" t="n"/>
+      <c r="T10" s="230" t="n"/>
+      <c r="U10" s="230" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="226" t="inlineStr">
+      <c r="A11" s="220" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="B11" s="230" t="inlineStr">
+      <c r="B11" s="226" t="inlineStr">
         <is>
           <t>The file format, physical medium, or dimensions of the resource.</t>
         </is>
@@ -10370,33 +10370,33 @@
         </is>
       </c>
       <c r="E11" s="92" t="n"/>
-      <c r="F11" s="231" t="inlineStr">
+      <c r="F11" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="231" t="inlineStr">
+      <c r="G11" s="227" t="inlineStr">
         <is>
           <t>dct:MediaTypeOrExtent (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="231" t="inlineStr">
+      <c r="H11" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I11" s="225" t="inlineStr">
+      <c r="I11" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J11" s="224" t="inlineStr">
+      <c r="J11" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K11" s="224" t="n"/>
-      <c r="L11" s="225" t="n"/>
+      <c r="K11" s="232" t="n"/>
+      <c r="L11" s="218" t="n"/>
       <c r="N11" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -10407,12 +10407,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S11" s="226" t="n"/>
-      <c r="T11" s="226" t="n"/>
-      <c r="U11" s="226" t="n"/>
+      <c r="S11" s="220" t="n"/>
+      <c r="T11" s="220" t="n"/>
+      <c r="U11" s="220" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="220" t="inlineStr">
+      <c r="A12" s="230" t="inlineStr">
         <is>
           <t>HVD Category</t>
         </is>
@@ -10422,7 +10422,7 @@
           <t>A data category defined in the High Value Dataset Implementing Regulation.</t>
         </is>
       </c>
-      <c r="C12" s="220" t="inlineStr">
+      <c r="C12" s="230" t="inlineStr">
         <is>
           <t>dcatap:hvdCategory</t>
         </is>
@@ -10433,33 +10433,33 @@
         </is>
       </c>
       <c r="E12" s="98" t="n"/>
-      <c r="F12" s="218" t="inlineStr">
+      <c r="F12" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="218" t="inlineStr">
+      <c r="G12" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="218" t="inlineStr">
+      <c r="H12" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I12" s="224" t="inlineStr">
+      <c r="I12" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="224" t="inlineStr">
+      <c r="J12" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K12" s="75" t="n"/>
-      <c r="L12" s="224" t="n"/>
+      <c r="L12" s="232" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10470,9 +10470,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S12" s="220" t="n"/>
-      <c r="T12" s="220" t="n"/>
-      <c r="U12" s="220" t="n"/>
+      <c r="S12" s="230" t="n"/>
+      <c r="T12" s="230" t="n"/>
+      <c r="U12" s="230" t="n"/>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="155" t="inlineStr">
@@ -10480,7 +10480,7 @@
           <t>identifier</t>
         </is>
       </c>
-      <c r="B13" s="230" t="inlineStr">
+      <c r="B13" s="226" t="inlineStr">
         <is>
           <t>An unambiguous reference to the resource within a given context.</t>
         </is>
@@ -10500,37 +10500,37 @@
           <t>Provide a unique identifier for the data service. This could be a globally unique and persistent identifier, such as a DOI, URN, or UUID. If no persistent identifier is available, you may use the accessURL or endpointURL as the identifier, provided it is stable and unique to the service.</t>
         </is>
       </c>
-      <c r="F13" s="231" t="inlineStr">
+      <c r="F13" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G13" s="231" t="inlineStr">
+      <c r="G13" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H13" s="231" t="n">
+      <c r="H13" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="225" t="inlineStr">
+      <c r="I13" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="224" t="inlineStr">
+      <c r="J13" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K13" s="75" t="n"/>
-      <c r="L13" s="225" t="n"/>
-      <c r="N13" s="224" t="inlineStr">
+      <c r="L13" s="218" t="n"/>
+      <c r="N13" s="232" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O13" s="224" t="inlineStr">
+      <c r="O13" s="232" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -10540,7 +10540,7 @@
       <c r="U13" s="155" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="220" t="inlineStr">
+      <c r="A14" s="230" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -10550,7 +10550,7 @@
           <t>A keyword or tag describing the resource.</t>
         </is>
       </c>
-      <c r="C14" s="220" t="inlineStr">
+      <c r="C14" s="230" t="inlineStr">
         <is>
           <t>dcat:keyword</t>
         </is>
@@ -10561,59 +10561,59 @@
         </is>
       </c>
       <c r="E14" s="29" t="n"/>
-      <c r="F14" s="218" t="inlineStr">
+      <c r="F14" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="218" t="inlineStr">
+      <c r="G14" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H14" s="218" t="inlineStr">
+      <c r="H14" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="224" t="inlineStr">
+      <c r="I14" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="224" t="inlineStr">
+      <c r="J14" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="75" t="n"/>
-      <c r="L14" s="224" t="n"/>
-      <c r="N14" s="224" t="inlineStr">
+      <c r="L14" s="232" t="n"/>
+      <c r="N14" s="232" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O14" s="224" t="inlineStr">
+      <c r="O14" s="232" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="S14" s="220" t="n"/>
-      <c r="T14" s="220" t="n"/>
-      <c r="U14" s="220" t="n"/>
+      <c r="S14" s="230" t="n"/>
+      <c r="T14" s="230" t="n"/>
+      <c r="U14" s="230" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="226" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>landing page</t>
         </is>
       </c>
-      <c r="B15" s="230" t="inlineStr">
+      <c r="B15" s="226" t="inlineStr">
         <is>
           <t>A Web page that can be navigated to in a Web browser to gain access to the catalogue, a dataset, its distributions and/or additional information.</t>
         </is>
       </c>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>dcat:landingPage</t>
         </is>
@@ -10628,33 +10628,33 @@
           <t>It is intended to point to a landing page at the original data service provider, not to a page on a third-party site, such as an aggregator.</t>
         </is>
       </c>
-      <c r="F15" s="231" t="inlineStr">
+      <c r="F15" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="231" t="inlineStr">
+      <c r="G15" s="227" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="231" t="inlineStr">
+      <c r="H15" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="225" t="inlineStr">
+      <c r="I15" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="224" t="inlineStr">
+      <c r="J15" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K15" s="75" t="n"/>
-      <c r="L15" s="225" t="n"/>
+      <c r="L15" s="218" t="n"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10665,12 +10665,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S15" s="226" t="n"/>
-      <c r="T15" s="226" t="n"/>
-      <c r="U15" s="226" t="n"/>
+      <c r="S15" s="220" t="n"/>
+      <c r="T15" s="220" t="n"/>
+      <c r="U15" s="220" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="220" t="inlineStr">
+      <c r="A16" s="230" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -10680,7 +10680,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C16" s="220" t="inlineStr">
+      <c r="C16" s="230" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -10695,33 +10695,33 @@
           <t>Indicates the natural language used in the data service, indicated with a value from the EU controlled vocabulary.</t>
         </is>
       </c>
-      <c r="F16" s="218" t="inlineStr">
+      <c r="F16" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="218" t="inlineStr">
+      <c r="G16" s="225" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="218" t="inlineStr">
+      <c r="H16" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I16" s="224" t="inlineStr">
+      <c r="I16" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="224" t="inlineStr">
+      <c r="J16" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K16" s="75" t="n"/>
-      <c r="L16" s="224" t="n"/>
+      <c r="L16" s="232" t="n"/>
       <c r="N16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -10732,22 +10732,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S16" s="220" t="n"/>
-      <c r="T16" s="220" t="n"/>
-      <c r="U16" s="220" t="n"/>
+      <c r="S16" s="230" t="n"/>
+      <c r="T16" s="230" t="n"/>
+      <c r="U16" s="230" t="n"/>
     </row>
     <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="226" t="inlineStr">
+      <c r="A17" s="220" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
       </c>
-      <c r="B17" s="230" t="inlineStr">
+      <c r="B17" s="226" t="inlineStr">
         <is>
           <t>A legal document giving official permission to do something with the resource.</t>
         </is>
       </c>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="C17" s="220" t="inlineStr">
         <is>
           <t>dct:license</t>
         </is>
@@ -10757,40 +10757,40 @@
           <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
         </is>
       </c>
-      <c r="E17" s="227" t="inlineStr">
+      <c r="E17" s="222" t="inlineStr">
         <is>
           <t>For public data, use a Creative Commons (CC) licence (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue data services, where data is not public, use the 'not open' licence from Geonovum and specify data reuse agreements in the dct:rights property.</t>
         </is>
       </c>
-      <c r="F17" s="231" t="inlineStr">
+      <c r="F17" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G17" s="231" t="inlineStr">
+      <c r="G17" s="227" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H17" s="231" t="n">
+      <c r="H17" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="225" t="inlineStr">
+      <c r="I17" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="224" t="inlineStr">
+      <c r="J17" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K17" s="224" t="inlineStr">
+      <c r="K17" s="232" t="inlineStr">
         <is>
           <t>access_service:license</t>
         </is>
       </c>
-      <c r="L17" s="225" t="n"/>
+      <c r="L17" s="218" t="n"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10801,12 +10801,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S17" s="226" t="n"/>
-      <c r="T17" s="226" t="n"/>
-      <c r="U17" s="226" t="n"/>
+      <c r="S17" s="220" t="n"/>
+      <c r="T17" s="220" t="n"/>
+      <c r="U17" s="220" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="220" t="inlineStr">
+      <c r="A18" s="230" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -10816,7 +10816,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C18" s="220" t="inlineStr">
+      <c r="C18" s="230" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -10831,33 +10831,33 @@
           <t>This property indicates the date of the last changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F18" s="218" t="inlineStr">
+      <c r="F18" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="218" t="inlineStr">
+      <c r="G18" s="225" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H18" s="218" t="inlineStr">
+      <c r="H18" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="224" t="inlineStr">
+      <c r="I18" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="224" t="inlineStr">
+      <c r="J18" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K18" s="75" t="n"/>
-      <c r="L18" s="224" t="n"/>
+      <c r="L18" s="232" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -10873,17 +10873,17 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S18" s="220" t="n"/>
-      <c r="T18" s="220" t="n"/>
-      <c r="U18" s="220" t="n"/>
+      <c r="S18" s="230" t="n"/>
+      <c r="T18" s="230" t="n"/>
+      <c r="U18" s="230" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="226" t="inlineStr">
+      <c r="A19" s="220" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="226" t="inlineStr">
         <is>
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="E19" s="92" t="n"/>
-      <c r="F19" s="231" t="inlineStr">
+      <c r="F19" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -10909,23 +10909,23 @@
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H19" s="231" t="inlineStr">
+      <c r="H19" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I19" s="225" t="inlineStr">
+      <c r="I19" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="224" t="inlineStr">
+      <c r="J19" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K19" s="75" t="n"/>
-      <c r="L19" s="225" t="inlineStr">
+      <c r="L19" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'adms_Identifier' tab.</t>
         </is>
@@ -10945,12 +10945,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S19" s="226" t="n"/>
-      <c r="T19" s="226" t="n"/>
-      <c r="U19" s="226" t="n"/>
+      <c r="S19" s="220" t="n"/>
+      <c r="T19" s="220" t="n"/>
+      <c r="U19" s="220" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="220" t="inlineStr">
+      <c r="A20" s="230" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -10960,7 +10960,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C20" s="220" t="inlineStr">
+      <c r="C20" s="230" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -10975,7 +10975,7 @@
           <t>The organisation or individual responsible for making the data service available. In the context of data services, the publisher is typically the organisation that manages or provides access to the service. For details, see the class Agent.</t>
         </is>
       </c>
-      <c r="F20" s="218" t="inlineStr">
+      <c r="F20" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -10985,21 +10985,21 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H20" s="218" t="n">
+      <c r="H20" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="224" t="inlineStr">
+      <c r="I20" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="224" t="inlineStr">
+      <c r="J20" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K20" s="224" t="n"/>
-      <c r="L20" s="224" t="inlineStr">
+      <c r="K20" s="232" t="n"/>
+      <c r="L20" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -11019,22 +11019,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S20" s="220" t="n"/>
-      <c r="T20" s="220" t="n"/>
-      <c r="U20" s="220" t="n"/>
+      <c r="S20" s="230" t="n"/>
+      <c r="T20" s="230" t="n"/>
+      <c r="U20" s="230" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="226" t="inlineStr">
+      <c r="A21" s="220" t="inlineStr">
         <is>
           <t>serves dataset</t>
         </is>
       </c>
-      <c r="B21" s="230" t="inlineStr">
+      <c r="B21" s="226" t="inlineStr">
         <is>
           <t>A collection of data that this data service can distribute.</t>
         </is>
       </c>
-      <c r="C21" s="226" t="inlineStr">
+      <c r="C21" s="220" t="inlineStr">
         <is>
           <t>dcat:servesDataset</t>
         </is>
@@ -11049,7 +11049,7 @@
           <t>This property connects the Data Service class to its corresponding dataset(s), ensuring every data service links to at least one dcat:Dataset. While essential for metadata implementation teams on each node, it’s less relevant for researchers to collect.</t>
         </is>
       </c>
-      <c r="F21" s="231" t="inlineStr">
+      <c r="F21" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11059,22 +11059,22 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H21" s="231" t="inlineStr">
+      <c r="H21" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I21" s="225" t="inlineStr">
+      <c r="I21" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="224" t="inlineStr">
+      <c r="J21" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="224" t="inlineStr">
+      <c r="K21" s="232" t="inlineStr">
         <is>
           <t>access_service:serves_dataset</t>
         </is>
@@ -11099,12 +11099,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S21" s="226" t="n"/>
-      <c r="T21" s="226" t="n"/>
-      <c r="U21" s="226" t="n"/>
+      <c r="S21" s="220" t="n"/>
+      <c r="T21" s="220" t="n"/>
+      <c r="U21" s="220" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="220" t="inlineStr">
+      <c r="A22" s="230" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -11114,7 +11114,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C22" s="220" t="inlineStr">
+      <c r="C22" s="230" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -11129,33 +11129,33 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, most data services will use NAL:data-theme 'HEAL', but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F22" s="218" t="inlineStr">
+      <c r="F22" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G22" s="218" t="inlineStr">
+      <c r="G22" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="218" t="inlineStr">
+      <c r="H22" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I22" s="224" t="inlineStr">
+      <c r="I22" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="224" t="inlineStr">
+      <c r="J22" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K22" s="75" t="n"/>
-      <c r="L22" s="224" t="n"/>
+      <c r="L22" s="232" t="n"/>
       <c r="N22" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -11171,17 +11171,17 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="S22" s="220" t="n"/>
-      <c r="T22" s="220" t="n"/>
-      <c r="U22" s="220" t="n"/>
+      <c r="S22" s="230" t="n"/>
+      <c r="T22" s="230" t="n"/>
+      <c r="U22" s="230" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="226" t="inlineStr">
+      <c r="A23" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="226" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
@@ -11201,27 +11201,27 @@
           <t>Provide a unique title for your data service, which can be repeated in multiple languages. Example: Patient counts per available diagnosis.</t>
         </is>
       </c>
-      <c r="F23" s="231" t="inlineStr">
+      <c r="F23" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G23" s="231" t="inlineStr">
+      <c r="G23" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H23" s="231" t="inlineStr">
+      <c r="H23" s="227" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I23" s="225" t="inlineStr">
+      <c r="I23" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J23" s="224" t="inlineStr">
+      <c r="J23" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -11232,12 +11232,12 @@
         </is>
       </c>
       <c r="L23" s="159" t="n"/>
-      <c r="N23" s="224" t="inlineStr">
+      <c r="N23" s="232" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O23" s="224" t="inlineStr">
+      <c r="O23" s="232" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -11245,9 +11245,9 @@
       <c r="R23" t="b">
         <v>1</v>
       </c>
-      <c r="S23" s="226" t="n"/>
-      <c r="T23" s="226" t="n"/>
-      <c r="U23" s="226" t="n"/>
+      <c r="S23" s="220" t="n"/>
+      <c r="T23" s="220" t="n"/>
+      <c r="U23" s="220" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="n"/>
@@ -12197,8 +12197,8 @@
     <col width="32.1640625" customWidth="1" style="234" min="18" max="18"/>
     <col width="9.1640625" customWidth="1" style="234" min="19" max="24"/>
     <col width="24.5" customWidth="1" min="25" max="27"/>
-    <col width="9.1640625" customWidth="1" style="234" min="28" max="29"/>
-    <col width="9.1640625" customWidth="1" style="234" min="30" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="30"/>
+    <col width="9.1640625" customWidth="1" style="234" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="112" customHeight="1">
@@ -13239,8 +13239,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
-    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
+    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -13827,8 +13827,8 @@
     <col width="28.83203125" customWidth="1" style="58" min="15" max="15"/>
     <col width="9.1640625" customWidth="1" style="58" min="16" max="21"/>
     <col width="20.1640625" customWidth="1" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="58" min="25" max="26"/>
-    <col width="9.1640625" customWidth="1" style="58" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="58" min="25" max="27"/>
+    <col width="9.1640625" customWidth="1" style="58" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="80" customHeight="1">
@@ -15119,8 +15119,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
-    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
+    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -16129,8 +16129,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
-    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
+    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -17135,8 +17135,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
-    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
+    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="P2" s="219" t="inlineStr">
         <is>
-          <t>dash:LiteralViewer</t>
+          <t>dash:URIViewer</t>
         </is>
       </c>
       <c r="Q2" s="219" t="inlineStr">
         <is>
-          <t>dash:TextFieldEditor</t>
+          <t>dash:URIEditor</t>
         </is>
       </c>
       <c r="U2" s="31" t="n"/>
@@ -18259,8 +18259,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="25"/>
-    <col width="9.1640625" customWidth="1" style="234" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
+    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -20396,7 +20396,7 @@
     <col width="20" bestFit="1" customWidth="1" style="221" min="1" max="1"/>
     <col width="40.5" customWidth="1" style="221" min="2" max="2"/>
     <col width="25.5" bestFit="1" customWidth="1" style="221" min="3" max="3"/>
-    <col width="25.5" customWidth="1" style="228" min="4" max="4"/>
+    <col width="25.5" customWidth="1" style="223" min="4" max="4"/>
     <col width="54.5" customWidth="1" style="221" min="5" max="5"/>
     <col width="22.1640625" customWidth="1" style="219" min="6" max="6"/>
     <col width="24" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
@@ -20408,8 +20408,8 @@
     <col width="27" customWidth="1" style="219" min="13" max="13"/>
     <col width="9.1640625" customWidth="1" style="219" min="14" max="19"/>
     <col width="20" customWidth="1" min="20" max="22"/>
-    <col width="9.1640625" customWidth="1" style="219" min="23" max="24"/>
-    <col width="9.1640625" customWidth="1" style="219" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="23" max="25"/>
+    <col width="9.1640625" customWidth="1" style="219" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="64" customFormat="1" customHeight="1" s="163">
@@ -20546,12 +20546,12 @@
         </is>
       </c>
       <c r="E2" s="98" t="n"/>
-      <c r="F2" s="218" t="inlineStr">
+      <c r="F2" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="218" t="inlineStr">
+      <c r="G2" s="225" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -20561,12 +20561,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I2" s="224" t="inlineStr">
+      <c r="I2" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="224" t="inlineStr">
+      <c r="J2" s="232" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -20576,8 +20576,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="224" t="n"/>
-      <c r="M2" s="224" t="n"/>
+      <c r="L2" s="232" t="n"/>
+      <c r="M2" s="232" t="n"/>
       <c r="O2" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20594,17 +20594,17 @@
       <c r="V2" s="97" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="226" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>catalogue</t>
         </is>
       </c>
-      <c r="B3" s="230" t="inlineStr">
+      <c r="B3" s="226" t="inlineStr">
         <is>
           <t>A catalogue that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C3" s="226" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dcat:catalog</t>
         </is>
@@ -20619,7 +20619,7 @@
           <t>For certain research projects, multiple catalogues may need to be organised in a nested manner. This property serves to connect the different catalogues with each other.</t>
         </is>
       </c>
-      <c r="F3" s="231" t="inlineStr">
+      <c r="F3" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20629,28 +20629,28 @@
           <t>dcat:Catalog</t>
         </is>
       </c>
-      <c r="H3" s="231" t="inlineStr">
+      <c r="H3" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="225" t="inlineStr">
+      <c r="I3" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J3" s="224" t="inlineStr">
+      <c r="J3" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K3" s="232" t="n"/>
+      <c r="K3" s="228" t="n"/>
       <c r="L3" s="100" t="inlineStr">
         <is>
           <t>If applicable, enter the URI of the connected dcat:Catalog.</t>
         </is>
       </c>
-      <c r="M3" s="225" t="n"/>
+      <c r="M3" s="218" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>hrishapes:CatalogShape</t>
@@ -20667,9 +20667,9 @@
         </is>
       </c>
       <c r="S3" s="69" t="n"/>
-      <c r="T3" s="226" t="n"/>
-      <c r="U3" s="226" t="n"/>
-      <c r="V3" s="226" t="n"/>
+      <c r="T3" s="220" t="n"/>
+      <c r="U3" s="220" t="n"/>
+      <c r="V3" s="220" t="n"/>
     </row>
     <row r="4" ht="95.25" customHeight="1">
       <c r="A4" s="97" t="inlineStr">
@@ -20682,7 +20682,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C4" s="220" t="inlineStr">
+      <c r="C4" s="230" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -20698,7 +20698,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F4" s="218" t="inlineStr">
+      <c r="F4" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20708,30 +20708,30 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H4" s="218" t="n">
+      <c r="H4" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="224" t="inlineStr">
+      <c r="I4" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="224" t="inlineStr">
+      <c r="J4" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K4" s="224" t="inlineStr">
+      <c r="K4" s="232" t="inlineStr">
         <is>
           <t>custom:contact</t>
         </is>
       </c>
-      <c r="L4" s="224" t="inlineStr">
+      <c r="L4" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M4" s="224" t="inlineStr">
+      <c r="M4" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -20757,17 +20757,17 @@
       <c r="V4" s="97" t="n"/>
     </row>
     <row r="5" ht="192" customHeight="1">
-      <c r="A5" s="226" t="inlineStr">
+      <c r="A5" s="220" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
       </c>
-      <c r="B5" s="230" t="inlineStr">
+      <c r="B5" s="226" t="inlineStr">
         <is>
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C5" s="226" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -20784,7 +20784,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F5" s="231" t="inlineStr">
+      <c r="F5" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20794,28 +20794,28 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H5" s="231" t="inlineStr">
+      <c r="H5" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I5" s="225" t="inlineStr">
+      <c r="I5" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="224" t="n"/>
-      <c r="K5" s="232" t="inlineStr">
+      <c r="J5" s="232" t="n"/>
+      <c r="K5" s="228" t="inlineStr">
         <is>
           <t>custom:creator</t>
         </is>
       </c>
-      <c r="L5" s="225" t="inlineStr">
+      <c r="L5" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M5" s="225" t="inlineStr">
+      <c r="M5" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -20836,12 +20836,12 @@
         </is>
       </c>
       <c r="S5" s="69" t="n"/>
-      <c r="T5" s="226" t="n"/>
-      <c r="U5" s="226" t="n"/>
-      <c r="V5" s="226" t="n"/>
+      <c r="T5" s="220" t="n"/>
+      <c r="U5" s="220" t="n"/>
+      <c r="V5" s="220" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="220" t="inlineStr">
+      <c r="A6" s="230" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
@@ -20851,7 +20851,7 @@
           <t>A dataset that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C6" s="220" t="inlineStr">
+      <c r="C6" s="230" t="inlineStr">
         <is>
           <t>dcat:dataset</t>
         </is>
@@ -20866,7 +20866,7 @@
           <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="218" t="inlineStr">
+      <c r="F6" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20881,12 +20881,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="224" t="inlineStr">
+      <c r="I6" s="232" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J6" s="224" t="inlineStr">
+      <c r="J6" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20897,7 +20897,7 @@
           <t>Enter the URI for all datasets contained in this catalogue.</t>
         </is>
       </c>
-      <c r="M6" s="224" t="n"/>
+      <c r="M6" s="232" t="n"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -20914,22 +20914,22 @@
         </is>
       </c>
       <c r="S6" s="69" t="n"/>
-      <c r="T6" s="220" t="n"/>
-      <c r="U6" s="220" t="n"/>
-      <c r="V6" s="220" t="n"/>
+      <c r="T6" s="230" t="n"/>
+      <c r="U6" s="230" t="n"/>
+      <c r="V6" s="230" t="n"/>
     </row>
     <row r="7" ht="29" customHeight="1">
-      <c r="A7" s="226" t="inlineStr">
+      <c r="A7" s="220" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B7" s="230" t="inlineStr">
+      <c r="B7" s="226" t="inlineStr">
         <is>
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C7" s="226" t="inlineStr">
+      <c r="C7" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -20944,38 +20944,38 @@
           <t>Briefly describe the catalogue and what it contains. You can repeat this in multiple languages.</t>
         </is>
       </c>
-      <c r="F7" s="231" t="inlineStr">
+      <c r="F7" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G7" s="231" t="inlineStr">
+      <c r="G7" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H7" s="231" t="inlineStr">
+      <c r="H7" s="227" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I7" s="225" t="inlineStr">
+      <c r="I7" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J7" s="224" t="inlineStr">
+      <c r="J7" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K7" s="232" t="inlineStr">
+      <c r="K7" s="228" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="L7" s="225" t="n"/>
-      <c r="M7" s="225" t="n"/>
+      <c r="L7" s="218" t="n"/>
+      <c r="M7" s="218" t="n"/>
       <c r="O7" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -20989,22 +20989,22 @@
       <c r="S7" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T7" s="226" t="n"/>
-      <c r="U7" s="226" t="n"/>
-      <c r="V7" s="226" t="n"/>
+      <c r="T7" s="220" t="n"/>
+      <c r="U7" s="220" t="n"/>
+      <c r="V7" s="220" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1">
-      <c r="A8" s="220" t="inlineStr">
+      <c r="A8" s="230" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B8" s="222" t="inlineStr">
+      <c r="B8" s="229" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="220" t="inlineStr">
+      <c r="C8" s="230" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -21014,39 +21014,39 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E8" s="223" t="inlineStr">
+      <c r="E8" s="231" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used.</t>
         </is>
       </c>
-      <c r="F8" s="218" t="inlineStr">
+      <c r="F8" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="218" t="inlineStr">
+      <c r="G8" s="225" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="218" t="inlineStr">
+      <c r="H8" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="224" t="inlineStr">
+      <c r="I8" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="224" t="inlineStr">
+      <c r="J8" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K8" s="103" t="n"/>
-      <c r="L8" s="224" t="n"/>
-      <c r="M8" s="224" t="n"/>
+      <c r="L8" s="232" t="n"/>
+      <c r="M8" s="232" t="n"/>
       <c r="O8" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21058,9 +21058,9 @@
         </is>
       </c>
       <c r="S8" s="69" t="n"/>
-      <c r="T8" s="220" t="n"/>
-      <c r="U8" s="220" t="n"/>
-      <c r="V8" s="220" t="n"/>
+      <c r="T8" s="230" t="n"/>
+      <c r="U8" s="230" t="n"/>
+      <c r="V8" s="230" t="n"/>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="D9" s="177" t="inlineStr">
@@ -21099,17 +21099,17 @@
       <c r="S12" s="69" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="226" t="inlineStr">
+      <c r="A13" s="220" t="inlineStr">
         <is>
           <t>has part</t>
         </is>
       </c>
-      <c r="B13" s="230" t="inlineStr">
+      <c r="B13" s="226" t="inlineStr">
         <is>
           <t>A related resource that is included either physically or logically in the described resource.</t>
         </is>
       </c>
-      <c r="C13" s="226" t="inlineStr">
+      <c r="C13" s="220" t="inlineStr">
         <is>
           <t>dct:hasPart</t>
         </is>
@@ -21125,7 +21125,7 @@
 Note that deeply nested structures should be avoided, and cannot currently be displayed in the National Health Data Catalogue.</t>
         </is>
       </c>
-      <c r="F13" s="231" t="inlineStr">
+      <c r="F13" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21135,17 +21135,17 @@
           <t>dcat:Catalog</t>
         </is>
       </c>
-      <c r="H13" s="231" t="inlineStr">
+      <c r="H13" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="225" t="inlineStr">
+      <c r="I13" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="224" t="inlineStr">
+      <c r="J13" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21156,7 +21156,7 @@
           <t>If applicable, add the URI of the dcat:Catalog that is part of this catalogue.</t>
         </is>
       </c>
-      <c r="M13" s="225" t="n"/>
+      <c r="M13" s="218" t="n"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>hrishapes:CatalogShape</t>
@@ -21173,12 +21173,12 @@
         </is>
       </c>
       <c r="S13" s="69" t="n"/>
-      <c r="T13" s="226" t="n"/>
-      <c r="U13" s="226" t="n"/>
-      <c r="V13" s="226" t="n"/>
+      <c r="T13" s="220" t="n"/>
+      <c r="U13" s="220" t="n"/>
+      <c r="V13" s="220" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="220" t="inlineStr">
+      <c r="A14" s="230" t="inlineStr">
         <is>
           <t>home page</t>
         </is>
@@ -21188,7 +21188,7 @@
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C14" s="220" t="inlineStr">
+      <c r="C14" s="230" t="inlineStr">
         <is>
           <t>foaf:homepage</t>
         </is>
@@ -21203,34 +21203,34 @@
           <t>The home page of the catalogue, if available.</t>
         </is>
       </c>
-      <c r="F14" s="218" t="inlineStr">
+      <c r="F14" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="218" t="inlineStr">
+      <c r="G14" s="225" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="218" t="inlineStr">
+      <c r="H14" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I14" s="224" t="inlineStr">
+      <c r="I14" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="224" t="inlineStr">
+      <c r="J14" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="103" t="n"/>
-      <c r="L14" s="224" t="n"/>
-      <c r="M14" s="224" t="n"/>
+      <c r="L14" s="232" t="n"/>
+      <c r="M14" s="232" t="n"/>
       <c r="O14" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21242,22 +21242,22 @@
         </is>
       </c>
       <c r="S14" s="69" t="n"/>
-      <c r="T14" s="220" t="n"/>
-      <c r="U14" s="220" t="n"/>
-      <c r="V14" s="220" t="n"/>
+      <c r="T14" s="230" t="n"/>
+      <c r="U14" s="230" t="n"/>
+      <c r="V14" s="230" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="226" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="B15" s="230" t="inlineStr">
+      <c r="B15" s="226" t="inlineStr">
         <is>
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -21267,33 +21267,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E15" s="230" t="inlineStr">
+      <c r="E15" s="226" t="inlineStr">
         <is>
           <t>The value of this property must be an IRI from the provided controlled vocabulary.
 For example: http://publications.europa.eu/resource/authority/language/NLD</t>
         </is>
       </c>
-      <c r="F15" s="231" t="inlineStr">
+      <c r="F15" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="231" t="inlineStr">
+      <c r="G15" s="227" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="231" t="inlineStr">
+      <c r="H15" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="225" t="inlineStr">
+      <c r="I15" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="224" t="inlineStr">
+      <c r="J15" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21303,8 +21303,8 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L15" s="225" t="n"/>
-      <c r="M15" s="225" t="n"/>
+      <c r="L15" s="218" t="n"/>
+      <c r="M15" s="218" t="n"/>
       <c r="O15" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21316,12 +21316,12 @@
         </is>
       </c>
       <c r="S15" s="69" t="n"/>
-      <c r="T15" s="226" t="n"/>
-      <c r="U15" s="226" t="n"/>
-      <c r="V15" s="226" t="n"/>
+      <c r="T15" s="220" t="n"/>
+      <c r="U15" s="220" t="n"/>
+      <c r="V15" s="220" t="n"/>
     </row>
     <row r="16" ht="85.25" customHeight="1">
-      <c r="A16" s="220" t="inlineStr">
+      <c r="A16" s="230" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
@@ -21347,27 +21347,27 @@
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
         </is>
       </c>
-      <c r="F16" s="218" t="inlineStr">
+      <c r="F16" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="218" t="inlineStr">
+      <c r="G16" s="225" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="218" t="inlineStr">
+      <c r="H16" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="224" t="inlineStr">
+      <c r="I16" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="224" t="inlineStr">
+      <c r="J16" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21377,8 +21377,8 @@
           <t>custom:licence</t>
         </is>
       </c>
-      <c r="L16" s="224" t="n"/>
-      <c r="M16" s="224" t="n"/>
+      <c r="L16" s="232" t="n"/>
+      <c r="M16" s="232" t="n"/>
       <c r="O16" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21390,22 +21390,22 @@
         </is>
       </c>
       <c r="S16" s="69" t="n"/>
-      <c r="T16" s="220" t="n"/>
-      <c r="U16" s="220" t="n"/>
-      <c r="V16" s="220" t="n"/>
+      <c r="T16" s="230" t="n"/>
+      <c r="U16" s="230" t="n"/>
+      <c r="V16" s="230" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="226" t="inlineStr">
+      <c r="A17" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
       </c>
-      <c r="B17" s="230" t="inlineStr">
+      <c r="B17" s="226" t="inlineStr">
         <is>
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="C17" s="220" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -21416,27 +21416,27 @@
         </is>
       </c>
       <c r="E17" s="100" t="n"/>
-      <c r="F17" s="231" t="inlineStr">
+      <c r="F17" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="231" t="inlineStr">
+      <c r="G17" s="227" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="231" t="inlineStr">
+      <c r="H17" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="225" t="inlineStr">
+      <c r="I17" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="224" t="inlineStr">
+      <c r="J17" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21446,8 +21446,8 @@
           <t>custom:modified</t>
         </is>
       </c>
-      <c r="L17" s="225" t="n"/>
-      <c r="M17" s="225" t="n"/>
+      <c r="L17" s="218" t="n"/>
+      <c r="M17" s="218" t="n"/>
       <c r="O17" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21464,12 +21464,12 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="T17" s="226" t="n"/>
-      <c r="U17" s="226" t="n"/>
-      <c r="V17" s="226" t="n"/>
+      <c r="T17" s="220" t="n"/>
+      <c r="U17" s="220" t="n"/>
+      <c r="V17" s="220" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="220" t="inlineStr">
+      <c r="A18" s="230" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -21494,7 +21494,7 @@
           <t>The organisation or individual that is the holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
         </is>
       </c>
-      <c r="F18" s="218" t="inlineStr">
+      <c r="F18" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -21504,15 +21504,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H18" s="218" t="n">
+      <c r="H18" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="224" t="inlineStr">
+      <c r="I18" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J18" s="224" t="inlineStr">
+      <c r="J18" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21522,12 +21522,12 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L18" s="224" t="inlineStr">
+      <c r="L18" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M18" s="224" t="inlineStr">
+      <c r="M18" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -21548,22 +21548,22 @@
         </is>
       </c>
       <c r="S18" s="69" t="n"/>
-      <c r="T18" s="220" t="n"/>
-      <c r="U18" s="220" t="n"/>
-      <c r="V18" s="220" t="n"/>
+      <c r="T18" s="230" t="n"/>
+      <c r="U18" s="230" t="n"/>
+      <c r="V18" s="230" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="226" t="inlineStr">
+      <c r="A19" s="220" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
       </c>
-      <c r="B19" s="230" t="inlineStr">
+      <c r="B19" s="226" t="inlineStr">
         <is>
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="226" t="inlineStr">
+      <c r="C19" s="220" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -21574,27 +21574,27 @@
         </is>
       </c>
       <c r="E19" s="92" t="n"/>
-      <c r="F19" s="231" t="inlineStr">
+      <c r="F19" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="231" t="inlineStr">
+      <c r="G19" s="227" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="231" t="inlineStr">
+      <c r="H19" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="225" t="inlineStr">
+      <c r="I19" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="225" t="inlineStr">
+      <c r="J19" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21604,8 +21604,8 @@
           <t>custom:issued</t>
         </is>
       </c>
-      <c r="L19" s="225" t="n"/>
-      <c r="M19" s="225" t="n"/>
+      <c r="L19" s="218" t="n"/>
+      <c r="M19" s="218" t="n"/>
       <c r="O19" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21622,12 +21622,12 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="T19" s="226" t="n"/>
-      <c r="U19" s="226" t="n"/>
-      <c r="V19" s="226" t="n"/>
+      <c r="T19" s="220" t="n"/>
+      <c r="U19" s="220" t="n"/>
+      <c r="V19" s="220" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="220" t="inlineStr">
+      <c r="A20" s="230" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -21637,7 +21637,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C20" s="220" t="inlineStr">
+      <c r="C20" s="230" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -21652,34 +21652,34 @@
           <t>The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
         </is>
       </c>
-      <c r="F20" s="218" t="inlineStr">
+      <c r="F20" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G20" s="218" t="inlineStr">
+      <c r="G20" s="225" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H20" s="218" t="inlineStr">
+      <c r="H20" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="224" t="inlineStr">
+      <c r="I20" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="224" t="inlineStr">
+      <c r="J20" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K20" s="75" t="n"/>
-      <c r="L20" s="224" t="n"/>
-      <c r="M20" s="224" t="n"/>
+      <c r="L20" s="232" t="n"/>
+      <c r="M20" s="232" t="n"/>
       <c r="O20" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21691,22 +21691,22 @@
         </is>
       </c>
       <c r="S20" s="69" t="n"/>
-      <c r="T20" s="220" t="n"/>
-      <c r="U20" s="220" t="n"/>
-      <c r="V20" s="220" t="n"/>
+      <c r="T20" s="230" t="n"/>
+      <c r="U20" s="230" t="n"/>
+      <c r="V20" s="230" t="n"/>
     </row>
     <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="226" t="inlineStr">
+      <c r="A21" s="220" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B21" s="230" t="inlineStr">
+      <c r="B21" s="226" t="inlineStr">
         <is>
           <t>A service that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C21" s="226" t="inlineStr">
+      <c r="C21" s="220" t="inlineStr">
         <is>
           <t>dcat:service</t>
         </is>
@@ -21721,38 +21721,38 @@
           <t>Some datasets may have real-time Data Services (e.g., Beacon API counting individuals). IT teams should define the relationship between the catalogue and the Data Service via this property. While crucial for interoperability, this property is not relevant for end users to collect.</t>
         </is>
       </c>
-      <c r="F21" s="231" t="inlineStr">
+      <c r="F21" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="231" t="inlineStr">
+      <c r="G21" s="227" t="inlineStr">
         <is>
           <t>dcat:DataService</t>
         </is>
       </c>
-      <c r="H21" s="231" t="inlineStr">
+      <c r="H21" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I21" s="225" t="inlineStr">
+      <c r="I21" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="225" t="inlineStr">
+      <c r="J21" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="232" t="n"/>
+      <c r="K21" s="228" t="n"/>
       <c r="L21" s="100" t="inlineStr">
         <is>
           <t>If applicable, enter the URI for dcat:DataService.</t>
         </is>
       </c>
-      <c r="M21" s="225" t="n"/>
+      <c r="M21" s="218" t="n"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>hrishapes:DataServiceShape</t>
@@ -21769,12 +21769,12 @@
         </is>
       </c>
       <c r="S21" s="69" t="n"/>
-      <c r="T21" s="226" t="n"/>
-      <c r="U21" s="226" t="n"/>
-      <c r="V21" s="226" t="n"/>
+      <c r="T21" s="220" t="n"/>
+      <c r="U21" s="220" t="n"/>
+      <c r="V21" s="220" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="220" t="inlineStr">
+      <c r="A22" s="230" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -21784,7 +21784,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C22" s="220" t="inlineStr">
+      <c r="C22" s="230" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="E22" s="29" t="n"/>
-      <c r="F22" s="218" t="inlineStr">
+      <c r="F22" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21805,17 +21805,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H22" s="218" t="inlineStr">
+      <c r="H22" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="224" t="inlineStr">
+      <c r="I22" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="224" t="inlineStr">
+      <c r="J22" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21825,8 +21825,8 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L22" s="224" t="n"/>
-      <c r="M22" s="224" t="n"/>
+      <c r="L22" s="232" t="n"/>
+      <c r="M22" s="232" t="n"/>
       <c r="N22" s="219" t="inlineStr">
         <is>
           <t>hrishapes:PeriodOfTimeShape</t>
@@ -21843,17 +21843,17 @@
         </is>
       </c>
       <c r="S22" s="69" t="n"/>
-      <c r="T22" s="220" t="n"/>
-      <c r="U22" s="220" t="n"/>
-      <c r="V22" s="220" t="n"/>
+      <c r="T22" s="230" t="n"/>
+      <c r="U22" s="230" t="n"/>
+      <c r="V22" s="230" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="226" t="inlineStr">
+      <c r="A23" s="220" t="inlineStr">
         <is>
           <t>themes</t>
         </is>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="226" t="inlineStr">
         <is>
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
@@ -21873,34 +21873,34 @@
           <t>This property refers to a knowledge organisation system used to classify the Catalogue's Datasets. It must include at least the value NAL:data-theme as this is the mandatory controlled vocabulary for dcat:theme.</t>
         </is>
       </c>
-      <c r="F23" s="231" t="inlineStr">
+      <c r="F23" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="231" t="inlineStr">
+      <c r="G23" s="227" t="inlineStr">
         <is>
           <t>skos:ConceptScheme (IRI)</t>
         </is>
       </c>
-      <c r="H23" s="231" t="inlineStr">
+      <c r="H23" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I23" s="225" t="inlineStr">
+      <c r="I23" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="225" t="inlineStr">
+      <c r="J23" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="170" t="n"/>
-      <c r="L23" s="225" t="n"/>
-      <c r="M23" s="225" t="n"/>
+      <c r="L23" s="218" t="n"/>
+      <c r="M23" s="218" t="n"/>
       <c r="O23" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21912,12 +21912,12 @@
         </is>
       </c>
       <c r="S23" s="69" t="n"/>
-      <c r="T23" s="226" t="n"/>
-      <c r="U23" s="226" t="n"/>
-      <c r="V23" s="226" t="n"/>
+      <c r="T23" s="220" t="n"/>
+      <c r="U23" s="220" t="n"/>
+      <c r="V23" s="220" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="220" t="inlineStr">
+      <c r="A24" s="230" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -21927,7 +21927,7 @@
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="220" t="inlineStr">
+      <c r="C24" s="230" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -21942,27 +21942,27 @@
           <t>Provide a unique title for your catalogue, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
         </is>
       </c>
-      <c r="F24" s="218" t="inlineStr">
+      <c r="F24" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G24" s="218" t="inlineStr">
+      <c r="G24" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="218" t="inlineStr">
+      <c r="H24" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I24" s="224" t="inlineStr">
+      <c r="I24" s="232" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J24" s="224" t="inlineStr">
+      <c r="J24" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21972,8 +21972,8 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L24" s="224" t="n"/>
-      <c r="M24" s="224" t="n"/>
+      <c r="L24" s="232" t="n"/>
+      <c r="M24" s="232" t="n"/>
       <c r="O24" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21987,16 +21987,16 @@
       <c r="S24" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="220" t="n"/>
-      <c r="U24" s="220" t="n"/>
-      <c r="V24" s="220" t="n"/>
+      <c r="T24" s="230" t="n"/>
+      <c r="U24" s="230" t="n"/>
+      <c r="V24" s="230" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J24"/>
   <mergeCells count="11">
     <mergeCell ref="H8:H12"/>
+    <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A8:A12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="I8:I12"/>
@@ -22142,8 +22142,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="221" min="1" max="1"/>
     <col width="40.5" customWidth="1" style="221" min="2" max="2"/>
     <col width="28.83203125" customWidth="1" style="221" min="3" max="3"/>
-    <col width="22.5" customWidth="1" style="228" min="4" max="4"/>
-    <col width="68.83203125" customWidth="1" style="228" min="5" max="5"/>
+    <col width="22.5" customWidth="1" style="223" min="4" max="4"/>
+    <col width="68.83203125" customWidth="1" style="223" min="5" max="5"/>
     <col width="18.5" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
     <col width="22.83203125" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
     <col width="13.5" customWidth="1" style="219" min="8" max="8"/>
@@ -22156,8 +22156,8 @@
     <col width="25.83203125" customWidth="1" style="219" min="15" max="15"/>
     <col width="9.1640625" customWidth="1" style="219" min="16" max="21"/>
     <col width="25.5" customWidth="1" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="219" min="25" max="26"/>
-    <col width="9.1640625" customWidth="1" style="219" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="25" max="27"/>
+    <col width="9.1640625" customWidth="1" style="219" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customFormat="1" customHeight="1" s="163">
@@ -22293,7 +22293,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="220" t="inlineStr">
+      <c r="C2" s="230" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -22312,25 +22312,25 @@
 Since most data contain personal information, these datasets will need to take the value 'non-public' for the access rights property.</t>
         </is>
       </c>
-      <c r="F2" s="218" t="inlineStr">
+      <c r="F2" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="218" t="inlineStr">
+      <c r="G2" s="225" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="218" t="n">
+      <c r="H2" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="224" t="inlineStr">
+      <c r="I2" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="224" t="inlineStr">
+      <c r="J2" s="232" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -22340,7 +22340,7 @@
           <t>custom:access_rights</t>
         </is>
       </c>
-      <c r="L2" s="224" t="n"/>
+      <c r="L2" s="232" t="n"/>
       <c r="P2" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22356,17 +22356,17 @@
       <c r="X2" s="97" t="n"/>
     </row>
     <row r="3" ht="209.25" customHeight="1">
-      <c r="A3" s="226" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
       </c>
-      <c r="B3" s="230" t="inlineStr">
+      <c r="B3" s="226" t="inlineStr">
         <is>
           <t>An alternative name for the dataset.</t>
         </is>
       </c>
-      <c r="C3" s="226" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dct:alternative</t>
         </is>
@@ -22376,40 +22376,40 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="230" t="inlineStr">
+      <c r="E3" s="226" t="inlineStr">
         <is>
           <t>This property contains an alternative name for the Dataset. This property can be repeated for parallel language versions of the alternative name.</t>
         </is>
       </c>
-      <c r="F3" s="218" t="inlineStr">
+      <c r="F3" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G3" s="231" t="inlineStr">
+      <c r="G3" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H3" s="231" t="inlineStr">
+      <c r="H3" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="225" t="inlineStr">
+      <c r="I3" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="224" t="inlineStr">
+      <c r="J3" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K3" s="232" t="n"/>
+      <c r="K3" s="228" t="n"/>
       <c r="L3" s="100" t="n"/>
-      <c r="M3" s="225" t="n"/>
-      <c r="N3" s="225" t="n"/>
+      <c r="M3" s="218" t="n"/>
+      <c r="N3" s="218" t="n"/>
       <c r="P3" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -22420,9 +22420,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V3" s="226" t="n"/>
-      <c r="W3" s="226" t="n"/>
-      <c r="X3" s="226" t="n"/>
+      <c r="V3" s="220" t="n"/>
+      <c r="W3" s="220" t="n"/>
+      <c r="X3" s="220" t="n"/>
     </row>
     <row r="4" ht="112" customHeight="1">
       <c r="A4" s="97" t="inlineStr">
@@ -22450,7 +22450,7 @@
           <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would be Data Services rather than Distributions.</t>
         </is>
       </c>
-      <c r="F4" s="231" t="inlineStr">
+      <c r="F4" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22460,17 +22460,17 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H4" s="218" t="inlineStr">
+      <c r="H4" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="224" t="inlineStr">
+      <c r="I4" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="224" t="inlineStr">
+      <c r="J4" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22480,7 +22480,7 @@
           <t>custom:analytics</t>
         </is>
       </c>
-      <c r="L4" s="224" t="inlineStr">
+      <c r="L4" s="232" t="inlineStr">
         <is>
           <t>If available, add the URI for the analytics distribution here.</t>
         </is>
@@ -22510,17 +22510,17 @@
       <c r="X4" s="97" t="n"/>
     </row>
     <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="226" t="inlineStr">
+      <c r="A5" s="220" t="inlineStr">
         <is>
           <t>anatomical location covered</t>
         </is>
       </c>
-      <c r="B5" s="230" t="inlineStr">
+      <c r="B5" s="226" t="inlineStr">
         <is>
           <t>Relates a dataset to an anatomical class that is Anatomical structure (SNOMED CT 91723000) or one of its subclasses, describing anatomical coverage of the dataset as a whole at metadata or catalogue level.</t>
         </is>
       </c>
-      <c r="C5" s="226" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>hri:anatomicalLocationCovered</t>
         </is>
@@ -22530,33 +22530,33 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E5" s="230" t="inlineStr">
+      <c r="E5" s="226" t="inlineStr">
         <is>
           <t>Use this property to indicate which anatomical parts of the body are covered by the Dataset. Select the relevant anatomical structure from SNOMED CT. Multiple anatomical locations can be provided.
 Example: A dataset containing lung imaging data can use Lung structure (http://snomed.info/id/39607008).</t>
         </is>
       </c>
-      <c r="F5" s="231" t="inlineStr">
+      <c r="F5" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="231" t="inlineStr">
+      <c r="G5" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="231" t="inlineStr">
+      <c r="H5" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I5" s="225" t="n"/>
-      <c r="J5" s="224" t="n"/>
-      <c r="K5" s="232" t="n"/>
+      <c r="I5" s="218" t="n"/>
+      <c r="J5" s="232" t="n"/>
+      <c r="K5" s="228" t="n"/>
       <c r="L5" s="100" t="n"/>
-      <c r="M5" s="225" t="n"/>
-      <c r="N5" s="225" t="n"/>
+      <c r="M5" s="218" t="n"/>
+      <c r="N5" s="218" t="n"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22572,9 +22572,9 @@
           <t>^http://snomed\.info/id/[0-9]{6,18}$</t>
         </is>
       </c>
-      <c r="V5" s="226" t="n"/>
-      <c r="W5" s="226" t="n"/>
-      <c r="X5" s="226" t="n"/>
+      <c r="V5" s="220" t="n"/>
+      <c r="W5" s="220" t="n"/>
+      <c r="X5" s="220" t="n"/>
     </row>
     <row r="6" ht="176" customFormat="1" customHeight="1" s="83">
       <c r="A6" s="97" t="inlineStr">
@@ -22587,7 +22587,7 @@
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C6" s="220" t="inlineStr">
+      <c r="C6" s="230" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -22605,12 +22605,12 @@
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) describes the legal basis for initial collection and processing of (personal) data.</t>
         </is>
       </c>
-      <c r="F6" s="218" t="inlineStr">
+      <c r="F6" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G6" s="218" t="inlineStr">
+      <c r="G6" s="225" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -22620,12 +22620,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="224" t="inlineStr">
+      <c r="I6" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="224" t="inlineStr">
+      <c r="J6" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22635,7 +22635,7 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L6" s="224" t="n"/>
+      <c r="L6" s="232" t="n"/>
       <c r="P6" s="83" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22656,12 +22656,12 @@
       <c r="X6" s="97" t="n"/>
     </row>
     <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="226" t="inlineStr">
+      <c r="A7" s="220" t="inlineStr">
         <is>
           <t>code values</t>
         </is>
       </c>
-      <c r="B7" s="230" t="inlineStr">
+      <c r="B7" s="226" t="inlineStr">
         <is>
           <t>Health classifications and their codes associated with the dataset</t>
         </is>
@@ -22682,39 +22682,39 @@
 Inside this property, you can provide the coding system of the dataset in the form of a Wikidata URI (example: https://www.wikidata.org/entity/P494 for ICD-10 ID) and the URI of the value that describes the dataset (example: https://icd.who.int/browse10/2019/en#/Y59.0 for viral vaccines).</t>
         </is>
       </c>
-      <c r="F7" s="231" t="inlineStr">
+      <c r="F7" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G7" s="231" t="inlineStr">
+      <c r="G7" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H7" s="231" t="inlineStr">
+      <c r="H7" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I7" s="225" t="inlineStr">
+      <c r="I7" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="224" t="inlineStr">
+      <c r="J7" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K7" s="232" t="inlineStr">
+      <c r="K7" s="228" t="inlineStr">
         <is>
           <t>custom:code_values</t>
         </is>
       </c>
-      <c r="L7" s="225" t="n"/>
-      <c r="M7" s="225" t="n"/>
-      <c r="N7" s="225" t="n"/>
+      <c r="L7" s="218" t="n"/>
+      <c r="M7" s="218" t="n"/>
+      <c r="N7" s="218" t="n"/>
       <c r="P7" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22725,12 +22725,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V7" s="226" t="n"/>
-      <c r="W7" s="226" t="n"/>
-      <c r="X7" s="226" t="n"/>
+      <c r="V7" s="220" t="n"/>
+      <c r="W7" s="220" t="n"/>
+      <c r="X7" s="220" t="n"/>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="220" t="inlineStr">
+      <c r="A8" s="230" t="inlineStr">
         <is>
           <t>coding system</t>
         </is>
@@ -22740,7 +22740,7 @@
           <t>Coding systems in use (e.g. ICD-10-CM, DGRs, SNOMED CT, ...)</t>
         </is>
       </c>
-      <c r="C8" s="220" t="inlineStr">
+      <c r="C8" s="230" t="inlineStr">
         <is>
           <t>healthdcatap:hasCodingSystem</t>
         </is>
@@ -22756,27 +22756,27 @@
 This property provides information on which coding systems are in use in your dataset. For this, Wikidata URIs must be used.</t>
         </is>
       </c>
-      <c r="F8" s="218" t="inlineStr">
+      <c r="F8" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="218" t="inlineStr">
+      <c r="G8" s="225" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="218" t="inlineStr">
+      <c r="H8" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="224" t="inlineStr">
+      <c r="I8" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="224" t="inlineStr">
+      <c r="J8" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22786,7 +22786,7 @@
           <t>custom:coding_system</t>
         </is>
       </c>
-      <c r="L8" s="224" t="n"/>
+      <c r="L8" s="232" t="n"/>
       <c r="P8" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22797,22 +22797,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V8" s="220" t="n"/>
-      <c r="W8" s="220" t="n"/>
-      <c r="X8" s="220" t="n"/>
+      <c r="V8" s="230" t="n"/>
+      <c r="W8" s="230" t="n"/>
+      <c r="X8" s="230" t="n"/>
     </row>
     <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="226" t="inlineStr">
+      <c r="A9" s="220" t="inlineStr">
         <is>
           <t>conforms to</t>
         </is>
       </c>
-      <c r="B9" s="230" t="inlineStr">
+      <c r="B9" s="226" t="inlineStr">
         <is>
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C9" s="226" t="inlineStr">
+      <c r="C9" s="220" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -22822,45 +22822,45 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E9" s="230" t="inlineStr">
+      <c r="E9" s="226" t="inlineStr">
         <is>
           <t>Note: The use of Wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
 If your data conforms to an established standard or specification, use this property to indicate which one. The Wikidata URI of the specification must be used. Example: https://www.wikidata.org/wiki/Q19597236 for FHIR.</t>
         </is>
       </c>
-      <c r="F9" s="231" t="inlineStr">
+      <c r="F9" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="231" t="inlineStr">
+      <c r="G9" s="227" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H9" s="231" t="inlineStr">
+      <c r="H9" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="225" t="inlineStr">
+      <c r="I9" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J9" s="224" t="inlineStr">
+      <c r="J9" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K9" s="232" t="inlineStr">
+      <c r="K9" s="228" t="inlineStr">
         <is>
           <t>custom:conforms_to</t>
         </is>
       </c>
-      <c r="L9" s="225" t="n"/>
-      <c r="M9" s="225" t="n"/>
-      <c r="N9" s="225" t="n"/>
+      <c r="L9" s="218" t="n"/>
+      <c r="M9" s="218" t="n"/>
+      <c r="N9" s="218" t="n"/>
       <c r="P9" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22871,12 +22871,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V9" s="226" t="n"/>
-      <c r="W9" s="226" t="n"/>
-      <c r="X9" s="226" t="n"/>
+      <c r="V9" s="220" t="n"/>
+      <c r="W9" s="220" t="n"/>
+      <c r="X9" s="220" t="n"/>
     </row>
     <row r="10" ht="123.75" customHeight="1">
-      <c r="A10" s="220" t="inlineStr">
+      <c r="A10" s="230" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -22886,7 +22886,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C10" s="220" t="inlineStr">
+      <c r="C10" s="230" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -22902,7 +22902,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F10" s="218" t="inlineStr">
+      <c r="F10" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -22912,15 +22912,15 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H10" s="218" t="n">
+      <c r="H10" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="224" t="inlineStr">
+      <c r="I10" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="224" t="inlineStr">
+      <c r="J10" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -22930,17 +22930,17 @@
           <t>custom:contact_</t>
         </is>
       </c>
-      <c r="L10" s="224" t="inlineStr">
+      <c r="L10" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M10" s="224" t="inlineStr">
+      <c r="M10" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="N10" s="224" t="inlineStr">
+      <c r="N10" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -22960,22 +22960,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V10" s="220" t="n"/>
-      <c r="W10" s="220" t="n"/>
-      <c r="X10" s="220" t="n"/>
+      <c r="V10" s="230" t="n"/>
+      <c r="W10" s="230" t="n"/>
+      <c r="X10" s="230" t="n"/>
     </row>
     <row r="11" ht="176" customHeight="1">
-      <c r="A11" s="226" t="inlineStr">
+      <c r="A11" s="220" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
       </c>
-      <c r="B11" s="230" t="inlineStr">
+      <c r="B11" s="226" t="inlineStr">
         <is>
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C11" s="226" t="inlineStr">
+      <c r="C11" s="220" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -22985,14 +22985,14 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E11" s="230" t="inlineStr">
+      <c r="E11" s="226" t="inlineStr">
         <is>
           <t>The creator (of the dataset) is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation/employer bearing investment risk, instead of an individual (e.g. an individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher: the organisation (not a department or subdivision of the organisation) where the dataset was created.
 If there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
 In case you wish to credit other contributors to the dataset, you can use the prov:qualifiedAttribution property. This could be useful if you wish to indicate, for example, the funding organisation(s), collaborating organisation(s) or name specific individuals (e.g., principal investigator) involved in creating or managing the dataset.</t>
         </is>
       </c>
-      <c r="F11" s="231" t="inlineStr">
+      <c r="F11" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -23002,37 +23002,37 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H11" s="231" t="inlineStr">
+      <c r="H11" s="227" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I11" s="225" t="inlineStr">
+      <c r="I11" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="224" t="inlineStr">
+      <c r="J11" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K11" s="232" t="inlineStr">
+      <c r="K11" s="228" t="inlineStr">
         <is>
           <t>custom:creator_</t>
         </is>
       </c>
-      <c r="L11" s="225" t="inlineStr">
+      <c r="L11" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M11" s="225" t="inlineStr">
+      <c r="M11" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N11" s="225" t="inlineStr">
+      <c r="N11" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -23052,12 +23052,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V11" s="226" t="n"/>
-      <c r="W11" s="226" t="n"/>
-      <c r="X11" s="226" t="n"/>
+      <c r="V11" s="220" t="n"/>
+      <c r="W11" s="220" t="n"/>
+      <c r="X11" s="220" t="n"/>
     </row>
     <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="220" t="inlineStr">
+      <c r="A12" s="230" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -23067,7 +23067,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="220" t="inlineStr">
+      <c r="C12" s="230" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -23082,27 +23082,27 @@
           <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ‘Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.’</t>
         </is>
       </c>
-      <c r="F12" s="218" t="inlineStr">
+      <c r="F12" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G12" s="218" t="inlineStr">
+      <c r="G12" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H12" s="218" t="inlineStr">
+      <c r="H12" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I12" s="224" t="inlineStr">
+      <c r="I12" s="232" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J12" s="224" t="inlineStr">
+      <c r="J12" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23112,7 +23112,7 @@
           <t>notes</t>
         </is>
       </c>
-      <c r="L12" s="224" t="n"/>
+      <c r="L12" s="232" t="n"/>
       <c r="P12" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23126,22 +23126,22 @@
       <c r="T12" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V12" s="220" t="n"/>
-      <c r="W12" s="220" t="n"/>
-      <c r="X12" s="220" t="n"/>
+      <c r="V12" s="230" t="n"/>
+      <c r="W12" s="230" t="n"/>
+      <c r="X12" s="230" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="226" t="inlineStr">
+      <c r="A13" s="220" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="B13" s="230" t="inlineStr">
+      <c r="B13" s="226" t="inlineStr">
         <is>
           <t>An available Distribution for the Dataset.</t>
         </is>
       </c>
-      <c r="C13" s="226" t="inlineStr">
+      <c r="C13" s="220" t="inlineStr">
         <is>
           <t>dcat:distribution</t>
         </is>
@@ -23156,7 +23156,7 @@
           <t>Metadata element used as a key link to the class Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="231" t="inlineStr">
+      <c r="F13" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23166,43 +23166,43 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H13" s="231" t="inlineStr">
+      <c r="H13" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="225" t="inlineStr">
+      <c r="I13" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J13" s="225" t="inlineStr">
+      <c r="J13" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K13" s="232" t="n"/>
-      <c r="L13" s="225" t="inlineStr">
+      <c r="K13" s="228" t="n"/>
+      <c r="L13" s="218" t="inlineStr">
         <is>
           <t>Enter the URI for dcat:Distribution.</t>
         </is>
       </c>
-      <c r="M13" s="225" t="inlineStr">
+      <c r="M13" s="218" t="inlineStr">
         <is>
           <t>Enter the URI for dcat:Distribution.</t>
         </is>
       </c>
-      <c r="N13" s="225" t="inlineStr">
+      <c r="N13" s="218" t="inlineStr">
         <is>
           <t>Enter the URI for dcat:Distribution.</t>
         </is>
       </c>
-      <c r="O13" s="229" t="inlineStr">
+      <c r="O13" s="224" t="inlineStr">
         <is>
           <t>hrishapes:DistributionShape</t>
         </is>
       </c>
-      <c r="P13" s="229" t="inlineStr">
+      <c r="P13" s="224" t="inlineStr">
         <is>
           <t>dash:DetailsViewer</t>
         </is>
@@ -23212,14 +23212,14 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S13" s="229" t="n"/>
-      <c r="T13" s="229" t="n"/>
-      <c r="V13" s="226" t="n"/>
-      <c r="W13" s="226" t="n"/>
-      <c r="X13" s="226" t="n"/>
+      <c r="S13" s="224" t="n"/>
+      <c r="T13" s="224" t="n"/>
+      <c r="V13" s="220" t="n"/>
+      <c r="W13" s="220" t="n"/>
+      <c r="X13" s="220" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="220" t="inlineStr">
+      <c r="A14" s="230" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
@@ -23229,7 +23229,7 @@
           <t>A page or document about this thing.</t>
         </is>
       </c>
-      <c r="C14" s="220" t="inlineStr">
+      <c r="C14" s="230" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -23244,27 +23244,27 @@
           <t>The value of this property is the IRI pointing to the web page or document about the dataset.</t>
         </is>
       </c>
-      <c r="F14" s="218" t="inlineStr">
+      <c r="F14" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="218" t="inlineStr">
+      <c r="G14" s="225" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="218" t="inlineStr">
+      <c r="H14" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="224" t="inlineStr">
+      <c r="I14" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="224" t="inlineStr">
+      <c r="J14" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23274,7 +23274,7 @@
           <t>custom:documentation</t>
         </is>
       </c>
-      <c r="L14" s="224" t="n"/>
+      <c r="L14" s="232" t="n"/>
       <c r="P14" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23285,22 +23285,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V14" s="220" t="n"/>
-      <c r="W14" s="220" t="n"/>
-      <c r="X14" s="220" t="n"/>
+      <c r="V14" s="230" t="n"/>
+      <c r="W14" s="230" t="n"/>
+      <c r="X14" s="230" t="n"/>
     </row>
     <row r="15" ht="160" customHeight="1">
-      <c r="A15" s="226" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>domain of the data</t>
         </is>
       </c>
-      <c r="B15" s="230" t="inlineStr">
+      <c r="B15" s="226" t="inlineStr">
         <is>
           <t>In this context, the definition should be considered as: The data domain(s) present in the Dataset.</t>
         </is>
       </c>
-      <c r="C15" s="226" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>edam:has_topic</t>
         </is>
@@ -23310,7 +23310,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="230" t="inlineStr">
+      <c r="E15" s="226" t="inlineStr">
         <is>
           <t>Select data domain(s) from the predefined value list, available at this link: https://github.com/Health-RI/health-ri-metadata/blob/v2.1-changes/Formalisation(shacl)/Core/ValueLists/edam-has-topic.tsv
 Note: This is a temporary location and it will change with the release. 
@@ -23318,31 +23318,31 @@
 See the property "measurement technique" for more information about the technique(s) used to generate the data in the Dataset.</t>
         </is>
       </c>
-      <c r="F15" s="218" t="inlineStr">
+      <c r="F15" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="231" t="inlineStr">
+      <c r="G15" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="231" t="inlineStr">
+      <c r="H15" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="225" t="inlineStr">
+      <c r="I15" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="225" t="n"/>
-      <c r="K15" s="232" t="n"/>
-      <c r="L15" s="225" t="n"/>
-      <c r="M15" s="225" t="n"/>
-      <c r="N15" s="225" t="n"/>
+      <c r="J15" s="218" t="n"/>
+      <c r="K15" s="228" t="n"/>
+      <c r="L15" s="218" t="n"/>
+      <c r="M15" s="218" t="n"/>
+      <c r="N15" s="218" t="n"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23353,12 +23353,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V15" s="226" t="n"/>
-      <c r="W15" s="226" t="n"/>
-      <c r="X15" s="226" t="n"/>
+      <c r="V15" s="220" t="n"/>
+      <c r="W15" s="220" t="n"/>
+      <c r="X15" s="220" t="n"/>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="220" t="inlineStr">
+      <c r="A16" s="230" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -23368,7 +23368,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C16" s="220" t="inlineStr">
+      <c r="C16" s="230" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -23378,33 +23378,33 @@
           <t>http://publications.europa.eu/resource/authority/frequency</t>
         </is>
       </c>
-      <c r="E16" s="223" t="inlineStr">
+      <c r="E16" s="231" t="inlineStr">
         <is>
           <t>The value of this property should be the IRI from the listed controlled vocabulary indicating the frequency at which the dataset is updated.
 For example: http://publications.europa.eu/resource/authority/frequency/WEEKLY</t>
         </is>
       </c>
-      <c r="F16" s="231" t="inlineStr">
+      <c r="F16" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="218" t="inlineStr">
+      <c r="G16" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="218" t="inlineStr">
+      <c r="H16" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="224" t="inlineStr">
+      <c r="I16" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="224" t="inlineStr">
+      <c r="J16" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23415,8 +23415,8 @@
         </is>
       </c>
       <c r="L16" s="107" t="n"/>
-      <c r="M16" s="224" t="n"/>
-      <c r="N16" s="224" t="n"/>
+      <c r="M16" s="232" t="n"/>
+      <c r="N16" s="232" t="n"/>
       <c r="P16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23427,22 +23427,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V16" s="220" t="n"/>
-      <c r="W16" s="220" t="n"/>
-      <c r="X16" s="220" t="n"/>
+      <c r="V16" s="230" t="n"/>
+      <c r="W16" s="230" t="n"/>
+      <c r="X16" s="230" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="226" t="inlineStr">
+      <c r="A17" s="220" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B17" s="230" t="inlineStr">
+      <c r="B17" s="226" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C17" s="226" t="inlineStr">
+      <c r="C17" s="220" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -23452,40 +23452,40 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E17" s="227" t="inlineStr">
+      <c r="E17" s="222" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F17" s="218" t="inlineStr">
+      <c r="F17" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="231" t="inlineStr">
+      <c r="G17" s="227" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H17" s="231" t="inlineStr">
+      <c r="H17" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I17" s="225" t="inlineStr">
+      <c r="I17" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="225" t="inlineStr">
+      <c r="J17" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K17" s="232" t="n"/>
-      <c r="L17" s="225" t="n"/>
-      <c r="M17" s="229" t="n"/>
-      <c r="N17" s="229" t="n"/>
+      <c r="K17" s="228" t="n"/>
+      <c r="L17" s="218" t="n"/>
+      <c r="M17" s="224" t="n"/>
+      <c r="N17" s="224" t="n"/>
       <c r="P17" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23496,9 +23496,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V17" s="226" t="n"/>
-      <c r="W17" s="226" t="n"/>
-      <c r="X17" s="226" t="n"/>
+      <c r="V17" s="220" t="n"/>
+      <c r="W17" s="220" t="n"/>
+      <c r="X17" s="220" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="D18" s="179" t="inlineStr">
@@ -23529,7 +23529,7 @@
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="220" t="inlineStr">
+      <c r="A22" s="230" t="inlineStr">
         <is>
           <t>has version</t>
         </is>
@@ -23539,7 +23539,7 @@
           <t>This resource has a more specific, versioned resource.</t>
         </is>
       </c>
-      <c r="C22" s="220" t="inlineStr">
+      <c r="C22" s="230" t="inlineStr">
         <is>
           <t>dcat:hasVersion</t>
         </is>
@@ -23549,12 +23549,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E22" s="223" t="inlineStr">
+      <c r="E22" s="231" t="inlineStr">
         <is>
           <t>Indicate the dataset that is another version of the current dataset.</t>
         </is>
       </c>
-      <c r="F22" s="231" t="inlineStr">
+      <c r="F22" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23564,17 +23564,17 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H22" s="218" t="inlineStr">
+      <c r="H22" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="224" t="inlineStr">
+      <c r="I22" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="224" t="inlineStr">
+      <c r="J22" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23589,8 +23589,8 @@
           <t>Enter the URI for the dcat:Dataset that is another version of the current Dataset.</t>
         </is>
       </c>
-      <c r="M22" s="224" t="n"/>
-      <c r="N22" s="224" t="n"/>
+      <c r="M22" s="232" t="n"/>
+      <c r="N22" s="232" t="n"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -23606,23 +23606,23 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V22" s="220" t="n"/>
-      <c r="W22" s="220" t="n"/>
-      <c r="X22" s="220" t="n"/>
+      <c r="V22" s="230" t="n"/>
+      <c r="W22" s="230" t="n"/>
+      <c r="X22" s="230" t="n"/>
     </row>
     <row r="23" ht="124" customHeight="1">
-      <c r="A23" s="226" t="inlineStr">
+      <c r="A23" s="220" t="inlineStr">
         <is>
           <t>health condition of interest</t>
         </is>
       </c>
-      <c r="B23" s="230" t="inlineStr">
+      <c r="B23" s="226" t="inlineStr">
         <is>
           <t xml:space="preserve">	
 Relates a dataset to a SNOMED CT, ICD-10, ICD-11, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
         </is>
       </c>
-      <c r="C23" s="226" t="inlineStr">
+      <c r="C23" s="220" t="inlineStr">
         <is>
           <t>hri:healthConditionOfInterest</t>
         </is>
@@ -23632,38 +23632,38 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E23" s="227" t="inlineStr">
+      <c r="E23" s="222" t="inlineStr">
         <is>
           <t xml:space="preserve">	
 Use this property to describe health conditions of interest in dataset-level metadata. Multiple values may be provided. Select only SNOMED CT, ICD-10, ICD-11, or ORPHAcode concepts that represent diseases, disorders, or other clinical conditions. The relation does not assert that any individual participant has been diagnosed with a condition and is not intended to enumerate diagnoses in individual records.
 Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
         </is>
       </c>
-      <c r="F23" s="218" t="inlineStr">
+      <c r="F23" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="231" t="inlineStr">
+      <c r="G23" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H23" s="231" t="inlineStr">
+      <c r="H23" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I23" s="225" t="inlineStr">
+      <c r="I23" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="225" t="n"/>
+      <c r="J23" s="218" t="n"/>
       <c r="K23" s="170" t="n"/>
       <c r="L23" s="100" t="n"/>
-      <c r="M23" s="225" t="n"/>
-      <c r="N23" s="225" t="n"/>
+      <c r="M23" s="218" t="n"/>
+      <c r="N23" s="218" t="n"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23676,15 +23676,15 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>^(http://snomed[.]info/id/[0-9]+|^http://id[.]who[.]int/icd/entity/[0-9]+$|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
-        </is>
-      </c>
-      <c r="V23" s="226" t="n"/>
-      <c r="W23" s="226" t="n"/>
-      <c r="X23" s="226" t="n"/>
+          <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/entity/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
+        </is>
+      </c>
+      <c r="V23" s="220" t="n"/>
+      <c r="W23" s="220" t="n"/>
+      <c r="X23" s="220" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="220" t="inlineStr">
+      <c r="A24" s="230" t="inlineStr">
         <is>
           <t>health theme</t>
         </is>
@@ -23694,7 +23694,7 @@
           <t>A category of the Dataset or tag describing the Dataset.</t>
         </is>
       </c>
-      <c r="C24" s="220" t="inlineStr">
+      <c r="C24" s="230" t="inlineStr">
         <is>
           <t>healthdcatap:healthTheme</t>
         </is>
@@ -23710,27 +23710,27 @@
 This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The Wikidata URI of the health theme must be used here.</t>
         </is>
       </c>
-      <c r="F24" s="218" t="inlineStr">
+      <c r="F24" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="218" t="inlineStr">
+      <c r="G24" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H24" s="218" t="inlineStr">
+      <c r="H24" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="224" t="inlineStr">
+      <c r="I24" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J24" s="224" t="inlineStr">
+      <c r="J24" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23740,7 +23740,7 @@
           <t>custom:health_theme</t>
         </is>
       </c>
-      <c r="L24" s="224" t="n"/>
+      <c r="L24" s="232" t="n"/>
       <c r="P24" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23751,22 +23751,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V24" s="220" t="n"/>
-      <c r="W24" s="220" t="n"/>
-      <c r="X24" s="220" t="n"/>
+      <c r="V24" s="230" t="n"/>
+      <c r="W24" s="230" t="n"/>
+      <c r="X24" s="230" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1">
-      <c r="A25" s="226" t="inlineStr">
+      <c r="A25" s="220" t="inlineStr">
         <is>
           <t>identifier</t>
         </is>
       </c>
-      <c r="B25" s="230" t="inlineStr">
+      <c r="B25" s="226" t="inlineStr">
         <is>
           <t>An unambiguous reference to the resource within a given context.</t>
         </is>
       </c>
-      <c r="C25" s="226" t="inlineStr">
+      <c r="C25" s="220" t="inlineStr">
         <is>
           <t>dct:identifier</t>
         </is>
@@ -23782,37 +23782,37 @@
 If your data is published in a repository, enter the provided DOI (Example: https://doi.org/10.34894/ZLOYOJ). If not, use the identifier of the dataset as generated in the FAIR data point (FDP). Ensure that metadata is updated if your situation changes.</t>
         </is>
       </c>
-      <c r="F25" s="231" t="inlineStr">
+      <c r="F25" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G25" s="231" t="inlineStr">
+      <c r="G25" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H25" s="231" t="n">
+      <c r="H25" s="227" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="225" t="inlineStr">
+      <c r="I25" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J25" s="225" t="inlineStr">
+      <c r="J25" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K25" s="232" t="inlineStr">
+      <c r="K25" s="228" t="inlineStr">
         <is>
           <t>custom:alternate_identifier</t>
         </is>
       </c>
-      <c r="L25" s="225" t="n"/>
-      <c r="M25" s="225" t="n"/>
-      <c r="N25" s="225" t="n"/>
+      <c r="L25" s="218" t="n"/>
+      <c r="M25" s="218" t="n"/>
+      <c r="N25" s="218" t="n"/>
       <c r="P25" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23823,12 +23823,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V25" s="226" t="n"/>
-      <c r="W25" s="226" t="n"/>
-      <c r="X25" s="226" t="n"/>
+      <c r="V25" s="220" t="n"/>
+      <c r="W25" s="220" t="n"/>
+      <c r="X25" s="220" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="220" t="inlineStr">
+      <c r="A26" s="230" t="inlineStr">
         <is>
           <t>in series</t>
         </is>
@@ -23838,7 +23838,7 @@
           <t>A dataset series of which the dataset is part.</t>
         </is>
       </c>
-      <c r="C26" s="220" t="inlineStr">
+      <c r="C26" s="230" t="inlineStr">
         <is>
           <t>dcat:inSeries</t>
         </is>
@@ -23853,7 +23853,7 @@
           <t xml:space="preserve">This property points to the Dataset Series of which the Dataset is part. </t>
         </is>
       </c>
-      <c r="F26" s="218" t="inlineStr">
+      <c r="F26" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23863,17 +23863,17 @@
           <t>dcat:DatasetSeries</t>
         </is>
       </c>
-      <c r="H26" s="218" t="inlineStr">
+      <c r="H26" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I26" s="224" t="inlineStr">
+      <c r="I26" s="232" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J26" s="224" t="inlineStr">
+      <c r="J26" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23904,22 +23904,22 @@
           <t>Dataset Series</t>
         </is>
       </c>
-      <c r="V26" s="220" t="n"/>
-      <c r="W26" s="220" t="n"/>
-      <c r="X26" s="220" t="n"/>
+      <c r="V26" s="230" t="n"/>
+      <c r="W26" s="230" t="n"/>
+      <c r="X26" s="230" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="226" t="inlineStr">
+      <c r="A27" s="220" t="inlineStr">
         <is>
           <t>is referenced by</t>
         </is>
       </c>
-      <c r="B27" s="230" t="inlineStr">
+      <c r="B27" s="226" t="inlineStr">
         <is>
           <t>A related resource that references, cites, or otherwise points to the described resource.</t>
         </is>
       </c>
-      <c r="C27" s="226" t="inlineStr">
+      <c r="C27" s="220" t="inlineStr">
         <is>
           <t>dct:isReferencedBy</t>
         </is>
@@ -23929,33 +23929,33 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E27" s="230" t="inlineStr">
+      <c r="E27" s="226" t="inlineStr">
         <is>
           <t>The value of this property is the IRI of the DOI for the publication or other related resource.
 For example: https://doi.org/10.1186/s13690-021-00709-x</t>
         </is>
       </c>
-      <c r="F27" s="231" t="inlineStr">
+      <c r="F27" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G27" s="231" t="inlineStr">
+      <c r="G27" s="227" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H27" s="231" t="inlineStr">
+      <c r="H27" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I27" s="225" t="inlineStr">
+      <c r="I27" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J27" s="225" t="inlineStr">
+      <c r="J27" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23965,9 +23965,9 @@
           <t>custom:is_referenced_by</t>
         </is>
       </c>
-      <c r="L27" s="225" t="n"/>
-      <c r="M27" s="225" t="n"/>
-      <c r="N27" s="225" t="n"/>
+      <c r="L27" s="218" t="n"/>
+      <c r="M27" s="218" t="n"/>
+      <c r="N27" s="218" t="n"/>
       <c r="P27" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23978,12 +23978,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V27" s="226" t="n"/>
-      <c r="W27" s="226" t="n"/>
-      <c r="X27" s="226" t="n"/>
+      <c r="V27" s="220" t="n"/>
+      <c r="W27" s="220" t="n"/>
+      <c r="X27" s="220" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="220" t="inlineStr">
+      <c r="A28" s="230" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -24008,27 +24008,27 @@
           <t>Add keywords to increase dataset discoverability. You can include keywords in different languages, submitting each keyword as a separate entry. Example: Physiological measures, Heart Rate, Stress Measures.</t>
         </is>
       </c>
-      <c r="F28" s="218" t="inlineStr">
+      <c r="F28" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G28" s="218" t="inlineStr">
+      <c r="G28" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H28" s="218" t="inlineStr">
+      <c r="H28" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I28" s="224" t="inlineStr">
+      <c r="I28" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J28" s="224" t="inlineStr">
+      <c r="J28" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24038,7 +24038,7 @@
           <t>tags</t>
         </is>
       </c>
-      <c r="L28" s="224" t="n"/>
+      <c r="L28" s="232" t="n"/>
       <c r="P28" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24049,17 +24049,17 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V28" s="220" t="n"/>
-      <c r="W28" s="220" t="n"/>
-      <c r="X28" s="220" t="n"/>
+      <c r="V28" s="230" t="n"/>
+      <c r="W28" s="230" t="n"/>
+      <c r="X28" s="230" t="n"/>
     </row>
     <row r="29" ht="128" customHeight="1">
-      <c r="A29" s="226" t="inlineStr">
+      <c r="A29" s="220" t="inlineStr">
         <is>
           <t>landing page</t>
         </is>
       </c>
-      <c r="B29" s="230" t="inlineStr">
+      <c r="B29" s="226" t="inlineStr">
         <is>
           <t>A web page that provides access to the Dataset, its Distributions and/or additional information.</t>
         </is>
@@ -24080,35 +24080,35 @@
 Example: For an EGA Dataset, dcat:landingPage points to the corresponding human-readable EGA Dataset page, like https://ega-archive.org/datasets/EGAD00001005083.</t>
         </is>
       </c>
-      <c r="F29" s="218" t="inlineStr">
+      <c r="F29" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G29" s="231" t="inlineStr">
+      <c r="G29" s="227" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H29" s="231" t="inlineStr">
+      <c r="H29" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I29" s="225" t="inlineStr">
+      <c r="I29" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J29" s="225" t="inlineStr">
+      <c r="J29" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K29" s="232" t="n"/>
-      <c r="L29" s="225" t="n"/>
-      <c r="M29" s="229" t="n"/>
-      <c r="N29" s="229" t="n"/>
+      <c r="K29" s="228" t="n"/>
+      <c r="L29" s="218" t="n"/>
+      <c r="M29" s="224" t="n"/>
+      <c r="N29" s="224" t="n"/>
       <c r="P29" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -24119,12 +24119,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V29" s="226" t="n"/>
-      <c r="W29" s="226" t="n"/>
-      <c r="X29" s="226" t="n"/>
+      <c r="V29" s="220" t="n"/>
+      <c r="W29" s="220" t="n"/>
+      <c r="X29" s="220" t="n"/>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="220" t="inlineStr">
+      <c r="A30" s="230" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -24149,27 +24149,27 @@
           <t xml:space="preserve">The language of the Dataset. For this property, the values from the EU Vocabularies Languages Named Authority List must be used. If your Dataset contains multiple languages, this property can be repeated. </t>
         </is>
       </c>
-      <c r="F30" s="231" t="inlineStr">
+      <c r="F30" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G30" s="218" t="inlineStr">
+      <c r="G30" s="225" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H30" s="218" t="inlineStr">
+      <c r="H30" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I30" s="225" t="inlineStr">
+      <c r="I30" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J30" s="225" t="inlineStr">
+      <c r="J30" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24179,9 +24179,9 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L30" s="224" t="n"/>
-      <c r="M30" s="224" t="n"/>
-      <c r="N30" s="224" t="n"/>
+      <c r="L30" s="232" t="n"/>
+      <c r="M30" s="232" t="n"/>
+      <c r="N30" s="232" t="n"/>
       <c r="P30" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24192,17 +24192,17 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V30" s="220" t="n"/>
-      <c r="W30" s="220" t="n"/>
-      <c r="X30" s="220" t="n"/>
+      <c r="V30" s="230" t="n"/>
+      <c r="W30" s="230" t="n"/>
+      <c r="X30" s="230" t="n"/>
     </row>
     <row r="31" ht="160" customHeight="1">
-      <c r="A31" s="226" t="inlineStr">
+      <c r="A31" s="220" t="inlineStr">
         <is>
           <t>legal basis</t>
         </is>
       </c>
-      <c r="B31" s="230" t="inlineStr">
+      <c r="B31" s="226" t="inlineStr">
         <is>
           <t>Indicates use or applicability of a Legal Basis.</t>
         </is>
@@ -24225,39 +24225,39 @@
 An example value for this property could be dpv:Consent.</t>
         </is>
       </c>
-      <c r="F31" s="218" t="inlineStr">
+      <c r="F31" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G31" s="231" t="inlineStr">
+      <c r="G31" s="227" t="inlineStr">
         <is>
           <t>dpv:LegalBasis (IRI)</t>
         </is>
       </c>
-      <c r="H31" s="231" t="inlineStr">
+      <c r="H31" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I31" s="225" t="inlineStr">
+      <c r="I31" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J31" s="225" t="inlineStr">
+      <c r="J31" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K31" s="232" t="inlineStr">
+      <c r="K31" s="228" t="inlineStr">
         <is>
           <t>custom:legal_basis</t>
         </is>
       </c>
-      <c r="L31" s="225" t="n"/>
-      <c r="M31" s="229" t="n"/>
-      <c r="N31" s="229" t="n"/>
+      <c r="L31" s="218" t="n"/>
+      <c r="M31" s="224" t="n"/>
+      <c r="N31" s="224" t="n"/>
       <c r="P31" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24268,12 +24268,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V31" s="226" t="n"/>
-      <c r="W31" s="226" t="n"/>
-      <c r="X31" s="226" t="n"/>
+      <c r="V31" s="220" t="n"/>
+      <c r="W31" s="220" t="n"/>
+      <c r="X31" s="220" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="220" t="inlineStr">
+      <c r="A32" s="230" t="inlineStr">
         <is>
           <t>maximum typical age</t>
         </is>
@@ -24283,7 +24283,7 @@
           <t>Maximum typical age of the population within the dataset</t>
         </is>
       </c>
-      <c r="C32" s="220" t="inlineStr">
+      <c r="C32" s="230" t="inlineStr">
         <is>
           <t>healthdcatap:maxTypicalAge</t>
         </is>
@@ -24298,27 +24298,27 @@
           <t>The approximate maximum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F32" s="231" t="inlineStr">
+      <c r="F32" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G32" s="218" t="inlineStr">
+      <c r="G32" s="225" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H32" s="218" t="inlineStr">
+      <c r="H32" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I32" s="224" t="inlineStr">
+      <c r="I32" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J32" s="224" t="inlineStr">
+      <c r="J32" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24328,9 +24328,9 @@
           <t>custom:max_typical_age</t>
         </is>
       </c>
-      <c r="L32" s="224" t="n"/>
-      <c r="M32" s="224" t="n"/>
-      <c r="N32" s="224" t="n"/>
+      <c r="L32" s="232" t="n"/>
+      <c r="M32" s="232" t="n"/>
+      <c r="N32" s="232" t="n"/>
       <c r="P32" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24341,17 +24341,17 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V32" s="220" t="n"/>
-      <c r="W32" s="220" t="n"/>
-      <c r="X32" s="220" t="n"/>
+      <c r="V32" s="230" t="n"/>
+      <c r="W32" s="230" t="n"/>
+      <c r="X32" s="230" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="226" t="inlineStr">
+      <c r="A33" s="220" t="inlineStr">
         <is>
           <t>minimum typical age</t>
         </is>
       </c>
-      <c r="B33" s="230" t="inlineStr">
+      <c r="B33" s="226" t="inlineStr">
         <is>
           <t>Minimum typical age of the population within the dataset</t>
         </is>
@@ -24371,39 +24371,39 @@
           <t>The approximate minimum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F33" s="218" t="inlineStr">
+      <c r="F33" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G33" s="231" t="inlineStr">
+      <c r="G33" s="227" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H33" s="231" t="inlineStr">
+      <c r="H33" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I33" s="225" t="inlineStr">
+      <c r="I33" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J33" s="225" t="inlineStr">
+      <c r="J33" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K33" s="232" t="inlineStr">
+      <c r="K33" s="228" t="inlineStr">
         <is>
           <t>custom:min_typical_age</t>
         </is>
       </c>
-      <c r="L33" s="225" t="n"/>
-      <c r="M33" s="229" t="n"/>
-      <c r="N33" s="229" t="n"/>
+      <c r="L33" s="218" t="n"/>
+      <c r="M33" s="224" t="n"/>
+      <c r="N33" s="224" t="n"/>
       <c r="P33" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24414,12 +24414,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V33" s="226" t="n"/>
-      <c r="W33" s="226" t="n"/>
-      <c r="X33" s="226" t="n"/>
+      <c r="V33" s="220" t="n"/>
+      <c r="W33" s="220" t="n"/>
+      <c r="X33" s="220" t="n"/>
     </row>
     <row r="34" ht="209.25" customHeight="1">
-      <c r="A34" s="220" t="inlineStr">
+      <c r="A34" s="230" t="inlineStr">
         <is>
           <t>measurement technique</t>
         </is>
@@ -24446,86 +24446,86 @@
 Note: This is a temporary location and it will change with the next release. </t>
         </is>
       </c>
-      <c r="F34" s="218" t="inlineStr">
+      <c r="F34" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G34" s="218" t="inlineStr">
+      <c r="G34" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H34" s="218" t="inlineStr">
+      <c r="H34" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I34" s="224" t="n"/>
-      <c r="J34" s="224" t="n"/>
+      <c r="I34" s="232" t="n"/>
+      <c r="J34" s="232" t="n"/>
       <c r="K34" s="75" t="n"/>
-      <c r="L34" s="224" t="n"/>
-      <c r="M34" s="224" t="n"/>
-      <c r="N34" s="224" t="n"/>
-      <c r="O34" s="224" t="n"/>
-      <c r="P34" s="224" t="inlineStr">
+      <c r="L34" s="232" t="n"/>
+      <c r="M34" s="232" t="n"/>
+      <c r="N34" s="232" t="n"/>
+      <c r="O34" s="232" t="n"/>
+      <c r="P34" s="232" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
         </is>
       </c>
-      <c r="Q34" s="224" t="inlineStr">
+      <c r="Q34" s="232" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="R34" s="224" t="n"/>
-      <c r="S34" s="224" t="n"/>
-      <c r="T34" s="224" t="n"/>
-      <c r="U34" s="224" t="n"/>
-      <c r="V34" s="220" t="n"/>
-      <c r="W34" s="220" t="n"/>
-      <c r="X34" s="220" t="n"/>
-      <c r="Y34" s="224" t="n"/>
-      <c r="Z34" s="224" t="n"/>
-      <c r="AA34" s="224" t="n"/>
-      <c r="AB34" s="224" t="n"/>
-      <c r="AC34" s="224" t="n"/>
-      <c r="AD34" s="224" t="n"/>
-      <c r="AE34" s="224" t="n"/>
-      <c r="AF34" s="224" t="n"/>
-      <c r="AG34" s="224" t="n"/>
-      <c r="AH34" s="224" t="n"/>
-      <c r="AI34" s="224" t="n"/>
-      <c r="AJ34" s="224" t="n"/>
-      <c r="AK34" s="224" t="n"/>
-      <c r="AL34" s="224" t="n"/>
-      <c r="AM34" s="224" t="n"/>
-      <c r="AN34" s="224" t="n"/>
-      <c r="AO34" s="224" t="n"/>
-      <c r="AP34" s="224" t="n"/>
-      <c r="AQ34" s="224" t="n"/>
-      <c r="AR34" s="224" t="n"/>
-      <c r="AS34" s="224" t="n"/>
-      <c r="AT34" s="224" t="n"/>
-      <c r="AU34" s="224" t="n"/>
-      <c r="AV34" s="224" t="n"/>
-      <c r="AW34" s="224" t="n"/>
-      <c r="AX34" s="224" t="n"/>
-      <c r="AY34" s="224" t="n"/>
-      <c r="AZ34" s="224" t="n"/>
+      <c r="R34" s="232" t="n"/>
+      <c r="S34" s="232" t="n"/>
+      <c r="T34" s="232" t="n"/>
+      <c r="U34" s="232" t="n"/>
+      <c r="V34" s="230" t="n"/>
+      <c r="W34" s="230" t="n"/>
+      <c r="X34" s="230" t="n"/>
+      <c r="Y34" s="232" t="n"/>
+      <c r="Z34" s="232" t="n"/>
+      <c r="AA34" s="232" t="n"/>
+      <c r="AB34" s="232" t="n"/>
+      <c r="AC34" s="232" t="n"/>
+      <c r="AD34" s="232" t="n"/>
+      <c r="AE34" s="232" t="n"/>
+      <c r="AF34" s="232" t="n"/>
+      <c r="AG34" s="232" t="n"/>
+      <c r="AH34" s="232" t="n"/>
+      <c r="AI34" s="232" t="n"/>
+      <c r="AJ34" s="232" t="n"/>
+      <c r="AK34" s="232" t="n"/>
+      <c r="AL34" s="232" t="n"/>
+      <c r="AM34" s="232" t="n"/>
+      <c r="AN34" s="232" t="n"/>
+      <c r="AO34" s="232" t="n"/>
+      <c r="AP34" s="232" t="n"/>
+      <c r="AQ34" s="232" t="n"/>
+      <c r="AR34" s="232" t="n"/>
+      <c r="AS34" s="232" t="n"/>
+      <c r="AT34" s="232" t="n"/>
+      <c r="AU34" s="232" t="n"/>
+      <c r="AV34" s="232" t="n"/>
+      <c r="AW34" s="232" t="n"/>
+      <c r="AX34" s="232" t="n"/>
+      <c r="AY34" s="232" t="n"/>
+      <c r="AZ34" s="232" t="n"/>
     </row>
     <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="226" t="inlineStr">
+      <c r="A35" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
       </c>
-      <c r="B35" s="230" t="inlineStr">
+      <c r="B35" s="226" t="inlineStr">
         <is>
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C35" s="226" t="inlineStr">
+      <c r="C35" s="220" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -24535,44 +24535,44 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E35" s="230" t="inlineStr">
+      <c r="E35" s="226" t="inlineStr">
         <is>
           <t>This property indicates changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F35" s="231" t="inlineStr">
+      <c r="F35" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G35" s="231" t="inlineStr">
+      <c r="G35" s="227" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H35" s="231" t="inlineStr">
+      <c r="H35" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I35" s="225" t="inlineStr">
+      <c r="I35" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J35" s="225" t="inlineStr">
+      <c r="J35" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K35" s="232" t="inlineStr">
+      <c r="K35" s="228" t="inlineStr">
         <is>
           <t>custom:modified</t>
         </is>
       </c>
-      <c r="L35" s="225" t="n"/>
-      <c r="M35" s="225" t="n"/>
-      <c r="N35" s="225" t="n"/>
+      <c r="L35" s="218" t="n"/>
+      <c r="M35" s="218" t="n"/>
+      <c r="N35" s="218" t="n"/>
       <c r="P35" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24588,12 +24588,12 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="V35" s="226" t="n"/>
-      <c r="W35" s="226" t="n"/>
-      <c r="X35" s="226" t="n"/>
+      <c r="V35" s="220" t="n"/>
+      <c r="W35" s="220" t="n"/>
+      <c r="X35" s="220" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="220" t="inlineStr">
+      <c r="A36" s="230" t="inlineStr">
         <is>
           <t>number of records</t>
         </is>
@@ -24603,7 +24603,7 @@
           <t>Size of the dataset in terms of the number of records</t>
         </is>
       </c>
-      <c r="C36" s="220" t="inlineStr">
+      <c r="C36" s="230" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfRecords</t>
         </is>
@@ -24618,27 +24618,27 @@
           <t>Number of records inside a Dataset.</t>
         </is>
       </c>
-      <c r="F36" s="218" t="inlineStr">
+      <c r="F36" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G36" s="218" t="inlineStr">
+      <c r="G36" s="225" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H36" s="218" t="inlineStr">
+      <c r="H36" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I36" s="224" t="inlineStr">
+      <c r="I36" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J36" s="224" t="inlineStr">
+      <c r="J36" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24648,7 +24648,7 @@
           <t>custom:number_of_records</t>
         </is>
       </c>
-      <c r="L36" s="224" t="n"/>
+      <c r="L36" s="232" t="n"/>
       <c r="P36" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24659,22 +24659,22 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V36" s="220" t="n"/>
-      <c r="W36" s="220" t="n"/>
-      <c r="X36" s="220" t="n"/>
+      <c r="V36" s="230" t="n"/>
+      <c r="W36" s="230" t="n"/>
+      <c r="X36" s="230" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="226" t="inlineStr">
+      <c r="A37" s="220" t="inlineStr">
         <is>
           <t>number of unique individuals</t>
         </is>
       </c>
-      <c r="B37" s="230" t="inlineStr">
+      <c r="B37" s="226" t="inlineStr">
         <is>
           <t>Number of records for unique individuals.</t>
         </is>
       </c>
-      <c r="C37" s="226" t="inlineStr">
+      <c r="C37" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfUniqueIndividuals</t>
         </is>
@@ -24684,44 +24684,44 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E37" s="230" t="inlineStr">
+      <c r="E37" s="226" t="inlineStr">
         <is>
           <t>This property is not mandatory, since not all datasets might include data from individuals.</t>
         </is>
       </c>
-      <c r="F37" s="231" t="inlineStr">
+      <c r="F37" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G37" s="231" t="inlineStr">
+      <c r="G37" s="227" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H37" s="231" t="inlineStr">
+      <c r="H37" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I37" s="225" t="inlineStr">
+      <c r="I37" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J37" s="225" t="inlineStr">
+      <c r="J37" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K37" s="232" t="inlineStr">
+      <c r="K37" s="228" t="inlineStr">
         <is>
           <t>custom:number_of_unique_individuals</t>
         </is>
       </c>
-      <c r="L37" s="225" t="n"/>
-      <c r="M37" s="225" t="n"/>
-      <c r="N37" s="225" t="n"/>
+      <c r="L37" s="218" t="n"/>
+      <c r="M37" s="218" t="n"/>
+      <c r="N37" s="218" t="n"/>
       <c r="P37" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24732,12 +24732,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V37" s="226" t="n"/>
-      <c r="W37" s="226" t="n"/>
-      <c r="X37" s="226" t="n"/>
+      <c r="V37" s="220" t="n"/>
+      <c r="W37" s="220" t="n"/>
+      <c r="X37" s="220" t="n"/>
     </row>
     <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="220" t="inlineStr">
+      <c r="A38" s="230" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
@@ -24747,7 +24747,7 @@
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
       </c>
-      <c r="C38" s="220" t="inlineStr">
+      <c r="C38" s="230" t="inlineStr">
         <is>
           <t>adms:identifier</t>
         </is>
@@ -24762,27 +24762,27 @@
           <t>Examples of secondary identifiers include MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (e.g. DOI).</t>
         </is>
       </c>
-      <c r="F38" s="218" t="inlineStr">
+      <c r="F38" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G38" s="218" t="inlineStr">
+      <c r="G38" s="225" t="inlineStr">
         <is>
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H38" s="218" t="inlineStr">
+      <c r="H38" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I38" s="224" t="inlineStr">
+      <c r="I38" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J38" s="224" t="inlineStr">
+      <c r="J38" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24792,7 +24792,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="L38" s="224" t="n"/>
+      <c r="L38" s="232" t="n"/>
       <c r="O38" s="219" t="inlineStr">
         <is>
           <t>hrishapes:IdentifierShape</t>
@@ -24808,22 +24808,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V38" s="220" t="n"/>
-      <c r="W38" s="220" t="n"/>
-      <c r="X38" s="220" t="n"/>
+      <c r="V38" s="230" t="n"/>
+      <c r="W38" s="230" t="n"/>
+      <c r="X38" s="230" t="n"/>
     </row>
     <row r="39" ht="64" customHeight="1">
-      <c r="A39" s="226" t="inlineStr">
+      <c r="A39" s="220" t="inlineStr">
         <is>
           <t>personal data</t>
         </is>
       </c>
-      <c r="B39" s="230" t="inlineStr">
+      <c r="B39" s="226" t="inlineStr">
         <is>
           <t>Indicates association with Personal Data.</t>
         </is>
       </c>
-      <c r="C39" s="226" t="inlineStr">
+      <c r="C39" s="220" t="inlineStr">
         <is>
           <t>dpv:hasPersonalData</t>
         </is>
@@ -24833,45 +24833,45 @@
           <t>https://w3c.github.io/dpv/2.0/pd/</t>
         </is>
       </c>
-      <c r="E39" s="227" t="inlineStr">
+      <c r="E39" s="222" t="inlineStr">
         <is>
           <t>The different types of personal information that are collected in the dataset can be indicated with this property. Values can be picked from the DPV taxonomy (see the Controlled vocabulary column).
 For example: dpv-pd:Gender</t>
         </is>
       </c>
-      <c r="F39" s="231" t="inlineStr">
+      <c r="F39" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G39" s="231" t="inlineStr">
+      <c r="G39" s="227" t="inlineStr">
         <is>
           <t>dpv:PersonalData (IRI)</t>
         </is>
       </c>
-      <c r="H39" s="231" t="inlineStr">
+      <c r="H39" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I39" s="225" t="inlineStr">
+      <c r="I39" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J39" s="225" t="inlineStr">
+      <c r="J39" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K39" s="232" t="inlineStr">
+      <c r="K39" s="228" t="inlineStr">
         <is>
           <t>custom:personal_data</t>
         </is>
       </c>
-      <c r="L39" s="225" t="n"/>
-      <c r="M39" s="225" t="n"/>
-      <c r="N39" s="225" t="n"/>
+      <c r="L39" s="218" t="n"/>
+      <c r="M39" s="218" t="n"/>
+      <c r="N39" s="218" t="n"/>
       <c r="P39" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24882,12 +24882,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V39" s="226" t="n"/>
-      <c r="W39" s="226" t="n"/>
-      <c r="X39" s="226" t="n"/>
+      <c r="V39" s="220" t="n"/>
+      <c r="W39" s="220" t="n"/>
+      <c r="X39" s="220" t="n"/>
     </row>
     <row r="40" ht="59" customHeight="1">
-      <c r="A40" s="220" t="inlineStr">
+      <c r="A40" s="230" t="inlineStr">
         <is>
           <t>population coverage</t>
         </is>
@@ -24897,7 +24897,7 @@
           <t>A definition of the population within the dataset</t>
         </is>
       </c>
-      <c r="C40" s="220" t="inlineStr">
+      <c r="C40" s="230" t="inlineStr">
         <is>
           <t>healthdcatap:populationCoverage</t>
         </is>
@@ -24912,27 +24912,27 @@
           <t>This field is a free-text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
         </is>
       </c>
-      <c r="F40" s="218" t="inlineStr">
+      <c r="F40" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G40" s="218" t="inlineStr">
+      <c r="G40" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H40" s="218" t="inlineStr">
+      <c r="H40" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I40" s="224" t="inlineStr">
+      <c r="I40" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J40" s="224" t="inlineStr">
+      <c r="J40" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24942,7 +24942,7 @@
           <t>custom:populatiion_coverage</t>
         </is>
       </c>
-      <c r="L40" s="224" t="n"/>
+      <c r="L40" s="232" t="n"/>
       <c r="P40" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24953,22 +24953,22 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V40" s="220" t="n"/>
-      <c r="W40" s="220" t="n"/>
-      <c r="X40" s="220" t="n"/>
+      <c r="V40" s="230" t="n"/>
+      <c r="W40" s="230" t="n"/>
+      <c r="X40" s="230" t="n"/>
     </row>
     <row r="41" ht="92" customHeight="1">
-      <c r="A41" s="226" t="inlineStr">
+      <c r="A41" s="220" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="B41" s="230" t="inlineStr">
+      <c r="B41" s="226" t="inlineStr">
         <is>
           <t>A statement about the lineage of a Dataset.</t>
         </is>
       </c>
-      <c r="C41" s="226" t="inlineStr">
+      <c r="C41" s="220" t="inlineStr">
         <is>
           <t>dct:provenance</t>
         </is>
@@ -24984,7 +24984,7 @@
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
         </is>
       </c>
-      <c r="F41" s="218" t="inlineStr">
+      <c r="F41" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24994,33 +24994,33 @@
           <t>dct:ProvenanceStatement</t>
         </is>
       </c>
-      <c r="H41" s="231" t="inlineStr">
+      <c r="H41" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I41" s="225" t="inlineStr">
+      <c r="I41" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J41" s="225" t="inlineStr">
+      <c r="J41" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K41" s="232" t="n"/>
-      <c r="L41" s="225" t="inlineStr">
+      <c r="K41" s="228" t="n"/>
+      <c r="L41" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'ProvenanceStatement' tab.</t>
         </is>
       </c>
-      <c r="M41" s="225" t="inlineStr">
+      <c r="M41" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'ProvenanceStatement' tab.</t>
         </is>
       </c>
-      <c r="N41" s="225" t="inlineStr">
+      <c r="N41" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'ProvenanceStatement' tab.</t>
         </is>
@@ -25040,12 +25040,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V41" s="226" t="n"/>
-      <c r="W41" s="226" t="n"/>
-      <c r="X41" s="226" t="n"/>
+      <c r="V41" s="220" t="n"/>
+      <c r="W41" s="220" t="n"/>
+      <c r="X41" s="220" t="n"/>
     </row>
     <row r="42" ht="112" customHeight="1">
-      <c r="A42" s="220" t="inlineStr">
+      <c r="A42" s="230" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -25055,7 +25055,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C42" s="220" t="inlineStr">
+      <c r="C42" s="230" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -25065,12 +25065,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E42" s="223" t="inlineStr">
+      <c r="E42" s="231" t="inlineStr">
         <is>
           <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalogue publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide information about the contributing organisations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
         </is>
       </c>
-      <c r="F42" s="231" t="inlineStr">
+      <c r="F42" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -25080,15 +25080,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H42" s="218" t="n">
+      <c r="H42" s="225" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="224" t="inlineStr">
+      <c r="I42" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J42" s="224" t="inlineStr">
+      <c r="J42" s="232" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -25098,17 +25098,17 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L42" s="224" t="inlineStr">
+      <c r="L42" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M42" s="224" t="inlineStr">
+      <c r="M42" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N42" s="224" t="inlineStr">
+      <c r="N42" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -25128,22 +25128,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V42" s="220" t="n"/>
-      <c r="W42" s="220" t="n"/>
-      <c r="X42" s="220" t="n"/>
+      <c r="V42" s="230" t="n"/>
+      <c r="W42" s="230" t="n"/>
+      <c r="X42" s="230" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="226" t="inlineStr">
+      <c r="A43" s="220" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="B43" s="230" t="inlineStr">
+      <c r="B43" s="226" t="inlineStr">
         <is>
           <t>Indicates association with Purpose.</t>
         </is>
       </c>
-      <c r="C43" s="226" t="inlineStr">
+      <c r="C43" s="220" t="inlineStr">
         <is>
           <t>dpv:hasPurpose</t>
         </is>
@@ -25153,45 +25153,45 @@
           <t>https://w3c.github.io/dpv/2.1/dpv/#vocab-purposes</t>
         </is>
       </c>
-      <c r="E43" s="227" t="inlineStr">
+      <c r="E43" s="222" t="inlineStr">
         <is>
           <t>One or more categories or sub-categories of purposes can be chosen from the taxonomy provided by dpv (see the Controlled vocabulary column). Try to be as specific as possible.
 An example value could be dpv:ResearchAndDevelopment.</t>
         </is>
       </c>
-      <c r="F43" s="218" t="inlineStr">
+      <c r="F43" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G43" s="231" t="inlineStr">
+      <c r="G43" s="227" t="inlineStr">
         <is>
           <t>dpv:Purpose (IRI)</t>
         </is>
       </c>
-      <c r="H43" s="231" t="inlineStr">
+      <c r="H43" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I43" s="225" t="inlineStr">
+      <c r="I43" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J43" s="225" t="inlineStr">
+      <c r="J43" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K43" s="232" t="inlineStr">
+      <c r="K43" s="228" t="inlineStr">
         <is>
           <t>custom:purpose</t>
         </is>
       </c>
-      <c r="L43" s="225" t="n"/>
-      <c r="M43" s="229" t="n"/>
-      <c r="N43" s="229" t="n"/>
+      <c r="L43" s="218" t="n"/>
+      <c r="M43" s="224" t="n"/>
+      <c r="N43" s="224" t="n"/>
       <c r="P43" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -25202,12 +25202,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V43" s="226" t="n"/>
-      <c r="W43" s="226" t="n"/>
-      <c r="X43" s="226" t="n"/>
+      <c r="V43" s="220" t="n"/>
+      <c r="W43" s="220" t="n"/>
+      <c r="X43" s="220" t="n"/>
     </row>
     <row r="44" ht="228" customHeight="1">
-      <c r="A44" s="220" t="inlineStr">
+      <c r="A44" s="230" t="inlineStr">
         <is>
           <t>qualified attribution</t>
         </is>
@@ -25236,7 +25236,7 @@
 The value for role in the Attribution class then becomes: https://standards.iso.org/iso/19115/resources/Codelists/gml/CI_RoleCode.xml#funder</t>
         </is>
       </c>
-      <c r="F44" s="231" t="inlineStr">
+      <c r="F44" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25246,33 +25246,33 @@
           <t>prov:Attribution</t>
         </is>
       </c>
-      <c r="H44" s="218" t="inlineStr">
+      <c r="H44" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I44" s="224" t="inlineStr">
+      <c r="I44" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J44" s="224" t="inlineStr">
+      <c r="J44" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K44" s="75" t="n"/>
-      <c r="L44" s="224" t="inlineStr">
+      <c r="L44" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="M44" s="224" t="inlineStr">
+      <c r="M44" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="N44" s="224" t="inlineStr">
+      <c r="N44" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
@@ -25292,22 +25292,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V44" s="220" t="n"/>
-      <c r="W44" s="220" t="n"/>
-      <c r="X44" s="220" t="n"/>
+      <c r="V44" s="230" t="n"/>
+      <c r="W44" s="230" t="n"/>
+      <c r="X44" s="230" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="226" t="inlineStr">
+      <c r="A45" s="220" t="inlineStr">
         <is>
           <t>qualified relation</t>
         </is>
       </c>
-      <c r="B45" s="230" t="inlineStr">
+      <c r="B45" s="226" t="inlineStr">
         <is>
           <t>Link to a description of a relationship with another resource.</t>
         </is>
       </c>
-      <c r="C45" s="226" t="inlineStr">
+      <c r="C45" s="220" t="inlineStr">
         <is>
           <t>dcat:qualifiedRelation</t>
         </is>
@@ -25322,7 +25322,7 @@
           <t>This property makes use of another small class (dcat:Relationship), in which you can indicate the related resource (via its identifier) and the nature of the relation (based on a controlled vocabulary, which is described in the information of the class).</t>
         </is>
       </c>
-      <c r="F45" s="218" t="inlineStr">
+      <c r="F45" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25332,37 +25332,37 @@
           <t>dcat:Relationship</t>
         </is>
       </c>
-      <c r="H45" s="231" t="inlineStr">
+      <c r="H45" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I45" s="225" t="inlineStr">
+      <c r="I45" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J45" s="225" t="inlineStr">
+      <c r="J45" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K45" s="232" t="inlineStr">
+      <c r="K45" s="228" t="inlineStr">
         <is>
           <t>custom:qualified_relation</t>
         </is>
       </c>
-      <c r="L45" s="225" t="inlineStr">
+      <c r="L45" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Relationship' tab.</t>
         </is>
       </c>
-      <c r="M45" s="225" t="inlineStr">
+      <c r="M45" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Relationship' tab.</t>
         </is>
       </c>
-      <c r="N45" s="225" t="inlineStr">
+      <c r="N45" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'Relationship' tab.</t>
         </is>
@@ -25382,12 +25382,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V45" s="226" t="n"/>
-      <c r="W45" s="226" t="n"/>
-      <c r="X45" s="226" t="n"/>
+      <c r="V45" s="220" t="n"/>
+      <c r="W45" s="220" t="n"/>
+      <c r="X45" s="220" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="220" t="inlineStr">
+      <c r="A46" s="230" t="inlineStr">
         <is>
           <t>quality annotation</t>
         </is>
@@ -25397,7 +25397,7 @@
           <t>Refers to a quality annotation.</t>
         </is>
       </c>
-      <c r="C46" s="220" t="inlineStr">
+      <c r="C46" s="230" t="inlineStr">
         <is>
           <t>dqv:hasQualityAnnotation</t>
         </is>
@@ -25412,7 +25412,7 @@
           <t>This property makes use of another small class (dqv:QualityCertificate), in which you indicate the IRI of the quality certificate, linked to the described resource (via the identifier of the dataset). See that class for more information.</t>
         </is>
       </c>
-      <c r="F46" s="231" t="inlineStr">
+      <c r="F46" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25422,33 +25422,33 @@
           <t>dqv:QualityCertificate</t>
         </is>
       </c>
-      <c r="H46" s="218" t="inlineStr">
+      <c r="H46" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I46" s="224" t="inlineStr">
+      <c r="I46" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J46" s="224" t="inlineStr">
+      <c r="J46" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K46" s="75" t="n"/>
-      <c r="L46" s="224" t="inlineStr">
+      <c r="L46" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="M46" s="224" t="inlineStr">
+      <c r="M46" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="N46" s="224" t="inlineStr">
+      <c r="N46" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
@@ -25468,22 +25468,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V46" s="220" t="n"/>
-      <c r="W46" s="220" t="n"/>
-      <c r="X46" s="220" t="n"/>
+      <c r="V46" s="230" t="n"/>
+      <c r="W46" s="230" t="n"/>
+      <c r="X46" s="230" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="226" t="inlineStr">
+      <c r="A47" s="220" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
       </c>
-      <c r="B47" s="230" t="inlineStr">
+      <c r="B47" s="226" t="inlineStr">
         <is>
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C47" s="226" t="inlineStr">
+      <c r="C47" s="220" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -25498,39 +25498,39 @@
           <t>This property should point to the first known date of issuance, such as the publication date in a data repository. Example: 2023-12-10T13:16:10.246Z.</t>
         </is>
       </c>
-      <c r="F47" s="218" t="inlineStr">
+      <c r="F47" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G47" s="231" t="inlineStr">
+      <c r="G47" s="227" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H47" s="231" t="inlineStr">
+      <c r="H47" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I47" s="225" t="inlineStr">
+      <c r="I47" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J47" s="225" t="inlineStr">
+      <c r="J47" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K47" s="232" t="inlineStr">
+      <c r="K47" s="228" t="inlineStr">
         <is>
           <t>custom:issued</t>
         </is>
       </c>
-      <c r="L47" s="225" t="n"/>
-      <c r="M47" s="229" t="n"/>
-      <c r="N47" s="229" t="n"/>
+      <c r="L47" s="218" t="n"/>
+      <c r="M47" s="224" t="n"/>
+      <c r="N47" s="224" t="n"/>
       <c r="P47" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -25546,12 +25546,12 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="V47" s="226" t="n"/>
-      <c r="W47" s="226" t="n"/>
-      <c r="X47" s="226" t="n"/>
+      <c r="V47" s="220" t="n"/>
+      <c r="W47" s="220" t="n"/>
+      <c r="X47" s="220" t="n"/>
     </row>
     <row r="48" ht="160" customHeight="1">
-      <c r="A48" s="220" t="inlineStr">
+      <c r="A48" s="230" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -25561,7 +25561,7 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C48" s="220" t="inlineStr">
+      <c r="C48" s="230" t="inlineStr">
         <is>
           <t>healthdcatap:retentionPeriod</t>
         </is>
@@ -25580,7 +25580,7 @@
 If a limit is known, provide both dcat:startDate and dcat:endDate.</t>
         </is>
       </c>
-      <c r="F48" s="231" t="inlineStr">
+      <c r="F48" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25590,17 +25590,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H48" s="218" t="inlineStr">
+      <c r="H48" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I48" s="224" t="inlineStr">
+      <c r="I48" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J48" s="224" t="inlineStr">
+      <c r="J48" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -25610,17 +25610,17 @@
           <t>custom:retention_period</t>
         </is>
       </c>
-      <c r="L48" s="224" t="inlineStr">
+      <c r="L48" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M48" s="224" t="inlineStr">
+      <c r="M48" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N48" s="224" t="inlineStr">
+      <c r="N48" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -25640,22 +25640,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V48" s="220" t="n"/>
-      <c r="W48" s="220" t="n"/>
-      <c r="X48" s="220" t="n"/>
+      <c r="V48" s="230" t="n"/>
+      <c r="W48" s="230" t="n"/>
+      <c r="X48" s="230" t="n"/>
     </row>
     <row r="49" ht="80" customHeight="1">
-      <c r="A49" s="226" t="inlineStr">
+      <c r="A49" s="220" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="B49" s="230" t="inlineStr">
+      <c r="B49" s="226" t="inlineStr">
         <is>
           <t>Links to a sample of an Asset (which is itself an Asset).</t>
         </is>
       </c>
-      <c r="C49" s="226" t="inlineStr">
+      <c r="C49" s="220" t="inlineStr">
         <is>
           <t>adms:sample</t>
         </is>
@@ -25670,7 +25670,7 @@
           <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can consist of anonymised or synthetic data, or a data dictionary provided in CSVW format. This is currently being further developed by the TEHDAS2 programme. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
         </is>
       </c>
-      <c r="F49" s="218" t="inlineStr">
+      <c r="F49" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25680,22 +25680,22 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H49" s="231" t="inlineStr">
+      <c r="H49" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I49" s="225" t="inlineStr">
+      <c r="I49" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J49" s="225" t="inlineStr">
+      <c r="J49" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K49" s="232" t="inlineStr">
+      <c r="K49" s="228" t="inlineStr">
         <is>
           <t>(issue on GitHub)</t>
         </is>
@@ -25705,8 +25705,8 @@
           <t>If available, add the URI for the sample distribution here.</t>
         </is>
       </c>
-      <c r="M49" s="225" t="n"/>
-      <c r="N49" s="225" t="n"/>
+      <c r="M49" s="218" t="n"/>
+      <c r="N49" s="218" t="n"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>hrishapes:DistributionShape</t>
@@ -25727,12 +25727,12 @@
           <t>Sample Distribution</t>
         </is>
       </c>
-      <c r="V49" s="226" t="n"/>
-      <c r="W49" s="226" t="n"/>
-      <c r="X49" s="226" t="n"/>
+      <c r="V49" s="220" t="n"/>
+      <c r="W49" s="220" t="n"/>
+      <c r="X49" s="220" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="220" t="inlineStr">
+      <c r="A50" s="230" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -25742,7 +25742,7 @@
           <t>A related resource from which the described resource is derived.</t>
         </is>
       </c>
-      <c r="C50" s="220" t="inlineStr">
+      <c r="C50" s="230" t="inlineStr">
         <is>
           <t>dct:source</t>
         </is>
@@ -25752,12 +25752,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E50" s="223" t="inlineStr">
+      <c r="E50" s="231" t="inlineStr">
         <is>
           <t>Indicate the dataset on which this described dataset is based.</t>
         </is>
       </c>
-      <c r="F50" s="231" t="inlineStr">
+      <c r="F50" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25767,17 +25767,17 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H50" s="218" t="inlineStr">
+      <c r="H50" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I50" s="224" t="inlineStr">
+      <c r="I50" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J50" s="224" t="inlineStr">
+      <c r="J50" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -25792,8 +25792,8 @@
           <t>If applicable, add the URI for the source dataset here.</t>
         </is>
       </c>
-      <c r="M50" s="224" t="n"/>
-      <c r="N50" s="224" t="n"/>
+      <c r="M50" s="232" t="n"/>
+      <c r="N50" s="232" t="n"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -25809,22 +25809,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V50" s="220" t="n"/>
-      <c r="W50" s="220" t="n"/>
-      <c r="X50" s="220" t="n"/>
+      <c r="V50" s="230" t="n"/>
+      <c r="W50" s="230" t="n"/>
+      <c r="X50" s="230" t="n"/>
     </row>
     <row r="51" ht="64" customHeight="1">
-      <c r="A51" s="226" t="inlineStr">
+      <c r="A51" s="220" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B51" s="230" t="inlineStr">
+      <c r="B51" s="226" t="inlineStr">
         <is>
           <t>The status of the Asset in the context of a particular workflow process.</t>
         </is>
       </c>
-      <c r="C51" s="226" t="inlineStr">
+      <c r="C51" s="220" t="inlineStr">
         <is>
           <t>adms:status</t>
         </is>
@@ -25840,39 +25840,39 @@
 For example: http://publications.europa.eu/resource/authority/dataset-status/COMPLETED</t>
         </is>
       </c>
-      <c r="F51" s="218" t="inlineStr">
+      <c r="F51" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G51" s="231" t="inlineStr">
+      <c r="G51" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H51" s="231" t="inlineStr">
+      <c r="H51" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I51" s="225" t="inlineStr">
+      <c r="I51" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J51" s="225" t="inlineStr">
+      <c r="J51" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K51" s="232" t="inlineStr">
+      <c r="K51" s="228" t="inlineStr">
         <is>
           <t>custom:status</t>
         </is>
       </c>
-      <c r="L51" s="225" t="n"/>
-      <c r="M51" s="225" t="n"/>
-      <c r="N51" s="225" t="n"/>
+      <c r="L51" s="218" t="n"/>
+      <c r="M51" s="218" t="n"/>
+      <c r="N51" s="218" t="n"/>
       <c r="P51" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -25883,12 +25883,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V51" s="226" t="n"/>
-      <c r="W51" s="226" t="n"/>
-      <c r="X51" s="226" t="n"/>
+      <c r="V51" s="220" t="n"/>
+      <c r="W51" s="220" t="n"/>
+      <c r="X51" s="220" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="220" t="inlineStr">
+      <c r="A52" s="230" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -25898,7 +25898,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C52" s="220" t="inlineStr">
+      <c r="C52" s="230" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -25913,7 +25913,7 @@
           <t>The start and end date of the period that the dataset covers. This property makes use of a small class: Period of Time, in which a start and end date can be given.</t>
         </is>
       </c>
-      <c r="F52" s="231" t="inlineStr">
+      <c r="F52" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25923,17 +25923,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H52" s="218" t="inlineStr">
+      <c r="H52" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I52" s="224" t="inlineStr">
+      <c r="I52" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J52" s="224" t="inlineStr">
+      <c r="J52" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -25943,17 +25943,17 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L52" s="224" t="inlineStr">
+      <c r="L52" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M52" s="224" t="inlineStr">
+      <c r="M52" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N52" s="224" t="inlineStr">
+      <c r="N52" s="232" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -25973,17 +25973,17 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V52" s="220" t="n"/>
-      <c r="W52" s="220" t="n"/>
-      <c r="X52" s="220" t="n"/>
+      <c r="V52" s="230" t="n"/>
+      <c r="W52" s="230" t="n"/>
+      <c r="X52" s="230" t="n"/>
     </row>
     <row r="53" ht="64" customHeight="1">
-      <c r="A53" s="226" t="inlineStr">
+      <c r="A53" s="220" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
       </c>
-      <c r="B53" s="230" t="inlineStr">
+      <c r="B53" s="226" t="inlineStr">
         <is>
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
@@ -26003,39 +26003,39 @@
           <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of datasets, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
         </is>
       </c>
-      <c r="F53" s="218" t="inlineStr">
+      <c r="F53" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G53" s="231" t="inlineStr">
+      <c r="G53" s="227" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H53" s="231" t="inlineStr">
+      <c r="H53" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I53" s="225" t="inlineStr">
+      <c r="I53" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J53" s="225" t="inlineStr">
+      <c r="J53" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K53" s="232" t="inlineStr">
+      <c r="K53" s="228" t="inlineStr">
         <is>
           <t>custom:temporal_resolution</t>
         </is>
       </c>
-      <c r="L53" s="225" t="n"/>
-      <c r="M53" s="225" t="n"/>
-      <c r="N53" s="225" t="n"/>
+      <c r="L53" s="218" t="n"/>
+      <c r="M53" s="218" t="n"/>
+      <c r="N53" s="218" t="n"/>
       <c r="P53" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26046,12 +26046,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V53" s="226" t="n"/>
-      <c r="W53" s="226" t="n"/>
-      <c r="X53" s="226" t="n"/>
+      <c r="V53" s="220" t="n"/>
+      <c r="W53" s="220" t="n"/>
+      <c r="X53" s="220" t="n"/>
     </row>
     <row r="54" ht="74.25" customHeight="1">
-      <c r="A54" s="220" t="inlineStr">
+      <c r="A54" s="230" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -26061,7 +26061,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C54" s="220" t="inlineStr">
+      <c r="C54" s="230" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -26076,27 +26076,27 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, all datasets will use the theme 'HEAL' (http://publications.europa.eu/resource/authority/data-theme/HEAL), but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F54" s="231" t="inlineStr">
+      <c r="F54" s="227" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G54" s="218" t="inlineStr">
+      <c r="G54" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H54" s="218" t="inlineStr">
+      <c r="H54" s="225" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I54" s="224" t="inlineStr">
+      <c r="I54" s="232" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J54" s="224" t="inlineStr">
+      <c r="J54" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -26106,9 +26106,9 @@
           <t>custom:theme</t>
         </is>
       </c>
-      <c r="L54" s="224" t="n"/>
-      <c r="M54" s="224" t="n"/>
-      <c r="N54" s="224" t="n"/>
+      <c r="L54" s="232" t="n"/>
+      <c r="M54" s="232" t="n"/>
+      <c r="N54" s="232" t="n"/>
       <c r="P54" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -26124,22 +26124,22 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="V54" s="220" t="n"/>
-      <c r="W54" s="220" t="n"/>
-      <c r="X54" s="220" t="n"/>
+      <c r="V54" s="230" t="n"/>
+      <c r="W54" s="230" t="n"/>
+      <c r="X54" s="230" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="226" t="inlineStr">
+      <c r="A55" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B55" s="230" t="inlineStr">
+      <c r="B55" s="226" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C55" s="226" t="inlineStr">
+      <c r="C55" s="220" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -26154,39 +26154,39 @@
           <t>Provide a unique title for your Dataset, which can be repeated in multiple languages. Example: Healthy Brain Study - Physiological Data</t>
         </is>
       </c>
-      <c r="F55" s="218" t="inlineStr">
+      <c r="F55" s="225" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G55" s="231" t="inlineStr">
+      <c r="G55" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H55" s="231" t="inlineStr">
+      <c r="H55" s="227" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I55" s="225" t="inlineStr">
+      <c r="I55" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J55" s="225" t="inlineStr">
+      <c r="J55" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K55" s="232" t="inlineStr">
+      <c r="K55" s="228" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="L55" s="225" t="n"/>
-      <c r="M55" s="225" t="n"/>
-      <c r="N55" s="225" t="n"/>
+      <c r="L55" s="218" t="n"/>
+      <c r="M55" s="218" t="n"/>
+      <c r="N55" s="218" t="n"/>
       <c r="P55" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26200,12 +26200,12 @@
       <c r="T55" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V55" s="226" t="n"/>
-      <c r="W55" s="226" t="n"/>
-      <c r="X55" s="226" t="n"/>
+      <c r="V55" s="220" t="n"/>
+      <c r="W55" s="220" t="n"/>
+      <c r="X55" s="220" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="220" t="inlineStr">
+      <c r="A56" s="230" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -26215,7 +26215,7 @@
           <t>The nature or genre of the resource.</t>
         </is>
       </c>
-      <c r="C56" s="220" t="inlineStr">
+      <c r="C56" s="230" t="inlineStr">
         <is>
           <t>dct:type</t>
         </is>
@@ -26231,27 +26231,27 @@
 The EU Dataset-type controlled vocabulary SHOULD be used.</t>
         </is>
       </c>
-      <c r="F56" s="231" t="inlineStr">
+      <c r="F56" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G56" s="218" t="inlineStr">
+      <c r="G56" s="225" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H56" s="218" t="inlineStr">
+      <c r="H56" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I56" s="224" t="inlineStr">
+      <c r="I56" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J56" s="224" t="inlineStr">
+      <c r="J56" s="232" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -26261,9 +26261,9 @@
           <t>custom:dcat_type</t>
         </is>
       </c>
-      <c r="L56" s="224" t="n"/>
-      <c r="M56" s="224" t="n"/>
-      <c r="N56" s="224" t="n"/>
+      <c r="L56" s="232" t="n"/>
+      <c r="M56" s="232" t="n"/>
+      <c r="N56" s="232" t="n"/>
       <c r="O56" s="84" t="n"/>
       <c r="P56" s="69" t="inlineStr">
         <is>
@@ -26277,22 +26277,22 @@
       </c>
       <c r="R56" s="84" t="n"/>
       <c r="T56" s="84" t="n"/>
-      <c r="V56" s="220" t="n"/>
-      <c r="W56" s="220" t="n"/>
-      <c r="X56" s="220" t="n"/>
+      <c r="V56" s="230" t="n"/>
+      <c r="W56" s="230" t="n"/>
+      <c r="X56" s="230" t="n"/>
     </row>
     <row r="57" ht="80" customHeight="1">
-      <c r="A57" s="226" t="inlineStr">
+      <c r="A57" s="220" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="B57" s="230" t="inlineStr">
+      <c r="B57" s="226" t="inlineStr">
         <is>
           <t>Links the Dataset to a CSVW TableGroup that provides a machine-readable description of the data variables.</t>
         </is>
       </c>
-      <c r="C57" s="226" t="inlineStr">
+      <c r="C57" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:hasVariables</t>
         </is>
@@ -26308,7 +26308,7 @@
 Use this property to link a structured dataset to a CSVW TableGroup that documents its data variables, columns, or fields in a machine-readable way.</t>
         </is>
       </c>
-      <c r="F57" s="231" t="inlineStr">
+      <c r="F57" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -26318,33 +26318,33 @@
           <t>csvw:TableGroup</t>
         </is>
       </c>
-      <c r="H57" s="231" t="inlineStr">
+      <c r="H57" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I57" s="225" t="inlineStr">
+      <c r="I57" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J57" s="225" t="inlineStr">
+      <c r="J57" s="218" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K57" s="232" t="n"/>
-      <c r="L57" s="225" t="inlineStr">
+      <c r="K57" s="228" t="n"/>
+      <c r="L57" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'TableGroup' tab.</t>
         </is>
       </c>
-      <c r="M57" s="225" t="inlineStr">
+      <c r="M57" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'TableGroup' tab.</t>
         </is>
       </c>
-      <c r="N57" s="225" t="inlineStr">
+      <c r="N57" s="218" t="inlineStr">
         <is>
           <t>Enter the value on the 'TableGroup' tab.</t>
         </is>
@@ -26369,12 +26369,12 @@
           <t>Variables</t>
         </is>
       </c>
-      <c r="V57" s="226" t="n"/>
-      <c r="W57" s="226" t="n"/>
-      <c r="X57" s="226" t="n"/>
+      <c r="V57" s="220" t="n"/>
+      <c r="W57" s="220" t="n"/>
+      <c r="X57" s="220" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="220" t="inlineStr">
+      <c r="A58" s="230" t="inlineStr">
         <is>
           <t>version</t>
         </is>
@@ -26384,7 +26384,7 @@
           <t>The version indicator (name or identifier) of a resource.</t>
         </is>
       </c>
-      <c r="C58" s="220" t="inlineStr">
+      <c r="C58" s="230" t="inlineStr">
         <is>
           <t>dcat:version</t>
         </is>
@@ -26399,27 +26399,27 @@
           <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
         </is>
       </c>
-      <c r="F58" s="218" t="inlineStr">
+      <c r="F58" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G58" s="218" t="inlineStr">
+      <c r="G58" s="225" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H58" s="218" t="inlineStr">
+      <c r="H58" s="225" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I58" s="224" t="inlineStr">
+      <c r="I58" s="232" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J58" s="224" t="inlineStr">
+      <c r="J58" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -26429,9 +26429,9 @@
           <t>custom:version</t>
         </is>
       </c>
-      <c r="L58" s="224" t="n"/>
-      <c r="M58" s="224" t="n"/>
-      <c r="N58" s="224" t="n"/>
+      <c r="L58" s="232" t="n"/>
+      <c r="M58" s="232" t="n"/>
+      <c r="N58" s="232" t="n"/>
       <c r="P58" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26443,22 +26443,22 @@
         </is>
       </c>
       <c r="S58" s="84" t="n"/>
-      <c r="V58" s="220" t="n"/>
-      <c r="W58" s="220" t="n"/>
-      <c r="X58" s="220" t="n"/>
+      <c r="V58" s="230" t="n"/>
+      <c r="W58" s="230" t="n"/>
+      <c r="X58" s="230" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="226" t="inlineStr">
+      <c r="A59" s="220" t="inlineStr">
         <is>
           <t>version notes</t>
         </is>
       </c>
-      <c r="B59" s="230" t="inlineStr">
+      <c r="B59" s="226" t="inlineStr">
         <is>
           <t>A description of changes between this version and the previous version of the Asset.</t>
         </is>
       </c>
-      <c r="C59" s="226" t="inlineStr">
+      <c r="C59" s="220" t="inlineStr">
         <is>
           <t>adms:versionNotes</t>
         </is>
@@ -26468,44 +26468,44 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E59" s="230" t="inlineStr">
+      <c r="E59" s="226" t="inlineStr">
         <is>
           <t>Provide a short description of changes made to the dataset since the previous version.</t>
         </is>
       </c>
-      <c r="F59" s="231" t="inlineStr">
+      <c r="F59" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G59" s="231" t="inlineStr">
+      <c r="G59" s="227" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H59" s="231" t="inlineStr">
+      <c r="H59" s="227" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I59" s="225" t="inlineStr">
+      <c r="I59" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J59" s="225" t="inlineStr">
+      <c r="J59" s="218" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K59" s="232" t="inlineStr">
+      <c r="K59" s="228" t="inlineStr">
         <is>
           <t>custom:version_notes</t>
         </is>
       </c>
-      <c r="L59" s="225" t="n"/>
-      <c r="M59" s="225" t="n"/>
-      <c r="N59" s="225" t="n"/>
+      <c r="L59" s="218" t="n"/>
+      <c r="M59" s="218" t="n"/>
+      <c r="N59" s="218" t="n"/>
       <c r="P59" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26519,12 +26519,12 @@
       <c r="T59" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V59" s="226" t="n"/>
-      <c r="W59" s="226" t="n"/>
-      <c r="X59" s="226" t="n"/>
+      <c r="V59" s="220" t="n"/>
+      <c r="W59" s="220" t="n"/>
+      <c r="X59" s="220" t="n"/>
     </row>
     <row r="60" ht="84.75" customHeight="1">
-      <c r="A60" s="220" t="inlineStr">
+      <c r="A60" s="230" t="inlineStr">
         <is>
           <t>was generated by</t>
         </is>
@@ -26534,7 +26534,7 @@
           <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
         </is>
       </c>
-      <c r="C60" s="220" t="inlineStr">
+      <c r="C60" s="230" t="inlineStr">
         <is>
           <t>prov:wasGeneratedBy</t>
         </is>
@@ -26544,7 +26544,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="F60" s="218" t="inlineStr">
+      <c r="F60" s="225" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -26554,25 +26554,25 @@
           <t>prov:Activity</t>
         </is>
       </c>
-      <c r="H60" s="218" t="inlineStr">
+      <c r="H60" s="225" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I60" s="224" t="inlineStr">
+      <c r="I60" s="232" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J60" s="224" t="inlineStr">
+      <c r="J60" s="232" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K60" s="75" t="n"/>
-      <c r="L60" s="224" t="n"/>
-      <c r="M60" s="224" t="n"/>
-      <c r="N60" s="224" t="n"/>
+      <c r="L60" s="232" t="n"/>
+      <c r="M60" s="232" t="n"/>
+      <c r="N60" s="232" t="n"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>hrishapes:ActivityShape</t>
@@ -26588,9 +26588,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V60" s="220" t="n"/>
-      <c r="W60" s="220" t="n"/>
-      <c r="X60" s="220" t="n"/>
+      <c r="V60" s="230" t="n"/>
+      <c r="W60" s="230" t="n"/>
+      <c r="X60" s="230" t="n"/>
     </row>
     <row r="61" customFormat="1" s="84">
       <c r="A61" s="110" t="n"/>
@@ -26771,8 +26771,8 @@
     <col width="36.5" customWidth="1" style="102" min="22" max="22"/>
     <col width="8.83203125" customWidth="1" style="102" min="23" max="28"/>
     <col width="18" customWidth="1" min="29" max="31"/>
-    <col width="8.83203125" customWidth="1" style="102" min="32" max="33"/>
-    <col width="8.83203125" customWidth="1" style="102" min="34" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="102" min="32" max="34"/>
+    <col width="8.83203125" customWidth="1" style="102" min="35" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customFormat="1" customHeight="1" s="165">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="J2" s="125" t="n"/>
       <c r="K2" s="126" t="n"/>
-      <c r="L2" s="224" t="n"/>
+      <c r="L2" s="232" t="n"/>
       <c r="X2" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27053,16 +27053,16 @@
           <t>_mail</t>
         </is>
       </c>
-      <c r="L3" s="225" t="n"/>
-      <c r="M3" s="225" t="n"/>
-      <c r="N3" s="225" t="n"/>
-      <c r="O3" s="225" t="n"/>
-      <c r="P3" s="225" t="n"/>
-      <c r="Q3" s="225" t="n"/>
-      <c r="R3" s="225" t="n"/>
-      <c r="S3" s="225" t="n"/>
-      <c r="T3" s="225" t="n"/>
-      <c r="U3" s="225" t="n"/>
+      <c r="L3" s="218" t="n"/>
+      <c r="M3" s="218" t="n"/>
+      <c r="N3" s="218" t="n"/>
+      <c r="O3" s="218" t="n"/>
+      <c r="P3" s="218" t="n"/>
+      <c r="Q3" s="218" t="n"/>
+      <c r="R3" s="218" t="n"/>
+      <c r="S3" s="218" t="n"/>
+      <c r="T3" s="218" t="n"/>
+      <c r="U3" s="218" t="n"/>
       <c r="X3" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -27142,7 +27142,7 @@
           <t>_id</t>
         </is>
       </c>
-      <c r="L4" s="224" t="n"/>
+      <c r="L4" s="232" t="n"/>
       <c r="X4" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27213,16 +27213,16 @@
           <t>_name</t>
         </is>
       </c>
-      <c r="L5" s="225" t="n"/>
-      <c r="M5" s="225" t="n"/>
-      <c r="N5" s="225" t="n"/>
-      <c r="O5" s="225" t="n"/>
-      <c r="P5" s="225" t="n"/>
-      <c r="Q5" s="225" t="n"/>
-      <c r="R5" s="225" t="n"/>
-      <c r="S5" s="225" t="n"/>
-      <c r="T5" s="225" t="n"/>
-      <c r="U5" s="225" t="n"/>
+      <c r="L5" s="218" t="n"/>
+      <c r="M5" s="218" t="n"/>
+      <c r="N5" s="218" t="n"/>
+      <c r="O5" s="218" t="n"/>
+      <c r="P5" s="218" t="n"/>
+      <c r="Q5" s="218" t="n"/>
+      <c r="R5" s="218" t="n"/>
+      <c r="S5" s="218" t="n"/>
+      <c r="T5" s="218" t="n"/>
+      <c r="U5" s="218" t="n"/>
       <c r="X5" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27246,7 +27246,7 @@
           <t>publisher note</t>
         </is>
       </c>
-      <c r="B6" s="222" t="inlineStr">
+      <c r="B6" s="229" t="inlineStr">
         <is>
           <t>A description of the publisher's activities.</t>
         </is>
@@ -27261,7 +27261,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E6" s="222" t="inlineStr">
+      <c r="E6" s="229" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the next major release.
 This property can be repeated for parallel language versions of the publisher notes. Example: "Sciensano is a research institute and the national public health institute of Belgium. It is a so-called federal scientific institution that operates under the authority of the federal minister of Public Health and the federal minister of Agriculture of Belgium."@en</t>
@@ -27293,7 +27293,7 @@
         </is>
       </c>
       <c r="K6" s="126" t="n"/>
-      <c r="L6" s="224" t="n"/>
+      <c r="L6" s="232" t="n"/>
       <c r="X6" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27312,17 +27312,17 @@
       <c r="AE6" s="133" t="n"/>
     </row>
     <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="226" t="inlineStr">
+      <c r="A7" s="220" t="inlineStr">
         <is>
           <t>publisher type</t>
         </is>
       </c>
-      <c r="B7" s="230" t="inlineStr">
+      <c r="B7" s="226" t="inlineStr">
         <is>
           <t>A type of organisation that makes the Dataset available.</t>
         </is>
       </c>
-      <c r="C7" s="226" t="inlineStr">
+      <c r="C7" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:publishertype</t>
         </is>
@@ -27338,22 +27338,22 @@
 Choose a term from the controlled vocabulary, which includes the following types: Academia-ScientificOrganisation, Company, IndustryConsortium, LocalAuthority, NationalAuthority, NonGovernmentalOrganisation, NonProfitOrganisation, PrivateIndividual, RegionalAuthority, StandardisationBody and SupraNationalAuthority. These should use URLs of the following form: http://purl.org/adms/publishertype/[type].</t>
         </is>
       </c>
-      <c r="F7" s="231" t="inlineStr">
+      <c r="F7" s="227" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G7" s="231" t="inlineStr">
+      <c r="G7" s="227" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H7" s="231" t="inlineStr">
+      <c r="H7" s="227" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="225" t="inlineStr">
+      <c r="I7" s="218" t="inlineStr">
         <is>
           <t>new</t>
         </is>
@@ -27364,16 +27364,16 @@
         </is>
       </c>
       <c r="K7" s="126" t="n"/>
-      <c r="L7" s="225" t="n"/>
-      <c r="M7" s="225" t="n"/>
-      <c r="N7" s="225" t="n"/>
-      <c r="O7" s="225" t="n"/>
-      <c r="P7" s="225" t="n"/>
-      <c r="Q7" s="225" t="n"/>
-      <c r="R7" s="225" t="n"/>
-      <c r="S7" s="225" t="n"/>
-      <c r="T7" s="225" t="n"/>
-      <c r="U7" s="225" t="n"/>
+      <c r="L7" s="218" t="n"/>
+      <c r="M7" s="218" t="n"/>
+      <c r="N7" s="218" t="n"/>
+      <c r="O7" s="218" t="n"/>
+      <c r="P7" s="218" t="n"/>
+      <c r="Q7" s="218" t="n"/>
+      <c r="R7" s="218" t="n"/>
+      <c r="S7" s="218" t="n"/>
+      <c r="T7" s="218" t="n"/>
+      <c r="U7" s="218" t="n"/>
       <c r="X7" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27384,9 +27384,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="AC7" s="226" t="n"/>
-      <c r="AD7" s="226" t="n"/>
-      <c r="AE7" s="226" t="n"/>
+      <c r="AC7" s="220" t="n"/>
+      <c r="AD7" s="220" t="n"/>
+      <c r="AE7" s="220" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="45" t="inlineStr">
@@ -27444,7 +27444,7 @@
           <t>_type</t>
         </is>
       </c>
-      <c r="L8" s="224" t="n"/>
+      <c r="L8" s="232" t="n"/>
       <c r="X8" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27513,16 +27513,16 @@
           <t>_url</t>
         </is>
       </c>
-      <c r="L9" s="225" t="n"/>
-      <c r="M9" s="225" t="n"/>
-      <c r="N9" s="225" t="n"/>
-      <c r="O9" s="225" t="n"/>
-      <c r="P9" s="225" t="n"/>
-      <c r="Q9" s="225" t="n"/>
-      <c r="R9" s="225" t="n"/>
-      <c r="S9" s="225" t="n"/>
-      <c r="T9" s="225" t="n"/>
-      <c r="U9" s="225" t="n"/>
+      <c r="L9" s="218" t="n"/>
+      <c r="M9" s="218" t="n"/>
+      <c r="N9" s="218" t="n"/>
+      <c r="O9" s="218" t="n"/>
+      <c r="P9" s="218" t="n"/>
+      <c r="Q9" s="218" t="n"/>
+      <c r="R9" s="218" t="n"/>
+      <c r="S9" s="218" t="n"/>
+      <c r="T9" s="218" t="n"/>
+      <c r="U9" s="218" t="n"/>
       <c r="X9" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -28384,8 +28384,8 @@
     <col width="33.5" customWidth="1" style="58" min="17" max="17"/>
     <col width="8.83203125" customWidth="1" style="58" min="18" max="23"/>
     <col width="24.5" customWidth="1" min="24" max="26"/>
-    <col width="8.83203125" customWidth="1" style="58" min="27" max="28"/>
-    <col width="8.83203125" customWidth="1" style="58" min="29" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="58" min="27" max="29"/>
+    <col width="8.83203125" customWidth="1" style="58" min="30" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="80" customFormat="1" customHeight="1" s="165">

--- a/Documents/Health-RI_v2.1.0.xlsx
+++ b/Documents/Health-RI_v2.1.0.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="-28200" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="4" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="-28200" windowWidth="34400" windowHeight="28200" tabRatio="600" firstSheet="4" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" state="visible" r:id="rId1"/>
@@ -1083,17 +1083,32 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1104,9 +1119,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1114,18 +1126,6 @@
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -6075,8 +6075,8 @@
     <col width="28.83203125" customWidth="1" style="234" min="13" max="13"/>
     <col width="9.1640625" customWidth="1" style="234" min="14" max="20"/>
     <col width="19.1640625" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
-    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="27"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customFormat="1" customHeight="1" s="165">
@@ -6197,17 +6197,17 @@
       </c>
     </row>
     <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="220" t="inlineStr">
+      <c r="A2" s="226" t="inlineStr">
         <is>
           <t>access service</t>
         </is>
       </c>
-      <c r="B2" s="226" t="inlineStr">
+      <c r="B2" s="230" t="inlineStr">
         <is>
           <t>A data service that gives access to the distribution of the dataset.</t>
         </is>
       </c>
-      <c r="C2" s="220" t="inlineStr">
+      <c r="C2" s="226" t="inlineStr">
         <is>
           <t>dcat:accessService</t>
         </is>
@@ -6222,7 +6222,7 @@
           <t>This property links the distribution class to the corresponding data service(s).</t>
         </is>
       </c>
-      <c r="F2" s="225" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6232,17 +6232,17 @@
           <t>dcat:DataService</t>
         </is>
       </c>
-      <c r="H2" s="227" t="inlineStr">
+      <c r="H2" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I2" s="218" t="inlineStr">
+      <c r="I2" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J2" s="232" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6283,12 +6283,12 @@
           <t>Data Service</t>
         </is>
       </c>
-      <c r="U2" s="220" t="n"/>
-      <c r="V2" s="220" t="n"/>
-      <c r="W2" s="220" t="n"/>
+      <c r="U2" s="226" t="n"/>
+      <c r="V2" s="226" t="n"/>
+      <c r="W2" s="226" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="230" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>access URL</t>
         </is>
@@ -6298,7 +6298,7 @@
           <t>A URL of the resource that gives access to a distribution of the dataset. E.g., landing page, feed, SPARQL endpoint.</t>
         </is>
       </c>
-      <c r="C3" s="230" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dcat:accessURL</t>
         </is>
@@ -6308,17 +6308,17 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="231" t="inlineStr">
+      <c r="E3" s="223" t="inlineStr">
         <is>
           <t>Add a link that points to where the dataset can be found. If it’s hosted in a Data Repository, include the link to its entry. For datasets not in a repository (like registries), but still available for secondary use, provide a link to an access request form or a webpage with instructions for accessing the data.</t>
         </is>
       </c>
-      <c r="F3" s="227" t="inlineStr">
+      <c r="F3" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G3" s="225" t="inlineStr">
+      <c r="G3" s="218" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -6326,12 +6326,12 @@
       <c r="H3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="232" t="inlineStr">
+      <c r="I3" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="232" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6341,8 +6341,8 @@
           <t>resource:access_url</t>
         </is>
       </c>
-      <c r="L3" s="232" t="n"/>
-      <c r="M3" s="232" t="n"/>
+      <c r="L3" s="224" t="n"/>
+      <c r="M3" s="224" t="n"/>
       <c r="O3" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6354,22 +6354,22 @@
         </is>
       </c>
       <c r="S3" s="121" t="n"/>
-      <c r="U3" s="230" t="n"/>
-      <c r="V3" s="230" t="n"/>
-      <c r="W3" s="230" t="n"/>
+      <c r="U3" s="220" t="n"/>
+      <c r="V3" s="220" t="n"/>
+      <c r="W3" s="220" t="n"/>
     </row>
     <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="220" t="inlineStr">
+      <c r="A4" s="226" t="inlineStr">
         <is>
           <t>applicable legislation</t>
         </is>
       </c>
-      <c r="B4" s="226" t="inlineStr">
+      <c r="B4" s="230" t="inlineStr">
         <is>
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C4" s="220" t="inlineStr">
+      <c r="C4" s="226" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -6384,27 +6384,27 @@
           <t>The legislation that mandates the creation or management of the Distribution.</t>
         </is>
       </c>
-      <c r="F4" s="225" t="inlineStr">
+      <c r="F4" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="227" t="inlineStr">
+      <c r="G4" s="231" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="227" t="inlineStr">
+      <c r="H4" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="218" t="inlineStr">
+      <c r="I4" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="232" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -6414,8 +6414,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L4" s="218" t="n"/>
-      <c r="M4" s="218" t="n"/>
+      <c r="L4" s="225" t="n"/>
+      <c r="M4" s="225" t="n"/>
       <c r="O4" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6427,9 +6427,9 @@
         </is>
       </c>
       <c r="S4" s="121" t="n"/>
-      <c r="U4" s="220" t="n"/>
-      <c r="V4" s="220" t="n"/>
-      <c r="W4" s="220" t="n"/>
+      <c r="U4" s="226" t="n"/>
+      <c r="V4" s="226" t="n"/>
+      <c r="W4" s="226" t="n"/>
     </row>
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="97" t="inlineStr">
@@ -6442,7 +6442,7 @@
           <t>An indication of how long it is planned to keep the Distribution of the Dataset available.</t>
         </is>
       </c>
-      <c r="C5" s="230" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>dcatap:availability</t>
         </is>
@@ -6457,12 +6457,12 @@
           <t>To indicate the planned availability of the Distribution, the EU planned-availability controlled vocabulary MUST be used.</t>
         </is>
       </c>
-      <c r="F5" s="225" t="inlineStr">
+      <c r="F5" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="225" t="inlineStr">
+      <c r="G5" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
@@ -6472,19 +6472,19 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="232" t="inlineStr">
+      <c r="I5" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="232" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="69" t="n"/>
-      <c r="L5" s="232" t="n"/>
-      <c r="M5" s="232" t="n"/>
+      <c r="L5" s="224" t="n"/>
+      <c r="M5" s="224" t="n"/>
       <c r="O5" s="203" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -6501,12 +6501,12 @@
       <c r="W5" s="97" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="220" t="inlineStr">
+      <c r="A6" s="226" t="inlineStr">
         <is>
           <t>byte size</t>
         </is>
       </c>
-      <c r="B6" s="226" t="inlineStr">
+      <c r="B6" s="230" t="inlineStr">
         <is>
           <t>The size of a distribution in bytes.</t>
         </is>
@@ -6526,27 +6526,27 @@
           <t>Describes the size of the distribution (the actual file) in bytes, and is therefore expressed as a non-negative integer. If the actual size is not known, it can be estimated.</t>
         </is>
       </c>
-      <c r="F6" s="227" t="inlineStr">
+      <c r="F6" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G6" s="227" t="inlineStr">
+      <c r="G6" s="231" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H6" s="227" t="inlineStr">
+      <c r="H6" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I6" s="218" t="inlineStr">
+      <c r="I6" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="232" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6556,8 +6556,8 @@
           <t>resource:size</t>
         </is>
       </c>
-      <c r="L6" s="218" t="n"/>
-      <c r="M6" s="218" t="n"/>
+      <c r="L6" s="225" t="n"/>
+      <c r="M6" s="225" t="n"/>
       <c r="O6" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6569,12 +6569,12 @@
         </is>
       </c>
       <c r="S6" s="121" t="n"/>
-      <c r="U6" s="220" t="n"/>
-      <c r="V6" s="220" t="n"/>
-      <c r="W6" s="220" t="n"/>
+      <c r="U6" s="226" t="n"/>
+      <c r="V6" s="226" t="n"/>
+      <c r="W6" s="226" t="n"/>
     </row>
     <row r="7" ht="64" customHeight="1">
-      <c r="A7" s="230" t="inlineStr">
+      <c r="A7" s="220" t="inlineStr">
         <is>
           <t>checksum</t>
         </is>
@@ -6584,7 +6584,7 @@
           <t>The checksum property provides a mechanism that can be used to verify that the contents of a file or package have not changed.</t>
         </is>
       </c>
-      <c r="C7" s="230" t="inlineStr">
+      <c r="C7" s="220" t="inlineStr">
         <is>
           <t>spdx:checksum</t>
         </is>
@@ -6599,7 +6599,7 @@
           <t>The checksum is related to the downloadURL. This property makes use of the spdx:Checksum class, which itself has two properties to indicate the checksum algorithm and checksum value (see Checksum class for further details).</t>
         </is>
       </c>
-      <c r="F7" s="225" t="inlineStr">
+      <c r="F7" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -6609,17 +6609,17 @@
           <t>spdx:Checksum</t>
         </is>
       </c>
-      <c r="H7" s="225" t="inlineStr">
+      <c r="H7" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="232" t="inlineStr">
+      <c r="I7" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="232" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6629,12 +6629,12 @@
           <t>resource:hash_algorithm/resource:hash_algorithm</t>
         </is>
       </c>
-      <c r="L7" s="232" t="inlineStr">
+      <c r="L7" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
       </c>
-      <c r="M7" s="232" t="inlineStr">
+      <c r="M7" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Checksum' tab.</t>
         </is>
@@ -6655,17 +6655,17 @@
         </is>
       </c>
       <c r="S7" s="121" t="n"/>
-      <c r="U7" s="230" t="n"/>
-      <c r="V7" s="230" t="n"/>
-      <c r="W7" s="230" t="n"/>
+      <c r="U7" s="220" t="n"/>
+      <c r="V7" s="220" t="n"/>
+      <c r="W7" s="220" t="n"/>
     </row>
     <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="220" t="inlineStr">
+      <c r="A8" s="226" t="inlineStr">
         <is>
           <t>compression format</t>
         </is>
       </c>
-      <c r="B8" s="226" t="inlineStr">
+      <c r="B8" s="230" t="inlineStr">
         <is>
           <t>The compression format of the distribution in which the data is compressed, e.g., to reduce the size of the downloadable file.</t>
         </is>
@@ -6685,27 +6685,27 @@
           <t>It MUST be expressed using a media type as defined in the official register of media types managed by IANA.</t>
         </is>
       </c>
-      <c r="F8" s="227" t="inlineStr">
+      <c r="F8" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="227" t="inlineStr">
+      <c r="G8" s="231" t="inlineStr">
         <is>
           <t>dct:MediaType (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="227" t="inlineStr">
+      <c r="H8" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I8" s="218" t="inlineStr">
+      <c r="I8" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="232" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6715,8 +6715,8 @@
           <t>resource:compress_format</t>
         </is>
       </c>
-      <c r="L8" s="218" t="n"/>
-      <c r="M8" s="218" t="n"/>
+      <c r="L8" s="225" t="n"/>
+      <c r="M8" s="225" t="n"/>
       <c r="O8" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -6728,12 +6728,12 @@
         </is>
       </c>
       <c r="S8" s="121" t="n"/>
-      <c r="U8" s="220" t="n"/>
-      <c r="V8" s="220" t="n"/>
-      <c r="W8" s="220" t="n"/>
+      <c r="U8" s="226" t="n"/>
+      <c r="V8" s="226" t="n"/>
+      <c r="W8" s="226" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="230" t="inlineStr">
+      <c r="A9" s="220" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6743,7 +6743,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C9" s="230" t="inlineStr">
+      <c r="C9" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -6758,27 +6758,27 @@
           <t>Provide specific details about the distribution here, complementing the description of the related Dataset. This field can be repeated for different language versions of the description.</t>
         </is>
       </c>
-      <c r="F9" s="225" t="inlineStr">
+      <c r="F9" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="225" t="inlineStr">
+      <c r="G9" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H9" s="225" t="inlineStr">
+      <c r="H9" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="232" t="inlineStr">
+      <c r="I9" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="232" t="inlineStr">
+      <c r="J9" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6788,8 +6788,8 @@
           <t>resource:description</t>
         </is>
       </c>
-      <c r="L9" s="232" t="n"/>
-      <c r="M9" s="232" t="n"/>
+      <c r="L9" s="224" t="n"/>
+      <c r="M9" s="224" t="n"/>
       <c r="O9" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -6803,22 +6803,22 @@
       <c r="S9" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="U9" s="230" t="n"/>
-      <c r="V9" s="230" t="n"/>
-      <c r="W9" s="230" t="n"/>
+      <c r="U9" s="220" t="n"/>
+      <c r="V9" s="220" t="n"/>
+      <c r="W9" s="220" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="220" t="inlineStr">
+      <c r="A10" s="226" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
       </c>
-      <c r="B10" s="226" t="inlineStr">
+      <c r="B10" s="230" t="inlineStr">
         <is>
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C10" s="220" t="inlineStr">
+      <c r="C10" s="226" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -6833,27 +6833,27 @@
           <t>This page can contain additional information about the distribution.</t>
         </is>
       </c>
-      <c r="F10" s="227" t="inlineStr">
+      <c r="F10" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G10" s="227" t="inlineStr">
+      <c r="G10" s="231" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H10" s="227" t="inlineStr">
+      <c r="H10" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I10" s="218" t="inlineStr">
+      <c r="I10" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J10" s="232" t="inlineStr">
+      <c r="J10" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -6863,8 +6863,8 @@
           <t>resource:documentation</t>
         </is>
       </c>
-      <c r="L10" s="218" t="n"/>
-      <c r="M10" s="218" t="n"/>
+      <c r="L10" s="225" t="n"/>
+      <c r="M10" s="225" t="n"/>
       <c r="O10" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6876,12 +6876,12 @@
         </is>
       </c>
       <c r="S10" s="121" t="n"/>
-      <c r="U10" s="220" t="n"/>
-      <c r="V10" s="220" t="n"/>
-      <c r="W10" s="220" t="n"/>
+      <c r="U10" s="226" t="n"/>
+      <c r="V10" s="226" t="n"/>
+      <c r="W10" s="226" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="230" t="inlineStr">
+      <c r="A11" s="220" t="inlineStr">
         <is>
           <t>download URL</t>
         </is>
@@ -6906,27 +6906,27 @@
           <t>If the dataset is openly accessible and available in a repository, you can directly include a link to the downloadable file here.</t>
         </is>
       </c>
-      <c r="F11" s="225" t="inlineStr">
+      <c r="F11" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="225" t="inlineStr">
+      <c r="G11" s="218" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="225" t="inlineStr">
+      <c r="H11" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="232" t="inlineStr">
+      <c r="I11" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="232" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -6936,8 +6936,8 @@
           <t>resource:download_url</t>
         </is>
       </c>
-      <c r="L11" s="232" t="n"/>
-      <c r="M11" s="232" t="n"/>
+      <c r="L11" s="224" t="n"/>
+      <c r="M11" s="224" t="n"/>
       <c r="O11" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -6949,22 +6949,22 @@
         </is>
       </c>
       <c r="S11" s="121" t="n"/>
-      <c r="U11" s="230" t="n"/>
-      <c r="V11" s="230" t="n"/>
-      <c r="W11" s="230" t="n"/>
+      <c r="U11" s="220" t="n"/>
+      <c r="V11" s="220" t="n"/>
+      <c r="W11" s="220" t="n"/>
     </row>
     <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="220" t="inlineStr">
+      <c r="A12" s="226" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="B12" s="226" t="inlineStr">
+      <c r="B12" s="230" t="inlineStr">
         <is>
           <t>The file format, physical medium, or dimensions of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="220" t="inlineStr">
+      <c r="C12" s="226" t="inlineStr">
         <is>
           <t>dct:format</t>
         </is>
@@ -6979,27 +6979,27 @@
           <t>This property can be used to describe a media format in more detail than "media type" (using IANA media type) when needed. Instances of this property should use a URL from the File Type vocabulary.</t>
         </is>
       </c>
-      <c r="F12" s="227" t="inlineStr">
+      <c r="F12" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="227" t="inlineStr">
+      <c r="G12" s="231" t="inlineStr">
         <is>
           <t>dct:MediaTypeOrExtent (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="227" t="inlineStr">
+      <c r="H12" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I12" s="218" t="inlineStr">
+      <c r="I12" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="232" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7009,8 +7009,8 @@
           <t>resource:format</t>
         </is>
       </c>
-      <c r="L12" s="218" t="n"/>
-      <c r="M12" s="218" t="n"/>
+      <c r="L12" s="225" t="n"/>
+      <c r="M12" s="225" t="n"/>
       <c r="O12" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7022,12 +7022,12 @@
         </is>
       </c>
       <c r="S12" s="121" t="n"/>
-      <c r="U12" s="220" t="n"/>
-      <c r="V12" s="220" t="n"/>
-      <c r="W12" s="220" t="n"/>
+      <c r="U12" s="226" t="n"/>
+      <c r="V12" s="226" t="n"/>
+      <c r="W12" s="226" t="n"/>
     </row>
     <row r="13" ht="99" customHeight="1">
-      <c r="A13" s="230" t="inlineStr">
+      <c r="A13" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -7037,7 +7037,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="230" t="inlineStr">
+      <c r="C13" s="220" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -7047,33 +7047,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E13" s="231" t="inlineStr">
+      <c r="E13" s="223" t="inlineStr">
         <is>
           <t>Indicates the natural language used in the Distribution, using a value from the EU controlled vocabulary. Not all distributions necessarily have a language; for example, those containing imaging data may not.
 Note that here the Health-RI model diverges from DCAT-AP NL, which allows a maximum of 1 language per Distribution. The Health-RI model allows multiple languages in the same Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="225" t="inlineStr">
+      <c r="F13" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="225" t="inlineStr">
+      <c r="G13" s="218" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H13" s="225" t="inlineStr">
+      <c r="H13" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="232" t="inlineStr">
+      <c r="I13" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="232" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7083,8 +7083,8 @@
           <t>resource:language</t>
         </is>
       </c>
-      <c r="L13" s="232" t="n"/>
-      <c r="M13" s="232" t="n"/>
+      <c r="L13" s="224" t="n"/>
+      <c r="M13" s="224" t="n"/>
       <c r="O13" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7096,22 +7096,22 @@
         </is>
       </c>
       <c r="S13" s="121" t="n"/>
-      <c r="U13" s="230" t="n"/>
-      <c r="V13" s="230" t="n"/>
-      <c r="W13" s="230" t="n"/>
+      <c r="U13" s="220" t="n"/>
+      <c r="V13" s="220" t="n"/>
+      <c r="W13" s="220" t="n"/>
     </row>
     <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="220" t="inlineStr">
+      <c r="A14" s="226" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
       </c>
-      <c r="B14" s="226" t="inlineStr">
+      <c r="B14" s="230" t="inlineStr">
         <is>
           <t>A legal document giving official permission to do something with the resource.</t>
         </is>
       </c>
-      <c r="C14" s="220" t="inlineStr">
+      <c r="C14" s="226" t="inlineStr">
         <is>
           <t>dct:license</t>
         </is>
@@ -7121,30 +7121,30 @@
           <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
         </is>
       </c>
-      <c r="E14" s="222" t="inlineStr">
+      <c r="E14" s="227" t="inlineStr">
         <is>
           <t>For public data, use a Creative Commons (CC) licence (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue distributions, where data is not public, use the 'not open' licence from Geonovum and specify data reuse agreements in the dct:rights property.</t>
         </is>
       </c>
-      <c r="F14" s="227" t="inlineStr">
+      <c r="F14" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G14" s="227" t="inlineStr">
+      <c r="G14" s="231" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="227" t="n">
+      <c r="H14" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="I14" s="218" t="inlineStr">
+      <c r="I14" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J14" s="232" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -7154,8 +7154,8 @@
           <t>resource:license</t>
         </is>
       </c>
-      <c r="L14" s="218" t="n"/>
-      <c r="M14" s="218" t="n"/>
+      <c r="L14" s="225" t="n"/>
+      <c r="M14" s="225" t="n"/>
       <c r="O14" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7167,12 +7167,12 @@
         </is>
       </c>
       <c r="S14" s="121" t="n"/>
-      <c r="U14" s="220" t="n"/>
-      <c r="V14" s="220" t="n"/>
-      <c r="W14" s="220" t="n"/>
+      <c r="U14" s="226" t="n"/>
+      <c r="V14" s="226" t="n"/>
+      <c r="W14" s="226" t="n"/>
     </row>
     <row r="15" ht="80" customHeight="1">
-      <c r="A15" s="230" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>linked schemas</t>
         </is>
@@ -7182,7 +7182,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C15" s="230" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -7197,27 +7197,27 @@
           <t xml:space="preserve">This property SHOULD be used to indicate the model, schema, ontology, view or profile that this representation of a dataset conforms to, in a machine-readable form. This is (generally) a complementary concern to the media-type or format. Use a reference to the official publication of the respective schema. </t>
         </is>
       </c>
-      <c r="F15" s="225" t="inlineStr">
+      <c r="F15" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="225" t="inlineStr">
+      <c r="G15" s="218" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="225" t="inlineStr">
+      <c r="H15" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="232" t="inlineStr">
+      <c r="I15" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="232" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7227,8 +7227,8 @@
           <t>resource:conforms_to</t>
         </is>
       </c>
-      <c r="L15" s="232" t="n"/>
-      <c r="M15" s="232" t="n"/>
+      <c r="L15" s="224" t="n"/>
+      <c r="M15" s="224" t="n"/>
       <c r="O15" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7240,22 +7240,22 @@
         </is>
       </c>
       <c r="S15" s="121" t="n"/>
-      <c r="U15" s="230" t="n"/>
-      <c r="V15" s="230" t="n"/>
-      <c r="W15" s="230" t="n"/>
+      <c r="U15" s="220" t="n"/>
+      <c r="V15" s="220" t="n"/>
+      <c r="W15" s="220" t="n"/>
     </row>
     <row r="16" ht="112" customHeight="1">
-      <c r="A16" s="220" t="inlineStr">
+      <c r="A16" s="226" t="inlineStr">
         <is>
           <t>media type</t>
         </is>
       </c>
-      <c r="B16" s="226" t="inlineStr">
+      <c r="B16" s="230" t="inlineStr">
         <is>
           <t>The media type of the distribution as defined by IANA.</t>
         </is>
       </c>
-      <c r="C16" s="220" t="inlineStr">
+      <c r="C16" s="226" t="inlineStr">
         <is>
           <t>dcat:mediaType</t>
         </is>
@@ -7265,34 +7265,34 @@
           <t>IANA Media Types</t>
         </is>
       </c>
-      <c r="E16" s="222" t="inlineStr">
+      <c r="E16" s="227" t="inlineStr">
         <is>
           <t>Use the specified vocabularies, prioritising IANA media types whenever possible. If unavailable, consider other ontologies, such as ZonMw generic terms, to describe the format.
 Example: https://www.iana.org/assignments/media-types/text/csv (for csv)
 If IANA media types do not sufficiently describe the format, use "format" to describe it in more detail.</t>
         </is>
       </c>
-      <c r="F16" s="227" t="inlineStr">
+      <c r="F16" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="227" t="inlineStr">
+      <c r="G16" s="231" t="inlineStr">
         <is>
           <t>dct:MediaType (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="227" t="inlineStr">
+      <c r="H16" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="218" t="inlineStr">
+      <c r="I16" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J16" s="232" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7302,8 +7302,8 @@
           <t>resource:mimetype</t>
         </is>
       </c>
-      <c r="L16" s="218" t="n"/>
-      <c r="M16" s="218" t="n"/>
+      <c r="L16" s="225" t="n"/>
+      <c r="M16" s="225" t="n"/>
       <c r="O16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7315,12 +7315,12 @@
         </is>
       </c>
       <c r="S16" s="121" t="n"/>
-      <c r="U16" s="220" t="n"/>
-      <c r="V16" s="220" t="n"/>
-      <c r="W16" s="220" t="n"/>
+      <c r="U16" s="226" t="n"/>
+      <c r="V16" s="226" t="n"/>
+      <c r="W16" s="226" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="230" t="inlineStr">
+      <c r="A17" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -7341,27 +7341,27 @@
         </is>
       </c>
       <c r="E17" s="98" t="n"/>
-      <c r="F17" s="225" t="inlineStr">
+      <c r="F17" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="225" t="inlineStr">
+      <c r="G17" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="225" t="inlineStr">
+      <c r="H17" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="232" t="inlineStr">
+      <c r="I17" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="232" t="inlineStr">
+      <c r="J17" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7371,8 +7371,8 @@
           <t>resource:modified</t>
         </is>
       </c>
-      <c r="L17" s="232" t="n"/>
-      <c r="M17" s="232" t="n"/>
+      <c r="L17" s="224" t="n"/>
+      <c r="M17" s="224" t="n"/>
       <c r="N17" s="219" t="n"/>
       <c r="O17" s="219" t="inlineStr">
         <is>
@@ -7390,22 +7390,22 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="U17" s="230" t="n"/>
-      <c r="V17" s="230" t="n"/>
-      <c r="W17" s="230" t="n"/>
+      <c r="U17" s="220" t="n"/>
+      <c r="V17" s="220" t="n"/>
+      <c r="W17" s="220" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="220" t="inlineStr">
+      <c r="A18" s="226" t="inlineStr">
         <is>
           <t>packaging format</t>
         </is>
       </c>
-      <c r="B18" s="226" t="inlineStr">
+      <c r="B18" s="230" t="inlineStr">
         <is>
           <t>The package format of the distribution in which one or more data files are grouped together, e.g., to enable a set of related files to be downloaded together.</t>
         </is>
       </c>
-      <c r="C18" s="220" t="inlineStr">
+      <c r="C18" s="226" t="inlineStr">
         <is>
           <t>dcat:packageFormat</t>
         </is>
@@ -7415,32 +7415,32 @@
           <t>IANA Media Types</t>
         </is>
       </c>
-      <c r="E18" s="226" t="inlineStr">
+      <c r="E18" s="230" t="inlineStr">
         <is>
           <t xml:space="preserve">It SHOULD be expressed using a media type as defined in the official register of media types managed by IANA. </t>
         </is>
       </c>
-      <c r="F18" s="227" t="inlineStr">
+      <c r="F18" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="227" t="inlineStr">
+      <c r="G18" s="231" t="inlineStr">
         <is>
           <t>dct:MediaType (IRI)</t>
         </is>
       </c>
-      <c r="H18" s="227" t="inlineStr">
+      <c r="H18" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="218" t="inlineStr">
+      <c r="I18" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="232" t="inlineStr">
+      <c r="J18" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7450,8 +7450,8 @@
           <t>resource:package_format</t>
         </is>
       </c>
-      <c r="L18" s="218" t="n"/>
-      <c r="M18" s="218" t="n"/>
+      <c r="L18" s="225" t="n"/>
+      <c r="M18" s="225" t="n"/>
       <c r="O18" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7463,12 +7463,12 @@
         </is>
       </c>
       <c r="S18" s="121" t="n"/>
-      <c r="U18" s="220" t="n"/>
-      <c r="V18" s="220" t="n"/>
-      <c r="W18" s="220" t="n"/>
+      <c r="U18" s="226" t="n"/>
+      <c r="V18" s="226" t="n"/>
+      <c r="W18" s="226" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="230" t="inlineStr">
+      <c r="A19" s="220" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -7478,7 +7478,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="230" t="inlineStr">
+      <c r="C19" s="220" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -7493,27 +7493,27 @@
           <t>The date the dataset distribution was issued.</t>
         </is>
       </c>
-      <c r="F19" s="225" t="inlineStr">
+      <c r="F19" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="225" t="inlineStr">
+      <c r="G19" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="225" t="inlineStr">
+      <c r="H19" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="232" t="inlineStr">
+      <c r="I19" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="232" t="inlineStr">
+      <c r="J19" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7523,8 +7523,8 @@
           <t>resource:issued</t>
         </is>
       </c>
-      <c r="L19" s="232" t="n"/>
-      <c r="M19" s="232" t="n"/>
+      <c r="L19" s="224" t="n"/>
+      <c r="M19" s="224" t="n"/>
       <c r="N19" s="219" t="n"/>
       <c r="O19" s="219" t="inlineStr">
         <is>
@@ -7542,12 +7542,12 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="U19" s="230" t="n"/>
-      <c r="V19" s="230" t="n"/>
-      <c r="W19" s="230" t="n"/>
+      <c r="U19" s="220" t="n"/>
+      <c r="V19" s="220" t="n"/>
+      <c r="W19" s="220" t="n"/>
     </row>
     <row r="20" ht="231" customHeight="1">
-      <c r="A20" s="220" t="inlineStr">
+      <c r="A20" s="226" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -7557,13 +7557,13 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C20" s="220" t="inlineStr">
+      <c r="C20" s="226" t="inlineStr">
         <is>
           <t>healthdcatap:retentionperiod</t>
         </is>
       </c>
       <c r="D20" s="92" t="n"/>
-      <c r="E20" s="226" t="inlineStr">
+      <c r="E20" s="230" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the upcoming major release. It is recommended to indicate the planned availability of the distribution with the newly added Distribution.availability property. 
 Use this property if the Distribution is only available for secondary use for a specific period of time (e.g. due to data protection, contractual, or project constraints).
@@ -7573,7 +7573,7 @@
 If a limit is known, provide both dcat:startDate and dcat:endDate.</t>
         </is>
       </c>
-      <c r="F20" s="227" t="inlineStr">
+      <c r="F20" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -7583,28 +7583,28 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H20" s="227" t="inlineStr">
+      <c r="H20" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="218" t="inlineStr">
+      <c r="I20" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="232" t="inlineStr">
+      <c r="J20" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K20" s="73" t="n"/>
-      <c r="L20" s="218" t="inlineStr">
+      <c r="L20" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M20" s="218" t="inlineStr">
+      <c r="M20" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -7625,12 +7625,12 @@
         </is>
       </c>
       <c r="S20" s="121" t="n"/>
-      <c r="U20" s="220" t="n"/>
-      <c r="V20" s="220" t="n"/>
-      <c r="W20" s="220" t="n"/>
+      <c r="U20" s="226" t="n"/>
+      <c r="V20" s="226" t="n"/>
+      <c r="W20" s="226" t="n"/>
     </row>
     <row r="21" ht="112" customHeight="1">
-      <c r="A21" s="230" t="inlineStr">
+      <c r="A21" s="220" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -7640,7 +7640,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C21" s="230" t="inlineStr">
+      <c r="C21" s="220" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -7661,7 +7661,7 @@
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="225" t="inlineStr">
+      <c r="G21" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
@@ -7671,12 +7671,12 @@
           <t>0..1</t>
         </is>
       </c>
-      <c r="I21" s="232" t="inlineStr">
+      <c r="I21" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J21" s="232" t="inlineStr">
+      <c r="J21" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7686,8 +7686,8 @@
           <t>resource:rights</t>
         </is>
       </c>
-      <c r="L21" s="232" t="n"/>
-      <c r="M21" s="232" t="n"/>
+      <c r="L21" s="224" t="n"/>
+      <c r="M21" s="224" t="n"/>
       <c r="O21" s="203" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -7699,22 +7699,22 @@
         </is>
       </c>
       <c r="S21" s="121" t="n"/>
-      <c r="U21" s="230" t="n"/>
-      <c r="V21" s="230" t="n"/>
-      <c r="W21" s="230" t="n"/>
+      <c r="U21" s="220" t="n"/>
+      <c r="V21" s="220" t="n"/>
+      <c r="W21" s="220" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="220" t="inlineStr">
+      <c r="A22" s="226" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B22" s="226" t="inlineStr">
+      <c r="B22" s="230" t="inlineStr">
         <is>
           <t>The status of the Asset in the context of a particular workflow process.</t>
         </is>
       </c>
-      <c r="C22" s="220" t="inlineStr">
+      <c r="C22" s="226" t="inlineStr">
         <is>
           <t>adms:status</t>
         </is>
@@ -7730,27 +7730,27 @@
           <t>It MUST take one of the following values from the provided controlled vocabulary: Completed, Deprecated, Under Development or Withdrawn.</t>
         </is>
       </c>
-      <c r="F22" s="227" t="inlineStr">
+      <c r="F22" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G22" s="227" t="inlineStr">
+      <c r="G22" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="227" t="inlineStr">
+      <c r="H22" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I22" s="218" t="inlineStr">
+      <c r="I22" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="232" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7760,8 +7760,8 @@
           <t>resource:status</t>
         </is>
       </c>
-      <c r="L22" s="218" t="n"/>
-      <c r="M22" s="218" t="n"/>
+      <c r="L22" s="225" t="n"/>
+      <c r="M22" s="225" t="n"/>
       <c r="O22" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -7773,12 +7773,12 @@
         </is>
       </c>
       <c r="S22" s="121" t="n"/>
-      <c r="U22" s="220" t="n"/>
-      <c r="V22" s="220" t="n"/>
-      <c r="W22" s="220" t="n"/>
+      <c r="U22" s="226" t="n"/>
+      <c r="V22" s="226" t="n"/>
+      <c r="W22" s="226" t="n"/>
     </row>
     <row r="23" ht="64" customHeight="1">
-      <c r="A23" s="230" t="inlineStr">
+      <c r="A23" s="220" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
@@ -7788,7 +7788,7 @@
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
       </c>
-      <c r="C23" s="230" t="inlineStr">
+      <c r="C23" s="220" t="inlineStr">
         <is>
           <t>dcat:temporalResolution</t>
         </is>
@@ -7803,34 +7803,34 @@
           <t>If applicable, this property indicates the minimum time period resolvable in the dataset distribution, expressed in xsd:duration format (for more information, see: https://www.w3schools.com/xml/schema_dtypes_date.asp).</t>
         </is>
       </c>
-      <c r="F23" s="225" t="inlineStr">
+      <c r="F23" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="225" t="inlineStr">
+      <c r="G23" s="218" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H23" s="225" t="inlineStr">
+      <c r="H23" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I23" s="232" t="inlineStr">
+      <c r="I23" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="232" t="inlineStr">
+      <c r="J23" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="74" t="n"/>
-      <c r="L23" s="232" t="n"/>
-      <c r="M23" s="232" t="n"/>
+      <c r="L23" s="224" t="n"/>
+      <c r="M23" s="224" t="n"/>
       <c r="O23" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7842,22 +7842,22 @@
         </is>
       </c>
       <c r="S23" s="121" t="n"/>
-      <c r="U23" s="230" t="n"/>
-      <c r="V23" s="230" t="n"/>
-      <c r="W23" s="230" t="n"/>
+      <c r="U23" s="220" t="n"/>
+      <c r="V23" s="220" t="n"/>
+      <c r="W23" s="220" t="n"/>
     </row>
     <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="220" t="inlineStr">
+      <c r="A24" s="226" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B24" s="226" t="inlineStr">
+      <c r="B24" s="230" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="220" t="inlineStr">
+      <c r="C24" s="226" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -7872,27 +7872,27 @@
           <t>A title given to the distribution, e.g. Data Access Request for the Healthy Brain Study</t>
         </is>
       </c>
-      <c r="F24" s="227" t="inlineStr">
+      <c r="F24" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="227" t="inlineStr">
+      <c r="G24" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="227" t="inlineStr">
+      <c r="H24" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="218" t="inlineStr">
+      <c r="I24" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J24" s="232" t="inlineStr">
+      <c r="J24" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -7902,8 +7902,8 @@
           <t>resource:name</t>
         </is>
       </c>
-      <c r="L24" s="218" t="n"/>
-      <c r="M24" s="218" t="n"/>
+      <c r="L24" s="225" t="n"/>
+      <c r="M24" s="225" t="n"/>
       <c r="O24" s="203" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -7917,9 +7917,9 @@
       <c r="S24" s="121" t="b">
         <v>1</v>
       </c>
-      <c r="U24" s="220" t="n"/>
-      <c r="V24" s="220" t="n"/>
-      <c r="W24" s="220" t="n"/>
+      <c r="U24" s="226" t="n"/>
+      <c r="V24" s="226" t="n"/>
+      <c r="W24" s="226" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="21" t="n"/>
@@ -8455,7 +8455,7 @@
     <col width="22.5" customWidth="1" style="221" min="1" max="1"/>
     <col width="43.5" bestFit="1" customWidth="1" style="221" min="2" max="2"/>
     <col width="26.5" customWidth="1" style="221" min="3" max="3"/>
-    <col width="24" customWidth="1" style="223" min="4" max="4"/>
+    <col width="24" customWidth="1" style="228" min="4" max="4"/>
     <col width="76.5" customWidth="1" style="221" min="5" max="5"/>
     <col width="16.5" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
     <col width="20.1640625" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
@@ -8466,8 +8466,8 @@
     <col width="24.6640625" customWidth="1" style="219" min="12" max="12"/>
     <col width="9.1640625" customWidth="1" style="219" min="13" max="18"/>
     <col width="22.5" customWidth="1" min="19" max="21"/>
-    <col width="9.1640625" customWidth="1" style="219" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="219" min="25" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="22" max="25"/>
+    <col width="9.1640625" customWidth="1" style="219" min="26" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customFormat="1" customHeight="1" s="163">
@@ -8583,32 +8583,32 @@
           <t>applicable legislation</t>
         </is>
       </c>
-      <c r="B2" s="226" t="inlineStr">
+      <c r="B2" s="230" t="inlineStr">
         <is>
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C2" s="226" t="inlineStr">
+      <c r="C2" s="230" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
       </c>
-      <c r="D2" s="226" t="inlineStr">
+      <c r="D2" s="230" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E2" s="226" t="inlineStr">
+      <c r="E2" s="230" t="inlineStr">
         <is>
           <t>The legislation that mandates the creation or management of the Dataset Series.</t>
         </is>
       </c>
-      <c r="F2" s="225" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="227" t="inlineStr">
+      <c r="G2" s="231" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -8623,7 +8623,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="232" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8633,7 +8633,7 @@
           <t>data_series:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="218" t="n"/>
+      <c r="L2" s="225" t="n"/>
       <c r="N2" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -8649,7 +8649,7 @@
       <c r="U2" s="155" t="n"/>
     </row>
     <row r="3" ht="64" customHeight="1">
-      <c r="A3" s="230" t="inlineStr">
+      <c r="A3" s="220" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -8659,7 +8659,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C3" s="230" t="inlineStr">
+      <c r="C3" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -8675,7 +8675,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F3" s="225" t="inlineStr">
+      <c r="F3" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -8685,17 +8685,17 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H3" s="225" t="inlineStr">
+      <c r="H3" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="232" t="inlineStr">
+      <c r="I3" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J3" s="232" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8705,7 +8705,7 @@
           <t>data_series::contact</t>
         </is>
       </c>
-      <c r="L3" s="232" t="inlineStr">
+      <c r="L3" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -8725,22 +8725,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S3" s="230" t="n"/>
-      <c r="T3" s="230" t="n"/>
-      <c r="U3" s="230" t="n"/>
+      <c r="S3" s="220" t="n"/>
+      <c r="T3" s="220" t="n"/>
+      <c r="U3" s="220" t="n"/>
     </row>
     <row r="4" ht="16" customHeight="1">
-      <c r="A4" s="220" t="inlineStr">
+      <c r="A4" s="226" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B4" s="226" t="inlineStr">
+      <c r="B4" s="230" t="inlineStr">
         <is>
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C4" s="220" t="inlineStr">
+      <c r="C4" s="226" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -8755,27 +8755,27 @@
           <t xml:space="preserve">Briefly describe the dataset series in the catalogue. You can repeat this in multiple languages. </t>
         </is>
       </c>
-      <c r="F4" s="227" t="inlineStr">
+      <c r="F4" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G4" s="227" t="inlineStr">
+      <c r="G4" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H4" s="227" t="inlineStr">
+      <c r="H4" s="231" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I4" s="218" t="inlineStr">
+      <c r="I4" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J4" s="232" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -8785,7 +8785,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L4" s="218" t="n"/>
+      <c r="L4" s="225" t="n"/>
       <c r="N4" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -8799,12 +8799,12 @@
       <c r="R4" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="S4" s="220" t="n"/>
-      <c r="T4" s="220" t="n"/>
-      <c r="U4" s="220" t="n"/>
+      <c r="S4" s="226" t="n"/>
+      <c r="T4" s="226" t="n"/>
+      <c r="U4" s="226" t="n"/>
     </row>
     <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="230" t="inlineStr">
+      <c r="A5" s="220" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -8814,7 +8814,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C5" s="230" t="inlineStr">
+      <c r="C5" s="220" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -8829,33 +8829,33 @@
           <t>The frequency of a dataset series is not equal to the frequency of the dataset in the collection.</t>
         </is>
       </c>
-      <c r="F5" s="225" t="inlineStr">
+      <c r="F5" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="225" t="inlineStr">
+      <c r="G5" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="225" t="inlineStr">
+      <c r="H5" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I5" s="232" t="inlineStr">
+      <c r="I5" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="232" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K5" s="74" t="n"/>
-      <c r="L5" s="232" t="n"/>
+      <c r="L5" s="224" t="n"/>
       <c r="N5" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -8866,22 +8866,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S5" s="230" t="n"/>
-      <c r="T5" s="230" t="n"/>
-      <c r="U5" s="230" t="n"/>
+      <c r="S5" s="220" t="n"/>
+      <c r="T5" s="220" t="n"/>
+      <c r="U5" s="220" t="n"/>
     </row>
     <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="220" t="inlineStr">
+      <c r="A6" s="226" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B6" s="226" t="inlineStr">
+      <c r="B6" s="230" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C6" s="220" t="inlineStr">
+      <c r="C6" s="226" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -8891,32 +8891,32 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E6" s="222" t="inlineStr">
+      <c r="E6" s="227" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F6" s="227" t="inlineStr">
+      <c r="F6" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G6" s="227" t="inlineStr">
+      <c r="G6" s="231" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H6" s="227" t="inlineStr">
+      <c r="H6" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="218" t="inlineStr">
+      <c r="I6" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="232" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -8926,7 +8926,7 @@
           <t>data_series::coverage</t>
         </is>
       </c>
-      <c r="L6" s="218" t="n"/>
+      <c r="L6" s="225" t="n"/>
       <c r="N6" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -8937,9 +8937,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S6" s="220" t="n"/>
-      <c r="T6" s="220" t="n"/>
-      <c r="U6" s="220" t="n"/>
+      <c r="S6" s="226" t="n"/>
+      <c r="T6" s="226" t="n"/>
+      <c r="U6" s="226" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="D7" s="179" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="230" t="inlineStr">
+      <c r="A11" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -8980,7 +8980,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C11" s="230" t="inlineStr">
+      <c r="C11" s="220" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -8995,27 +8995,27 @@
           <t>This is not equal to the most recently modified dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F11" s="225" t="inlineStr">
+      <c r="F11" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="225" t="inlineStr">
+      <c r="G11" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H11" s="225" t="inlineStr">
+      <c r="H11" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I11" s="232" t="inlineStr">
+      <c r="I11" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J11" s="232" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9025,7 +9025,7 @@
           <t>data_series::modified</t>
         </is>
       </c>
-      <c r="L11" s="232" t="n"/>
+      <c r="L11" s="224" t="n"/>
       <c r="N11" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9041,12 +9041,12 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S11" s="230" t="n"/>
-      <c r="T11" s="230" t="n"/>
-      <c r="U11" s="230" t="n"/>
+      <c r="S11" s="220" t="n"/>
+      <c r="T11" s="220" t="n"/>
+      <c r="U11" s="220" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="220" t="inlineStr">
+      <c r="A12" s="226" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -9056,7 +9056,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C12" s="220" t="inlineStr">
+      <c r="C12" s="226" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -9071,7 +9071,7 @@
           <t xml:space="preserve">The publisher of the dataset series may not be the publisher of all datasets. For example, a digital archive could take over the publishing of older datasets in the series. </t>
         </is>
       </c>
-      <c r="F12" s="225" t="inlineStr">
+      <c r="F12" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -9081,17 +9081,17 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H12" s="227" t="inlineStr">
+      <c r="H12" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I12" s="227" t="inlineStr">
+      <c r="I12" s="231" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J12" s="232" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9101,7 +9101,7 @@
           <t>data_series::publisher</t>
         </is>
       </c>
-      <c r="L12" s="218" t="inlineStr">
+      <c r="L12" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -9121,12 +9121,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S12" s="220" t="n"/>
-      <c r="T12" s="220" t="n"/>
-      <c r="U12" s="220" t="n"/>
+      <c r="S12" s="226" t="n"/>
+      <c r="T12" s="226" t="n"/>
+      <c r="U12" s="226" t="n"/>
     </row>
     <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="230" t="inlineStr">
+      <c r="A13" s="220" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
@@ -9136,7 +9136,7 @@
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C13" s="230" t="inlineStr">
+      <c r="C13" s="220" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -9151,27 +9151,27 @@
           <t>The moment when the dataset series was established as a managed resource. This is not equal to the release date of the oldest dataset in the collection of the dataset series.</t>
         </is>
       </c>
-      <c r="F13" s="227" t="inlineStr">
+      <c r="F13" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G13" s="225" t="inlineStr">
+      <c r="G13" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H13" s="225" t="inlineStr">
+      <c r="H13" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I13" s="225" t="inlineStr">
+      <c r="I13" s="218" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J13" s="232" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9181,7 +9181,7 @@
           <t>data_series:issued</t>
         </is>
       </c>
-      <c r="L13" s="232" t="n"/>
+      <c r="L13" s="224" t="n"/>
       <c r="N13" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9197,22 +9197,22 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S13" s="230" t="n"/>
-      <c r="T13" s="230" t="n"/>
-      <c r="U13" s="230" t="n"/>
+      <c r="S13" s="220" t="n"/>
+      <c r="T13" s="220" t="n"/>
+      <c r="U13" s="220" t="n"/>
     </row>
     <row r="14" ht="49" customHeight="1">
-      <c r="A14" s="220" t="inlineStr">
+      <c r="A14" s="226" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
       </c>
-      <c r="B14" s="220" t="inlineStr">
+      <c r="B14" s="226" t="inlineStr">
         <is>
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C14" s="220" t="inlineStr">
+      <c r="C14" s="226" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -9227,7 +9227,7 @@
           <t>When temporal coverage is a dimension in the dataset series, the temporal coverage of each dataset in the collection should be part of the series' temporal coverage. In that case, an open-ended value is recommended, e.g. after 2012.</t>
         </is>
       </c>
-      <c r="F14" s="225" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -9247,7 +9247,7 @@
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="232" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9257,7 +9257,7 @@
           <t>data_series::temporal</t>
         </is>
       </c>
-      <c r="L14" s="218" t="inlineStr">
+      <c r="L14" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -9277,22 +9277,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S14" s="220" t="n"/>
-      <c r="T14" s="220" t="n"/>
-      <c r="U14" s="220" t="n"/>
+      <c r="S14" s="226" t="n"/>
+      <c r="T14" s="226" t="n"/>
+      <c r="U14" s="226" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="230" t="inlineStr">
+      <c r="A15" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B15" s="230" t="inlineStr">
+      <c r="B15" s="220" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C15" s="230" t="inlineStr">
+      <c r="C15" s="220" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -9302,32 +9302,32 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="230" t="inlineStr">
+      <c r="E15" s="220" t="inlineStr">
         <is>
           <t xml:space="preserve">Provide a unique title for your Dataset Series, which can be repeated in multiple languages. </t>
         </is>
       </c>
-      <c r="F15" s="227" t="inlineStr">
+      <c r="F15" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G15" s="225" t="inlineStr">
+      <c r="G15" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H15" s="225" t="inlineStr">
+      <c r="H15" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I15" s="225" t="inlineStr">
+      <c r="I15" s="218" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J15" s="232" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -9337,7 +9337,7 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L15" s="232" t="n"/>
+      <c r="L15" s="224" t="n"/>
       <c r="N15" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -9351,9 +9351,9 @@
       <c r="R15" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="S15" s="230" t="n"/>
-      <c r="T15" s="230" t="n"/>
-      <c r="U15" s="230" t="n"/>
+      <c r="S15" s="220" t="n"/>
+      <c r="T15" s="220" t="n"/>
+      <c r="U15" s="220" t="n"/>
     </row>
     <row r="16">
       <c r="K16" s="219" t="n"/>
@@ -9479,16 +9479,16 @@
   <autoFilter ref="A1:L15"/>
   <mergeCells count="11">
     <mergeCell ref="J6:J10"/>
-    <mergeCell ref="C6:C10"/>
+    <mergeCell ref="A6:A10"/>
     <mergeCell ref="I6:I10"/>
     <mergeCell ref="B6:B10"/>
     <mergeCell ref="E6:E10"/>
-    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="C6:C10"/>
     <mergeCell ref="H6:H10"/>
     <mergeCell ref="G6:G10"/>
+    <mergeCell ref="F6:F10"/>
+    <mergeCell ref="K6:K10"/>
     <mergeCell ref="L6:L10"/>
-    <mergeCell ref="K6:K10"/>
-    <mergeCell ref="A6:A10"/>
   </mergeCells>
   <conditionalFormatting sqref="F2:F6 F11:F15">
     <cfRule type="cellIs" priority="11" operator="equal" dxfId="10">
@@ -9732,7 +9732,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="230" t="inlineStr">
+      <c r="C2" s="220" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -9747,30 +9747,30 @@
           <t>Information that indicates whether the Dataset is publicly accessible, has access restrictions or is not public. This property must take one of the predefined values listed in the Access Rights Named Authority List provided by the Publications Office. This designation informs data users whether the dataset is considered open data or is classified as non-public. For example, for non-public data, use the value: http://publications.europa.eu/resource/authority/access-right/NON_PUBLIC</t>
         </is>
       </c>
-      <c r="F2" s="225" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="225" t="inlineStr">
+      <c r="G2" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="225" t="n">
+      <c r="H2" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="232" t="inlineStr">
+      <c r="I2" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="232" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K2" s="232" t="inlineStr">
+      <c r="K2" s="224" t="inlineStr">
         <is>
           <t>access_service:access_rights</t>
         </is>
@@ -9791,17 +9791,17 @@
       <c r="U2" s="97" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="220" t="inlineStr">
+      <c r="A3" s="226" t="inlineStr">
         <is>
           <t>applicable legislation</t>
         </is>
       </c>
-      <c r="B3" s="226" t="inlineStr">
+      <c r="B3" s="230" t="inlineStr">
         <is>
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C3" s="220" t="inlineStr">
+      <c r="C3" s="226" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -9811,34 +9811,34 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="226" t="n"/>
-      <c r="F3" s="227" t="inlineStr">
+      <c r="E3" s="230" t="n"/>
+      <c r="F3" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G3" s="227" t="inlineStr">
+      <c r="G3" s="231" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
       </c>
-      <c r="H3" s="227" t="inlineStr">
+      <c r="H3" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="218" t="inlineStr">
+      <c r="I3" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="232" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K3" s="75" t="n"/>
-      <c r="L3" s="218" t="n"/>
+      <c r="L3" s="225" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9849,12 +9849,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S3" s="220" t="n"/>
-      <c r="T3" s="220" t="n"/>
-      <c r="U3" s="220" t="n"/>
+      <c r="S3" s="226" t="n"/>
+      <c r="T3" s="226" t="n"/>
+      <c r="U3" s="226" t="n"/>
     </row>
     <row r="4" ht="92.25" customHeight="1">
-      <c r="A4" s="230" t="inlineStr">
+      <c r="A4" s="220" t="inlineStr">
         <is>
           <t>application profile</t>
         </is>
@@ -9864,7 +9864,7 @@
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C4" s="230" t="inlineStr">
+      <c r="C4" s="220" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -9879,33 +9879,33 @@
           <t>The standards referred to here SHOULD describe the Data Service and not the data it serves. The latter is provided by the dataset with which this Data Service is connected. For instance, the data service adheres to the OGC WFS API standard, while the associated dataset adheres to the INSPIRE Address data model.</t>
         </is>
       </c>
-      <c r="F4" s="225" t="inlineStr">
+      <c r="F4" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G4" s="225" t="inlineStr">
+      <c r="G4" s="218" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H4" s="225" t="inlineStr">
+      <c r="H4" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="232" t="inlineStr">
+      <c r="I4" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="232" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K4" s="232" t="n"/>
-      <c r="L4" s="232" t="n"/>
+      <c r="K4" s="224" t="n"/>
+      <c r="L4" s="224" t="n"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -9916,9 +9916,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S4" s="230" t="n"/>
-      <c r="T4" s="230" t="n"/>
-      <c r="U4" s="230" t="n"/>
+      <c r="S4" s="220" t="n"/>
+      <c r="T4" s="220" t="n"/>
+      <c r="U4" s="220" t="n"/>
     </row>
     <row r="5" ht="64" customHeight="1">
       <c r="A5" s="155" t="inlineStr">
@@ -9926,12 +9926,12 @@
           <t>contact point</t>
         </is>
       </c>
-      <c r="B5" s="226" t="inlineStr">
+      <c r="B5" s="230" t="inlineStr">
         <is>
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C5" s="220" t="inlineStr">
+      <c r="C5" s="226" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -9947,7 +9947,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F5" s="227" t="inlineStr">
+      <c r="F5" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -9957,21 +9957,21 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H5" s="227" t="n">
+      <c r="H5" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="218" t="inlineStr">
+      <c r="I5" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="232" t="inlineStr">
+      <c r="J5" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K5" s="75" t="n"/>
-      <c r="L5" s="218" t="inlineStr">
+      <c r="L5" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -9996,7 +9996,7 @@
       <c r="U5" s="155" t="n"/>
     </row>
     <row r="6" ht="160" customHeight="1">
-      <c r="A6" s="230" t="inlineStr">
+      <c r="A6" s="220" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
@@ -10006,7 +10006,7 @@
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C6" s="230" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -10023,7 +10023,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="225" t="inlineStr">
+      <c r="F6" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -10033,23 +10033,23 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H6" s="225" t="inlineStr">
+      <c r="H6" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I6" s="232" t="inlineStr">
+      <c r="I6" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="232" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K6" s="75" t="n"/>
-      <c r="L6" s="232" t="inlineStr">
+      <c r="L6" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -10069,22 +10069,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S6" s="230" t="n"/>
-      <c r="T6" s="230" t="n"/>
-      <c r="U6" s="230" t="n"/>
+      <c r="S6" s="220" t="n"/>
+      <c r="T6" s="220" t="n"/>
+      <c r="U6" s="220" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="220" t="inlineStr">
+      <c r="A7" s="226" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
       </c>
-      <c r="B7" s="226" t="inlineStr">
+      <c r="B7" s="230" t="inlineStr">
         <is>
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C7" s="220" t="inlineStr">
+      <c r="C7" s="226" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -10095,33 +10095,33 @@
         </is>
       </c>
       <c r="E7" s="92" t="n"/>
-      <c r="F7" s="227" t="inlineStr">
+      <c r="F7" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G7" s="227" t="inlineStr">
+      <c r="G7" s="231" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H7" s="227" t="inlineStr">
+      <c r="H7" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I7" s="218" t="inlineStr">
+      <c r="I7" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="232" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K7" s="232" t="n"/>
-      <c r="L7" s="218" t="n"/>
+      <c r="K7" s="224" t="n"/>
+      <c r="L7" s="225" t="n"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10132,9 +10132,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S7" s="220" t="n"/>
-      <c r="T7" s="220" t="n"/>
-      <c r="U7" s="220" t="n"/>
+      <c r="S7" s="226" t="n"/>
+      <c r="T7" s="226" t="n"/>
+      <c r="U7" s="226" t="n"/>
     </row>
     <row r="8" ht="42" customHeight="1">
       <c r="A8" s="97" t="inlineStr">
@@ -10147,7 +10147,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="230" t="inlineStr">
+      <c r="C8" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -10162,43 +10162,43 @@
           <t>Briefly describe the data service provided. You can repeat this description in multiple languages. Example: A data service that provides API access to real-time electrocardiogram (ECG) monitoring data for clinical research applications.</t>
         </is>
       </c>
-      <c r="F8" s="225" t="inlineStr">
+      <c r="F8" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G8" s="225" t="inlineStr">
+      <c r="G8" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H8" s="225" t="inlineStr">
+      <c r="H8" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I8" s="232" t="inlineStr">
+      <c r="I8" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="232" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K8" s="232" t="inlineStr">
+      <c r="K8" s="224" t="inlineStr">
         <is>
           <t>access_service:description</t>
         </is>
       </c>
-      <c r="L8" s="232" t="n"/>
-      <c r="N8" s="232" t="inlineStr">
+      <c r="L8" s="224" t="n"/>
+      <c r="N8" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O8" s="232" t="inlineStr">
+      <c r="O8" s="224" t="inlineStr">
         <is>
           <t>dash:TextAreaEditor</t>
         </is>
@@ -10211,17 +10211,17 @@
       <c r="U8" s="97" t="n"/>
     </row>
     <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="220" t="inlineStr">
+      <c r="A9" s="226" t="inlineStr">
         <is>
           <t>endpoint description</t>
         </is>
       </c>
-      <c r="B9" s="226" t="inlineStr">
+      <c r="B9" s="230" t="inlineStr">
         <is>
           <t>A description of the services available via the endpoints, including their operations, parameters, etc.</t>
         </is>
       </c>
-      <c r="C9" s="220" t="inlineStr">
+      <c r="C9" s="226" t="inlineStr">
         <is>
           <t>dcat:endpointDescription</t>
         </is>
@@ -10236,25 +10236,25 @@
           <t>Provides technical documentation that explains how to access and interact with the data service’s endpoint.</t>
         </is>
       </c>
-      <c r="F9" s="227" t="inlineStr">
+      <c r="F9" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G9" s="227" t="inlineStr">
+      <c r="G9" s="231" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H9" s="227" t="n">
+      <c r="H9" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="218" t="inlineStr">
+      <c r="I9" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J9" s="232" t="inlineStr">
+      <c r="J9" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10264,7 +10264,7 @@
           <t>access_service:endpoint_description</t>
         </is>
       </c>
-      <c r="L9" s="218" t="n"/>
+      <c r="L9" s="225" t="n"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10275,12 +10275,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S9" s="220" t="n"/>
-      <c r="T9" s="220" t="n"/>
-      <c r="U9" s="220" t="n"/>
+      <c r="S9" s="226" t="n"/>
+      <c r="T9" s="226" t="n"/>
+      <c r="U9" s="226" t="n"/>
     </row>
     <row r="10" ht="48" customHeight="1">
-      <c r="A10" s="230" t="inlineStr">
+      <c r="A10" s="220" t="inlineStr">
         <is>
           <t>endpoint URL</t>
         </is>
@@ -10290,7 +10290,7 @@
           <t>The root location or primary endpoint of the service (a Web-resolvable IRI).</t>
         </is>
       </c>
-      <c r="C10" s="230" t="inlineStr">
+      <c r="C10" s="220" t="inlineStr">
         <is>
           <t>dcat:endpointURL</t>
         </is>
@@ -10305,12 +10305,12 @@
           <t>Provide the URL of the endpoint that users can interact with to access the data service. This should be a direct link to the service's endpoint, such as an API URL, SPARQL endpoint, or similar.</t>
         </is>
       </c>
-      <c r="F10" s="225" t="inlineStr">
+      <c r="F10" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G10" s="225" t="inlineStr">
+      <c r="G10" s="218" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
@@ -10318,12 +10318,12 @@
       <c r="H10" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="232" t="inlineStr">
+      <c r="I10" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="232" t="inlineStr">
+      <c r="J10" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -10333,7 +10333,7 @@
           <t>access_service:endpoint_url</t>
         </is>
       </c>
-      <c r="L10" s="232" t="n"/>
+      <c r="L10" s="224" t="n"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10344,17 +10344,17 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S10" s="230" t="n"/>
-      <c r="T10" s="230" t="n"/>
-      <c r="U10" s="230" t="n"/>
+      <c r="S10" s="220" t="n"/>
+      <c r="T10" s="220" t="n"/>
+      <c r="U10" s="220" t="n"/>
     </row>
     <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="220" t="inlineStr">
+      <c r="A11" s="226" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="B11" s="226" t="inlineStr">
+      <c r="B11" s="230" t="inlineStr">
         <is>
           <t>The file format, physical medium, or dimensions of the resource.</t>
         </is>
@@ -10370,33 +10370,33 @@
         </is>
       </c>
       <c r="E11" s="92" t="n"/>
-      <c r="F11" s="227" t="inlineStr">
+      <c r="F11" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G11" s="227" t="inlineStr">
+      <c r="G11" s="231" t="inlineStr">
         <is>
           <t>dct:MediaTypeOrExtent (IRI)</t>
         </is>
       </c>
-      <c r="H11" s="227" t="inlineStr">
+      <c r="H11" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I11" s="218" t="inlineStr">
+      <c r="I11" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J11" s="232" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K11" s="232" t="n"/>
-      <c r="L11" s="218" t="n"/>
+      <c r="K11" s="224" t="n"/>
+      <c r="L11" s="225" t="n"/>
       <c r="N11" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -10407,12 +10407,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S11" s="220" t="n"/>
-      <c r="T11" s="220" t="n"/>
-      <c r="U11" s="220" t="n"/>
+      <c r="S11" s="226" t="n"/>
+      <c r="T11" s="226" t="n"/>
+      <c r="U11" s="226" t="n"/>
     </row>
     <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="230" t="inlineStr">
+      <c r="A12" s="220" t="inlineStr">
         <is>
           <t>HVD Category</t>
         </is>
@@ -10422,7 +10422,7 @@
           <t>A data category defined in the High Value Dataset Implementing Regulation.</t>
         </is>
       </c>
-      <c r="C12" s="230" t="inlineStr">
+      <c r="C12" s="220" t="inlineStr">
         <is>
           <t>dcatap:hvdCategory</t>
         </is>
@@ -10433,33 +10433,33 @@
         </is>
       </c>
       <c r="E12" s="98" t="n"/>
-      <c r="F12" s="225" t="inlineStr">
+      <c r="F12" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G12" s="225" t="inlineStr">
+      <c r="G12" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H12" s="225" t="inlineStr">
+      <c r="H12" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I12" s="232" t="inlineStr">
+      <c r="I12" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J12" s="232" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K12" s="75" t="n"/>
-      <c r="L12" s="232" t="n"/>
+      <c r="L12" s="224" t="n"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10470,9 +10470,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S12" s="230" t="n"/>
-      <c r="T12" s="230" t="n"/>
-      <c r="U12" s="230" t="n"/>
+      <c r="S12" s="220" t="n"/>
+      <c r="T12" s="220" t="n"/>
+      <c r="U12" s="220" t="n"/>
     </row>
     <row r="13" ht="64" customHeight="1">
       <c r="A13" s="155" t="inlineStr">
@@ -10480,7 +10480,7 @@
           <t>identifier</t>
         </is>
       </c>
-      <c r="B13" s="226" t="inlineStr">
+      <c r="B13" s="230" t="inlineStr">
         <is>
           <t>An unambiguous reference to the resource within a given context.</t>
         </is>
@@ -10500,37 +10500,37 @@
           <t>Provide a unique identifier for the data service. This could be a globally unique and persistent identifier, such as a DOI, URN, or UUID. If no persistent identifier is available, you may use the accessURL or endpointURL as the identifier, provided it is stable and unique to the service.</t>
         </is>
       </c>
-      <c r="F13" s="227" t="inlineStr">
+      <c r="F13" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G13" s="227" t="inlineStr">
+      <c r="G13" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H13" s="227" t="n">
+      <c r="H13" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="218" t="inlineStr">
+      <c r="I13" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="232" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K13" s="75" t="n"/>
-      <c r="L13" s="218" t="n"/>
-      <c r="N13" s="232" t="inlineStr">
+      <c r="L13" s="225" t="n"/>
+      <c r="N13" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O13" s="232" t="inlineStr">
+      <c r="O13" s="224" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -10540,7 +10540,7 @@
       <c r="U13" s="155" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="230" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -10550,7 +10550,7 @@
           <t>A keyword or tag describing the resource.</t>
         </is>
       </c>
-      <c r="C14" s="230" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>dcat:keyword</t>
         </is>
@@ -10561,59 +10561,59 @@
         </is>
       </c>
       <c r="E14" s="29" t="n"/>
-      <c r="F14" s="225" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="225" t="inlineStr">
+      <c r="G14" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H14" s="225" t="inlineStr">
+      <c r="H14" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="232" t="inlineStr">
+      <c r="I14" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="232" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="75" t="n"/>
-      <c r="L14" s="232" t="n"/>
-      <c r="N14" s="232" t="inlineStr">
+      <c r="L14" s="224" t="n"/>
+      <c r="N14" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O14" s="232" t="inlineStr">
+      <c r="O14" s="224" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="S14" s="230" t="n"/>
-      <c r="T14" s="230" t="n"/>
-      <c r="U14" s="230" t="n"/>
+      <c r="S14" s="220" t="n"/>
+      <c r="T14" s="220" t="n"/>
+      <c r="U14" s="220" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="220" t="inlineStr">
+      <c r="A15" s="226" t="inlineStr">
         <is>
           <t>landing page</t>
         </is>
       </c>
-      <c r="B15" s="226" t="inlineStr">
+      <c r="B15" s="230" t="inlineStr">
         <is>
           <t>A Web page that can be navigated to in a Web browser to gain access to the catalogue, a dataset, its distributions and/or additional information.</t>
         </is>
       </c>
-      <c r="C15" s="220" t="inlineStr">
+      <c r="C15" s="226" t="inlineStr">
         <is>
           <t>dcat:landingPage</t>
         </is>
@@ -10628,33 +10628,33 @@
           <t>It is intended to point to a landing page at the original data service provider, not to a page on a third-party site, such as an aggregator.</t>
         </is>
       </c>
-      <c r="F15" s="227" t="inlineStr">
+      <c r="F15" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="227" t="inlineStr">
+      <c r="G15" s="231" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="227" t="inlineStr">
+      <c r="H15" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="218" t="inlineStr">
+      <c r="I15" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="232" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K15" s="75" t="n"/>
-      <c r="L15" s="218" t="n"/>
+      <c r="L15" s="225" t="n"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10665,12 +10665,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S15" s="220" t="n"/>
-      <c r="T15" s="220" t="n"/>
-      <c r="U15" s="220" t="n"/>
+      <c r="S15" s="226" t="n"/>
+      <c r="T15" s="226" t="n"/>
+      <c r="U15" s="226" t="n"/>
     </row>
     <row r="16" ht="48" customHeight="1">
-      <c r="A16" s="230" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -10680,7 +10680,7 @@
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C16" s="230" t="inlineStr">
+      <c r="C16" s="220" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -10695,33 +10695,33 @@
           <t>Indicates the natural language used in the data service, indicated with a value from the EU controlled vocabulary.</t>
         </is>
       </c>
-      <c r="F16" s="225" t="inlineStr">
+      <c r="F16" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="225" t="inlineStr">
+      <c r="G16" s="218" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="225" t="inlineStr">
+      <c r="H16" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I16" s="232" t="inlineStr">
+      <c r="I16" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="232" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K16" s="75" t="n"/>
-      <c r="L16" s="232" t="n"/>
+      <c r="L16" s="224" t="n"/>
       <c r="N16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -10732,22 +10732,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S16" s="230" t="n"/>
-      <c r="T16" s="230" t="n"/>
-      <c r="U16" s="230" t="n"/>
+      <c r="S16" s="220" t="n"/>
+      <c r="T16" s="220" t="n"/>
+      <c r="U16" s="220" t="n"/>
     </row>
     <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="220" t="inlineStr">
+      <c r="A17" s="226" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
       </c>
-      <c r="B17" s="226" t="inlineStr">
+      <c r="B17" s="230" t="inlineStr">
         <is>
           <t>A legal document giving official permission to do something with the resource.</t>
         </is>
       </c>
-      <c r="C17" s="220" t="inlineStr">
+      <c r="C17" s="226" t="inlineStr">
         <is>
           <t>dct:license</t>
         </is>
@@ -10757,40 +10757,40 @@
           <t>https://definities.geostandaarden.nl/dcat-ap-nl/nl/</t>
         </is>
       </c>
-      <c r="E17" s="222" t="inlineStr">
+      <c r="E17" s="227" t="inlineStr">
         <is>
           <t>For public data, use a Creative Commons (CC) licence (see Geonovum options in the Controlled Vocabulary column). For most National Health Data Catalogue data services, where data is not public, use the 'not open' licence from Geonovum and specify data reuse agreements in the dct:rights property.</t>
         </is>
       </c>
-      <c r="F17" s="227" t="inlineStr">
+      <c r="F17" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G17" s="227" t="inlineStr">
+      <c r="G17" s="231" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H17" s="227" t="n">
+      <c r="H17" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="218" t="inlineStr">
+      <c r="I17" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="232" t="inlineStr">
+      <c r="J17" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K17" s="232" t="inlineStr">
+      <c r="K17" s="224" t="inlineStr">
         <is>
           <t>access_service:license</t>
         </is>
       </c>
-      <c r="L17" s="218" t="n"/>
+      <c r="L17" s="225" t="n"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -10801,12 +10801,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="S17" s="220" t="n"/>
-      <c r="T17" s="220" t="n"/>
-      <c r="U17" s="220" t="n"/>
+      <c r="S17" s="226" t="n"/>
+      <c r="T17" s="226" t="n"/>
+      <c r="U17" s="226" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="230" t="inlineStr">
+      <c r="A18" s="220" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
@@ -10816,7 +10816,7 @@
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C18" s="230" t="inlineStr">
+      <c r="C18" s="220" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -10831,33 +10831,33 @@
           <t>This property indicates the date of the last changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F18" s="225" t="inlineStr">
+      <c r="F18" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G18" s="225" t="inlineStr">
+      <c r="G18" s="218" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H18" s="225" t="inlineStr">
+      <c r="H18" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I18" s="232" t="inlineStr">
+      <c r="I18" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J18" s="232" t="inlineStr">
+      <c r="J18" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K18" s="75" t="n"/>
-      <c r="L18" s="232" t="n"/>
+      <c r="L18" s="224" t="n"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -10873,17 +10873,17 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="S18" s="230" t="n"/>
-      <c r="T18" s="230" t="n"/>
-      <c r="U18" s="230" t="n"/>
+      <c r="S18" s="220" t="n"/>
+      <c r="T18" s="220" t="n"/>
+      <c r="U18" s="220" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="220" t="inlineStr">
+      <c r="A19" s="226" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
       </c>
-      <c r="B19" s="226" t="inlineStr">
+      <c r="B19" s="230" t="inlineStr">
         <is>
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
@@ -10899,7 +10899,7 @@
         </is>
       </c>
       <c r="E19" s="92" t="n"/>
-      <c r="F19" s="227" t="inlineStr">
+      <c r="F19" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -10909,23 +10909,23 @@
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H19" s="227" t="inlineStr">
+      <c r="H19" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I19" s="218" t="inlineStr">
+      <c r="I19" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="232" t="inlineStr">
+      <c r="J19" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K19" s="75" t="n"/>
-      <c r="L19" s="218" t="inlineStr">
+      <c r="L19" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'adms_Identifier' tab.</t>
         </is>
@@ -10945,12 +10945,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S19" s="220" t="n"/>
-      <c r="T19" s="220" t="n"/>
-      <c r="U19" s="220" t="n"/>
+      <c r="S19" s="226" t="n"/>
+      <c r="T19" s="226" t="n"/>
+      <c r="U19" s="226" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="230" t="inlineStr">
+      <c r="A20" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -10960,7 +10960,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C20" s="230" t="inlineStr">
+      <c r="C20" s="220" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -10975,7 +10975,7 @@
           <t>The organisation or individual responsible for making the data service available. In the context of data services, the publisher is typically the organisation that manages or provides access to the service. For details, see the class Agent.</t>
         </is>
       </c>
-      <c r="F20" s="225" t="inlineStr">
+      <c r="F20" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -10985,21 +10985,21 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H20" s="225" t="n">
+      <c r="H20" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="232" t="inlineStr">
+      <c r="I20" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="232" t="inlineStr">
+      <c r="J20" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K20" s="232" t="n"/>
-      <c r="L20" s="232" t="inlineStr">
+      <c r="K20" s="224" t="n"/>
+      <c r="L20" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -11019,22 +11019,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S20" s="230" t="n"/>
-      <c r="T20" s="230" t="n"/>
-      <c r="U20" s="230" t="n"/>
+      <c r="S20" s="220" t="n"/>
+      <c r="T20" s="220" t="n"/>
+      <c r="U20" s="220" t="n"/>
     </row>
     <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="220" t="inlineStr">
+      <c r="A21" s="226" t="inlineStr">
         <is>
           <t>serves dataset</t>
         </is>
       </c>
-      <c r="B21" s="226" t="inlineStr">
+      <c r="B21" s="230" t="inlineStr">
         <is>
           <t>A collection of data that this data service can distribute.</t>
         </is>
       </c>
-      <c r="C21" s="220" t="inlineStr">
+      <c r="C21" s="226" t="inlineStr">
         <is>
           <t>dcat:servesDataset</t>
         </is>
@@ -11049,7 +11049,7 @@
           <t>This property connects the Data Service class to its corresponding dataset(s), ensuring every data service links to at least one dcat:Dataset. While essential for metadata implementation teams on each node, it’s less relevant for researchers to collect.</t>
         </is>
       </c>
-      <c r="F21" s="227" t="inlineStr">
+      <c r="F21" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -11059,22 +11059,22 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H21" s="227" t="inlineStr">
+      <c r="H21" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I21" s="218" t="inlineStr">
+      <c r="I21" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="232" t="inlineStr">
+      <c r="J21" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="232" t="inlineStr">
+      <c r="K21" s="224" t="inlineStr">
         <is>
           <t>access_service:serves_dataset</t>
         </is>
@@ -11099,12 +11099,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S21" s="220" t="n"/>
-      <c r="T21" s="220" t="n"/>
-      <c r="U21" s="220" t="n"/>
+      <c r="S21" s="226" t="n"/>
+      <c r="T21" s="226" t="n"/>
+      <c r="U21" s="226" t="n"/>
     </row>
     <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="230" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -11114,7 +11114,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C22" s="230" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -11129,33 +11129,33 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, most data services will use NAL:data-theme 'HEAL', but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F22" s="225" t="inlineStr">
+      <c r="F22" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G22" s="225" t="inlineStr">
+      <c r="G22" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H22" s="225" t="inlineStr">
+      <c r="H22" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I22" s="232" t="inlineStr">
+      <c r="I22" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="232" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
       <c r="K22" s="75" t="n"/>
-      <c r="L22" s="232" t="n"/>
+      <c r="L22" s="224" t="n"/>
       <c r="N22" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -11171,17 +11171,17 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="S22" s="230" t="n"/>
-      <c r="T22" s="230" t="n"/>
-      <c r="U22" s="230" t="n"/>
+      <c r="S22" s="220" t="n"/>
+      <c r="T22" s="220" t="n"/>
+      <c r="U22" s="220" t="n"/>
     </row>
     <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="220" t="inlineStr">
+      <c r="A23" s="226" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B23" s="226" t="inlineStr">
+      <c r="B23" s="230" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
@@ -11201,27 +11201,27 @@
           <t>Provide a unique title for your data service, which can be repeated in multiple languages. Example: Patient counts per available diagnosis.</t>
         </is>
       </c>
-      <c r="F23" s="227" t="inlineStr">
+      <c r="F23" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G23" s="227" t="inlineStr">
+      <c r="G23" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H23" s="227" t="inlineStr">
+      <c r="H23" s="231" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I23" s="218" t="inlineStr">
+      <c r="I23" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J23" s="232" t="inlineStr">
+      <c r="J23" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -11232,12 +11232,12 @@
         </is>
       </c>
       <c r="L23" s="159" t="n"/>
-      <c r="N23" s="232" t="inlineStr">
+      <c r="N23" s="224" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
         </is>
       </c>
-      <c r="O23" s="232" t="inlineStr">
+      <c r="O23" s="224" t="inlineStr">
         <is>
           <t>dash:TextFieldEditor</t>
         </is>
@@ -11245,9 +11245,9 @@
       <c r="R23" t="b">
         <v>1</v>
       </c>
-      <c r="S23" s="220" t="n"/>
-      <c r="T23" s="220" t="n"/>
-      <c r="U23" s="220" t="n"/>
+      <c r="S23" s="226" t="n"/>
+      <c r="T23" s="226" t="n"/>
+      <c r="U23" s="226" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="21" t="n"/>
@@ -12197,8 +12197,8 @@
     <col width="32.1640625" customWidth="1" style="234" min="18" max="18"/>
     <col width="9.1640625" customWidth="1" style="234" min="19" max="24"/>
     <col width="24.5" customWidth="1" min="25" max="27"/>
-    <col width="9.1640625" customWidth="1" style="234" min="28" max="30"/>
-    <col width="9.1640625" customWidth="1" style="234" min="31" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="31"/>
+    <col width="9.1640625" customWidth="1" style="234" min="32" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="112" customHeight="1">
@@ -13239,8 +13239,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
-    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="27"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -13827,8 +13827,8 @@
     <col width="28.83203125" customWidth="1" style="58" min="15" max="15"/>
     <col width="9.1640625" customWidth="1" style="58" min="16" max="21"/>
     <col width="20.1640625" customWidth="1" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="58" min="25" max="27"/>
-    <col width="9.1640625" customWidth="1" style="58" min="28" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="58" min="25" max="28"/>
+    <col width="9.1640625" customWidth="1" style="58" min="29" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="80" customHeight="1">
@@ -15119,8 +15119,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
-    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="27"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -16129,8 +16129,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
-    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="27"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -17135,8 +17135,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
-    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="27"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -18259,8 +18259,8 @@
     <col width="33.1640625" customWidth="1" style="234" min="14" max="14"/>
     <col width="9.1640625" customWidth="1" style="234" min="15" max="20"/>
     <col width="17.83203125" customWidth="1" min="21" max="23"/>
-    <col width="9.1640625" customWidth="1" style="234" min="24" max="26"/>
-    <col width="9.1640625" customWidth="1" style="234" min="27" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="234" min="24" max="27"/>
+    <col width="9.1640625" customWidth="1" style="234" min="28" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="71.25" customHeight="1">
@@ -20396,7 +20396,7 @@
     <col width="20" bestFit="1" customWidth="1" style="221" min="1" max="1"/>
     <col width="40.5" customWidth="1" style="221" min="2" max="2"/>
     <col width="25.5" bestFit="1" customWidth="1" style="221" min="3" max="3"/>
-    <col width="25.5" customWidth="1" style="223" min="4" max="4"/>
+    <col width="25.5" customWidth="1" style="228" min="4" max="4"/>
     <col width="54.5" customWidth="1" style="221" min="5" max="5"/>
     <col width="22.1640625" customWidth="1" style="219" min="6" max="6"/>
     <col width="24" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
@@ -20408,8 +20408,8 @@
     <col width="27" customWidth="1" style="219" min="13" max="13"/>
     <col width="9.1640625" customWidth="1" style="219" min="14" max="19"/>
     <col width="20" customWidth="1" min="20" max="22"/>
-    <col width="9.1640625" customWidth="1" style="219" min="23" max="25"/>
-    <col width="9.1640625" customWidth="1" style="219" min="26" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="23" max="26"/>
+    <col width="9.1640625" customWidth="1" style="219" min="27" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="64" customFormat="1" customHeight="1" s="163">
@@ -20546,12 +20546,12 @@
         </is>
       </c>
       <c r="E2" s="98" t="n"/>
-      <c r="F2" s="225" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G2" s="225" t="inlineStr">
+      <c r="G2" s="218" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -20561,12 +20561,12 @@
           <t>0..n</t>
         </is>
       </c>
-      <c r="I2" s="232" t="inlineStr">
+      <c r="I2" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="232" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -20576,8 +20576,8 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L2" s="232" t="n"/>
-      <c r="M2" s="232" t="n"/>
+      <c r="L2" s="224" t="n"/>
+      <c r="M2" s="224" t="n"/>
       <c r="O2" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -20594,17 +20594,17 @@
       <c r="V2" s="97" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="220" t="inlineStr">
+      <c r="A3" s="226" t="inlineStr">
         <is>
           <t>catalogue</t>
         </is>
       </c>
-      <c r="B3" s="226" t="inlineStr">
+      <c r="B3" s="230" t="inlineStr">
         <is>
           <t>A catalogue that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C3" s="220" t="inlineStr">
+      <c r="C3" s="226" t="inlineStr">
         <is>
           <t>dcat:catalog</t>
         </is>
@@ -20619,7 +20619,7 @@
           <t>For certain research projects, multiple catalogues may need to be organised in a nested manner. This property serves to connect the different catalogues with each other.</t>
         </is>
       </c>
-      <c r="F3" s="227" t="inlineStr">
+      <c r="F3" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20629,28 +20629,28 @@
           <t>dcat:Catalog</t>
         </is>
       </c>
-      <c r="H3" s="227" t="inlineStr">
+      <c r="H3" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="218" t="inlineStr">
+      <c r="I3" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J3" s="232" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K3" s="228" t="n"/>
+      <c r="K3" s="232" t="n"/>
       <c r="L3" s="100" t="inlineStr">
         <is>
           <t>If applicable, enter the URI of the connected dcat:Catalog.</t>
         </is>
       </c>
-      <c r="M3" s="218" t="n"/>
+      <c r="M3" s="225" t="n"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>hrishapes:CatalogShape</t>
@@ -20667,9 +20667,9 @@
         </is>
       </c>
       <c r="S3" s="69" t="n"/>
-      <c r="T3" s="220" t="n"/>
-      <c r="U3" s="220" t="n"/>
-      <c r="V3" s="220" t="n"/>
+      <c r="T3" s="226" t="n"/>
+      <c r="U3" s="226" t="n"/>
+      <c r="V3" s="226" t="n"/>
     </row>
     <row r="4" ht="95.25" customHeight="1">
       <c r="A4" s="97" t="inlineStr">
@@ -20682,7 +20682,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C4" s="230" t="inlineStr">
+      <c r="C4" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -20698,7 +20698,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F4" s="225" t="inlineStr">
+      <c r="F4" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20708,30 +20708,30 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H4" s="225" t="n">
+      <c r="H4" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="232" t="inlineStr">
+      <c r="I4" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="232" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K4" s="232" t="inlineStr">
+      <c r="K4" s="224" t="inlineStr">
         <is>
           <t>custom:contact</t>
         </is>
       </c>
-      <c r="L4" s="232" t="inlineStr">
+      <c r="L4" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M4" s="232" t="inlineStr">
+      <c r="M4" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -20757,17 +20757,17 @@
       <c r="V4" s="97" t="n"/>
     </row>
     <row r="5" ht="192" customHeight="1">
-      <c r="A5" s="220" t="inlineStr">
+      <c r="A5" s="226" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
       </c>
-      <c r="B5" s="226" t="inlineStr">
+      <c r="B5" s="230" t="inlineStr">
         <is>
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C5" s="220" t="inlineStr">
+      <c r="C5" s="226" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -20784,7 +20784,7 @@
 Note that the Health-RI model diverges from DCAT-AP NL here, which reduces the maximum number of creators to 1. The Health-RI model allows the specification of multiple creators of a catalogue.</t>
         </is>
       </c>
-      <c r="F5" s="227" t="inlineStr">
+      <c r="F5" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -20794,28 +20794,28 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H5" s="227" t="inlineStr">
+      <c r="H5" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I5" s="218" t="inlineStr">
+      <c r="I5" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J5" s="232" t="n"/>
-      <c r="K5" s="228" t="inlineStr">
+      <c r="J5" s="224" t="n"/>
+      <c r="K5" s="232" t="inlineStr">
         <is>
           <t>custom:creator</t>
         </is>
       </c>
-      <c r="L5" s="218" t="inlineStr">
+      <c r="L5" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M5" s="218" t="inlineStr">
+      <c r="M5" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -20836,12 +20836,12 @@
         </is>
       </c>
       <c r="S5" s="69" t="n"/>
-      <c r="T5" s="220" t="n"/>
-      <c r="U5" s="220" t="n"/>
-      <c r="V5" s="220" t="n"/>
+      <c r="T5" s="226" t="n"/>
+      <c r="U5" s="226" t="n"/>
+      <c r="V5" s="226" t="n"/>
     </row>
     <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="230" t="inlineStr">
+      <c r="A6" s="220" t="inlineStr">
         <is>
           <t>dataset</t>
         </is>
@@ -20851,7 +20851,7 @@
           <t>A dataset that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C6" s="230" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dcat:dataset</t>
         </is>
@@ -20866,7 +20866,7 @@
           <t>Each catalogue contains one or more datasets. This property serves to link datasets to a catalogue. Therefore, a dataset is always contained inside a catalogue.</t>
         </is>
       </c>
-      <c r="F6" s="225" t="inlineStr">
+      <c r="F6" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -20881,12 +20881,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="232" t="inlineStr">
+      <c r="I6" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J6" s="232" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -20897,7 +20897,7 @@
           <t>Enter the URI for all datasets contained in this catalogue.</t>
         </is>
       </c>
-      <c r="M6" s="232" t="n"/>
+      <c r="M6" s="224" t="n"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -20914,22 +20914,22 @@
         </is>
       </c>
       <c r="S6" s="69" t="n"/>
-      <c r="T6" s="230" t="n"/>
-      <c r="U6" s="230" t="n"/>
-      <c r="V6" s="230" t="n"/>
+      <c r="T6" s="220" t="n"/>
+      <c r="U6" s="220" t="n"/>
+      <c r="V6" s="220" t="n"/>
     </row>
     <row r="7" ht="29" customHeight="1">
-      <c r="A7" s="220" t="inlineStr">
+      <c r="A7" s="226" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B7" s="226" t="inlineStr">
+      <c r="B7" s="230" t="inlineStr">
         <is>
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C7" s="220" t="inlineStr">
+      <c r="C7" s="226" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -20944,38 +20944,38 @@
           <t>Briefly describe the catalogue and what it contains. You can repeat this in multiple languages.</t>
         </is>
       </c>
-      <c r="F7" s="227" t="inlineStr">
+      <c r="F7" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G7" s="227" t="inlineStr">
+      <c r="G7" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H7" s="227" t="inlineStr">
+      <c r="H7" s="231" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I7" s="218" t="inlineStr">
+      <c r="I7" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J7" s="232" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K7" s="228" t="inlineStr">
+      <c r="K7" s="232" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="L7" s="218" t="n"/>
-      <c r="M7" s="218" t="n"/>
+      <c r="L7" s="225" t="n"/>
+      <c r="M7" s="225" t="n"/>
       <c r="O7" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -20989,22 +20989,22 @@
       <c r="S7" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T7" s="220" t="n"/>
-      <c r="U7" s="220" t="n"/>
-      <c r="V7" s="220" t="n"/>
+      <c r="T7" s="226" t="n"/>
+      <c r="U7" s="226" t="n"/>
+      <c r="V7" s="226" t="n"/>
     </row>
     <row r="8" ht="29" customHeight="1">
-      <c r="A8" s="230" t="inlineStr">
+      <c r="A8" s="220" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B8" s="229" t="inlineStr">
+      <c r="B8" s="222" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C8" s="230" t="inlineStr">
+      <c r="C8" s="220" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -21014,39 +21014,39 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E8" s="231" t="inlineStr">
+      <c r="E8" s="223" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used.</t>
         </is>
       </c>
-      <c r="F8" s="225" t="inlineStr">
+      <c r="F8" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="225" t="inlineStr">
+      <c r="G8" s="218" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="225" t="inlineStr">
+      <c r="H8" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="232" t="inlineStr">
+      <c r="I8" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="232" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K8" s="103" t="n"/>
-      <c r="L8" s="232" t="n"/>
-      <c r="M8" s="232" t="n"/>
+      <c r="L8" s="224" t="n"/>
+      <c r="M8" s="224" t="n"/>
       <c r="O8" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21058,9 +21058,9 @@
         </is>
       </c>
       <c r="S8" s="69" t="n"/>
-      <c r="T8" s="230" t="n"/>
-      <c r="U8" s="230" t="n"/>
-      <c r="V8" s="230" t="n"/>
+      <c r="T8" s="220" t="n"/>
+      <c r="U8" s="220" t="n"/>
+      <c r="V8" s="220" t="n"/>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="D9" s="177" t="inlineStr">
@@ -21099,17 +21099,17 @@
       <c r="S12" s="69" t="n"/>
     </row>
     <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="220" t="inlineStr">
+      <c r="A13" s="226" t="inlineStr">
         <is>
           <t>has part</t>
         </is>
       </c>
-      <c r="B13" s="226" t="inlineStr">
+      <c r="B13" s="230" t="inlineStr">
         <is>
           <t>A related resource that is included either physically or logically in the described resource.</t>
         </is>
       </c>
-      <c r="C13" s="220" t="inlineStr">
+      <c r="C13" s="226" t="inlineStr">
         <is>
           <t>dct:hasPart</t>
         </is>
@@ -21125,7 +21125,7 @@
 Note that deeply nested structures should be avoided, and cannot currently be displayed in the National Health Data Catalogue.</t>
         </is>
       </c>
-      <c r="F13" s="227" t="inlineStr">
+      <c r="F13" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21135,17 +21135,17 @@
           <t>dcat:Catalog</t>
         </is>
       </c>
-      <c r="H13" s="227" t="inlineStr">
+      <c r="H13" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="218" t="inlineStr">
+      <c r="I13" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J13" s="232" t="inlineStr">
+      <c r="J13" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21156,7 +21156,7 @@
           <t>If applicable, add the URI of the dcat:Catalog that is part of this catalogue.</t>
         </is>
       </c>
-      <c r="M13" s="218" t="n"/>
+      <c r="M13" s="225" t="n"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>hrishapes:CatalogShape</t>
@@ -21173,12 +21173,12 @@
         </is>
       </c>
       <c r="S13" s="69" t="n"/>
-      <c r="T13" s="220" t="n"/>
-      <c r="U13" s="220" t="n"/>
-      <c r="V13" s="220" t="n"/>
+      <c r="T13" s="226" t="n"/>
+      <c r="U13" s="226" t="n"/>
+      <c r="V13" s="226" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="230" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>home page</t>
         </is>
@@ -21188,7 +21188,7 @@
           <t>A homepage for some thing.</t>
         </is>
       </c>
-      <c r="C14" s="230" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>foaf:homepage</t>
         </is>
@@ -21203,34 +21203,34 @@
           <t>The home page of the catalogue, if available.</t>
         </is>
       </c>
-      <c r="F14" s="225" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="225" t="inlineStr">
+      <c r="G14" s="218" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="225" t="inlineStr">
+      <c r="H14" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I14" s="232" t="inlineStr">
+      <c r="I14" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="232" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K14" s="103" t="n"/>
-      <c r="L14" s="232" t="n"/>
-      <c r="M14" s="232" t="n"/>
+      <c r="L14" s="224" t="n"/>
+      <c r="M14" s="224" t="n"/>
       <c r="O14" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21242,22 +21242,22 @@
         </is>
       </c>
       <c r="S14" s="69" t="n"/>
-      <c r="T14" s="230" t="n"/>
-      <c r="U14" s="230" t="n"/>
-      <c r="V14" s="230" t="n"/>
+      <c r="T14" s="220" t="n"/>
+      <c r="U14" s="220" t="n"/>
+      <c r="V14" s="220" t="n"/>
     </row>
     <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="220" t="inlineStr">
+      <c r="A15" s="226" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="B15" s="226" t="inlineStr">
+      <c r="B15" s="230" t="inlineStr">
         <is>
           <t>A language of the resource.</t>
         </is>
       </c>
-      <c r="C15" s="220" t="inlineStr">
+      <c r="C15" s="226" t="inlineStr">
         <is>
           <t>dct:language</t>
         </is>
@@ -21267,33 +21267,33 @@
           <t>http://publications.europa.eu/resource/authority/language</t>
         </is>
       </c>
-      <c r="E15" s="226" t="inlineStr">
+      <c r="E15" s="230" t="inlineStr">
         <is>
           <t>The value of this property must be an IRI from the provided controlled vocabulary.
 For example: http://publications.europa.eu/resource/authority/language/NLD</t>
         </is>
       </c>
-      <c r="F15" s="227" t="inlineStr">
+      <c r="F15" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="227" t="inlineStr">
+      <c r="G15" s="231" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="227" t="inlineStr">
+      <c r="H15" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="218" t="inlineStr">
+      <c r="I15" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="232" t="inlineStr">
+      <c r="J15" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21303,8 +21303,8 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L15" s="218" t="n"/>
-      <c r="M15" s="218" t="n"/>
+      <c r="L15" s="225" t="n"/>
+      <c r="M15" s="225" t="n"/>
       <c r="O15" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21316,12 +21316,12 @@
         </is>
       </c>
       <c r="S15" s="69" t="n"/>
-      <c r="T15" s="220" t="n"/>
-      <c r="U15" s="220" t="n"/>
-      <c r="V15" s="220" t="n"/>
+      <c r="T15" s="226" t="n"/>
+      <c r="U15" s="226" t="n"/>
+      <c r="V15" s="226" t="n"/>
     </row>
     <row r="16" ht="85.25" customHeight="1">
-      <c r="A16" s="230" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>licence</t>
         </is>
@@ -21347,27 +21347,27 @@
 The licences for Distributions and Data Services are not specified here. They are specified in the licence properties of their respective classes.</t>
         </is>
       </c>
-      <c r="F16" s="225" t="inlineStr">
+      <c r="F16" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="225" t="inlineStr">
+      <c r="G16" s="218" t="inlineStr">
         <is>
           <t>dct:LicenseDocument (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="225" t="inlineStr">
+      <c r="H16" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="232" t="inlineStr">
+      <c r="I16" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="232" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21377,8 +21377,8 @@
           <t>custom:licence</t>
         </is>
       </c>
-      <c r="L16" s="232" t="n"/>
-      <c r="M16" s="232" t="n"/>
+      <c r="L16" s="224" t="n"/>
+      <c r="M16" s="224" t="n"/>
       <c r="O16" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21390,22 +21390,22 @@
         </is>
       </c>
       <c r="S16" s="69" t="n"/>
-      <c r="T16" s="230" t="n"/>
-      <c r="U16" s="230" t="n"/>
-      <c r="V16" s="230" t="n"/>
+      <c r="T16" s="220" t="n"/>
+      <c r="U16" s="220" t="n"/>
+      <c r="V16" s="220" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="220" t="inlineStr">
+      <c r="A17" s="226" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
       </c>
-      <c r="B17" s="226" t="inlineStr">
+      <c r="B17" s="230" t="inlineStr">
         <is>
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C17" s="220" t="inlineStr">
+      <c r="C17" s="226" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -21416,27 +21416,27 @@
         </is>
       </c>
       <c r="E17" s="100" t="n"/>
-      <c r="F17" s="227" t="inlineStr">
+      <c r="F17" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="227" t="inlineStr">
+      <c r="G17" s="231" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H17" s="227" t="inlineStr">
+      <c r="H17" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I17" s="218" t="inlineStr">
+      <c r="I17" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="232" t="inlineStr">
+      <c r="J17" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21446,8 +21446,8 @@
           <t>custom:modified</t>
         </is>
       </c>
-      <c r="L17" s="218" t="n"/>
-      <c r="M17" s="218" t="n"/>
+      <c r="L17" s="225" t="n"/>
+      <c r="M17" s="225" t="n"/>
       <c r="O17" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21464,12 +21464,12 @@
         </is>
       </c>
       <c r="S17" s="69" t="n"/>
-      <c r="T17" s="220" t="n"/>
-      <c r="U17" s="220" t="n"/>
-      <c r="V17" s="220" t="n"/>
+      <c r="T17" s="226" t="n"/>
+      <c r="U17" s="226" t="n"/>
+      <c r="V17" s="226" t="n"/>
     </row>
     <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="230" t="inlineStr">
+      <c r="A18" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -21494,7 +21494,7 @@
           <t>The organisation or individual that is the holder of the intellectual property rights of a dataset. For more details about the publisher, see the class Agent. Example: Radboudumc.</t>
         </is>
       </c>
-      <c r="F18" s="225" t="inlineStr">
+      <c r="F18" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -21504,15 +21504,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H18" s="225" t="n">
+      <c r="H18" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="232" t="inlineStr">
+      <c r="I18" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J18" s="232" t="inlineStr">
+      <c r="J18" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21522,12 +21522,12 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L18" s="232" t="inlineStr">
+      <c r="L18" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M18" s="232" t="inlineStr">
+      <c r="M18" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -21548,22 +21548,22 @@
         </is>
       </c>
       <c r="S18" s="69" t="n"/>
-      <c r="T18" s="230" t="n"/>
-      <c r="U18" s="230" t="n"/>
-      <c r="V18" s="230" t="n"/>
+      <c r="T18" s="220" t="n"/>
+      <c r="U18" s="220" t="n"/>
+      <c r="V18" s="220" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="220" t="inlineStr">
+      <c r="A19" s="226" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
       </c>
-      <c r="B19" s="226" t="inlineStr">
+      <c r="B19" s="230" t="inlineStr">
         <is>
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C19" s="220" t="inlineStr">
+      <c r="C19" s="226" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -21574,27 +21574,27 @@
         </is>
       </c>
       <c r="E19" s="92" t="n"/>
-      <c r="F19" s="227" t="inlineStr">
+      <c r="F19" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G19" s="227" t="inlineStr">
+      <c r="G19" s="231" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H19" s="227" t="inlineStr">
+      <c r="H19" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I19" s="218" t="inlineStr">
+      <c r="I19" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J19" s="218" t="inlineStr">
+      <c r="J19" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21604,8 +21604,8 @@
           <t>custom:issued</t>
         </is>
       </c>
-      <c r="L19" s="218" t="n"/>
-      <c r="M19" s="218" t="n"/>
+      <c r="L19" s="225" t="n"/>
+      <c r="M19" s="225" t="n"/>
       <c r="O19" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21622,12 +21622,12 @@
         </is>
       </c>
       <c r="S19" s="69" t="n"/>
-      <c r="T19" s="220" t="n"/>
-      <c r="U19" s="220" t="n"/>
-      <c r="V19" s="220" t="n"/>
+      <c r="T19" s="226" t="n"/>
+      <c r="U19" s="226" t="n"/>
+      <c r="V19" s="226" t="n"/>
     </row>
     <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="230" t="inlineStr">
+      <c r="A20" s="220" t="inlineStr">
         <is>
           <t>rights</t>
         </is>
@@ -21637,7 +21637,7 @@
           <t>Information about rights held in and over the resource.</t>
         </is>
       </c>
-      <c r="C20" s="230" t="inlineStr">
+      <c r="C20" s="220" t="inlineStr">
         <is>
           <t>dct:rights</t>
         </is>
@@ -21652,34 +21652,34 @@
           <t>The rights statement should be a free-text statement placed at a web-accessible location such that the value of this property is the IRI pointing to that statement.</t>
         </is>
       </c>
-      <c r="F20" s="225" t="inlineStr">
+      <c r="F20" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G20" s="225" t="inlineStr">
+      <c r="G20" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H20" s="225" t="inlineStr">
+      <c r="H20" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I20" s="232" t="inlineStr">
+      <c r="I20" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J20" s="232" t="inlineStr">
+      <c r="J20" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K20" s="75" t="n"/>
-      <c r="L20" s="232" t="n"/>
-      <c r="M20" s="232" t="n"/>
+      <c r="L20" s="224" t="n"/>
+      <c r="M20" s="224" t="n"/>
       <c r="O20" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -21691,22 +21691,22 @@
         </is>
       </c>
       <c r="S20" s="69" t="n"/>
-      <c r="T20" s="230" t="n"/>
-      <c r="U20" s="230" t="n"/>
-      <c r="V20" s="230" t="n"/>
+      <c r="T20" s="220" t="n"/>
+      <c r="U20" s="220" t="n"/>
+      <c r="V20" s="220" t="n"/>
     </row>
     <row r="21" ht="64" customHeight="1">
-      <c r="A21" s="220" t="inlineStr">
+      <c r="A21" s="226" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B21" s="226" t="inlineStr">
+      <c r="B21" s="230" t="inlineStr">
         <is>
           <t>A service that is listed in the catalogue.</t>
         </is>
       </c>
-      <c r="C21" s="220" t="inlineStr">
+      <c r="C21" s="226" t="inlineStr">
         <is>
           <t>dcat:service</t>
         </is>
@@ -21721,38 +21721,38 @@
           <t>Some datasets may have real-time Data Services (e.g., Beacon API counting individuals). IT teams should define the relationship between the catalogue and the Data Service via this property. While crucial for interoperability, this property is not relevant for end users to collect.</t>
         </is>
       </c>
-      <c r="F21" s="227" t="inlineStr">
+      <c r="F21" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G21" s="227" t="inlineStr">
+      <c r="G21" s="231" t="inlineStr">
         <is>
           <t>dcat:DataService</t>
         </is>
       </c>
-      <c r="H21" s="227" t="inlineStr">
+      <c r="H21" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I21" s="218" t="inlineStr">
+      <c r="I21" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J21" s="218" t="inlineStr">
+      <c r="J21" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K21" s="228" t="n"/>
+      <c r="K21" s="232" t="n"/>
       <c r="L21" s="100" t="inlineStr">
         <is>
           <t>If applicable, enter the URI for dcat:DataService.</t>
         </is>
       </c>
-      <c r="M21" s="218" t="n"/>
+      <c r="M21" s="225" t="n"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>hrishapes:DataServiceShape</t>
@@ -21769,12 +21769,12 @@
         </is>
       </c>
       <c r="S21" s="69" t="n"/>
-      <c r="T21" s="220" t="n"/>
-      <c r="U21" s="220" t="n"/>
-      <c r="V21" s="220" t="n"/>
+      <c r="T21" s="226" t="n"/>
+      <c r="U21" s="226" t="n"/>
+      <c r="V21" s="226" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="230" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -21784,7 +21784,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C22" s="230" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -21795,7 +21795,7 @@
         </is>
       </c>
       <c r="E22" s="29" t="n"/>
-      <c r="F22" s="225" t="inlineStr">
+      <c r="F22" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -21805,17 +21805,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H22" s="225" t="inlineStr">
+      <c r="H22" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="232" t="inlineStr">
+      <c r="I22" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="232" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21825,8 +21825,8 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L22" s="232" t="n"/>
-      <c r="M22" s="232" t="n"/>
+      <c r="L22" s="224" t="n"/>
+      <c r="M22" s="224" t="n"/>
       <c r="N22" s="219" t="inlineStr">
         <is>
           <t>hrishapes:PeriodOfTimeShape</t>
@@ -21843,17 +21843,17 @@
         </is>
       </c>
       <c r="S22" s="69" t="n"/>
-      <c r="T22" s="230" t="n"/>
-      <c r="U22" s="230" t="n"/>
-      <c r="V22" s="230" t="n"/>
+      <c r="T22" s="220" t="n"/>
+      <c r="U22" s="220" t="n"/>
+      <c r="V22" s="220" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1">
-      <c r="A23" s="220" t="inlineStr">
+      <c r="A23" s="226" t="inlineStr">
         <is>
           <t>themes</t>
         </is>
       </c>
-      <c r="B23" s="226" t="inlineStr">
+      <c r="B23" s="230" t="inlineStr">
         <is>
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
@@ -21873,34 +21873,34 @@
           <t>This property refers to a knowledge organisation system used to classify the Catalogue's Datasets. It must include at least the value NAL:data-theme as this is the mandatory controlled vocabulary for dcat:theme.</t>
         </is>
       </c>
-      <c r="F23" s="227" t="inlineStr">
+      <c r="F23" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="227" t="inlineStr">
+      <c r="G23" s="231" t="inlineStr">
         <is>
           <t>skos:ConceptScheme (IRI)</t>
         </is>
       </c>
-      <c r="H23" s="227" t="inlineStr">
+      <c r="H23" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I23" s="218" t="inlineStr">
+      <c r="I23" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="218" t="inlineStr">
+      <c r="J23" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K23" s="170" t="n"/>
-      <c r="L23" s="218" t="n"/>
-      <c r="M23" s="218" t="n"/>
+      <c r="L23" s="225" t="n"/>
+      <c r="M23" s="225" t="n"/>
       <c r="O23" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -21912,12 +21912,12 @@
         </is>
       </c>
       <c r="S23" s="69" t="n"/>
-      <c r="T23" s="220" t="n"/>
-      <c r="U23" s="220" t="n"/>
-      <c r="V23" s="220" t="n"/>
+      <c r="T23" s="226" t="n"/>
+      <c r="U23" s="226" t="n"/>
+      <c r="V23" s="226" t="n"/>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="230" t="inlineStr">
+      <c r="A24" s="220" t="inlineStr">
         <is>
           <t>title</t>
         </is>
@@ -21927,7 +21927,7 @@
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C24" s="230" t="inlineStr">
+      <c r="C24" s="220" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -21942,27 +21942,27 @@
           <t>Provide a unique title for your catalogue, which can be repeated in multiple languages. Example: Healthy Brain Study.</t>
         </is>
       </c>
-      <c r="F24" s="225" t="inlineStr">
+      <c r="F24" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G24" s="225" t="inlineStr">
+      <c r="G24" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H24" s="225" t="inlineStr">
+      <c r="H24" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I24" s="232" t="inlineStr">
+      <c r="I24" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J24" s="232" t="inlineStr">
+      <c r="J24" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -21972,8 +21972,8 @@
           <t>title</t>
         </is>
       </c>
-      <c r="L24" s="232" t="n"/>
-      <c r="M24" s="232" t="n"/>
+      <c r="L24" s="224" t="n"/>
+      <c r="M24" s="224" t="n"/>
       <c r="O24" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -21987,16 +21987,16 @@
       <c r="S24" s="69" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="230" t="n"/>
-      <c r="U24" s="230" t="n"/>
-      <c r="V24" s="230" t="n"/>
+      <c r="T24" s="220" t="n"/>
+      <c r="U24" s="220" t="n"/>
+      <c r="V24" s="220" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:J24"/>
   <mergeCells count="11">
     <mergeCell ref="H8:H12"/>
+    <mergeCell ref="B8:B12"/>
     <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
     <mergeCell ref="E8:E12"/>
     <mergeCell ref="C8:C12"/>
     <mergeCell ref="I8:I12"/>
@@ -22142,8 +22142,8 @@
     <col width="25.5" bestFit="1" customWidth="1" style="221" min="1" max="1"/>
     <col width="40.5" customWidth="1" style="221" min="2" max="2"/>
     <col width="28.83203125" customWidth="1" style="221" min="3" max="3"/>
-    <col width="22.5" customWidth="1" style="223" min="4" max="4"/>
-    <col width="68.83203125" customWidth="1" style="223" min="5" max="5"/>
+    <col width="22.5" customWidth="1" style="228" min="4" max="4"/>
+    <col width="68.83203125" customWidth="1" style="228" min="5" max="5"/>
     <col width="18.5" bestFit="1" customWidth="1" style="219" min="6" max="6"/>
     <col width="22.83203125" bestFit="1" customWidth="1" style="219" min="7" max="7"/>
     <col width="13.5" customWidth="1" style="219" min="8" max="8"/>
@@ -22156,8 +22156,8 @@
     <col width="25.83203125" customWidth="1" style="219" min="15" max="15"/>
     <col width="9.1640625" customWidth="1" style="219" min="16" max="21"/>
     <col width="25.5" customWidth="1" min="22" max="24"/>
-    <col width="9.1640625" customWidth="1" style="219" min="25" max="27"/>
-    <col width="9.1640625" customWidth="1" style="219" min="28" max="16384"/>
+    <col width="9.1640625" customWidth="1" style="219" min="25" max="28"/>
+    <col width="9.1640625" customWidth="1" style="219" min="29" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customFormat="1" customHeight="1" s="163">
@@ -22293,7 +22293,7 @@
           <t>Information about who can access the resource or an indication of its security status.</t>
         </is>
       </c>
-      <c r="C2" s="230" t="inlineStr">
+      <c r="C2" s="220" t="inlineStr">
         <is>
           <t>dct:accessRights</t>
         </is>
@@ -22312,25 +22312,25 @@
 Since most data contain personal information, these datasets will need to take the value 'non-public' for the access rights property.</t>
         </is>
       </c>
-      <c r="F2" s="225" t="inlineStr">
+      <c r="F2" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G2" s="225" t="inlineStr">
+      <c r="G2" s="218" t="inlineStr">
         <is>
           <t>dct:RightsStatement (IRI)</t>
         </is>
       </c>
-      <c r="H2" s="225" t="n">
+      <c r="H2" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="232" t="inlineStr">
+      <c r="I2" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J2" s="232" t="inlineStr">
+      <c r="J2" s="224" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -22340,7 +22340,7 @@
           <t>custom:access_rights</t>
         </is>
       </c>
-      <c r="L2" s="232" t="n"/>
+      <c r="L2" s="224" t="n"/>
       <c r="P2" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22356,17 +22356,17 @@
       <c r="X2" s="97" t="n"/>
     </row>
     <row r="3" ht="209.25" customHeight="1">
-      <c r="A3" s="220" t="inlineStr">
+      <c r="A3" s="226" t="inlineStr">
         <is>
           <t>alternative</t>
         </is>
       </c>
-      <c r="B3" s="226" t="inlineStr">
+      <c r="B3" s="230" t="inlineStr">
         <is>
           <t>An alternative name for the dataset.</t>
         </is>
       </c>
-      <c r="C3" s="220" t="inlineStr">
+      <c r="C3" s="226" t="inlineStr">
         <is>
           <t>dct:alternative</t>
         </is>
@@ -22376,40 +22376,40 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E3" s="226" t="inlineStr">
+      <c r="E3" s="230" t="inlineStr">
         <is>
           <t>This property contains an alternative name for the Dataset. This property can be repeated for parallel language versions of the alternative name.</t>
         </is>
       </c>
-      <c r="F3" s="225" t="inlineStr">
+      <c r="F3" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G3" s="227" t="inlineStr">
+      <c r="G3" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H3" s="227" t="inlineStr">
+      <c r="H3" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I3" s="218" t="inlineStr">
+      <c r="I3" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J3" s="232" t="inlineStr">
+      <c r="J3" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K3" s="228" t="n"/>
+      <c r="K3" s="232" t="n"/>
       <c r="L3" s="100" t="n"/>
-      <c r="M3" s="218" t="n"/>
-      <c r="N3" s="218" t="n"/>
+      <c r="M3" s="225" t="n"/>
+      <c r="N3" s="225" t="n"/>
       <c r="P3" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -22420,9 +22420,9 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V3" s="220" t="n"/>
-      <c r="W3" s="220" t="n"/>
-      <c r="X3" s="220" t="n"/>
+      <c r="V3" s="226" t="n"/>
+      <c r="W3" s="226" t="n"/>
+      <c r="X3" s="226" t="n"/>
     </row>
     <row r="4" ht="112" customHeight="1">
       <c r="A4" s="97" t="inlineStr">
@@ -22450,7 +22450,7 @@
           <t>Publishers are encouraged to provide URLs pointing to document repositories where users can access or request associated resources such as technical reports of the dataset, quality measurements, usability indicators, etc. Note that HealthDCAT-AP also mentions API endpoints or analytics services, but these would be Data Services rather than Distributions.</t>
         </is>
       </c>
-      <c r="F4" s="227" t="inlineStr">
+      <c r="F4" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -22460,17 +22460,17 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H4" s="225" t="inlineStr">
+      <c r="H4" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I4" s="232" t="inlineStr">
+      <c r="I4" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J4" s="232" t="inlineStr">
+      <c r="J4" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22480,7 +22480,7 @@
           <t>custom:analytics</t>
         </is>
       </c>
-      <c r="L4" s="232" t="inlineStr">
+      <c r="L4" s="224" t="inlineStr">
         <is>
           <t>If available, add the URI for the analytics distribution here.</t>
         </is>
@@ -22510,17 +22510,17 @@
       <c r="X4" s="97" t="n"/>
     </row>
     <row r="5" ht="80" customHeight="1">
-      <c r="A5" s="220" t="inlineStr">
+      <c r="A5" s="226" t="inlineStr">
         <is>
           <t>anatomical location covered</t>
         </is>
       </c>
-      <c r="B5" s="226" t="inlineStr">
+      <c r="B5" s="230" t="inlineStr">
         <is>
           <t>Relates a dataset to an anatomical class that is Anatomical structure (SNOMED CT 91723000) or one of its subclasses, describing anatomical coverage of the dataset as a whole at metadata or catalogue level.</t>
         </is>
       </c>
-      <c r="C5" s="220" t="inlineStr">
+      <c r="C5" s="226" t="inlineStr">
         <is>
           <t>hri:anatomicalLocationCovered</t>
         </is>
@@ -22530,33 +22530,33 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E5" s="226" t="inlineStr">
+      <c r="E5" s="230" t="inlineStr">
         <is>
           <t>Use this property to indicate which anatomical parts of the body are covered by the Dataset. Select the relevant anatomical structure from SNOMED CT. Multiple anatomical locations can be provided.
 Example: A dataset containing lung imaging data can use Lung structure (http://snomed.info/id/39607008).</t>
         </is>
       </c>
-      <c r="F5" s="227" t="inlineStr">
+      <c r="F5" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G5" s="227" t="inlineStr">
+      <c r="G5" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H5" s="227" t="inlineStr">
+      <c r="H5" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I5" s="218" t="n"/>
-      <c r="J5" s="232" t="n"/>
-      <c r="K5" s="228" t="n"/>
+      <c r="I5" s="225" t="n"/>
+      <c r="J5" s="224" t="n"/>
+      <c r="K5" s="232" t="n"/>
       <c r="L5" s="100" t="n"/>
-      <c r="M5" s="218" t="n"/>
-      <c r="N5" s="218" t="n"/>
+      <c r="M5" s="225" t="n"/>
+      <c r="N5" s="225" t="n"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22572,9 +22572,9 @@
           <t>^http://snomed\.info/id/[0-9]{6,18}$</t>
         </is>
       </c>
-      <c r="V5" s="220" t="n"/>
-      <c r="W5" s="220" t="n"/>
-      <c r="X5" s="220" t="n"/>
+      <c r="V5" s="226" t="n"/>
+      <c r="W5" s="226" t="n"/>
+      <c r="X5" s="226" t="n"/>
     </row>
     <row r="6" ht="176" customFormat="1" customHeight="1" s="83">
       <c r="A6" s="97" t="inlineStr">
@@ -22587,7 +22587,7 @@
           <t>The legislation that is applicable to this resource.</t>
         </is>
       </c>
-      <c r="C6" s="230" t="inlineStr">
+      <c r="C6" s="220" t="inlineStr">
         <is>
           <t>dcatap:applicableLegislation</t>
         </is>
@@ -22605,12 +22605,12 @@
 While the applicable legislation indicates which legislation mandates the publication of the dataset, the legal basis property (also in Datasets) describes the legal basis for initial collection and processing of (personal) data.</t>
         </is>
       </c>
-      <c r="F6" s="225" t="inlineStr">
+      <c r="F6" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G6" s="225" t="inlineStr">
+      <c r="G6" s="218" t="inlineStr">
         <is>
           <t>eli:LegalResource (IRI)</t>
         </is>
@@ -22620,12 +22620,12 @@
           <t>1..n</t>
         </is>
       </c>
-      <c r="I6" s="232" t="inlineStr">
+      <c r="I6" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J6" s="232" t="inlineStr">
+      <c r="J6" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22635,7 +22635,7 @@
           <t>custom:applicable_legislation</t>
         </is>
       </c>
-      <c r="L6" s="232" t="n"/>
+      <c r="L6" s="224" t="n"/>
       <c r="P6" s="83" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22656,12 +22656,12 @@
       <c r="X6" s="97" t="n"/>
     </row>
     <row r="7" ht="80" customHeight="1">
-      <c r="A7" s="220" t="inlineStr">
+      <c r="A7" s="226" t="inlineStr">
         <is>
           <t>code values</t>
         </is>
       </c>
-      <c r="B7" s="226" t="inlineStr">
+      <c r="B7" s="230" t="inlineStr">
         <is>
           <t>Health classifications and their codes associated with the dataset</t>
         </is>
@@ -22682,39 +22682,39 @@
 Inside this property, you can provide the coding system of the dataset in the form of a Wikidata URI (example: https://www.wikidata.org/entity/P494 for ICD-10 ID) and the URI of the value that describes the dataset (example: https://icd.who.int/browse10/2019/en#/Y59.0 for viral vaccines).</t>
         </is>
       </c>
-      <c r="F7" s="227" t="inlineStr">
+      <c r="F7" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G7" s="227" t="inlineStr">
+      <c r="G7" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H7" s="227" t="inlineStr">
+      <c r="H7" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I7" s="218" t="inlineStr">
+      <c r="I7" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J7" s="232" t="inlineStr">
+      <c r="J7" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K7" s="228" t="inlineStr">
+      <c r="K7" s="232" t="inlineStr">
         <is>
           <t>custom:code_values</t>
         </is>
       </c>
-      <c r="L7" s="218" t="n"/>
-      <c r="M7" s="218" t="n"/>
-      <c r="N7" s="218" t="n"/>
+      <c r="L7" s="225" t="n"/>
+      <c r="M7" s="225" t="n"/>
+      <c r="N7" s="225" t="n"/>
       <c r="P7" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -22725,12 +22725,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V7" s="220" t="n"/>
-      <c r="W7" s="220" t="n"/>
-      <c r="X7" s="220" t="n"/>
+      <c r="V7" s="226" t="n"/>
+      <c r="W7" s="226" t="n"/>
+      <c r="X7" s="226" t="n"/>
     </row>
     <row r="8" ht="64" customHeight="1">
-      <c r="A8" s="230" t="inlineStr">
+      <c r="A8" s="220" t="inlineStr">
         <is>
           <t>coding system</t>
         </is>
@@ -22740,7 +22740,7 @@
           <t>Coding systems in use (e.g. ICD-10-CM, DGRs, SNOMED CT, ...)</t>
         </is>
       </c>
-      <c r="C8" s="230" t="inlineStr">
+      <c r="C8" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:hasCodingSystem</t>
         </is>
@@ -22756,27 +22756,27 @@
 This property provides information on which coding systems are in use in your dataset. For this, Wikidata URIs must be used.</t>
         </is>
       </c>
-      <c r="F8" s="225" t="inlineStr">
+      <c r="F8" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G8" s="225" t="inlineStr">
+      <c r="G8" s="218" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H8" s="225" t="inlineStr">
+      <c r="H8" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I8" s="232" t="inlineStr">
+      <c r="I8" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J8" s="232" t="inlineStr">
+      <c r="J8" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -22786,7 +22786,7 @@
           <t>custom:coding_system</t>
         </is>
       </c>
-      <c r="L8" s="232" t="n"/>
+      <c r="L8" s="224" t="n"/>
       <c r="P8" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22797,22 +22797,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V8" s="230" t="n"/>
-      <c r="W8" s="230" t="n"/>
-      <c r="X8" s="230" t="n"/>
+      <c r="V8" s="220" t="n"/>
+      <c r="W8" s="220" t="n"/>
+      <c r="X8" s="220" t="n"/>
     </row>
     <row r="9" ht="80" customHeight="1">
-      <c r="A9" s="220" t="inlineStr">
+      <c r="A9" s="226" t="inlineStr">
         <is>
           <t>conforms to</t>
         </is>
       </c>
-      <c r="B9" s="226" t="inlineStr">
+      <c r="B9" s="230" t="inlineStr">
         <is>
           <t>An established standard to which the described resource conforms.</t>
         </is>
       </c>
-      <c r="C9" s="220" t="inlineStr">
+      <c r="C9" s="226" t="inlineStr">
         <is>
           <t>dct:conformsTo</t>
         </is>
@@ -22822,45 +22822,45 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E9" s="226" t="inlineStr">
+      <c r="E9" s="230" t="inlineStr">
         <is>
           <t>Note: The use of Wikidata URIs will be replaced with the terms from a controlled vocabulary in the next major release.
 If your data conforms to an established standard or specification, use this property to indicate which one. The Wikidata URI of the specification must be used. Example: https://www.wikidata.org/wiki/Q19597236 for FHIR.</t>
         </is>
       </c>
-      <c r="F9" s="227" t="inlineStr">
+      <c r="F9" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G9" s="227" t="inlineStr">
+      <c r="G9" s="231" t="inlineStr">
         <is>
           <t>dct:Standard (IRI)</t>
         </is>
       </c>
-      <c r="H9" s="227" t="inlineStr">
+      <c r="H9" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I9" s="218" t="inlineStr">
+      <c r="I9" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J9" s="232" t="inlineStr">
+      <c r="J9" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K9" s="228" t="inlineStr">
+      <c r="K9" s="232" t="inlineStr">
         <is>
           <t>custom:conforms_to</t>
         </is>
       </c>
-      <c r="L9" s="218" t="n"/>
-      <c r="M9" s="218" t="n"/>
-      <c r="N9" s="218" t="n"/>
+      <c r="L9" s="225" t="n"/>
+      <c r="M9" s="225" t="n"/>
+      <c r="N9" s="225" t="n"/>
       <c r="P9" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -22871,12 +22871,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V9" s="220" t="n"/>
-      <c r="W9" s="220" t="n"/>
-      <c r="X9" s="220" t="n"/>
+      <c r="V9" s="226" t="n"/>
+      <c r="W9" s="226" t="n"/>
+      <c r="X9" s="226" t="n"/>
     </row>
     <row r="10" ht="123.75" customHeight="1">
-      <c r="A10" s="230" t="inlineStr">
+      <c r="A10" s="220" t="inlineStr">
         <is>
           <t>contact point</t>
         </is>
@@ -22886,7 +22886,7 @@
           <t>Relevant contact information for the catalogued resource.</t>
         </is>
       </c>
-      <c r="C10" s="230" t="inlineStr">
+      <c r="C10" s="220" t="inlineStr">
         <is>
           <t>dcat:contactPoint</t>
         </is>
@@ -22902,7 +22902,7 @@
 Whenever possible, use general contact information (for example, from a department) instead of the contact information of an individual.</t>
         </is>
       </c>
-      <c r="F10" s="225" t="inlineStr">
+      <c r="F10" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -22912,15 +22912,15 @@
           <t>vcard:Kind</t>
         </is>
       </c>
-      <c r="H10" s="225" t="n">
+      <c r="H10" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="232" t="inlineStr">
+      <c r="I10" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J10" s="232" t="inlineStr">
+      <c r="J10" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -22930,17 +22930,17 @@
           <t>custom:contact_</t>
         </is>
       </c>
-      <c r="L10" s="232" t="inlineStr">
+      <c r="L10" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="M10" s="232" t="inlineStr">
+      <c r="M10" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
       </c>
-      <c r="N10" s="232" t="inlineStr">
+      <c r="N10" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Kind' tab.</t>
         </is>
@@ -22960,22 +22960,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V10" s="230" t="n"/>
-      <c r="W10" s="230" t="n"/>
-      <c r="X10" s="230" t="n"/>
+      <c r="V10" s="220" t="n"/>
+      <c r="W10" s="220" t="n"/>
+      <c r="X10" s="220" t="n"/>
     </row>
     <row r="11" ht="176" customHeight="1">
-      <c r="A11" s="220" t="inlineStr">
+      <c r="A11" s="226" t="inlineStr">
         <is>
           <t>creator</t>
         </is>
       </c>
-      <c r="B11" s="226" t="inlineStr">
+      <c r="B11" s="230" t="inlineStr">
         <is>
           <t>An entity responsible for making the resource.</t>
         </is>
       </c>
-      <c r="C11" s="220" t="inlineStr">
+      <c r="C11" s="226" t="inlineStr">
         <is>
           <t>dct:creator</t>
         </is>
@@ -22985,14 +22985,14 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E11" s="226" t="inlineStr">
+      <c r="E11" s="230" t="inlineStr">
         <is>
           <t>The creator (of the dataset) is the entity responsible for making the resource. According to Dutch databank and copyright law, this is in most cases the organisation/employer bearing investment risk, instead of an individual (e.g. an individual researcher). Therefore, in many cases, this might be the same Agent as the dct:publisher: the organisation (not a department or subdivision of the organisation) where the dataset was created.
 If there are multiple (collaborating) organisations involved in data creation, all of them can be stated as dct:creator, as the model allows more than one creator.
 In case you wish to credit other contributors to the dataset, you can use the prov:qualifiedAttribution property. This could be useful if you wish to indicate, for example, the funding organisation(s), collaborating organisation(s) or name specific individuals (e.g., principal investigator) involved in creating or managing the dataset.</t>
         </is>
       </c>
-      <c r="F11" s="227" t="inlineStr">
+      <c r="F11" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -23002,37 +23002,37 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H11" s="227" t="inlineStr">
+      <c r="H11" s="231" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I11" s="218" t="inlineStr">
+      <c r="I11" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J11" s="232" t="inlineStr">
+      <c r="J11" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K11" s="228" t="inlineStr">
+      <c r="K11" s="232" t="inlineStr">
         <is>
           <t>custom:creator_</t>
         </is>
       </c>
-      <c r="L11" s="218" t="inlineStr">
+      <c r="L11" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M11" s="218" t="inlineStr">
+      <c r="M11" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N11" s="218" t="inlineStr">
+      <c r="N11" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -23052,12 +23052,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V11" s="220" t="n"/>
-      <c r="W11" s="220" t="n"/>
-      <c r="X11" s="220" t="n"/>
+      <c r="V11" s="226" t="n"/>
+      <c r="W11" s="226" t="n"/>
+      <c r="X11" s="226" t="n"/>
     </row>
     <row r="12" ht="64" customHeight="1">
-      <c r="A12" s="230" t="inlineStr">
+      <c r="A12" s="220" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -23067,7 +23067,7 @@
           <t>An account of the resource.</t>
         </is>
       </c>
-      <c r="C12" s="230" t="inlineStr">
+      <c r="C12" s="220" t="inlineStr">
         <is>
           <t>dct:description</t>
         </is>
@@ -23082,27 +23082,27 @@
           <t>Brief description of the dataset. You can repeat this property in multiple languages. Example: ‘Collection of physiological data of Healthy Brain Study participants. This collection includes measurements via biowearables for heart rate, oxygenation, systolic and diastolic measures and stress levels.’</t>
         </is>
       </c>
-      <c r="F12" s="225" t="inlineStr">
+      <c r="F12" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G12" s="225" t="inlineStr">
+      <c r="G12" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H12" s="225" t="inlineStr">
+      <c r="H12" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I12" s="232" t="inlineStr">
+      <c r="I12" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J12" s="232" t="inlineStr">
+      <c r="J12" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23112,7 +23112,7 @@
           <t>notes</t>
         </is>
       </c>
-      <c r="L12" s="232" t="n"/>
+      <c r="L12" s="224" t="n"/>
       <c r="P12" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23126,22 +23126,22 @@
       <c r="T12" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V12" s="230" t="n"/>
-      <c r="W12" s="230" t="n"/>
-      <c r="X12" s="230" t="n"/>
+      <c r="V12" s="220" t="n"/>
+      <c r="W12" s="220" t="n"/>
+      <c r="X12" s="220" t="n"/>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="220" t="inlineStr">
+      <c r="A13" s="226" t="inlineStr">
         <is>
           <t>distribution</t>
         </is>
       </c>
-      <c r="B13" s="226" t="inlineStr">
+      <c r="B13" s="230" t="inlineStr">
         <is>
           <t>An available Distribution for the Dataset.</t>
         </is>
       </c>
-      <c r="C13" s="220" t="inlineStr">
+      <c r="C13" s="226" t="inlineStr">
         <is>
           <t>dcat:distribution</t>
         </is>
@@ -23156,7 +23156,7 @@
           <t>Metadata element used as a key link to the class Distribution.</t>
         </is>
       </c>
-      <c r="F13" s="227" t="inlineStr">
+      <c r="F13" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23166,43 +23166,43 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H13" s="227" t="inlineStr">
+      <c r="H13" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I13" s="218" t="inlineStr">
+      <c r="I13" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J13" s="218" t="inlineStr">
+      <c r="J13" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K13" s="228" t="n"/>
-      <c r="L13" s="218" t="inlineStr">
+      <c r="K13" s="232" t="n"/>
+      <c r="L13" s="225" t="inlineStr">
         <is>
           <t>Enter the URI for dcat:Distribution.</t>
         </is>
       </c>
-      <c r="M13" s="218" t="inlineStr">
+      <c r="M13" s="225" t="inlineStr">
         <is>
           <t>Enter the URI for dcat:Distribution.</t>
         </is>
       </c>
-      <c r="N13" s="218" t="inlineStr">
+      <c r="N13" s="225" t="inlineStr">
         <is>
           <t>Enter the URI for dcat:Distribution.</t>
         </is>
       </c>
-      <c r="O13" s="224" t="inlineStr">
+      <c r="O13" s="229" t="inlineStr">
         <is>
           <t>hrishapes:DistributionShape</t>
         </is>
       </c>
-      <c r="P13" s="224" t="inlineStr">
+      <c r="P13" s="229" t="inlineStr">
         <is>
           <t>dash:DetailsViewer</t>
         </is>
@@ -23212,14 +23212,14 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="S13" s="224" t="n"/>
-      <c r="T13" s="224" t="n"/>
-      <c r="V13" s="220" t="n"/>
-      <c r="W13" s="220" t="n"/>
-      <c r="X13" s="220" t="n"/>
+      <c r="S13" s="229" t="n"/>
+      <c r="T13" s="229" t="n"/>
+      <c r="V13" s="226" t="n"/>
+      <c r="W13" s="226" t="n"/>
+      <c r="X13" s="226" t="n"/>
     </row>
     <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="230" t="inlineStr">
+      <c r="A14" s="220" t="inlineStr">
         <is>
           <t>documentation</t>
         </is>
@@ -23229,7 +23229,7 @@
           <t>A page or document about this thing.</t>
         </is>
       </c>
-      <c r="C14" s="230" t="inlineStr">
+      <c r="C14" s="220" t="inlineStr">
         <is>
           <t>foaf:page</t>
         </is>
@@ -23244,27 +23244,27 @@
           <t>The value of this property is the IRI pointing to the web page or document about the dataset.</t>
         </is>
       </c>
-      <c r="F14" s="225" t="inlineStr">
+      <c r="F14" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G14" s="225" t="inlineStr">
+      <c r="G14" s="218" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H14" s="225" t="inlineStr">
+      <c r="H14" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I14" s="232" t="inlineStr">
+      <c r="I14" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J14" s="232" t="inlineStr">
+      <c r="J14" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23274,7 +23274,7 @@
           <t>custom:documentation</t>
         </is>
       </c>
-      <c r="L14" s="232" t="n"/>
+      <c r="L14" s="224" t="n"/>
       <c r="P14" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23285,22 +23285,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V14" s="230" t="n"/>
-      <c r="W14" s="230" t="n"/>
-      <c r="X14" s="230" t="n"/>
+      <c r="V14" s="220" t="n"/>
+      <c r="W14" s="220" t="n"/>
+      <c r="X14" s="220" t="n"/>
     </row>
     <row r="15" ht="160" customHeight="1">
-      <c r="A15" s="220" t="inlineStr">
+      <c r="A15" s="226" t="inlineStr">
         <is>
           <t>domain of the data</t>
         </is>
       </c>
-      <c r="B15" s="226" t="inlineStr">
+      <c r="B15" s="230" t="inlineStr">
         <is>
           <t>In this context, the definition should be considered as: The data domain(s) present in the Dataset.</t>
         </is>
       </c>
-      <c r="C15" s="220" t="inlineStr">
+      <c r="C15" s="226" t="inlineStr">
         <is>
           <t>edam:has_topic</t>
         </is>
@@ -23310,7 +23310,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E15" s="226" t="inlineStr">
+      <c r="E15" s="230" t="inlineStr">
         <is>
           <t>Select data domain(s) from the predefined value list, available at this link: https://github.com/Health-RI/health-ri-metadata/blob/v2.1-changes/Formalisation(shacl)/Core/ValueLists/edam-has-topic.tsv
 Note: This is a temporary location and it will change with the release. 
@@ -23318,31 +23318,31 @@
 See the property "measurement technique" for more information about the technique(s) used to generate the data in the Dataset.</t>
         </is>
       </c>
-      <c r="F15" s="225" t="inlineStr">
+      <c r="F15" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G15" s="227" t="inlineStr">
+      <c r="G15" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H15" s="227" t="inlineStr">
+      <c r="H15" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I15" s="218" t="inlineStr">
+      <c r="I15" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J15" s="218" t="n"/>
-      <c r="K15" s="228" t="n"/>
-      <c r="L15" s="218" t="n"/>
-      <c r="M15" s="218" t="n"/>
-      <c r="N15" s="218" t="n"/>
+      <c r="J15" s="225" t="n"/>
+      <c r="K15" s="232" t="n"/>
+      <c r="L15" s="225" t="n"/>
+      <c r="M15" s="225" t="n"/>
+      <c r="N15" s="225" t="n"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23353,12 +23353,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V15" s="220" t="n"/>
-      <c r="W15" s="220" t="n"/>
-      <c r="X15" s="220" t="n"/>
+      <c r="V15" s="226" t="n"/>
+      <c r="W15" s="226" t="n"/>
+      <c r="X15" s="226" t="n"/>
     </row>
     <row r="16" ht="69.75" customHeight="1">
-      <c r="A16" s="230" t="inlineStr">
+      <c r="A16" s="220" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
@@ -23368,7 +23368,7 @@
           <t>The frequency with which items are added to a collection.</t>
         </is>
       </c>
-      <c r="C16" s="230" t="inlineStr">
+      <c r="C16" s="220" t="inlineStr">
         <is>
           <t>dct:accrualPeriodicity</t>
         </is>
@@ -23378,33 +23378,33 @@
           <t>http://publications.europa.eu/resource/authority/frequency</t>
         </is>
       </c>
-      <c r="E16" s="231" t="inlineStr">
+      <c r="E16" s="223" t="inlineStr">
         <is>
           <t>The value of this property should be the IRI from the listed controlled vocabulary indicating the frequency at which the dataset is updated.
 For example: http://publications.europa.eu/resource/authority/frequency/WEEKLY</t>
         </is>
       </c>
-      <c r="F16" s="227" t="inlineStr">
+      <c r="F16" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G16" s="225" t="inlineStr">
+      <c r="G16" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H16" s="225" t="inlineStr">
+      <c r="H16" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I16" s="232" t="inlineStr">
+      <c r="I16" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J16" s="232" t="inlineStr">
+      <c r="J16" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23415,8 +23415,8 @@
         </is>
       </c>
       <c r="L16" s="107" t="n"/>
-      <c r="M16" s="232" t="n"/>
-      <c r="N16" s="232" t="n"/>
+      <c r="M16" s="224" t="n"/>
+      <c r="N16" s="224" t="n"/>
       <c r="P16" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23427,22 +23427,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V16" s="230" t="n"/>
-      <c r="W16" s="230" t="n"/>
-      <c r="X16" s="230" t="n"/>
+      <c r="V16" s="220" t="n"/>
+      <c r="W16" s="220" t="n"/>
+      <c r="X16" s="220" t="n"/>
     </row>
     <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="220" t="inlineStr">
+      <c r="A17" s="226" t="inlineStr">
         <is>
           <t>geographical coverage</t>
         </is>
       </c>
-      <c r="B17" s="226" t="inlineStr">
+      <c r="B17" s="230" t="inlineStr">
         <is>
           <t>Spatial characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C17" s="220" t="inlineStr">
+      <c r="C17" s="226" t="inlineStr">
         <is>
           <t>dct:spatial</t>
         </is>
@@ -23452,40 +23452,40 @@
           <t>EU Vocabularies Continents Named Authority List</t>
         </is>
       </c>
-      <c r="E17" s="222" t="inlineStr">
+      <c r="E17" s="227" t="inlineStr">
         <is>
           <t>The EU Vocabularies Named Authority Lists must be used for continents, countries and places that are in those lists; if a particular location is not in one of the mentioned Named Authority Lists, GeoNames URIs must be used. For districts or neighbourhoods in NL, the Dutch vocabulary can be used. However, it might in many cases be desirable to keep the geographical coverage broader (e.g. indicating that NL is covered), to avoid exposing detailed information about subjects' locations.</t>
         </is>
       </c>
-      <c r="F17" s="225" t="inlineStr">
+      <c r="F17" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G17" s="227" t="inlineStr">
+      <c r="G17" s="231" t="inlineStr">
         <is>
           <t>dct:Location (IRI)</t>
         </is>
       </c>
-      <c r="H17" s="227" t="inlineStr">
+      <c r="H17" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I17" s="218" t="inlineStr">
+      <c r="I17" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J17" s="218" t="inlineStr">
+      <c r="J17" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K17" s="228" t="n"/>
-      <c r="L17" s="218" t="n"/>
-      <c r="M17" s="224" t="n"/>
-      <c r="N17" s="224" t="n"/>
+      <c r="K17" s="232" t="n"/>
+      <c r="L17" s="225" t="n"/>
+      <c r="M17" s="229" t="n"/>
+      <c r="N17" s="229" t="n"/>
       <c r="P17" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23496,9 +23496,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V17" s="220" t="n"/>
-      <c r="W17" s="220" t="n"/>
-      <c r="X17" s="220" t="n"/>
+      <c r="V17" s="226" t="n"/>
+      <c r="W17" s="226" t="n"/>
+      <c r="X17" s="226" t="n"/>
     </row>
     <row r="18" ht="32" customHeight="1">
       <c r="D18" s="179" t="inlineStr">
@@ -23529,7 +23529,7 @@
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="230" t="inlineStr">
+      <c r="A22" s="220" t="inlineStr">
         <is>
           <t>has version</t>
         </is>
@@ -23539,7 +23539,7 @@
           <t>This resource has a more specific, versioned resource.</t>
         </is>
       </c>
-      <c r="C22" s="230" t="inlineStr">
+      <c r="C22" s="220" t="inlineStr">
         <is>
           <t>dcat:hasVersion</t>
         </is>
@@ -23549,12 +23549,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E22" s="231" t="inlineStr">
+      <c r="E22" s="223" t="inlineStr">
         <is>
           <t>Indicate the dataset that is another version of the current dataset.</t>
         </is>
       </c>
-      <c r="F22" s="227" t="inlineStr">
+      <c r="F22" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23564,17 +23564,17 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H22" s="225" t="inlineStr">
+      <c r="H22" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I22" s="232" t="inlineStr">
+      <c r="I22" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J22" s="232" t="inlineStr">
+      <c r="J22" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23589,8 +23589,8 @@
           <t>Enter the URI for the dcat:Dataset that is another version of the current Dataset.</t>
         </is>
       </c>
-      <c r="M22" s="232" t="n"/>
-      <c r="N22" s="232" t="n"/>
+      <c r="M22" s="224" t="n"/>
+      <c r="N22" s="224" t="n"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -23606,23 +23606,23 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V22" s="230" t="n"/>
-      <c r="W22" s="230" t="n"/>
-      <c r="X22" s="230" t="n"/>
+      <c r="V22" s="220" t="n"/>
+      <c r="W22" s="220" t="n"/>
+      <c r="X22" s="220" t="n"/>
     </row>
     <row r="23" ht="124" customHeight="1">
-      <c r="A23" s="220" t="inlineStr">
+      <c r="A23" s="226" t="inlineStr">
         <is>
           <t>health condition of interest</t>
         </is>
       </c>
-      <c r="B23" s="226" t="inlineStr">
+      <c r="B23" s="230" t="inlineStr">
         <is>
           <t xml:space="preserve">	
 Relates a dataset to a SNOMED CT, ICD-10, ICD-11, or ORPHAcode concept representing a disease, disorder, or other clinical condition that the dataset concerns as a whole.</t>
         </is>
       </c>
-      <c r="C23" s="220" t="inlineStr">
+      <c r="C23" s="226" t="inlineStr">
         <is>
           <t>hri:healthConditionOfInterest</t>
         </is>
@@ -23632,38 +23632,38 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E23" s="222" t="inlineStr">
+      <c r="E23" s="227" t="inlineStr">
         <is>
           <t xml:space="preserve">	
 Use this property to describe health conditions of interest in dataset-level metadata. Multiple values may be provided. Select only SNOMED CT, ICD-10, ICD-11, or ORPHAcode concepts that represent diseases, disorders, or other clinical conditions. The relation does not assert that any individual participant has been diagnosed with a condition and is not intended to enumerate diagnoses in individual records.
 Example: A Dataset concerning myocardial infarction can use http://snomed.info/id/22298006.</t>
         </is>
       </c>
-      <c r="F23" s="225" t="inlineStr">
+      <c r="F23" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G23" s="227" t="inlineStr">
+      <c r="G23" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H23" s="227" t="inlineStr">
+      <c r="H23" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I23" s="218" t="inlineStr">
+      <c r="I23" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J23" s="218" t="n"/>
+      <c r="J23" s="225" t="n"/>
       <c r="K23" s="170" t="n"/>
       <c r="L23" s="100" t="n"/>
-      <c r="M23" s="218" t="n"/>
-      <c r="N23" s="218" t="n"/>
+      <c r="M23" s="225" t="n"/>
+      <c r="N23" s="225" t="n"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -23679,12 +23679,12 @@
           <t>^(http://snomed[.]info/id/[0-9]+|http://id[.]who[.]int/icd/entity/[0-9]+|http://id[.]who[.]int/icd/release/10/([0-9]{4}/)?[A-Za-z0-9][A-Za-z0-9.-]* |http://id[.]who[.]int/icd/release/11/.+ |http://www[.]orpha[.]net/ORDO/Orphanet_[0-9]+)$</t>
         </is>
       </c>
-      <c r="V23" s="220" t="n"/>
-      <c r="W23" s="220" t="n"/>
-      <c r="X23" s="220" t="n"/>
+      <c r="V23" s="226" t="n"/>
+      <c r="W23" s="226" t="n"/>
+      <c r="X23" s="226" t="n"/>
     </row>
     <row r="24" ht="96" customHeight="1">
-      <c r="A24" s="230" t="inlineStr">
+      <c r="A24" s="220" t="inlineStr">
         <is>
           <t>health theme</t>
         </is>
@@ -23694,7 +23694,7 @@
           <t>A category of the Dataset or tag describing the Dataset.</t>
         </is>
       </c>
-      <c r="C24" s="230" t="inlineStr">
+      <c r="C24" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:healthTheme</t>
         </is>
@@ -23710,27 +23710,27 @@
 This property is a structured way to tag the dataset with different health themes. This could include, for example, the specific disease the dataset is about. More details can be provided, if desirable, in the keywords property.  The Wikidata URI of the health theme must be used here.</t>
         </is>
       </c>
-      <c r="F24" s="225" t="inlineStr">
+      <c r="F24" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G24" s="225" t="inlineStr">
+      <c r="G24" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H24" s="225" t="inlineStr">
+      <c r="H24" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I24" s="232" t="inlineStr">
+      <c r="I24" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J24" s="232" t="inlineStr">
+      <c r="J24" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -23740,7 +23740,7 @@
           <t>custom:health_theme</t>
         </is>
       </c>
-      <c r="L24" s="232" t="n"/>
+      <c r="L24" s="224" t="n"/>
       <c r="P24" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23751,22 +23751,22 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V24" s="230" t="n"/>
-      <c r="W24" s="230" t="n"/>
-      <c r="X24" s="230" t="n"/>
+      <c r="V24" s="220" t="n"/>
+      <c r="W24" s="220" t="n"/>
+      <c r="X24" s="220" t="n"/>
     </row>
     <row r="25" ht="96" customHeight="1">
-      <c r="A25" s="220" t="inlineStr">
+      <c r="A25" s="226" t="inlineStr">
         <is>
           <t>identifier</t>
         </is>
       </c>
-      <c r="B25" s="226" t="inlineStr">
+      <c r="B25" s="230" t="inlineStr">
         <is>
           <t>An unambiguous reference to the resource within a given context.</t>
         </is>
       </c>
-      <c r="C25" s="220" t="inlineStr">
+      <c r="C25" s="226" t="inlineStr">
         <is>
           <t>dct:identifier</t>
         </is>
@@ -23782,37 +23782,37 @@
 If your data is published in a repository, enter the provided DOI (Example: https://doi.org/10.34894/ZLOYOJ). If not, use the identifier of the dataset as generated in the FAIR data point (FDP). Ensure that metadata is updated if your situation changes.</t>
         </is>
       </c>
-      <c r="F25" s="227" t="inlineStr">
+      <c r="F25" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G25" s="227" t="inlineStr">
+      <c r="G25" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H25" s="227" t="n">
+      <c r="H25" s="231" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="218" t="inlineStr">
+      <c r="I25" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J25" s="218" t="inlineStr">
+      <c r="J25" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K25" s="228" t="inlineStr">
+      <c r="K25" s="232" t="inlineStr">
         <is>
           <t>custom:alternate_identifier</t>
         </is>
       </c>
-      <c r="L25" s="218" t="n"/>
-      <c r="M25" s="218" t="n"/>
-      <c r="N25" s="218" t="n"/>
+      <c r="L25" s="225" t="n"/>
+      <c r="M25" s="225" t="n"/>
+      <c r="N25" s="225" t="n"/>
       <c r="P25" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -23823,12 +23823,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V25" s="220" t="n"/>
-      <c r="W25" s="220" t="n"/>
-      <c r="X25" s="220" t="n"/>
+      <c r="V25" s="226" t="n"/>
+      <c r="W25" s="226" t="n"/>
+      <c r="X25" s="226" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="230" t="inlineStr">
+      <c r="A26" s="220" t="inlineStr">
         <is>
           <t>in series</t>
         </is>
@@ -23838,7 +23838,7 @@
           <t>A dataset series of which the dataset is part.</t>
         </is>
       </c>
-      <c r="C26" s="230" t="inlineStr">
+      <c r="C26" s="220" t="inlineStr">
         <is>
           <t>dcat:inSeries</t>
         </is>
@@ -23853,7 +23853,7 @@
           <t xml:space="preserve">This property points to the Dataset Series of which the Dataset is part. </t>
         </is>
       </c>
-      <c r="F26" s="225" t="inlineStr">
+      <c r="F26" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -23863,17 +23863,17 @@
           <t>dcat:DatasetSeries</t>
         </is>
       </c>
-      <c r="H26" s="225" t="inlineStr">
+      <c r="H26" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I26" s="232" t="inlineStr">
+      <c r="I26" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J26" s="232" t="inlineStr">
+      <c r="J26" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23904,22 +23904,22 @@
           <t>Dataset Series</t>
         </is>
       </c>
-      <c r="V26" s="230" t="n"/>
-      <c r="W26" s="230" t="n"/>
-      <c r="X26" s="230" t="n"/>
+      <c r="V26" s="220" t="n"/>
+      <c r="W26" s="220" t="n"/>
+      <c r="X26" s="220" t="n"/>
     </row>
     <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="220" t="inlineStr">
+      <c r="A27" s="226" t="inlineStr">
         <is>
           <t>is referenced by</t>
         </is>
       </c>
-      <c r="B27" s="226" t="inlineStr">
+      <c r="B27" s="230" t="inlineStr">
         <is>
           <t>A related resource that references, cites, or otherwise points to the described resource.</t>
         </is>
       </c>
-      <c r="C27" s="220" t="inlineStr">
+      <c r="C27" s="226" t="inlineStr">
         <is>
           <t>dct:isReferencedBy</t>
         </is>
@@ -23929,33 +23929,33 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E27" s="226" t="inlineStr">
+      <c r="E27" s="230" t="inlineStr">
         <is>
           <t>The value of this property is the IRI of the DOI for the publication or other related resource.
 For example: https://doi.org/10.1186/s13690-021-00709-x</t>
         </is>
       </c>
-      <c r="F27" s="227" t="inlineStr">
+      <c r="F27" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G27" s="227" t="inlineStr">
+      <c r="G27" s="231" t="inlineStr">
         <is>
           <t>rdfs:Resource (IRI)</t>
         </is>
       </c>
-      <c r="H27" s="227" t="inlineStr">
+      <c r="H27" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I27" s="218" t="inlineStr">
+      <c r="I27" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J27" s="218" t="inlineStr">
+      <c r="J27" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -23965,9 +23965,9 @@
           <t>custom:is_referenced_by</t>
         </is>
       </c>
-      <c r="L27" s="218" t="n"/>
-      <c r="M27" s="218" t="n"/>
-      <c r="N27" s="218" t="n"/>
+      <c r="L27" s="225" t="n"/>
+      <c r="M27" s="225" t="n"/>
+      <c r="N27" s="225" t="n"/>
       <c r="P27" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -23978,12 +23978,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V27" s="220" t="n"/>
-      <c r="W27" s="220" t="n"/>
-      <c r="X27" s="220" t="n"/>
+      <c r="V27" s="226" t="n"/>
+      <c r="W27" s="226" t="n"/>
+      <c r="X27" s="226" t="n"/>
     </row>
     <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="230" t="inlineStr">
+      <c r="A28" s="220" t="inlineStr">
         <is>
           <t>keyword</t>
         </is>
@@ -24008,27 +24008,27 @@
           <t>Add keywords to increase dataset discoverability. You can include keywords in different languages, submitting each keyword as a separate entry. Example: Physiological measures, Heart Rate, Stress Measures.</t>
         </is>
       </c>
-      <c r="F28" s="225" t="inlineStr">
+      <c r="F28" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G28" s="225" t="inlineStr">
+      <c r="G28" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H28" s="225" t="inlineStr">
+      <c r="H28" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I28" s="232" t="inlineStr">
+      <c r="I28" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J28" s="232" t="inlineStr">
+      <c r="J28" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24038,7 +24038,7 @@
           <t>tags</t>
         </is>
       </c>
-      <c r="L28" s="232" t="n"/>
+      <c r="L28" s="224" t="n"/>
       <c r="P28" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24049,17 +24049,17 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V28" s="230" t="n"/>
-      <c r="W28" s="230" t="n"/>
-      <c r="X28" s="230" t="n"/>
+      <c r="V28" s="220" t="n"/>
+      <c r="W28" s="220" t="n"/>
+      <c r="X28" s="220" t="n"/>
     </row>
     <row r="29" ht="128" customHeight="1">
-      <c r="A29" s="220" t="inlineStr">
+      <c r="A29" s="226" t="inlineStr">
         <is>
           <t>landing page</t>
         </is>
       </c>
-      <c r="B29" s="226" t="inlineStr">
+      <c r="B29" s="230" t="inlineStr">
         <is>
           <t>A web page that provides access to the Dataset, its Distributions and/or additional information.</t>
         </is>
@@ -24080,35 +24080,35 @@
 Example: For an EGA Dataset, dcat:landingPage points to the corresponding human-readable EGA Dataset page, like https://ega-archive.org/datasets/EGAD00001005083.</t>
         </is>
       </c>
-      <c r="F29" s="225" t="inlineStr">
+      <c r="F29" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G29" s="227" t="inlineStr">
+      <c r="G29" s="231" t="inlineStr">
         <is>
           <t>foaf:Document (IRI)</t>
         </is>
       </c>
-      <c r="H29" s="227" t="inlineStr">
+      <c r="H29" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I29" s="218" t="inlineStr">
+      <c r="I29" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J29" s="218" t="inlineStr">
+      <c r="J29" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K29" s="228" t="n"/>
-      <c r="L29" s="218" t="n"/>
-      <c r="M29" s="224" t="n"/>
-      <c r="N29" s="224" t="n"/>
+      <c r="K29" s="232" t="n"/>
+      <c r="L29" s="225" t="n"/>
+      <c r="M29" s="229" t="n"/>
+      <c r="N29" s="229" t="n"/>
       <c r="P29" s="219" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -24119,12 +24119,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V29" s="220" t="n"/>
-      <c r="W29" s="220" t="n"/>
-      <c r="X29" s="220" t="n"/>
+      <c r="V29" s="226" t="n"/>
+      <c r="W29" s="226" t="n"/>
+      <c r="X29" s="226" t="n"/>
     </row>
     <row r="30" ht="48" customHeight="1">
-      <c r="A30" s="230" t="inlineStr">
+      <c r="A30" s="220" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -24149,27 +24149,27 @@
           <t xml:space="preserve">The language of the Dataset. For this property, the values from the EU Vocabularies Languages Named Authority List must be used. If your Dataset contains multiple languages, this property can be repeated. </t>
         </is>
       </c>
-      <c r="F30" s="227" t="inlineStr">
+      <c r="F30" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G30" s="225" t="inlineStr">
+      <c r="G30" s="218" t="inlineStr">
         <is>
           <t>dct:LinguisticSystem (IRI)</t>
         </is>
       </c>
-      <c r="H30" s="225" t="inlineStr">
+      <c r="H30" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I30" s="218" t="inlineStr">
+      <c r="I30" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J30" s="218" t="inlineStr">
+      <c r="J30" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24179,9 +24179,9 @@
           <t>custom:language</t>
         </is>
       </c>
-      <c r="L30" s="232" t="n"/>
-      <c r="M30" s="232" t="n"/>
-      <c r="N30" s="232" t="n"/>
+      <c r="L30" s="224" t="n"/>
+      <c r="M30" s="224" t="n"/>
+      <c r="N30" s="224" t="n"/>
       <c r="P30" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24192,17 +24192,17 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V30" s="230" t="n"/>
-      <c r="W30" s="230" t="n"/>
-      <c r="X30" s="230" t="n"/>
+      <c r="V30" s="220" t="n"/>
+      <c r="W30" s="220" t="n"/>
+      <c r="X30" s="220" t="n"/>
     </row>
     <row r="31" ht="160" customHeight="1">
-      <c r="A31" s="220" t="inlineStr">
+      <c r="A31" s="226" t="inlineStr">
         <is>
           <t>legal basis</t>
         </is>
       </c>
-      <c r="B31" s="226" t="inlineStr">
+      <c r="B31" s="230" t="inlineStr">
         <is>
           <t>Indicates use or applicability of a Legal Basis.</t>
         </is>
@@ -24225,39 +24225,39 @@
 An example value for this property could be dpv:Consent.</t>
         </is>
       </c>
-      <c r="F31" s="225" t="inlineStr">
+      <c r="F31" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G31" s="227" t="inlineStr">
+      <c r="G31" s="231" t="inlineStr">
         <is>
           <t>dpv:LegalBasis (IRI)</t>
         </is>
       </c>
-      <c r="H31" s="227" t="inlineStr">
+      <c r="H31" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I31" s="218" t="inlineStr">
+      <c r="I31" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J31" s="218" t="inlineStr">
+      <c r="J31" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K31" s="228" t="inlineStr">
+      <c r="K31" s="232" t="inlineStr">
         <is>
           <t>custom:legal_basis</t>
         </is>
       </c>
-      <c r="L31" s="218" t="n"/>
-      <c r="M31" s="224" t="n"/>
-      <c r="N31" s="224" t="n"/>
+      <c r="L31" s="225" t="n"/>
+      <c r="M31" s="229" t="n"/>
+      <c r="N31" s="229" t="n"/>
       <c r="P31" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24268,12 +24268,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V31" s="220" t="n"/>
-      <c r="W31" s="220" t="n"/>
-      <c r="X31" s="220" t="n"/>
+      <c r="V31" s="226" t="n"/>
+      <c r="W31" s="226" t="n"/>
+      <c r="X31" s="226" t="n"/>
     </row>
     <row r="32" ht="32" customHeight="1">
-      <c r="A32" s="230" t="inlineStr">
+      <c r="A32" s="220" t="inlineStr">
         <is>
           <t>maximum typical age</t>
         </is>
@@ -24283,7 +24283,7 @@
           <t>Maximum typical age of the population within the dataset</t>
         </is>
       </c>
-      <c r="C32" s="230" t="inlineStr">
+      <c r="C32" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:maxTypicalAge</t>
         </is>
@@ -24298,27 +24298,27 @@
           <t>The approximate maximum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F32" s="227" t="inlineStr">
+      <c r="F32" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G32" s="225" t="inlineStr">
+      <c r="G32" s="218" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H32" s="225" t="inlineStr">
+      <c r="H32" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I32" s="232" t="inlineStr">
+      <c r="I32" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J32" s="232" t="inlineStr">
+      <c r="J32" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24328,9 +24328,9 @@
           <t>custom:max_typical_age</t>
         </is>
       </c>
-      <c r="L32" s="232" t="n"/>
-      <c r="M32" s="232" t="n"/>
-      <c r="N32" s="232" t="n"/>
+      <c r="L32" s="224" t="n"/>
+      <c r="M32" s="224" t="n"/>
+      <c r="N32" s="224" t="n"/>
       <c r="P32" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24341,17 +24341,17 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V32" s="230" t="n"/>
-      <c r="W32" s="230" t="n"/>
-      <c r="X32" s="230" t="n"/>
+      <c r="V32" s="220" t="n"/>
+      <c r="W32" s="220" t="n"/>
+      <c r="X32" s="220" t="n"/>
     </row>
     <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="220" t="inlineStr">
+      <c r="A33" s="226" t="inlineStr">
         <is>
           <t>minimum typical age</t>
         </is>
       </c>
-      <c r="B33" s="226" t="inlineStr">
+      <c r="B33" s="230" t="inlineStr">
         <is>
           <t>Minimum typical age of the population within the dataset</t>
         </is>
@@ -24371,39 +24371,39 @@
           <t>The approximate minimum age of subjects in the dataset, if applicable. Approximate age is given to protect potentially sensitive information of subjects in the dataset.</t>
         </is>
       </c>
-      <c r="F33" s="225" t="inlineStr">
+      <c r="F33" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G33" s="227" t="inlineStr">
+      <c r="G33" s="231" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H33" s="227" t="inlineStr">
+      <c r="H33" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I33" s="218" t="inlineStr">
+      <c r="I33" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J33" s="218" t="inlineStr">
+      <c r="J33" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K33" s="228" t="inlineStr">
+      <c r="K33" s="232" t="inlineStr">
         <is>
           <t>custom:min_typical_age</t>
         </is>
       </c>
-      <c r="L33" s="218" t="n"/>
-      <c r="M33" s="224" t="n"/>
-      <c r="N33" s="224" t="n"/>
+      <c r="L33" s="225" t="n"/>
+      <c r="M33" s="229" t="n"/>
+      <c r="N33" s="229" t="n"/>
       <c r="P33" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24414,12 +24414,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V33" s="220" t="n"/>
-      <c r="W33" s="220" t="n"/>
-      <c r="X33" s="220" t="n"/>
+      <c r="V33" s="226" t="n"/>
+      <c r="W33" s="226" t="n"/>
+      <c r="X33" s="226" t="n"/>
     </row>
     <row r="34" ht="209.25" customHeight="1">
-      <c r="A34" s="230" t="inlineStr">
+      <c r="A34" s="220" t="inlineStr">
         <is>
           <t>measurement technique</t>
         </is>
@@ -24446,86 +24446,86 @@
 Note: This is a temporary location and it will change with the next release. </t>
         </is>
       </c>
-      <c r="F34" s="225" t="inlineStr">
+      <c r="F34" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G34" s="225" t="inlineStr">
+      <c r="G34" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H34" s="225" t="inlineStr">
+      <c r="H34" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I34" s="232" t="n"/>
-      <c r="J34" s="232" t="n"/>
+      <c r="I34" s="224" t="n"/>
+      <c r="J34" s="224" t="n"/>
       <c r="K34" s="75" t="n"/>
-      <c r="L34" s="232" t="n"/>
-      <c r="M34" s="232" t="n"/>
-      <c r="N34" s="232" t="n"/>
-      <c r="O34" s="232" t="n"/>
-      <c r="P34" s="232" t="inlineStr">
+      <c r="L34" s="224" t="n"/>
+      <c r="M34" s="224" t="n"/>
+      <c r="N34" s="224" t="n"/>
+      <c r="O34" s="224" t="n"/>
+      <c r="P34" s="224" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
         </is>
       </c>
-      <c r="Q34" s="232" t="inlineStr">
+      <c r="Q34" s="224" t="inlineStr">
         <is>
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="R34" s="232" t="n"/>
-      <c r="S34" s="232" t="n"/>
-      <c r="T34" s="232" t="n"/>
-      <c r="U34" s="232" t="n"/>
-      <c r="V34" s="230" t="n"/>
-      <c r="W34" s="230" t="n"/>
-      <c r="X34" s="230" t="n"/>
-      <c r="Y34" s="232" t="n"/>
-      <c r="Z34" s="232" t="n"/>
-      <c r="AA34" s="232" t="n"/>
-      <c r="AB34" s="232" t="n"/>
-      <c r="AC34" s="232" t="n"/>
-      <c r="AD34" s="232" t="n"/>
-      <c r="AE34" s="232" t="n"/>
-      <c r="AF34" s="232" t="n"/>
-      <c r="AG34" s="232" t="n"/>
-      <c r="AH34" s="232" t="n"/>
-      <c r="AI34" s="232" t="n"/>
-      <c r="AJ34" s="232" t="n"/>
-      <c r="AK34" s="232" t="n"/>
-      <c r="AL34" s="232" t="n"/>
-      <c r="AM34" s="232" t="n"/>
-      <c r="AN34" s="232" t="n"/>
-      <c r="AO34" s="232" t="n"/>
-      <c r="AP34" s="232" t="n"/>
-      <c r="AQ34" s="232" t="n"/>
-      <c r="AR34" s="232" t="n"/>
-      <c r="AS34" s="232" t="n"/>
-      <c r="AT34" s="232" t="n"/>
-      <c r="AU34" s="232" t="n"/>
-      <c r="AV34" s="232" t="n"/>
-      <c r="AW34" s="232" t="n"/>
-      <c r="AX34" s="232" t="n"/>
-      <c r="AY34" s="232" t="n"/>
-      <c r="AZ34" s="232" t="n"/>
+      <c r="R34" s="224" t="n"/>
+      <c r="S34" s="224" t="n"/>
+      <c r="T34" s="224" t="n"/>
+      <c r="U34" s="224" t="n"/>
+      <c r="V34" s="220" t="n"/>
+      <c r="W34" s="220" t="n"/>
+      <c r="X34" s="220" t="n"/>
+      <c r="Y34" s="224" t="n"/>
+      <c r="Z34" s="224" t="n"/>
+      <c r="AA34" s="224" t="n"/>
+      <c r="AB34" s="224" t="n"/>
+      <c r="AC34" s="224" t="n"/>
+      <c r="AD34" s="224" t="n"/>
+      <c r="AE34" s="224" t="n"/>
+      <c r="AF34" s="224" t="n"/>
+      <c r="AG34" s="224" t="n"/>
+      <c r="AH34" s="224" t="n"/>
+      <c r="AI34" s="224" t="n"/>
+      <c r="AJ34" s="224" t="n"/>
+      <c r="AK34" s="224" t="n"/>
+      <c r="AL34" s="224" t="n"/>
+      <c r="AM34" s="224" t="n"/>
+      <c r="AN34" s="224" t="n"/>
+      <c r="AO34" s="224" t="n"/>
+      <c r="AP34" s="224" t="n"/>
+      <c r="AQ34" s="224" t="n"/>
+      <c r="AR34" s="224" t="n"/>
+      <c r="AS34" s="224" t="n"/>
+      <c r="AT34" s="224" t="n"/>
+      <c r="AU34" s="224" t="n"/>
+      <c r="AV34" s="224" t="n"/>
+      <c r="AW34" s="224" t="n"/>
+      <c r="AX34" s="224" t="n"/>
+      <c r="AY34" s="224" t="n"/>
+      <c r="AZ34" s="224" t="n"/>
     </row>
     <row r="35" ht="48" customHeight="1">
-      <c r="A35" s="220" t="inlineStr">
+      <c r="A35" s="226" t="inlineStr">
         <is>
           <t>modification date</t>
         </is>
       </c>
-      <c r="B35" s="226" t="inlineStr">
+      <c r="B35" s="230" t="inlineStr">
         <is>
           <t>Date on which the resource was changed.</t>
         </is>
       </c>
-      <c r="C35" s="220" t="inlineStr">
+      <c r="C35" s="226" t="inlineStr">
         <is>
           <t>dct:modified</t>
         </is>
@@ -24535,44 +24535,44 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E35" s="226" t="inlineStr">
+      <c r="E35" s="230" t="inlineStr">
         <is>
           <t>This property indicates changes to the dataset, not the metadata record. An absent value may mean the resource hasn't changed since publication, the modification date is unknown, or the resource is continuously updated.</t>
         </is>
       </c>
-      <c r="F35" s="227" t="inlineStr">
+      <c r="F35" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G35" s="227" t="inlineStr">
+      <c r="G35" s="231" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H35" s="227" t="inlineStr">
+      <c r="H35" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I35" s="218" t="inlineStr">
+      <c r="I35" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J35" s="218" t="inlineStr">
+      <c r="J35" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K35" s="228" t="inlineStr">
+      <c r="K35" s="232" t="inlineStr">
         <is>
           <t>custom:modified</t>
         </is>
       </c>
-      <c r="L35" s="218" t="n"/>
-      <c r="M35" s="218" t="n"/>
-      <c r="N35" s="218" t="n"/>
+      <c r="L35" s="225" t="n"/>
+      <c r="M35" s="225" t="n"/>
+      <c r="N35" s="225" t="n"/>
       <c r="P35" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24588,12 +24588,12 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="V35" s="220" t="n"/>
-      <c r="W35" s="220" t="n"/>
-      <c r="X35" s="220" t="n"/>
+      <c r="V35" s="226" t="n"/>
+      <c r="W35" s="226" t="n"/>
+      <c r="X35" s="226" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="230" t="inlineStr">
+      <c r="A36" s="220" t="inlineStr">
         <is>
           <t>number of records</t>
         </is>
@@ -24603,7 +24603,7 @@
           <t>Size of the dataset in terms of the number of records</t>
         </is>
       </c>
-      <c r="C36" s="230" t="inlineStr">
+      <c r="C36" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfRecords</t>
         </is>
@@ -24618,27 +24618,27 @@
           <t>Number of records inside a Dataset.</t>
         </is>
       </c>
-      <c r="F36" s="225" t="inlineStr">
+      <c r="F36" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G36" s="225" t="inlineStr">
+      <c r="G36" s="218" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H36" s="225" t="inlineStr">
+      <c r="H36" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I36" s="232" t="inlineStr">
+      <c r="I36" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J36" s="232" t="inlineStr">
+      <c r="J36" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24648,7 +24648,7 @@
           <t>custom:number_of_records</t>
         </is>
       </c>
-      <c r="L36" s="232" t="n"/>
+      <c r="L36" s="224" t="n"/>
       <c r="P36" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24659,22 +24659,22 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V36" s="230" t="n"/>
-      <c r="W36" s="230" t="n"/>
-      <c r="X36" s="230" t="n"/>
+      <c r="V36" s="220" t="n"/>
+      <c r="W36" s="220" t="n"/>
+      <c r="X36" s="220" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="220" t="inlineStr">
+      <c r="A37" s="226" t="inlineStr">
         <is>
           <t>number of unique individuals</t>
         </is>
       </c>
-      <c r="B37" s="226" t="inlineStr">
+      <c r="B37" s="230" t="inlineStr">
         <is>
           <t>Number of records for unique individuals.</t>
         </is>
       </c>
-      <c r="C37" s="220" t="inlineStr">
+      <c r="C37" s="226" t="inlineStr">
         <is>
           <t>healthdcatap:numberOfUniqueIndividuals</t>
         </is>
@@ -24684,44 +24684,44 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E37" s="226" t="inlineStr">
+      <c r="E37" s="230" t="inlineStr">
         <is>
           <t>This property is not mandatory, since not all datasets might include data from individuals.</t>
         </is>
       </c>
-      <c r="F37" s="227" t="inlineStr">
+      <c r="F37" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G37" s="227" t="inlineStr">
+      <c r="G37" s="231" t="inlineStr">
         <is>
           <t>xsd:nonNegativeInteger</t>
         </is>
       </c>
-      <c r="H37" s="227" t="inlineStr">
+      <c r="H37" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I37" s="218" t="inlineStr">
+      <c r="I37" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J37" s="218" t="inlineStr">
+      <c r="J37" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K37" s="228" t="inlineStr">
+      <c r="K37" s="232" t="inlineStr">
         <is>
           <t>custom:number_of_unique_individuals</t>
         </is>
       </c>
-      <c r="L37" s="218" t="n"/>
-      <c r="M37" s="218" t="n"/>
-      <c r="N37" s="218" t="n"/>
+      <c r="L37" s="225" t="n"/>
+      <c r="M37" s="225" t="n"/>
+      <c r="N37" s="225" t="n"/>
       <c r="P37" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24732,12 +24732,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V37" s="220" t="n"/>
-      <c r="W37" s="220" t="n"/>
-      <c r="X37" s="220" t="n"/>
+      <c r="V37" s="226" t="n"/>
+      <c r="W37" s="226" t="n"/>
+      <c r="X37" s="226" t="n"/>
     </row>
     <row r="38" ht="64" customHeight="1">
-      <c r="A38" s="230" t="inlineStr">
+      <c r="A38" s="220" t="inlineStr">
         <is>
           <t>other identifier</t>
         </is>
@@ -24747,7 +24747,7 @@
           <t>Links a resource to an adms:Identifier class.</t>
         </is>
       </c>
-      <c r="C38" s="230" t="inlineStr">
+      <c r="C38" s="220" t="inlineStr">
         <is>
           <t>adms:identifier</t>
         </is>
@@ -24762,27 +24762,27 @@
           <t>Examples of secondary identifiers include MAST/ADS, DataCite, DOI, EZID or W3ID (if not used for the original identifier). This property makes use of another small class: adms:Identifier, where you provide the identifier and the name of the identifier schema (e.g. DOI).</t>
         </is>
       </c>
-      <c r="F38" s="225" t="inlineStr">
+      <c r="F38" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G38" s="225" t="inlineStr">
+      <c r="G38" s="218" t="inlineStr">
         <is>
           <t>adms:Identifier</t>
         </is>
       </c>
-      <c r="H38" s="225" t="inlineStr">
+      <c r="H38" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I38" s="232" t="inlineStr">
+      <c r="I38" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J38" s="232" t="inlineStr">
+      <c r="J38" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -24792,7 +24792,7 @@
           <t>?</t>
         </is>
       </c>
-      <c r="L38" s="232" t="n"/>
+      <c r="L38" s="224" t="n"/>
       <c r="O38" s="219" t="inlineStr">
         <is>
           <t>hrishapes:IdentifierShape</t>
@@ -24808,22 +24808,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V38" s="230" t="n"/>
-      <c r="W38" s="230" t="n"/>
-      <c r="X38" s="230" t="n"/>
+      <c r="V38" s="220" t="n"/>
+      <c r="W38" s="220" t="n"/>
+      <c r="X38" s="220" t="n"/>
     </row>
     <row r="39" ht="64" customHeight="1">
-      <c r="A39" s="220" t="inlineStr">
+      <c r="A39" s="226" t="inlineStr">
         <is>
           <t>personal data</t>
         </is>
       </c>
-      <c r="B39" s="226" t="inlineStr">
+      <c r="B39" s="230" t="inlineStr">
         <is>
           <t>Indicates association with Personal Data.</t>
         </is>
       </c>
-      <c r="C39" s="220" t="inlineStr">
+      <c r="C39" s="226" t="inlineStr">
         <is>
           <t>dpv:hasPersonalData</t>
         </is>
@@ -24833,45 +24833,45 @@
           <t>https://w3c.github.io/dpv/2.0/pd/</t>
         </is>
       </c>
-      <c r="E39" s="222" t="inlineStr">
+      <c r="E39" s="227" t="inlineStr">
         <is>
           <t>The different types of personal information that are collected in the dataset can be indicated with this property. Values can be picked from the DPV taxonomy (see the Controlled vocabulary column).
 For example: dpv-pd:Gender</t>
         </is>
       </c>
-      <c r="F39" s="227" t="inlineStr">
+      <c r="F39" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G39" s="227" t="inlineStr">
+      <c r="G39" s="231" t="inlineStr">
         <is>
           <t>dpv:PersonalData (IRI)</t>
         </is>
       </c>
-      <c r="H39" s="227" t="inlineStr">
+      <c r="H39" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I39" s="218" t="inlineStr">
+      <c r="I39" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J39" s="218" t="inlineStr">
+      <c r="J39" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K39" s="228" t="inlineStr">
+      <c r="K39" s="232" t="inlineStr">
         <is>
           <t>custom:personal_data</t>
         </is>
       </c>
-      <c r="L39" s="218" t="n"/>
-      <c r="M39" s="218" t="n"/>
-      <c r="N39" s="218" t="n"/>
+      <c r="L39" s="225" t="n"/>
+      <c r="M39" s="225" t="n"/>
+      <c r="N39" s="225" t="n"/>
       <c r="P39" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -24882,12 +24882,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V39" s="220" t="n"/>
-      <c r="W39" s="220" t="n"/>
-      <c r="X39" s="220" t="n"/>
+      <c r="V39" s="226" t="n"/>
+      <c r="W39" s="226" t="n"/>
+      <c r="X39" s="226" t="n"/>
     </row>
     <row r="40" ht="59" customHeight="1">
-      <c r="A40" s="230" t="inlineStr">
+      <c r="A40" s="220" t="inlineStr">
         <is>
           <t>population coverage</t>
         </is>
@@ -24897,7 +24897,7 @@
           <t>A definition of the population within the dataset</t>
         </is>
       </c>
-      <c r="C40" s="230" t="inlineStr">
+      <c r="C40" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:populationCoverage</t>
         </is>
@@ -24912,27 +24912,27 @@
           <t>This field is a free-text description of the population covered in the dataset. For example, "Adults aged 18–65 diagnosed with type 2 diabetes in the Netherlands between 2015 and 2020".</t>
         </is>
       </c>
-      <c r="F40" s="225" t="inlineStr">
+      <c r="F40" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G40" s="225" t="inlineStr">
+      <c r="G40" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H40" s="225" t="inlineStr">
+      <c r="H40" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I40" s="232" t="inlineStr">
+      <c r="I40" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J40" s="232" t="inlineStr">
+      <c r="J40" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -24942,7 +24942,7 @@
           <t>custom:populatiion_coverage</t>
         </is>
       </c>
-      <c r="L40" s="232" t="n"/>
+      <c r="L40" s="224" t="n"/>
       <c r="P40" s="69" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -24953,22 +24953,22 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V40" s="230" t="n"/>
-      <c r="W40" s="230" t="n"/>
-      <c r="X40" s="230" t="n"/>
+      <c r="V40" s="220" t="n"/>
+      <c r="W40" s="220" t="n"/>
+      <c r="X40" s="220" t="n"/>
     </row>
     <row r="41" ht="92" customHeight="1">
-      <c r="A41" s="220" t="inlineStr">
+      <c r="A41" s="226" t="inlineStr">
         <is>
           <t>provenance</t>
         </is>
       </c>
-      <c r="B41" s="226" t="inlineStr">
+      <c r="B41" s="230" t="inlineStr">
         <is>
           <t>A statement about the lineage of a Dataset.</t>
         </is>
       </c>
-      <c r="C41" s="220" t="inlineStr">
+      <c r="C41" s="226" t="inlineStr">
         <is>
           <t>dct:provenance</t>
         </is>
@@ -24984,7 +24984,7 @@
 This is where the collection-method statements not captured by dedicated properties can be listed.</t>
         </is>
       </c>
-      <c r="F41" s="225" t="inlineStr">
+      <c r="F41" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -24994,33 +24994,33 @@
           <t>dct:ProvenanceStatement</t>
         </is>
       </c>
-      <c r="H41" s="227" t="inlineStr">
+      <c r="H41" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I41" s="218" t="inlineStr">
+      <c r="I41" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J41" s="218" t="inlineStr">
+      <c r="J41" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K41" s="228" t="n"/>
-      <c r="L41" s="218" t="inlineStr">
+      <c r="K41" s="232" t="n"/>
+      <c r="L41" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'ProvenanceStatement' tab.</t>
         </is>
       </c>
-      <c r="M41" s="218" t="inlineStr">
+      <c r="M41" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'ProvenanceStatement' tab.</t>
         </is>
       </c>
-      <c r="N41" s="218" t="inlineStr">
+      <c r="N41" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'ProvenanceStatement' tab.</t>
         </is>
@@ -25040,12 +25040,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V41" s="220" t="n"/>
-      <c r="W41" s="220" t="n"/>
-      <c r="X41" s="220" t="n"/>
+      <c r="V41" s="226" t="n"/>
+      <c r="W41" s="226" t="n"/>
+      <c r="X41" s="226" t="n"/>
     </row>
     <row r="42" ht="112" customHeight="1">
-      <c r="A42" s="230" t="inlineStr">
+      <c r="A42" s="220" t="inlineStr">
         <is>
           <t>publisher</t>
         </is>
@@ -25055,7 +25055,7 @@
           <t>An entity responsible for making the resource available.</t>
         </is>
       </c>
-      <c r="C42" s="230" t="inlineStr">
+      <c r="C42" s="220" t="inlineStr">
         <is>
           <t>dct:publisher</t>
         </is>
@@ -25065,12 +25065,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E42" s="231" t="inlineStr">
+      <c r="E42" s="223" t="inlineStr">
         <is>
           <t>This property identifies the organisation or individual responsible for making the dataset available. For datasets, this is typically the employer of the data creators. In simple cases, the dataset publisher may be the same as the catalogue publisher. In more complex settings, such as when datasets come from multiple institutions within a consortium, the consortium should be listed as the publisher where possible. If no formal consortium can be specified, provide information about the contributing organisations or individuals under dct:creator instead. For more details, refer to the Agent class.</t>
         </is>
       </c>
-      <c r="F42" s="227" t="inlineStr">
+      <c r="F42" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
@@ -25080,15 +25080,15 @@
           <t>foaf:Agent</t>
         </is>
       </c>
-      <c r="H42" s="225" t="n">
+      <c r="H42" s="218" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="232" t="inlineStr">
+      <c r="I42" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J42" s="232" t="inlineStr">
+      <c r="J42" s="224" t="inlineStr">
         <is>
           <t>Health and NL</t>
         </is>
@@ -25098,17 +25098,17 @@
           <t>custom:publisher</t>
         </is>
       </c>
-      <c r="L42" s="232" t="inlineStr">
+      <c r="L42" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="M42" s="232" t="inlineStr">
+      <c r="M42" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
       </c>
-      <c r="N42" s="232" t="inlineStr">
+      <c r="N42" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Agent' tab.</t>
         </is>
@@ -25128,22 +25128,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V42" s="230" t="n"/>
-      <c r="W42" s="230" t="n"/>
-      <c r="X42" s="230" t="n"/>
+      <c r="V42" s="220" t="n"/>
+      <c r="W42" s="220" t="n"/>
+      <c r="X42" s="220" t="n"/>
     </row>
     <row r="43" ht="48" customHeight="1">
-      <c r="A43" s="220" t="inlineStr">
+      <c r="A43" s="226" t="inlineStr">
         <is>
           <t>purpose</t>
         </is>
       </c>
-      <c r="B43" s="226" t="inlineStr">
+      <c r="B43" s="230" t="inlineStr">
         <is>
           <t>Indicates association with Purpose.</t>
         </is>
       </c>
-      <c r="C43" s="220" t="inlineStr">
+      <c r="C43" s="226" t="inlineStr">
         <is>
           <t>dpv:hasPurpose</t>
         </is>
@@ -25153,45 +25153,45 @@
           <t>https://w3c.github.io/dpv/2.1/dpv/#vocab-purposes</t>
         </is>
       </c>
-      <c r="E43" s="222" t="inlineStr">
+      <c r="E43" s="227" t="inlineStr">
         <is>
           <t>One or more categories or sub-categories of purposes can be chosen from the taxonomy provided by dpv (see the Controlled vocabulary column). Try to be as specific as possible.
 An example value could be dpv:ResearchAndDevelopment.</t>
         </is>
       </c>
-      <c r="F43" s="225" t="inlineStr">
+      <c r="F43" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G43" s="227" t="inlineStr">
+      <c r="G43" s="231" t="inlineStr">
         <is>
           <t>dpv:Purpose (IRI)</t>
         </is>
       </c>
-      <c r="H43" s="227" t="inlineStr">
+      <c r="H43" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I43" s="218" t="inlineStr">
+      <c r="I43" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J43" s="218" t="inlineStr">
+      <c r="J43" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K43" s="228" t="inlineStr">
+      <c r="K43" s="232" t="inlineStr">
         <is>
           <t>custom:purpose</t>
         </is>
       </c>
-      <c r="L43" s="218" t="n"/>
-      <c r="M43" s="224" t="n"/>
-      <c r="N43" s="224" t="n"/>
+      <c r="L43" s="225" t="n"/>
+      <c r="M43" s="229" t="n"/>
+      <c r="N43" s="229" t="n"/>
       <c r="P43" s="219" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -25202,12 +25202,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V43" s="220" t="n"/>
-      <c r="W43" s="220" t="n"/>
-      <c r="X43" s="220" t="n"/>
+      <c r="V43" s="226" t="n"/>
+      <c r="W43" s="226" t="n"/>
+      <c r="X43" s="226" t="n"/>
     </row>
     <row r="44" ht="228" customHeight="1">
-      <c r="A44" s="230" t="inlineStr">
+      <c r="A44" s="220" t="inlineStr">
         <is>
           <t>qualified attribution</t>
         </is>
@@ -25236,7 +25236,7 @@
 The value for role in the Attribution class then becomes: https://standards.iso.org/iso/19115/resources/Codelists/gml/CI_RoleCode.xml#funder</t>
         </is>
       </c>
-      <c r="F44" s="227" t="inlineStr">
+      <c r="F44" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25246,33 +25246,33 @@
           <t>prov:Attribution</t>
         </is>
       </c>
-      <c r="H44" s="225" t="inlineStr">
+      <c r="H44" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I44" s="232" t="inlineStr">
+      <c r="I44" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J44" s="232" t="inlineStr">
+      <c r="J44" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K44" s="75" t="n"/>
-      <c r="L44" s="232" t="inlineStr">
+      <c r="L44" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="M44" s="232" t="inlineStr">
+      <c r="M44" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
       </c>
-      <c r="N44" s="232" t="inlineStr">
+      <c r="N44" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'Attribution' tab.</t>
         </is>
@@ -25292,22 +25292,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V44" s="230" t="n"/>
-      <c r="W44" s="230" t="n"/>
-      <c r="X44" s="230" t="n"/>
+      <c r="V44" s="220" t="n"/>
+      <c r="W44" s="220" t="n"/>
+      <c r="X44" s="220" t="n"/>
     </row>
     <row r="45" ht="48" customHeight="1">
-      <c r="A45" s="220" t="inlineStr">
+      <c r="A45" s="226" t="inlineStr">
         <is>
           <t>qualified relation</t>
         </is>
       </c>
-      <c r="B45" s="226" t="inlineStr">
+      <c r="B45" s="230" t="inlineStr">
         <is>
           <t>Link to a description of a relationship with another resource.</t>
         </is>
       </c>
-      <c r="C45" s="220" t="inlineStr">
+      <c r="C45" s="226" t="inlineStr">
         <is>
           <t>dcat:qualifiedRelation</t>
         </is>
@@ -25322,7 +25322,7 @@
           <t>This property makes use of another small class (dcat:Relationship), in which you can indicate the related resource (via its identifier) and the nature of the relation (based on a controlled vocabulary, which is described in the information of the class).</t>
         </is>
       </c>
-      <c r="F45" s="225" t="inlineStr">
+      <c r="F45" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25332,37 +25332,37 @@
           <t>dcat:Relationship</t>
         </is>
       </c>
-      <c r="H45" s="227" t="inlineStr">
+      <c r="H45" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I45" s="218" t="inlineStr">
+      <c r="I45" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J45" s="218" t="inlineStr">
+      <c r="J45" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K45" s="228" t="inlineStr">
+      <c r="K45" s="232" t="inlineStr">
         <is>
           <t>custom:qualified_relation</t>
         </is>
       </c>
-      <c r="L45" s="218" t="inlineStr">
+      <c r="L45" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Relationship' tab.</t>
         </is>
       </c>
-      <c r="M45" s="218" t="inlineStr">
+      <c r="M45" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Relationship' tab.</t>
         </is>
       </c>
-      <c r="N45" s="218" t="inlineStr">
+      <c r="N45" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'Relationship' tab.</t>
         </is>
@@ -25382,12 +25382,12 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V45" s="220" t="n"/>
-      <c r="W45" s="220" t="n"/>
-      <c r="X45" s="220" t="n"/>
+      <c r="V45" s="226" t="n"/>
+      <c r="W45" s="226" t="n"/>
+      <c r="X45" s="226" t="n"/>
     </row>
     <row r="46" ht="48" customHeight="1">
-      <c r="A46" s="230" t="inlineStr">
+      <c r="A46" s="220" t="inlineStr">
         <is>
           <t>quality annotation</t>
         </is>
@@ -25397,7 +25397,7 @@
           <t>Refers to a quality annotation.</t>
         </is>
       </c>
-      <c r="C46" s="230" t="inlineStr">
+      <c r="C46" s="220" t="inlineStr">
         <is>
           <t>dqv:hasQualityAnnotation</t>
         </is>
@@ -25412,7 +25412,7 @@
           <t>This property makes use of another small class (dqv:QualityCertificate), in which you indicate the IRI of the quality certificate, linked to the described resource (via the identifier of the dataset). See that class for more information.</t>
         </is>
       </c>
-      <c r="F46" s="227" t="inlineStr">
+      <c r="F46" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25422,33 +25422,33 @@
           <t>dqv:QualityCertificate</t>
         </is>
       </c>
-      <c r="H46" s="225" t="inlineStr">
+      <c r="H46" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I46" s="232" t="inlineStr">
+      <c r="I46" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J46" s="232" t="inlineStr">
+      <c r="J46" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
       <c r="K46" s="75" t="n"/>
-      <c r="L46" s="232" t="inlineStr">
+      <c r="L46" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="M46" s="232" t="inlineStr">
+      <c r="M46" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
       </c>
-      <c r="N46" s="232" t="inlineStr">
+      <c r="N46" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'QualityCertificate' tab.</t>
         </is>
@@ -25468,22 +25468,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V46" s="230" t="n"/>
-      <c r="W46" s="230" t="n"/>
-      <c r="X46" s="230" t="n"/>
+      <c r="V46" s="220" t="n"/>
+      <c r="W46" s="220" t="n"/>
+      <c r="X46" s="220" t="n"/>
     </row>
     <row r="47" ht="32" customHeight="1">
-      <c r="A47" s="220" t="inlineStr">
+      <c r="A47" s="226" t="inlineStr">
         <is>
           <t>release date</t>
         </is>
       </c>
-      <c r="B47" s="226" t="inlineStr">
+      <c r="B47" s="230" t="inlineStr">
         <is>
           <t>Date of formal issuance of the resource.</t>
         </is>
       </c>
-      <c r="C47" s="220" t="inlineStr">
+      <c r="C47" s="226" t="inlineStr">
         <is>
           <t>dct:issued</t>
         </is>
@@ -25498,39 +25498,39 @@
           <t>This property should point to the first known date of issuance, such as the publication date in a data repository. Example: 2023-12-10T13:16:10.246Z.</t>
         </is>
       </c>
-      <c r="F47" s="225" t="inlineStr">
+      <c r="F47" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G47" s="227" t="inlineStr">
+      <c r="G47" s="231" t="inlineStr">
         <is>
           <t>xsd:dateTime</t>
         </is>
       </c>
-      <c r="H47" s="227" t="inlineStr">
+      <c r="H47" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I47" s="218" t="inlineStr">
+      <c r="I47" s="225" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J47" s="218" t="inlineStr">
+      <c r="J47" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K47" s="228" t="inlineStr">
+      <c r="K47" s="232" t="inlineStr">
         <is>
           <t>custom:issued</t>
         </is>
       </c>
-      <c r="L47" s="218" t="n"/>
-      <c r="M47" s="224" t="n"/>
-      <c r="N47" s="224" t="n"/>
+      <c r="L47" s="225" t="n"/>
+      <c r="M47" s="229" t="n"/>
+      <c r="N47" s="229" t="n"/>
       <c r="P47" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -25546,12 +25546,12 @@
           <t>^\d{4}-\d{2}-\d{2}T\d{2}:\d{2}:\d{2}(\.\d+)?(Z|[+-]\d{2}:\d{2})$</t>
         </is>
       </c>
-      <c r="V47" s="220" t="n"/>
-      <c r="W47" s="220" t="n"/>
-      <c r="X47" s="220" t="n"/>
+      <c r="V47" s="226" t="n"/>
+      <c r="W47" s="226" t="n"/>
+      <c r="X47" s="226" t="n"/>
     </row>
     <row r="48" ht="160" customHeight="1">
-      <c r="A48" s="230" t="inlineStr">
+      <c r="A48" s="220" t="inlineStr">
         <is>
           <t>retention period</t>
         </is>
@@ -25561,7 +25561,7 @@
           <t>A temporal period during which the dataset is available for secondary use.</t>
         </is>
       </c>
-      <c r="C48" s="230" t="inlineStr">
+      <c r="C48" s="220" t="inlineStr">
         <is>
           <t>healthdcatap:retentionPeriod</t>
         </is>
@@ -25580,7 +25580,7 @@
 If a limit is known, provide both dcat:startDate and dcat:endDate.</t>
         </is>
       </c>
-      <c r="F48" s="227" t="inlineStr">
+      <c r="F48" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25590,17 +25590,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H48" s="225" t="inlineStr">
+      <c r="H48" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I48" s="232" t="inlineStr">
+      <c r="I48" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J48" s="232" t="inlineStr">
+      <c r="J48" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -25610,17 +25610,17 @@
           <t>custom:retention_period</t>
         </is>
       </c>
-      <c r="L48" s="232" t="inlineStr">
+      <c r="L48" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M48" s="232" t="inlineStr">
+      <c r="M48" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N48" s="232" t="inlineStr">
+      <c r="N48" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -25640,22 +25640,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V48" s="230" t="n"/>
-      <c r="W48" s="230" t="n"/>
-      <c r="X48" s="230" t="n"/>
+      <c r="V48" s="220" t="n"/>
+      <c r="W48" s="220" t="n"/>
+      <c r="X48" s="220" t="n"/>
     </row>
     <row r="49" ht="80" customHeight="1">
-      <c r="A49" s="220" t="inlineStr">
+      <c r="A49" s="226" t="inlineStr">
         <is>
           <t>sample</t>
         </is>
       </c>
-      <c r="B49" s="226" t="inlineStr">
+      <c r="B49" s="230" t="inlineStr">
         <is>
           <t>Links to a sample of an Asset (which is itself an Asset).</t>
         </is>
       </c>
-      <c r="C49" s="220" t="inlineStr">
+      <c r="C49" s="226" t="inlineStr">
         <is>
           <t>adms:sample</t>
         </is>
@@ -25670,7 +25670,7 @@
           <t>This property makes use of the dcat:Distribution class to describe a sample distribution of the dataset, which can consist of anonymised or synthetic data, or a data dictionary provided in CSVW format. This is currently being further developed by the TEHDAS2 programme. More information can be found here: https://healthdcat-ap.github.io/#sample-distribution</t>
         </is>
       </c>
-      <c r="F49" s="225" t="inlineStr">
+      <c r="F49" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25680,22 +25680,22 @@
           <t>dcat:Distribution</t>
         </is>
       </c>
-      <c r="H49" s="227" t="inlineStr">
+      <c r="H49" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I49" s="218" t="inlineStr">
+      <c r="I49" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J49" s="218" t="inlineStr">
+      <c r="J49" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K49" s="228" t="inlineStr">
+      <c r="K49" s="232" t="inlineStr">
         <is>
           <t>(issue on GitHub)</t>
         </is>
@@ -25705,8 +25705,8 @@
           <t>If available, add the URI for the sample distribution here.</t>
         </is>
       </c>
-      <c r="M49" s="218" t="n"/>
-      <c r="N49" s="218" t="n"/>
+      <c r="M49" s="225" t="n"/>
+      <c r="N49" s="225" t="n"/>
       <c r="O49" t="inlineStr">
         <is>
           <t>hrishapes:DistributionShape</t>
@@ -25727,12 +25727,12 @@
           <t>Sample Distribution</t>
         </is>
       </c>
-      <c r="V49" s="220" t="n"/>
-      <c r="W49" s="220" t="n"/>
-      <c r="X49" s="220" t="n"/>
+      <c r="V49" s="226" t="n"/>
+      <c r="W49" s="226" t="n"/>
+      <c r="X49" s="226" t="n"/>
     </row>
     <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="230" t="inlineStr">
+      <c r="A50" s="220" t="inlineStr">
         <is>
           <t>source</t>
         </is>
@@ -25742,7 +25742,7 @@
           <t>A related resource from which the described resource is derived.</t>
         </is>
       </c>
-      <c r="C50" s="230" t="inlineStr">
+      <c r="C50" s="220" t="inlineStr">
         <is>
           <t>dct:source</t>
         </is>
@@ -25752,12 +25752,12 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E50" s="231" t="inlineStr">
+      <c r="E50" s="223" t="inlineStr">
         <is>
           <t>Indicate the dataset on which this described dataset is based.</t>
         </is>
       </c>
-      <c r="F50" s="227" t="inlineStr">
+      <c r="F50" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25767,17 +25767,17 @@
           <t>dcat:Dataset</t>
         </is>
       </c>
-      <c r="H50" s="225" t="inlineStr">
+      <c r="H50" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I50" s="232" t="inlineStr">
+      <c r="I50" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J50" s="232" t="inlineStr">
+      <c r="J50" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -25792,8 +25792,8 @@
           <t>If applicable, add the URI for the source dataset here.</t>
         </is>
       </c>
-      <c r="M50" s="232" t="n"/>
-      <c r="N50" s="232" t="n"/>
+      <c r="M50" s="224" t="n"/>
+      <c r="N50" s="224" t="n"/>
       <c r="O50" t="inlineStr">
         <is>
           <t>hrishapes:DatasetShape</t>
@@ -25809,22 +25809,22 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V50" s="230" t="n"/>
-      <c r="W50" s="230" t="n"/>
-      <c r="X50" s="230" t="n"/>
+      <c r="V50" s="220" t="n"/>
+      <c r="W50" s="220" t="n"/>
+      <c r="X50" s="220" t="n"/>
     </row>
     <row r="51" ht="64" customHeight="1">
-      <c r="A51" s="220" t="inlineStr">
+      <c r="A51" s="226" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B51" s="226" t="inlineStr">
+      <c r="B51" s="230" t="inlineStr">
         <is>
           <t>The status of the Asset in the context of a particular workflow process.</t>
         </is>
       </c>
-      <c r="C51" s="220" t="inlineStr">
+      <c r="C51" s="226" t="inlineStr">
         <is>
           <t>adms:status</t>
         </is>
@@ -25840,39 +25840,39 @@
 For example: http://publications.europa.eu/resource/authority/dataset-status/COMPLETED</t>
         </is>
       </c>
-      <c r="F51" s="225" t="inlineStr">
+      <c r="F51" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G51" s="227" t="inlineStr">
+      <c r="G51" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H51" s="227" t="inlineStr">
+      <c r="H51" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I51" s="218" t="inlineStr">
+      <c r="I51" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J51" s="218" t="inlineStr">
+      <c r="J51" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K51" s="228" t="inlineStr">
+      <c r="K51" s="232" t="inlineStr">
         <is>
           <t>custom:status</t>
         </is>
       </c>
-      <c r="L51" s="218" t="n"/>
-      <c r="M51" s="218" t="n"/>
-      <c r="N51" s="218" t="n"/>
+      <c r="L51" s="225" t="n"/>
+      <c r="M51" s="225" t="n"/>
+      <c r="N51" s="225" t="n"/>
       <c r="P51" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -25883,12 +25883,12 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="V51" s="220" t="n"/>
-      <c r="W51" s="220" t="n"/>
-      <c r="X51" s="220" t="n"/>
+      <c r="V51" s="226" t="n"/>
+      <c r="W51" s="226" t="n"/>
+      <c r="X51" s="226" t="n"/>
     </row>
     <row r="52" ht="32" customHeight="1">
-      <c r="A52" s="230" t="inlineStr">
+      <c r="A52" s="220" t="inlineStr">
         <is>
           <t>temporal coverage</t>
         </is>
@@ -25898,7 +25898,7 @@
           <t>Temporal characteristics of the resource.</t>
         </is>
       </c>
-      <c r="C52" s="230" t="inlineStr">
+      <c r="C52" s="220" t="inlineStr">
         <is>
           <t>dct:temporal</t>
         </is>
@@ -25913,7 +25913,7 @@
           <t>The start and end date of the period that the dataset covers. This property makes use of a small class: Period of Time, in which a start and end date can be given.</t>
         </is>
       </c>
-      <c r="F52" s="227" t="inlineStr">
+      <c r="F52" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -25923,17 +25923,17 @@
           <t>dct:PeriodOfTime</t>
         </is>
       </c>
-      <c r="H52" s="225" t="inlineStr">
+      <c r="H52" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I52" s="232" t="inlineStr">
+      <c r="I52" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J52" s="232" t="inlineStr">
+      <c r="J52" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
@@ -25943,17 +25943,17 @@
           <t>custom:temporal_coverage</t>
         </is>
       </c>
-      <c r="L52" s="232" t="inlineStr">
+      <c r="L52" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="M52" s="232" t="inlineStr">
+      <c r="M52" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
       </c>
-      <c r="N52" s="232" t="inlineStr">
+      <c r="N52" s="224" t="inlineStr">
         <is>
           <t>Enter the value on the 'PeriodOfTime' tab.</t>
         </is>
@@ -25973,17 +25973,17 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V52" s="230" t="n"/>
-      <c r="W52" s="230" t="n"/>
-      <c r="X52" s="230" t="n"/>
+      <c r="V52" s="220" t="n"/>
+      <c r="W52" s="220" t="n"/>
+      <c r="X52" s="220" t="n"/>
     </row>
     <row r="53" ht="64" customHeight="1">
-      <c r="A53" s="220" t="inlineStr">
+      <c r="A53" s="226" t="inlineStr">
         <is>
           <t>temporal resolution</t>
         </is>
       </c>
-      <c r="B53" s="226" t="inlineStr">
+      <c r="B53" s="230" t="inlineStr">
         <is>
           <t>Minimum time period resolvable in the dataset.</t>
         </is>
@@ -26003,39 +26003,39 @@
           <t>If the dataset is a time-series, this should correspond to the spacing of items in the series. For other kinds of datasets, this property will usually indicate the smallest time difference between items in the dataset. The time period has to be provided in the xsd:duration format.</t>
         </is>
       </c>
-      <c r="F53" s="225" t="inlineStr">
+      <c r="F53" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G53" s="227" t="inlineStr">
+      <c r="G53" s="231" t="inlineStr">
         <is>
           <t>xsd:duration</t>
         </is>
       </c>
-      <c r="H53" s="227" t="inlineStr">
+      <c r="H53" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I53" s="218" t="inlineStr">
+      <c r="I53" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J53" s="218" t="inlineStr">
+      <c r="J53" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
       </c>
-      <c r="K53" s="228" t="inlineStr">
+      <c r="K53" s="232" t="inlineStr">
         <is>
           <t>custom:temporal_resolution</t>
         </is>
       </c>
-      <c r="L53" s="218" t="n"/>
-      <c r="M53" s="218" t="n"/>
-      <c r="N53" s="218" t="n"/>
+      <c r="L53" s="225" t="n"/>
+      <c r="M53" s="225" t="n"/>
+      <c r="N53" s="225" t="n"/>
       <c r="P53" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26046,12 +26046,12 @@
           <t>dash:TextFieldEditor</t>
         </is>
       </c>
-      <c r="V53" s="220" t="n"/>
-      <c r="W53" s="220" t="n"/>
-      <c r="X53" s="220" t="n"/>
+      <c r="V53" s="226" t="n"/>
+      <c r="W53" s="226" t="n"/>
+      <c r="X53" s="226" t="n"/>
     </row>
     <row r="54" ht="74.25" customHeight="1">
-      <c r="A54" s="230" t="inlineStr">
+      <c r="A54" s="220" t="inlineStr">
         <is>
           <t>theme</t>
         </is>
@@ -26061,7 +26061,7 @@
           <t>A main category of the resource. A resource can have multiple themes.</t>
         </is>
       </c>
-      <c r="C54" s="230" t="inlineStr">
+      <c r="C54" s="220" t="inlineStr">
         <is>
           <t>dcat:theme</t>
         </is>
@@ -26076,27 +26076,27 @@
           <t>This property should use a controlled vocabulary. In the Health Data Catalogue, all datasets will use the theme 'HEAL' (http://publications.europa.eu/resource/authority/data-theme/HEAL), but additional values from the same vocabulary are allowed.</t>
         </is>
       </c>
-      <c r="F54" s="227" t="inlineStr">
+      <c r="F54" s="231" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G54" s="225" t="inlineStr">
+      <c r="G54" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H54" s="225" t="inlineStr">
+      <c r="H54" s="218" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I54" s="232" t="inlineStr">
+      <c r="I54" s="224" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J54" s="232" t="inlineStr">
+      <c r="J54" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -26106,9 +26106,9 @@
           <t>custom:theme</t>
         </is>
       </c>
-      <c r="L54" s="232" t="n"/>
-      <c r="M54" s="232" t="n"/>
-      <c r="N54" s="232" t="n"/>
+      <c r="L54" s="224" t="n"/>
+      <c r="M54" s="224" t="n"/>
+      <c r="N54" s="224" t="n"/>
       <c r="P54" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -26124,22 +26124,22 @@
           <t>http://publications.europa.eu/resource/authority/data-theme/HEAL</t>
         </is>
       </c>
-      <c r="V54" s="230" t="n"/>
-      <c r="W54" s="230" t="n"/>
-      <c r="X54" s="230" t="n"/>
+      <c r="V54" s="220" t="n"/>
+      <c r="W54" s="220" t="n"/>
+      <c r="X54" s="220" t="n"/>
     </row>
     <row r="55" ht="32" customHeight="1">
-      <c r="A55" s="220" t="inlineStr">
+      <c r="A55" s="226" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B55" s="226" t="inlineStr">
+      <c r="B55" s="230" t="inlineStr">
         <is>
           <t>A name given to the resource.</t>
         </is>
       </c>
-      <c r="C55" s="220" t="inlineStr">
+      <c r="C55" s="226" t="inlineStr">
         <is>
           <t>dct:title</t>
         </is>
@@ -26154,39 +26154,39 @@
           <t>Provide a unique title for your Dataset, which can be repeated in multiple languages. Example: Healthy Brain Study - Physiological Data</t>
         </is>
       </c>
-      <c r="F55" s="225" t="inlineStr">
+      <c r="F55" s="218" t="inlineStr">
         <is>
           <t>Mandatory</t>
         </is>
       </c>
-      <c r="G55" s="227" t="inlineStr">
+      <c r="G55" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H55" s="227" t="inlineStr">
+      <c r="H55" s="231" t="inlineStr">
         <is>
           <t>1..n</t>
         </is>
       </c>
-      <c r="I55" s="218" t="inlineStr">
+      <c r="I55" s="225" t="inlineStr">
         <is>
           <t>Identical to v1</t>
         </is>
       </c>
-      <c r="J55" s="218" t="inlineStr">
+      <c r="J55" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K55" s="228" t="inlineStr">
+      <c r="K55" s="232" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="L55" s="218" t="n"/>
-      <c r="M55" s="218" t="n"/>
-      <c r="N55" s="218" t="n"/>
+      <c r="L55" s="225" t="n"/>
+      <c r="M55" s="225" t="n"/>
+      <c r="N55" s="225" t="n"/>
       <c r="P55" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26200,12 +26200,12 @@
       <c r="T55" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V55" s="220" t="n"/>
-      <c r="W55" s="220" t="n"/>
-      <c r="X55" s="220" t="n"/>
+      <c r="V55" s="226" t="n"/>
+      <c r="W55" s="226" t="n"/>
+      <c r="X55" s="226" t="n"/>
     </row>
     <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="230" t="inlineStr">
+      <c r="A56" s="220" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -26215,7 +26215,7 @@
           <t>The nature or genre of the resource.</t>
         </is>
       </c>
-      <c r="C56" s="230" t="inlineStr">
+      <c r="C56" s="220" t="inlineStr">
         <is>
           <t>dct:type</t>
         </is>
@@ -26231,27 +26231,27 @@
 The EU Dataset-type controlled vocabulary SHOULD be used.</t>
         </is>
       </c>
-      <c r="F56" s="227" t="inlineStr">
+      <c r="F56" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G56" s="225" t="inlineStr">
+      <c r="G56" s="218" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H56" s="225" t="inlineStr">
+      <c r="H56" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I56" s="232" t="inlineStr">
+      <c r="I56" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J56" s="232" t="inlineStr">
+      <c r="J56" s="224" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
@@ -26261,9 +26261,9 @@
           <t>custom:dcat_type</t>
         </is>
       </c>
-      <c r="L56" s="232" t="n"/>
-      <c r="M56" s="232" t="n"/>
-      <c r="N56" s="232" t="n"/>
+      <c r="L56" s="224" t="n"/>
+      <c r="M56" s="224" t="n"/>
+      <c r="N56" s="224" t="n"/>
       <c r="O56" s="84" t="n"/>
       <c r="P56" s="69" t="inlineStr">
         <is>
@@ -26277,22 +26277,22 @@
       </c>
       <c r="R56" s="84" t="n"/>
       <c r="T56" s="84" t="n"/>
-      <c r="V56" s="230" t="n"/>
-      <c r="W56" s="230" t="n"/>
-      <c r="X56" s="230" t="n"/>
+      <c r="V56" s="220" t="n"/>
+      <c r="W56" s="220" t="n"/>
+      <c r="X56" s="220" t="n"/>
     </row>
     <row r="57" ht="80" customHeight="1">
-      <c r="A57" s="220" t="inlineStr">
+      <c r="A57" s="226" t="inlineStr">
         <is>
           <t>variables</t>
         </is>
       </c>
-      <c r="B57" s="226" t="inlineStr">
+      <c r="B57" s="230" t="inlineStr">
         <is>
           <t>Links the Dataset to a CSVW TableGroup that provides a machine-readable description of the data variables.</t>
         </is>
       </c>
-      <c r="C57" s="220" t="inlineStr">
+      <c r="C57" s="226" t="inlineStr">
         <is>
           <t>healthdcatap:hasVariables</t>
         </is>
@@ -26308,7 +26308,7 @@
 Use this property to link a structured dataset to a CSVW TableGroup that documents its data variables, columns, or fields in a machine-readable way.</t>
         </is>
       </c>
-      <c r="F57" s="227" t="inlineStr">
+      <c r="F57" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -26318,33 +26318,33 @@
           <t>csvw:TableGroup</t>
         </is>
       </c>
-      <c r="H57" s="227" t="inlineStr">
+      <c r="H57" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I57" s="218" t="inlineStr">
+      <c r="I57" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J57" s="218" t="inlineStr">
+      <c r="J57" s="225" t="inlineStr">
         <is>
           <t>HealthDCAT-AP</t>
         </is>
       </c>
-      <c r="K57" s="228" t="n"/>
-      <c r="L57" s="218" t="inlineStr">
+      <c r="K57" s="232" t="n"/>
+      <c r="L57" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'TableGroup' tab.</t>
         </is>
       </c>
-      <c r="M57" s="218" t="inlineStr">
+      <c r="M57" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'TableGroup' tab.</t>
         </is>
       </c>
-      <c r="N57" s="218" t="inlineStr">
+      <c r="N57" s="225" t="inlineStr">
         <is>
           <t>Enter the value on the 'TableGroup' tab.</t>
         </is>
@@ -26366,15 +26366,15 @@
       </c>
       <c r="U57" s="219" t="inlineStr">
         <is>
-          <t>Variables</t>
-        </is>
-      </c>
-      <c r="V57" s="220" t="n"/>
-      <c r="W57" s="220" t="n"/>
-      <c r="X57" s="220" t="n"/>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="V57" s="226" t="n"/>
+      <c r="W57" s="226" t="n"/>
+      <c r="X57" s="226" t="n"/>
     </row>
     <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="230" t="inlineStr">
+      <c r="A58" s="220" t="inlineStr">
         <is>
           <t>version</t>
         </is>
@@ -26384,7 +26384,7 @@
           <t>The version indicator (name or identifier) of a resource.</t>
         </is>
       </c>
-      <c r="C58" s="230" t="inlineStr">
+      <c r="C58" s="220" t="inlineStr">
         <is>
           <t>dcat:version</t>
         </is>
@@ -26399,27 +26399,27 @@
           <t>Suggested practice: track major_version.minor_version. Register a new identifier for major changes (e.g., 1.0.0 for an unchanged dataset).</t>
         </is>
       </c>
-      <c r="F58" s="225" t="inlineStr">
+      <c r="F58" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G58" s="225" t="inlineStr">
+      <c r="G58" s="218" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H58" s="225" t="inlineStr">
+      <c r="H58" s="218" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I58" s="232" t="inlineStr">
+      <c r="I58" s="224" t="inlineStr">
         <is>
           <t>Adapted from v1</t>
         </is>
       </c>
-      <c r="J58" s="232" t="inlineStr">
+      <c r="J58" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP NL</t>
         </is>
@@ -26429,9 +26429,9 @@
           <t>custom:version</t>
         </is>
       </c>
-      <c r="L58" s="232" t="n"/>
-      <c r="M58" s="232" t="n"/>
-      <c r="N58" s="232" t="n"/>
+      <c r="L58" s="224" t="n"/>
+      <c r="M58" s="224" t="n"/>
+      <c r="N58" s="224" t="n"/>
       <c r="P58" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26443,22 +26443,22 @@
         </is>
       </c>
       <c r="S58" s="84" t="n"/>
-      <c r="V58" s="230" t="n"/>
-      <c r="W58" s="230" t="n"/>
-      <c r="X58" s="230" t="n"/>
+      <c r="V58" s="220" t="n"/>
+      <c r="W58" s="220" t="n"/>
+      <c r="X58" s="220" t="n"/>
     </row>
     <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="220" t="inlineStr">
+      <c r="A59" s="226" t="inlineStr">
         <is>
           <t>version notes</t>
         </is>
       </c>
-      <c r="B59" s="226" t="inlineStr">
+      <c r="B59" s="230" t="inlineStr">
         <is>
           <t>A description of changes between this version and the previous version of the Asset.</t>
         </is>
       </c>
-      <c r="C59" s="220" t="inlineStr">
+      <c r="C59" s="226" t="inlineStr">
         <is>
           <t>adms:versionNotes</t>
         </is>
@@ -26468,44 +26468,44 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E59" s="226" t="inlineStr">
+      <c r="E59" s="230" t="inlineStr">
         <is>
           <t>Provide a short description of changes made to the dataset since the previous version.</t>
         </is>
       </c>
-      <c r="F59" s="227" t="inlineStr">
+      <c r="F59" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G59" s="227" t="inlineStr">
+      <c r="G59" s="231" t="inlineStr">
         <is>
           <t>rdfs:Literal</t>
         </is>
       </c>
-      <c r="H59" s="227" t="inlineStr">
+      <c r="H59" s="231" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I59" s="218" t="inlineStr">
+      <c r="I59" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J59" s="218" t="inlineStr">
+      <c r="J59" s="225" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
-      <c r="K59" s="228" t="inlineStr">
+      <c r="K59" s="232" t="inlineStr">
         <is>
           <t>custom:version_notes</t>
         </is>
       </c>
-      <c r="L59" s="218" t="n"/>
-      <c r="M59" s="218" t="n"/>
-      <c r="N59" s="218" t="n"/>
+      <c r="L59" s="225" t="n"/>
+      <c r="M59" s="225" t="n"/>
+      <c r="N59" s="225" t="n"/>
       <c r="P59" s="219" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -26519,12 +26519,12 @@
       <c r="T59" s="219" t="b">
         <v>1</v>
       </c>
-      <c r="V59" s="220" t="n"/>
-      <c r="W59" s="220" t="n"/>
-      <c r="X59" s="220" t="n"/>
+      <c r="V59" s="226" t="n"/>
+      <c r="W59" s="226" t="n"/>
+      <c r="X59" s="226" t="n"/>
     </row>
     <row r="60" ht="84.75" customHeight="1">
-      <c r="A60" s="230" t="inlineStr">
+      <c r="A60" s="220" t="inlineStr">
         <is>
           <t>was generated by</t>
         </is>
@@ -26534,7 +26534,7 @@
           <t>Generation is the completion of production of a new entity by an activity. This entity did not exist before generation and becomes available for usage after this generation.</t>
         </is>
       </c>
-      <c r="C60" s="230" t="inlineStr">
+      <c r="C60" s="220" t="inlineStr">
         <is>
           <t>prov:wasGeneratedBy</t>
         </is>
@@ -26544,7 +26544,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="F60" s="225" t="inlineStr">
+      <c r="F60" s="218" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
@@ -26554,25 +26554,25 @@
           <t>prov:Activity</t>
         </is>
       </c>
-      <c r="H60" s="225" t="inlineStr">
+      <c r="H60" s="218" t="inlineStr">
         <is>
           <t>0..n</t>
         </is>
       </c>
-      <c r="I60" s="232" t="inlineStr">
+      <c r="I60" s="224" t="inlineStr">
         <is>
           <t>new</t>
         </is>
       </c>
-      <c r="J60" s="232" t="inlineStr">
+      <c r="J60" s="224" t="inlineStr">
         <is>
           <t>DCAT-AP v3</t>
         </is>
       </c>
       <c r="K60" s="75" t="n"/>
-      <c r="L60" s="232" t="n"/>
-      <c r="M60" s="232" t="n"/>
-      <c r="N60" s="232" t="n"/>
+      <c r="L60" s="224" t="n"/>
+      <c r="M60" s="224" t="n"/>
+      <c r="N60" s="224" t="n"/>
       <c r="O60" t="inlineStr">
         <is>
           <t>hrishapes:ActivityShape</t>
@@ -26588,9 +26588,9 @@
           <t>dash:BlankNodeEditor</t>
         </is>
       </c>
-      <c r="V60" s="230" t="n"/>
-      <c r="W60" s="230" t="n"/>
-      <c r="X60" s="230" t="n"/>
+      <c r="V60" s="220" t="n"/>
+      <c r="W60" s="220" t="n"/>
+      <c r="X60" s="220" t="n"/>
     </row>
     <row r="61" customFormat="1" s="84">
       <c r="A61" s="110" t="n"/>
@@ -26771,8 +26771,8 @@
     <col width="36.5" customWidth="1" style="102" min="22" max="22"/>
     <col width="8.83203125" customWidth="1" style="102" min="23" max="28"/>
     <col width="18" customWidth="1" min="29" max="31"/>
-    <col width="8.83203125" customWidth="1" style="102" min="32" max="34"/>
-    <col width="8.83203125" customWidth="1" style="102" min="35" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="102" min="32" max="35"/>
+    <col width="8.83203125" customWidth="1" style="102" min="36" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="96" customFormat="1" customHeight="1" s="165">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="J2" s="125" t="n"/>
       <c r="K2" s="126" t="n"/>
-      <c r="L2" s="232" t="n"/>
+      <c r="L2" s="224" t="n"/>
       <c r="X2" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27053,16 +27053,16 @@
           <t>_mail</t>
         </is>
       </c>
-      <c r="L3" s="218" t="n"/>
-      <c r="M3" s="218" t="n"/>
-      <c r="N3" s="218" t="n"/>
-      <c r="O3" s="218" t="n"/>
-      <c r="P3" s="218" t="n"/>
-      <c r="Q3" s="218" t="n"/>
-      <c r="R3" s="218" t="n"/>
-      <c r="S3" s="218" t="n"/>
-      <c r="T3" s="218" t="n"/>
-      <c r="U3" s="218" t="n"/>
+      <c r="L3" s="225" t="n"/>
+      <c r="M3" s="225" t="n"/>
+      <c r="N3" s="225" t="n"/>
+      <c r="O3" s="225" t="n"/>
+      <c r="P3" s="225" t="n"/>
+      <c r="Q3" s="225" t="n"/>
+      <c r="R3" s="225" t="n"/>
+      <c r="S3" s="225" t="n"/>
+      <c r="T3" s="225" t="n"/>
+      <c r="U3" s="225" t="n"/>
       <c r="X3" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -27142,7 +27142,7 @@
           <t>_id</t>
         </is>
       </c>
-      <c r="L4" s="232" t="n"/>
+      <c r="L4" s="224" t="n"/>
       <c r="X4" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27213,16 +27213,16 @@
           <t>_name</t>
         </is>
       </c>
-      <c r="L5" s="218" t="n"/>
-      <c r="M5" s="218" t="n"/>
-      <c r="N5" s="218" t="n"/>
-      <c r="O5" s="218" t="n"/>
-      <c r="P5" s="218" t="n"/>
-      <c r="Q5" s="218" t="n"/>
-      <c r="R5" s="218" t="n"/>
-      <c r="S5" s="218" t="n"/>
-      <c r="T5" s="218" t="n"/>
-      <c r="U5" s="218" t="n"/>
+      <c r="L5" s="225" t="n"/>
+      <c r="M5" s="225" t="n"/>
+      <c r="N5" s="225" t="n"/>
+      <c r="O5" s="225" t="n"/>
+      <c r="P5" s="225" t="n"/>
+      <c r="Q5" s="225" t="n"/>
+      <c r="R5" s="225" t="n"/>
+      <c r="S5" s="225" t="n"/>
+      <c r="T5" s="225" t="n"/>
+      <c r="U5" s="225" t="n"/>
       <c r="X5" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27246,7 +27246,7 @@
           <t>publisher note</t>
         </is>
       </c>
-      <c r="B6" s="229" t="inlineStr">
+      <c r="B6" s="222" t="inlineStr">
         <is>
           <t>A description of the publisher's activities.</t>
         </is>
@@ -27261,7 +27261,7 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="E6" s="229" t="inlineStr">
+      <c r="E6" s="222" t="inlineStr">
         <is>
           <t>Note: This property will be deprecated in the next major release.
 This property can be repeated for parallel language versions of the publisher notes. Example: "Sciensano is a research institute and the national public health institute of Belgium. It is a so-called federal scientific institution that operates under the authority of the federal minister of Public Health and the federal minister of Agriculture of Belgium."@en</t>
@@ -27293,7 +27293,7 @@
         </is>
       </c>
       <c r="K6" s="126" t="n"/>
-      <c r="L6" s="232" t="n"/>
+      <c r="L6" s="224" t="n"/>
       <c r="X6" s="102" t="inlineStr">
         <is>
           <t>dash:LiteralViewer</t>
@@ -27312,17 +27312,17 @@
       <c r="AE6" s="133" t="n"/>
     </row>
     <row r="7" ht="112" customHeight="1">
-      <c r="A7" s="220" t="inlineStr">
+      <c r="A7" s="226" t="inlineStr">
         <is>
           <t>publisher type</t>
         </is>
       </c>
-      <c r="B7" s="226" t="inlineStr">
+      <c r="B7" s="230" t="inlineStr">
         <is>
           <t>A type of organisation that makes the Dataset available.</t>
         </is>
       </c>
-      <c r="C7" s="220" t="inlineStr">
+      <c r="C7" s="226" t="inlineStr">
         <is>
           <t>healthdcatap:publishertype</t>
         </is>
@@ -27338,22 +27338,22 @@
 Choose a term from the controlled vocabulary, which includes the following types: Academia-ScientificOrganisation, Company, IndustryConsortium, LocalAuthority, NationalAuthority, NonGovernmentalOrganisation, NonProfitOrganisation, PrivateIndividual, RegionalAuthority, StandardisationBody and SupraNationalAuthority. These should use URLs of the following form: http://purl.org/adms/publishertype/[type].</t>
         </is>
       </c>
-      <c r="F7" s="227" t="inlineStr">
+      <c r="F7" s="231" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="G7" s="227" t="inlineStr">
+      <c r="G7" s="231" t="inlineStr">
         <is>
           <t>skos:Concept (IRI)</t>
         </is>
       </c>
-      <c r="H7" s="227" t="inlineStr">
+      <c r="H7" s="231" t="inlineStr">
         <is>
           <t>0..1</t>
         </is>
       </c>
-      <c r="I7" s="218" t="inlineStr">
+      <c r="I7" s="225" t="inlineStr">
         <is>
           <t>new</t>
         </is>
@@ -27364,16 +27364,16 @@
         </is>
       </c>
       <c r="K7" s="126" t="n"/>
-      <c r="L7" s="218" t="n"/>
-      <c r="M7" s="218" t="n"/>
-      <c r="N7" s="218" t="n"/>
-      <c r="O7" s="218" t="n"/>
-      <c r="P7" s="218" t="n"/>
-      <c r="Q7" s="218" t="n"/>
-      <c r="R7" s="218" t="n"/>
-      <c r="S7" s="218" t="n"/>
-      <c r="T7" s="218" t="n"/>
-      <c r="U7" s="218" t="n"/>
+      <c r="L7" s="225" t="n"/>
+      <c r="M7" s="225" t="n"/>
+      <c r="N7" s="225" t="n"/>
+      <c r="O7" s="225" t="n"/>
+      <c r="P7" s="225" t="n"/>
+      <c r="Q7" s="225" t="n"/>
+      <c r="R7" s="225" t="n"/>
+      <c r="S7" s="225" t="n"/>
+      <c r="T7" s="225" t="n"/>
+      <c r="U7" s="225" t="n"/>
       <c r="X7" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27384,9 +27384,9 @@
           <t>dash:URIEditor</t>
         </is>
       </c>
-      <c r="AC7" s="220" t="n"/>
-      <c r="AD7" s="220" t="n"/>
-      <c r="AE7" s="220" t="n"/>
+      <c r="AC7" s="226" t="n"/>
+      <c r="AD7" s="226" t="n"/>
+      <c r="AE7" s="226" t="n"/>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" s="45" t="inlineStr">
@@ -27444,7 +27444,7 @@
           <t>_type</t>
         </is>
       </c>
-      <c r="L8" s="232" t="n"/>
+      <c r="L8" s="224" t="n"/>
       <c r="X8" s="69" t="inlineStr">
         <is>
           <t>dash:LabelViewer</t>
@@ -27513,16 +27513,16 @@
           <t>_url</t>
         </is>
       </c>
-      <c r="L9" s="218" t="n"/>
-      <c r="M9" s="218" t="n"/>
-      <c r="N9" s="218" t="n"/>
-      <c r="O9" s="218" t="n"/>
-      <c r="P9" s="218" t="n"/>
-      <c r="Q9" s="218" t="n"/>
-      <c r="R9" s="218" t="n"/>
-      <c r="S9" s="218" t="n"/>
-      <c r="T9" s="218" t="n"/>
-      <c r="U9" s="218" t="n"/>
+      <c r="L9" s="225" t="n"/>
+      <c r="M9" s="225" t="n"/>
+      <c r="N9" s="225" t="n"/>
+      <c r="O9" s="225" t="n"/>
+      <c r="P9" s="225" t="n"/>
+      <c r="Q9" s="225" t="n"/>
+      <c r="R9" s="225" t="n"/>
+      <c r="S9" s="225" t="n"/>
+      <c r="T9" s="225" t="n"/>
+      <c r="U9" s="225" t="n"/>
       <c r="X9" s="102" t="inlineStr">
         <is>
           <t>dash:URIViewer</t>
@@ -28384,8 +28384,8 @@
     <col width="33.5" customWidth="1" style="58" min="17" max="17"/>
     <col width="8.83203125" customWidth="1" style="58" min="18" max="23"/>
     <col width="24.5" customWidth="1" min="24" max="26"/>
-    <col width="8.83203125" customWidth="1" style="58" min="27" max="29"/>
-    <col width="8.83203125" customWidth="1" style="58" min="30" max="16384"/>
+    <col width="8.83203125" customWidth="1" style="58" min="27" max="30"/>
+    <col width="8.83203125" customWidth="1" style="58" min="31" max="16384"/>
   </cols>
   <sheetData>
     <row r="1" ht="80" customFormat="1" customHeight="1" s="165">
